--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.6561</v>
+        <v>24.5316</v>
       </c>
       <c r="C2" t="n">
-        <v>41.7525</v>
+        <v>20.671</v>
       </c>
       <c r="D2" t="n">
-        <v>55.1145</v>
+        <v>53.6229</v>
       </c>
       <c r="E2" t="n">
-        <v>19.873</v>
+        <v>19.7009</v>
       </c>
       <c r="F2" t="n">
-        <v>37.4096</v>
+        <v>36.8388</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>24.4891</v>
+        <v>24.164</v>
       </c>
       <c r="C3" t="n">
-        <v>41.1432</v>
+        <v>20.1678</v>
       </c>
       <c r="D3" t="n">
-        <v>54.2599</v>
+        <v>53.1489</v>
       </c>
       <c r="E3" t="n">
-        <v>19.1736</v>
+        <v>19.0838</v>
       </c>
       <c r="F3" t="n">
-        <v>36.7636</v>
+        <v>36.2918</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>23.9504</v>
+        <v>22.9278</v>
       </c>
       <c r="C4" t="n">
-        <v>40.8631</v>
+        <v>19.6984</v>
       </c>
       <c r="D4" t="n">
-        <v>53.6276</v>
+        <v>52.7264</v>
       </c>
       <c r="E4" t="n">
-        <v>18.6172</v>
+        <v>18.535</v>
       </c>
       <c r="F4" t="n">
-        <v>36.2705</v>
+        <v>35.7166</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>23.426</v>
+        <v>23.212</v>
       </c>
       <c r="C5" t="n">
-        <v>40.2834</v>
+        <v>19.2564</v>
       </c>
       <c r="D5" t="n">
-        <v>53.0096</v>
+        <v>52.2405</v>
       </c>
       <c r="E5" t="n">
-        <v>18.081</v>
+        <v>18.0458</v>
       </c>
       <c r="F5" t="n">
-        <v>35.7751</v>
+        <v>35.3097</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.7116</v>
+        <v>22.2212</v>
       </c>
       <c r="C6" t="n">
-        <v>39.9207</v>
+        <v>18.8477</v>
       </c>
       <c r="D6" t="n">
-        <v>52.4798</v>
+        <v>51.8131</v>
       </c>
       <c r="E6" t="n">
-        <v>17.758</v>
+        <v>17.6637</v>
       </c>
       <c r="F6" t="n">
-        <v>35.4467</v>
+        <v>35.0056</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>22.2932</v>
+        <v>21.8794</v>
       </c>
       <c r="C7" t="n">
-        <v>39.5153</v>
+        <v>18.5582</v>
       </c>
       <c r="D7" t="n">
-        <v>68.0997</v>
+        <v>66.6495</v>
       </c>
       <c r="E7" t="n">
-        <v>17.4658</v>
+        <v>17.5627</v>
       </c>
       <c r="F7" t="n">
-        <v>35.2233</v>
+        <v>34.8817</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1578</v>
+        <v>21.5631</v>
       </c>
       <c r="C8" t="n">
-        <v>39.3777</v>
+        <v>27.3799</v>
       </c>
       <c r="D8" t="n">
-        <v>66.71980000000001</v>
+        <v>65.1246</v>
       </c>
       <c r="E8" t="n">
-        <v>17.7403</v>
+        <v>17.5057</v>
       </c>
       <c r="F8" t="n">
-        <v>35.2701</v>
+        <v>34.9783</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>22.8559</v>
+        <v>21.8677</v>
       </c>
       <c r="C9" t="n">
-        <v>39.3255</v>
+        <v>26.5523</v>
       </c>
       <c r="D9" t="n">
-        <v>65.2405</v>
+        <v>63.6883</v>
       </c>
       <c r="E9" t="n">
-        <v>26.9313</v>
+        <v>26.5289</v>
       </c>
       <c r="F9" t="n">
-        <v>43.4215</v>
+        <v>43.0399</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>31.1719</v>
+        <v>30.6095</v>
       </c>
       <c r="C10" t="n">
-        <v>48.5445</v>
+        <v>25.6442</v>
       </c>
       <c r="D10" t="n">
-        <v>64.0866</v>
+        <v>62.4459</v>
       </c>
       <c r="E10" t="n">
-        <v>25.9111</v>
+        <v>25.6737</v>
       </c>
       <c r="F10" t="n">
-        <v>42.4856</v>
+        <v>42.0749</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>30.2557</v>
+        <v>29.7245</v>
       </c>
       <c r="C11" t="n">
-        <v>47.4923</v>
+        <v>24.8628</v>
       </c>
       <c r="D11" t="n">
-        <v>62.9515</v>
+        <v>61.1452</v>
       </c>
       <c r="E11" t="n">
-        <v>25.0994</v>
+        <v>24.7935</v>
       </c>
       <c r="F11" t="n">
-        <v>41.5882</v>
+        <v>41.055</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>29.2485</v>
+        <v>28.9708</v>
       </c>
       <c r="C12" t="n">
-        <v>46.705</v>
+        <v>24.1367</v>
       </c>
       <c r="D12" t="n">
-        <v>61.5302</v>
+        <v>59.9061</v>
       </c>
       <c r="E12" t="n">
-        <v>24.2678</v>
+        <v>23.9852</v>
       </c>
       <c r="F12" t="n">
-        <v>40.6912</v>
+        <v>40.1143</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>28.7673</v>
+        <v>27.8123</v>
       </c>
       <c r="C13" t="n">
-        <v>45.4766</v>
+        <v>23.3847</v>
       </c>
       <c r="D13" t="n">
-        <v>60.6016</v>
+        <v>59.0985</v>
       </c>
       <c r="E13" t="n">
-        <v>23.3789</v>
+        <v>23.2408</v>
       </c>
       <c r="F13" t="n">
-        <v>39.8902</v>
+        <v>39.291</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>27.5656</v>
+        <v>27.2101</v>
       </c>
       <c r="C14" t="n">
-        <v>44.5363</v>
+        <v>22.7759</v>
       </c>
       <c r="D14" t="n">
-        <v>59.6365</v>
+        <v>58.2203</v>
       </c>
       <c r="E14" t="n">
-        <v>22.7221</v>
+        <v>22.5371</v>
       </c>
       <c r="F14" t="n">
-        <v>39.1058</v>
+        <v>38.5646</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>26.7994</v>
+        <v>26.2365</v>
       </c>
       <c r="C15" t="n">
-        <v>43.8216</v>
+        <v>22.1445</v>
       </c>
       <c r="D15" t="n">
-        <v>58.9414</v>
+        <v>57.3887</v>
       </c>
       <c r="E15" t="n">
-        <v>22.0891</v>
+        <v>21.8656</v>
       </c>
       <c r="F15" t="n">
-        <v>38.392</v>
+        <v>37.8085</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>26.3004</v>
+        <v>25.7403</v>
       </c>
       <c r="C16" t="n">
-        <v>43.0396</v>
+        <v>21.5246</v>
       </c>
       <c r="D16" t="n">
-        <v>58.1916</v>
+        <v>56.9223</v>
       </c>
       <c r="E16" t="n">
-        <v>21.4113</v>
+        <v>21.335</v>
       </c>
       <c r="F16" t="n">
-        <v>37.736</v>
+        <v>37.1698</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>25.4634</v>
+        <v>25.1843</v>
       </c>
       <c r="C17" t="n">
-        <v>42.4797</v>
+        <v>20.9389</v>
       </c>
       <c r="D17" t="n">
-        <v>57.5393</v>
+        <v>56.2776</v>
       </c>
       <c r="E17" t="n">
-        <v>20.9229</v>
+        <v>20.6883</v>
       </c>
       <c r="F17" t="n">
-        <v>37.0739</v>
+        <v>36.636</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>25.0643</v>
+        <v>24.4602</v>
       </c>
       <c r="C18" t="n">
-        <v>42.0272</v>
+        <v>20.447</v>
       </c>
       <c r="D18" t="n">
-        <v>56.9186</v>
+        <v>55.2586</v>
       </c>
       <c r="E18" t="n">
-        <v>20.3757</v>
+        <v>20.2274</v>
       </c>
       <c r="F18" t="n">
-        <v>36.555</v>
+        <v>36.065</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>24.4983</v>
+        <v>24.0796</v>
       </c>
       <c r="C19" t="n">
-        <v>41.4124</v>
+        <v>20.0114</v>
       </c>
       <c r="D19" t="n">
-        <v>56.3027</v>
+        <v>54.7054</v>
       </c>
       <c r="E19" t="n">
-        <v>20.1544</v>
+        <v>19.7444</v>
       </c>
       <c r="F19" t="n">
-        <v>36.1371</v>
+        <v>35.5236</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>24.1018</v>
+        <v>23.8261</v>
       </c>
       <c r="C20" t="n">
-        <v>41.1325</v>
+        <v>19.6203</v>
       </c>
       <c r="D20" t="n">
-        <v>55.8185</v>
+        <v>54.2105</v>
       </c>
       <c r="E20" t="n">
-        <v>19.5629</v>
+        <v>19.7205</v>
       </c>
       <c r="F20" t="n">
-        <v>35.7525</v>
+        <v>35.2398</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>24.6265</v>
+        <v>23.3199</v>
       </c>
       <c r="C21" t="n">
-        <v>40.272</v>
+        <v>19.3162</v>
       </c>
       <c r="D21" t="n">
-        <v>73.336</v>
+        <v>72.1801</v>
       </c>
       <c r="E21" t="n">
-        <v>19.5232</v>
+        <v>19.3782</v>
       </c>
       <c r="F21" t="n">
-        <v>35.5488</v>
+        <v>35.0037</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>23.1921</v>
+        <v>23.1012</v>
       </c>
       <c r="C22" t="n">
-        <v>40.1207</v>
+        <v>28.0102</v>
       </c>
       <c r="D22" t="n">
-        <v>71.75230000000001</v>
+        <v>70.50960000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>19.6834</v>
+        <v>19.4912</v>
       </c>
       <c r="F22" t="n">
-        <v>35.615</v>
+        <v>35.0626</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>23.7825</v>
+        <v>22.7908</v>
       </c>
       <c r="C23" t="n">
-        <v>40.0669</v>
+        <v>27.1092</v>
       </c>
       <c r="D23" t="n">
-        <v>70.3347</v>
+        <v>68.99930000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>28.8033</v>
+        <v>28.5523</v>
       </c>
       <c r="F23" t="n">
-        <v>44.2694</v>
+        <v>43.8119</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>32.1492</v>
+        <v>32.139</v>
       </c>
       <c r="C24" t="n">
-        <v>49.6563</v>
+        <v>26.2807</v>
       </c>
       <c r="D24" t="n">
-        <v>69.02979999999999</v>
+        <v>67.6866</v>
       </c>
       <c r="E24" t="n">
-        <v>27.6845</v>
+        <v>27.6459</v>
       </c>
       <c r="F24" t="n">
-        <v>43.3859</v>
+        <v>42.7851</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>30.666</v>
+        <v>30.7333</v>
       </c>
       <c r="C25" t="n">
-        <v>48.7622</v>
+        <v>25.55</v>
       </c>
       <c r="D25" t="n">
-        <v>67.62520000000001</v>
+        <v>66.4037</v>
       </c>
       <c r="E25" t="n">
-        <v>27.0569</v>
+        <v>27.0853</v>
       </c>
       <c r="F25" t="n">
-        <v>42.4536</v>
+        <v>42.0394</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>30.0625</v>
+        <v>29.8874</v>
       </c>
       <c r="C26" t="n">
-        <v>47.8697</v>
+        <v>24.7958</v>
       </c>
       <c r="D26" t="n">
-        <v>66.5046</v>
+        <v>65.00749999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>26.1771</v>
+        <v>25.8399</v>
       </c>
       <c r="F26" t="n">
-        <v>41.5718</v>
+        <v>41.0464</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.9682</v>
+        <v>29.0459</v>
       </c>
       <c r="C27" t="n">
-        <v>46.9579</v>
+        <v>24.0529</v>
       </c>
       <c r="D27" t="n">
-        <v>65.4524</v>
+        <v>64.1583</v>
       </c>
       <c r="E27" t="n">
-        <v>25.0728</v>
+        <v>24.9898</v>
       </c>
       <c r="F27" t="n">
-        <v>40.748</v>
+        <v>40.2425</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>28.0345</v>
+        <v>28.0715</v>
       </c>
       <c r="C28" t="n">
-        <v>45.9834</v>
+        <v>23.4118</v>
       </c>
       <c r="D28" t="n">
-        <v>64.4425</v>
+        <v>63.1219</v>
       </c>
       <c r="E28" t="n">
-        <v>24.3749</v>
+        <v>24.3252</v>
       </c>
       <c r="F28" t="n">
-        <v>40.0206</v>
+        <v>39.3968</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>27.4686</v>
+        <v>27.2709</v>
       </c>
       <c r="C29" t="n">
-        <v>44.9729</v>
+        <v>22.7646</v>
       </c>
       <c r="D29" t="n">
-        <v>63.6598</v>
+        <v>62.4064</v>
       </c>
       <c r="E29" t="n">
-        <v>23.5186</v>
+        <v>23.5154</v>
       </c>
       <c r="F29" t="n">
-        <v>39.2868</v>
+        <v>38.6746</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>26.8094</v>
+        <v>26.7729</v>
       </c>
       <c r="C30" t="n">
-        <v>44.1772</v>
+        <v>22.116</v>
       </c>
       <c r="D30" t="n">
-        <v>62.8621</v>
+        <v>61.492</v>
       </c>
       <c r="E30" t="n">
-        <v>22.9215</v>
+        <v>22.7534</v>
       </c>
       <c r="F30" t="n">
-        <v>38.5814</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.9978</v>
+        <v>25.9707</v>
       </c>
       <c r="C31" t="n">
-        <v>43.4844</v>
+        <v>21.5987</v>
       </c>
       <c r="D31" t="n">
-        <v>62.1745</v>
+        <v>60.914</v>
       </c>
       <c r="E31" t="n">
-        <v>22.224</v>
+        <v>22.1217</v>
       </c>
       <c r="F31" t="n">
-        <v>37.8703</v>
+        <v>37.4132</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.5784</v>
+        <v>25.5685</v>
       </c>
       <c r="C32" t="n">
-        <v>42.669</v>
+        <v>21.04</v>
       </c>
       <c r="D32" t="n">
-        <v>61.4783</v>
+        <v>60.424</v>
       </c>
       <c r="E32" t="n">
-        <v>21.6169</v>
+        <v>21.5754</v>
       </c>
       <c r="F32" t="n">
-        <v>37.3037</v>
+        <v>36.8623</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>25.0557</v>
+        <v>24.9844</v>
       </c>
       <c r="C33" t="n">
-        <v>42.0509</v>
+        <v>20.588</v>
       </c>
       <c r="D33" t="n">
-        <v>60.9889</v>
+        <v>59.9971</v>
       </c>
       <c r="E33" t="n">
-        <v>21.2388</v>
+        <v>21.0749</v>
       </c>
       <c r="F33" t="n">
-        <v>36.8262</v>
+        <v>36.3824</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>24.6171</v>
+        <v>24.3615</v>
       </c>
       <c r="C34" t="n">
-        <v>41.6482</v>
+        <v>20.2601</v>
       </c>
       <c r="D34" t="n">
-        <v>60.4204</v>
+        <v>59.2669</v>
       </c>
       <c r="E34" t="n">
-        <v>20.8312</v>
+        <v>20.8935</v>
       </c>
       <c r="F34" t="n">
-        <v>36.3957</v>
+        <v>36.0224</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>24.134</v>
+        <v>24.0471</v>
       </c>
       <c r="C35" t="n">
-        <v>41.3422</v>
+        <v>19.8692</v>
       </c>
       <c r="D35" t="n">
-        <v>78.94070000000001</v>
+        <v>77.8323</v>
       </c>
       <c r="E35" t="n">
-        <v>20.6275</v>
+        <v>20.4811</v>
       </c>
       <c r="F35" t="n">
-        <v>36.1612</v>
+        <v>35.8146</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>24.1519</v>
+        <v>23.5586</v>
       </c>
       <c r="C36" t="n">
-        <v>40.8937</v>
+        <v>19.5755</v>
       </c>
       <c r="D36" t="n">
-        <v>77.1807</v>
+        <v>76.0818</v>
       </c>
       <c r="E36" t="n">
-        <v>20.5212</v>
+        <v>20.3216</v>
       </c>
       <c r="F36" t="n">
-        <v>36.1532</v>
+        <v>35.796</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.8521</v>
+        <v>23.3221</v>
       </c>
       <c r="C37" t="n">
-        <v>40.9525</v>
+        <v>27.847</v>
       </c>
       <c r="D37" t="n">
-        <v>75.62869999999999</v>
+        <v>74.4374</v>
       </c>
       <c r="E37" t="n">
-        <v>29.8042</v>
+        <v>29.9357</v>
       </c>
       <c r="F37" t="n">
-        <v>44.9152</v>
+        <v>44.7688</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>32.3658</v>
+        <v>32.2472</v>
       </c>
       <c r="C38" t="n">
-        <v>52.2932</v>
+        <v>27.1006</v>
       </c>
       <c r="D38" t="n">
-        <v>74.1892</v>
+        <v>73.12269999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>28.9701</v>
+        <v>29.1099</v>
       </c>
       <c r="F38" t="n">
-        <v>44.045</v>
+        <v>43.8447</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>31.4909</v>
+        <v>31.2807</v>
       </c>
       <c r="C39" t="n">
-        <v>51.3388</v>
+        <v>26.3359</v>
       </c>
       <c r="D39" t="n">
-        <v>72.72280000000001</v>
+        <v>71.75320000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>27.806</v>
+        <v>28.0445</v>
       </c>
       <c r="F39" t="n">
-        <v>43.1821</v>
+        <v>42.9041</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>30.0138</v>
+        <v>30.5029</v>
       </c>
       <c r="C40" t="n">
-        <v>50.1851</v>
+        <v>25.5939</v>
       </c>
       <c r="D40" t="n">
-        <v>71.4187</v>
+        <v>70.4426</v>
       </c>
       <c r="E40" t="n">
-        <v>27.1081</v>
+        <v>27.1188</v>
       </c>
       <c r="F40" t="n">
-        <v>42.8318</v>
+        <v>42.4765</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>29.5453</v>
+        <v>29.5887</v>
       </c>
       <c r="C41" t="n">
-        <v>49.2548</v>
+        <v>24.8561</v>
       </c>
       <c r="D41" t="n">
-        <v>70.236</v>
+        <v>69.12139999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>26.0641</v>
+        <v>26.1383</v>
       </c>
       <c r="F41" t="n">
-        <v>41.9705</v>
+        <v>41.6145</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>29.178</v>
+        <v>28.8449</v>
       </c>
       <c r="C42" t="n">
-        <v>48.4349</v>
+        <v>24.1846</v>
       </c>
       <c r="D42" t="n">
-        <v>69.16540000000001</v>
+        <v>68.1271</v>
       </c>
       <c r="E42" t="n">
-        <v>25.2433</v>
+        <v>25.4648</v>
       </c>
       <c r="F42" t="n">
-        <v>41.01</v>
+        <v>40.7328</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>28.3693</v>
+        <v>28.5003</v>
       </c>
       <c r="C43" t="n">
-        <v>47.6991</v>
+        <v>23.5324</v>
       </c>
       <c r="D43" t="n">
-        <v>68.3085</v>
+        <v>66.9144</v>
       </c>
       <c r="E43" t="n">
-        <v>24.7598</v>
+        <v>24.3807</v>
       </c>
       <c r="F43" t="n">
-        <v>40.4962</v>
+        <v>40.021</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>28.1058</v>
+        <v>28.6521</v>
       </c>
       <c r="C44" t="n">
-        <v>46.861</v>
+        <v>23.0355</v>
       </c>
       <c r="D44" t="n">
-        <v>67.3142</v>
+        <v>66.0337</v>
       </c>
       <c r="E44" t="n">
-        <v>23.7574</v>
+        <v>23.7079</v>
       </c>
       <c r="F44" t="n">
-        <v>39.832</v>
+        <v>39.2942</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>26.7395</v>
+        <v>28.3755</v>
       </c>
       <c r="C45" t="n">
-        <v>45.9892</v>
+        <v>22.4186</v>
       </c>
       <c r="D45" t="n">
-        <v>66.55500000000001</v>
+        <v>65.3681</v>
       </c>
       <c r="E45" t="n">
-        <v>23.1172</v>
+        <v>23.0573</v>
       </c>
       <c r="F45" t="n">
-        <v>39.2532</v>
+        <v>38.6865</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>26.8735</v>
+        <v>26.1931</v>
       </c>
       <c r="C46" t="n">
-        <v>45.2901</v>
+        <v>21.8761</v>
       </c>
       <c r="D46" t="n">
-        <v>65.9037</v>
+        <v>64.7383</v>
       </c>
       <c r="E46" t="n">
-        <v>22.505</v>
+        <v>22.455</v>
       </c>
       <c r="F46" t="n">
-        <v>38.69</v>
+        <v>38.146</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>25.6311</v>
+        <v>26.8138</v>
       </c>
       <c r="C47" t="n">
-        <v>44.6856</v>
+        <v>21.3234</v>
       </c>
       <c r="D47" t="n">
-        <v>65.2086</v>
+        <v>64.2676</v>
       </c>
       <c r="E47" t="n">
-        <v>22.0051</v>
+        <v>21.9083</v>
       </c>
       <c r="F47" t="n">
-        <v>38.3787</v>
+        <v>37.6849</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>26.1738</v>
+        <v>26.0072</v>
       </c>
       <c r="C48" t="n">
-        <v>44.4797</v>
+        <v>20.9356</v>
       </c>
       <c r="D48" t="n">
-        <v>64.66079999999999</v>
+        <v>63.4373</v>
       </c>
       <c r="E48" t="n">
-        <v>21.8083</v>
+        <v>21.4403</v>
       </c>
       <c r="F48" t="n">
-        <v>37.9966</v>
+        <v>37.3385</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>25.9598</v>
+        <v>25.5527</v>
       </c>
       <c r="C49" t="n">
-        <v>43.9009</v>
+        <v>20.5874</v>
       </c>
       <c r="D49" t="n">
-        <v>64.17740000000001</v>
+        <v>63.0896</v>
       </c>
       <c r="E49" t="n">
-        <v>21.32</v>
+        <v>21.2019</v>
       </c>
       <c r="F49" t="n">
-        <v>37.7375</v>
+        <v>37.0955</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>24.3443</v>
+        <v>24.9122</v>
       </c>
       <c r="C50" t="n">
-        <v>43.4701</v>
+        <v>20.4002</v>
       </c>
       <c r="D50" t="n">
-        <v>81.9781</v>
+        <v>80.7543</v>
       </c>
       <c r="E50" t="n">
-        <v>21.1518</v>
+        <v>21.0581</v>
       </c>
       <c r="F50" t="n">
-        <v>37.6694</v>
+        <v>37.0068</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>24.5254</v>
+        <v>25.0084</v>
       </c>
       <c r="C51" t="n">
-        <v>43.0015</v>
+        <v>28.6838</v>
       </c>
       <c r="D51" t="n">
-        <v>80.2512</v>
+        <v>79.02670000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>31.1417</v>
+        <v>31.1439</v>
       </c>
       <c r="F51" t="n">
-        <v>46.957</v>
+        <v>46.663</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>24.3252</v>
+        <v>25.1527</v>
       </c>
       <c r="C52" t="n">
-        <v>42.8846</v>
+        <v>27.8896</v>
       </c>
       <c r="D52" t="n">
-        <v>78.58110000000001</v>
+        <v>77.352</v>
       </c>
       <c r="E52" t="n">
-        <v>29.9324</v>
+        <v>30.0025</v>
       </c>
       <c r="F52" t="n">
-        <v>46.0095</v>
+        <v>45.7889</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>32.9628</v>
+        <v>33.3916</v>
       </c>
       <c r="C53" t="n">
-        <v>52.6615</v>
+        <v>27.148</v>
       </c>
       <c r="D53" t="n">
-        <v>77.0714</v>
+        <v>75.8249</v>
       </c>
       <c r="E53" t="n">
-        <v>29.4371</v>
+        <v>29.0585</v>
       </c>
       <c r="F53" t="n">
-        <v>45.2351</v>
+        <v>44.9344</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>31.8809</v>
+        <v>32.3254</v>
       </c>
       <c r="C54" t="n">
-        <v>51.5955</v>
+        <v>26.4369</v>
       </c>
       <c r="D54" t="n">
-        <v>75.5436</v>
+        <v>74.41459999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>28.2452</v>
+        <v>28.2944</v>
       </c>
       <c r="F54" t="n">
-        <v>44.2802</v>
+        <v>44.1175</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>31.4208</v>
+        <v>31.29</v>
       </c>
       <c r="C55" t="n">
-        <v>50.8642</v>
+        <v>25.7218</v>
       </c>
       <c r="D55" t="n">
-        <v>74.27800000000001</v>
+        <v>73.10639999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>27.4448</v>
+        <v>27.1609</v>
       </c>
       <c r="F55" t="n">
-        <v>43.5799</v>
+        <v>43.344</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>30.9536</v>
+        <v>30.0354</v>
       </c>
       <c r="C56" t="n">
-        <v>49.7617</v>
+        <v>25.2127</v>
       </c>
       <c r="D56" t="n">
-        <v>73.1006</v>
+        <v>72.0431</v>
       </c>
       <c r="E56" t="n">
-        <v>26.5604</v>
+        <v>26.4685</v>
       </c>
       <c r="F56" t="n">
-        <v>42.9203</v>
+        <v>42.8111</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>29.5801</v>
+        <v>29.22</v>
       </c>
       <c r="C57" t="n">
-        <v>49.3042</v>
+        <v>24.5539</v>
       </c>
       <c r="D57" t="n">
-        <v>71.9589</v>
+        <v>70.8138</v>
       </c>
       <c r="E57" t="n">
-        <v>25.8449</v>
+        <v>25.7401</v>
       </c>
       <c r="F57" t="n">
-        <v>42.0872</v>
+        <v>42.1933</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.764</v>
+        <v>28.8413</v>
       </c>
       <c r="C58" t="n">
-        <v>48.6674</v>
+        <v>24.0806</v>
       </c>
       <c r="D58" t="n">
-        <v>70.99550000000001</v>
+        <v>69.952</v>
       </c>
       <c r="E58" t="n">
-        <v>25.1337</v>
+        <v>25.1882</v>
       </c>
       <c r="F58" t="n">
-        <v>41.6638</v>
+        <v>41.559</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>28.0172</v>
+        <v>28.519</v>
       </c>
       <c r="C59" t="n">
-        <v>48.0084</v>
+        <v>23.3497</v>
       </c>
       <c r="D59" t="n">
-        <v>70.1052</v>
+        <v>69.033</v>
       </c>
       <c r="E59" t="n">
-        <v>24.4363</v>
+        <v>24.1968</v>
       </c>
       <c r="F59" t="n">
-        <v>40.9442</v>
+        <v>40.9825</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>27.7795</v>
+        <v>28.2611</v>
       </c>
       <c r="C60" t="n">
-        <v>47.3285</v>
+        <v>22.7974</v>
       </c>
       <c r="D60" t="n">
-        <v>69.4046</v>
+        <v>68.3759</v>
       </c>
       <c r="E60" t="n">
-        <v>23.6967</v>
+        <v>23.6818</v>
       </c>
       <c r="F60" t="n">
-        <v>40.4951</v>
+        <v>40.4962</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.9937</v>
+        <v>27.1023</v>
       </c>
       <c r="C61" t="n">
-        <v>46.8264</v>
+        <v>22.5303</v>
       </c>
       <c r="D61" t="n">
-        <v>68.6827</v>
+        <v>67.5959</v>
       </c>
       <c r="E61" t="n">
-        <v>23.2827</v>
+        <v>23.258</v>
       </c>
       <c r="F61" t="n">
-        <v>39.9505</v>
+        <v>40.096</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>26.5029</v>
+        <v>26.2497</v>
       </c>
       <c r="C62" t="n">
-        <v>46.2602</v>
+        <v>21.967</v>
       </c>
       <c r="D62" t="n">
-        <v>67.98399999999999</v>
+        <v>66.8685</v>
       </c>
       <c r="E62" t="n">
-        <v>22.7593</v>
+        <v>22.628</v>
       </c>
       <c r="F62" t="n">
-        <v>39.6665</v>
+        <v>39.706</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>26.3761</v>
+        <v>26.3424</v>
       </c>
       <c r="C63" t="n">
-        <v>45.9706</v>
+        <v>21.7375</v>
       </c>
       <c r="D63" t="n">
-        <v>67.42749999999999</v>
+        <v>66.47410000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>22.4241</v>
+        <v>22.2966</v>
       </c>
       <c r="F63" t="n">
-        <v>39.4083</v>
+        <v>39.5642</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>26.5145</v>
+        <v>26.3447</v>
       </c>
       <c r="C64" t="n">
-        <v>45.892</v>
+        <v>21.4699</v>
       </c>
       <c r="D64" t="n">
-        <v>88.1537</v>
+        <v>87.0403</v>
       </c>
       <c r="E64" t="n">
-        <v>22.3391</v>
+        <v>22.1073</v>
       </c>
       <c r="F64" t="n">
-        <v>39.3786</v>
+        <v>39.4494</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.8322</v>
+        <v>25.8228</v>
       </c>
       <c r="C65" t="n">
-        <v>45.6787</v>
+        <v>30.6115</v>
       </c>
       <c r="D65" t="n">
-        <v>86.3352</v>
+        <v>84.8625</v>
       </c>
       <c r="E65" t="n">
-        <v>22.4442</v>
+        <v>22.2736</v>
       </c>
       <c r="F65" t="n">
-        <v>39.5506</v>
+        <v>39.6339</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.8441</v>
+        <v>25.8876</v>
       </c>
       <c r="C66" t="n">
-        <v>45.8258</v>
+        <v>29.9132</v>
       </c>
       <c r="D66" t="n">
-        <v>84.4926</v>
+        <v>83.0282</v>
       </c>
       <c r="E66" t="n">
-        <v>33.5808</v>
+        <v>34.6568</v>
       </c>
       <c r="F66" t="n">
-        <v>50.4873</v>
+        <v>49.9531</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>40.4218</v>
+        <v>43.1011</v>
       </c>
       <c r="C67" t="n">
-        <v>61.3436</v>
+        <v>29.4038</v>
       </c>
       <c r="D67" t="n">
-        <v>82.8669</v>
+        <v>81.3519</v>
       </c>
       <c r="E67" t="n">
-        <v>32.3513</v>
+        <v>33.7319</v>
       </c>
       <c r="F67" t="n">
-        <v>49.9565</v>
+        <v>49.1023</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>39.2786</v>
+        <v>41.623</v>
       </c>
       <c r="C68" t="n">
-        <v>60.6096</v>
+        <v>28.5382</v>
       </c>
       <c r="D68" t="n">
-        <v>81.34999999999999</v>
+        <v>79.8193</v>
       </c>
       <c r="E68" t="n">
-        <v>31.6749</v>
+        <v>32.9186</v>
       </c>
       <c r="F68" t="n">
-        <v>49.2489</v>
+        <v>48.5777</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>41.544</v>
+        <v>40.2847</v>
       </c>
       <c r="C69" t="n">
-        <v>59.5584</v>
+        <v>28.0735</v>
       </c>
       <c r="D69" t="n">
-        <v>80.08880000000001</v>
+        <v>78.501</v>
       </c>
       <c r="E69" t="n">
-        <v>30.6064</v>
+        <v>32.1809</v>
       </c>
       <c r="F69" t="n">
-        <v>48.7341</v>
+        <v>48.1077</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>37.9881</v>
+        <v>40.3706</v>
       </c>
       <c r="C70" t="n">
-        <v>58.8493</v>
+        <v>27.7088</v>
       </c>
       <c r="D70" t="n">
-        <v>79.0919</v>
+        <v>77.38939999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>29.7077</v>
+        <v>31.0481</v>
       </c>
       <c r="F70" t="n">
-        <v>47.9282</v>
+        <v>47.3391</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>39.6171</v>
+        <v>39.1786</v>
       </c>
       <c r="C71" t="n">
-        <v>58.1619</v>
+        <v>27.0549</v>
       </c>
       <c r="D71" t="n">
-        <v>78.13339999999999</v>
+        <v>76.5851</v>
       </c>
       <c r="E71" t="n">
-        <v>28.8513</v>
+        <v>30.3198</v>
       </c>
       <c r="F71" t="n">
-        <v>47.2465</v>
+        <v>46.6981</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>37.9404</v>
+        <v>38.7048</v>
       </c>
       <c r="C72" t="n">
-        <v>57.2307</v>
+        <v>26.6299</v>
       </c>
       <c r="D72" t="n">
-        <v>77.43980000000001</v>
+        <v>75.9753</v>
       </c>
       <c r="E72" t="n">
-        <v>28.4386</v>
+        <v>29.5999</v>
       </c>
       <c r="F72" t="n">
-        <v>46.6331</v>
+        <v>46.1988</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>36.8215</v>
+        <v>38.3613</v>
       </c>
       <c r="C73" t="n">
-        <v>56.5749</v>
+        <v>26.189</v>
       </c>
       <c r="D73" t="n">
-        <v>76.93729999999999</v>
+        <v>75.70910000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>27.9622</v>
+        <v>28.9163</v>
       </c>
       <c r="F73" t="n">
-        <v>46.0694</v>
+        <v>45.6595</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>36.134</v>
+        <v>36.4394</v>
       </c>
       <c r="C74" t="n">
-        <v>56.0931</v>
+        <v>25.8253</v>
       </c>
       <c r="D74" t="n">
-        <v>76.67959999999999</v>
+        <v>75.4106</v>
       </c>
       <c r="E74" t="n">
-        <v>26.9004</v>
+        <v>28.1742</v>
       </c>
       <c r="F74" t="n">
-        <v>45.5869</v>
+        <v>45.2111</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>38.1139</v>
+        <v>37.8073</v>
       </c>
       <c r="C75" t="n">
-        <v>55.6611</v>
+        <v>25.3485</v>
       </c>
       <c r="D75" t="n">
-        <v>76.2535</v>
+        <v>74.6477</v>
       </c>
       <c r="E75" t="n">
-        <v>26.52</v>
+        <v>27.6122</v>
       </c>
       <c r="F75" t="n">
-        <v>45.1616</v>
+        <v>44.8566</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>34.4954</v>
+        <v>34.1797</v>
       </c>
       <c r="C76" t="n">
-        <v>55.3156</v>
+        <v>24.9881</v>
       </c>
       <c r="D76" t="n">
-        <v>76.0737</v>
+        <v>74.74290000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>26.0829</v>
+        <v>27.2397</v>
       </c>
       <c r="F76" t="n">
-        <v>44.8022</v>
+        <v>44.5898</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>34.8693</v>
+        <v>34.4379</v>
       </c>
       <c r="C77" t="n">
-        <v>55.2557</v>
+        <v>24.5144</v>
       </c>
       <c r="D77" t="n">
-        <v>76.063</v>
+        <v>74.9036</v>
       </c>
       <c r="E77" t="n">
-        <v>25.8</v>
+        <v>26.8099</v>
       </c>
       <c r="F77" t="n">
-        <v>44.5239</v>
+        <v>44.5068</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>33.3477</v>
+        <v>33.7363</v>
       </c>
       <c r="C78" t="n">
-        <v>54.6292</v>
+        <v>24.2938</v>
       </c>
       <c r="D78" t="n">
-        <v>123.496</v>
+        <v>123.717</v>
       </c>
       <c r="E78" t="n">
-        <v>25.3886</v>
+        <v>26.5487</v>
       </c>
       <c r="F78" t="n">
-        <v>44.4236</v>
+        <v>44.3466</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>34.6607</v>
+        <v>32.9241</v>
       </c>
       <c r="C79" t="n">
-        <v>54.6368</v>
+        <v>34.1033</v>
       </c>
       <c r="D79" t="n">
-        <v>121.35</v>
+        <v>121.717</v>
       </c>
       <c r="E79" t="n">
-        <v>25.4699</v>
+        <v>26.465</v>
       </c>
       <c r="F79" t="n">
-        <v>44.5551</v>
+        <v>44.5466</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>33.2192</v>
+        <v>33.5123</v>
       </c>
       <c r="C80" t="n">
-        <v>54.6946</v>
+        <v>33.869</v>
       </c>
       <c r="D80" t="n">
-        <v>119.617</v>
+        <v>119.768</v>
       </c>
       <c r="E80" t="n">
-        <v>40.4435</v>
+        <v>42.6662</v>
       </c>
       <c r="F80" t="n">
-        <v>72.8329</v>
+        <v>72.4046</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>45.22</v>
+        <v>45.2105</v>
       </c>
       <c r="C81" t="n">
-        <v>89.1421</v>
+        <v>33.6981</v>
       </c>
       <c r="D81" t="n">
-        <v>118.052</v>
+        <v>118.24</v>
       </c>
       <c r="E81" t="n">
-        <v>39.6516</v>
+        <v>41.6181</v>
       </c>
       <c r="F81" t="n">
-        <v>73.68219999999999</v>
+        <v>72.3128</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>50.87</v>
+        <v>51.0161</v>
       </c>
       <c r="C82" t="n">
-        <v>89.741</v>
+        <v>33.4218</v>
       </c>
       <c r="D82" t="n">
-        <v>116.62</v>
+        <v>117.557</v>
       </c>
       <c r="E82" t="n">
-        <v>38.647</v>
+        <v>40.7687</v>
       </c>
       <c r="F82" t="n">
-        <v>72.2422</v>
+        <v>71.5883</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>43.1969</v>
+        <v>50.7035</v>
       </c>
       <c r="C83" t="n">
-        <v>90.5201</v>
+        <v>32.8961</v>
       </c>
       <c r="D83" t="n">
-        <v>115.733</v>
+        <v>116.77</v>
       </c>
       <c r="E83" t="n">
-        <v>37.9225</v>
+        <v>39.8165</v>
       </c>
       <c r="F83" t="n">
-        <v>73.8304</v>
+        <v>72.9166</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>45.8292</v>
+        <v>48.6854</v>
       </c>
       <c r="C84" t="n">
-        <v>90.8967</v>
+        <v>32.7101</v>
       </c>
       <c r="D84" t="n">
-        <v>115.796</v>
+        <v>116.389</v>
       </c>
       <c r="E84" t="n">
-        <v>36.9451</v>
+        <v>38.8306</v>
       </c>
       <c r="F84" t="n">
-        <v>72.51349999999999</v>
+        <v>69.6427</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>46.4933</v>
+        <v>44.1096</v>
       </c>
       <c r="C85" t="n">
-        <v>89.504</v>
+        <v>32.3021</v>
       </c>
       <c r="D85" t="n">
-        <v>115.158</v>
+        <v>115.751</v>
       </c>
       <c r="E85" t="n">
-        <v>36.1238</v>
+        <v>37.8841</v>
       </c>
       <c r="F85" t="n">
-        <v>70.1589</v>
+        <v>69.6538</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>43.114</v>
+        <v>49.6796</v>
       </c>
       <c r="C86" t="n">
-        <v>87.2932</v>
+        <v>32.0347</v>
       </c>
       <c r="D86" t="n">
-        <v>115.185</v>
+        <v>116.022</v>
       </c>
       <c r="E86" t="n">
-        <v>35.1247</v>
+        <v>36.9159</v>
       </c>
       <c r="F86" t="n">
-        <v>68.7381</v>
+        <v>68.2893</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>46.0935</v>
+        <v>46.5325</v>
       </c>
       <c r="C87" t="n">
-        <v>86.28149999999999</v>
+        <v>31.6323</v>
       </c>
       <c r="D87" t="n">
-        <v>115.635</v>
+        <v>116.093</v>
       </c>
       <c r="E87" t="n">
-        <v>34.3437</v>
+        <v>36.0221</v>
       </c>
       <c r="F87" t="n">
-        <v>67.3434</v>
+        <v>66.8563</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>40.9998</v>
+        <v>43.0412</v>
       </c>
       <c r="C88" t="n">
-        <v>84.84780000000001</v>
+        <v>31.3808</v>
       </c>
       <c r="D88" t="n">
-        <v>116.311</v>
+        <v>116.86</v>
       </c>
       <c r="E88" t="n">
-        <v>33.6111</v>
+        <v>35.2797</v>
       </c>
       <c r="F88" t="n">
-        <v>66.3824</v>
+        <v>65.8896</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>42.5661</v>
+        <v>43.5965</v>
       </c>
       <c r="C89" t="n">
-        <v>84.3741</v>
+        <v>30.9755</v>
       </c>
       <c r="D89" t="n">
-        <v>117.231</v>
+        <v>117.668</v>
       </c>
       <c r="E89" t="n">
-        <v>32.9524</v>
+        <v>34.3609</v>
       </c>
       <c r="F89" t="n">
-        <v>65.53449999999999</v>
+        <v>64.89060000000001</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>43.8121</v>
+        <v>41.6682</v>
       </c>
       <c r="C90" t="n">
-        <v>82.7002</v>
+        <v>30.6912</v>
       </c>
       <c r="D90" t="n">
-        <v>118.247</v>
+        <v>118.336</v>
       </c>
       <c r="E90" t="n">
-        <v>32.2611</v>
+        <v>33.5117</v>
       </c>
       <c r="F90" t="n">
-        <v>64.7944</v>
+        <v>64.35639999999999</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>43.2003</v>
+        <v>45.1239</v>
       </c>
       <c r="C91" t="n">
-        <v>81.5526</v>
+        <v>30.3711</v>
       </c>
       <c r="D91" t="n">
-        <v>120.001</v>
+        <v>120.331</v>
       </c>
       <c r="E91" t="n">
-        <v>31.574</v>
+        <v>32.9475</v>
       </c>
       <c r="F91" t="n">
-        <v>63.6657</v>
+        <v>63.2486</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>39.7869</v>
+        <v>41.4072</v>
       </c>
       <c r="C92" t="n">
-        <v>81.5544</v>
+        <v>29.9911</v>
       </c>
       <c r="D92" t="n">
-        <v>177.482</v>
+        <v>181.478</v>
       </c>
       <c r="E92" t="n">
-        <v>31.0435</v>
+        <v>32.3655</v>
       </c>
       <c r="F92" t="n">
-        <v>63.8931</v>
+        <v>62.6765</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>42.3442</v>
+        <v>41.6186</v>
       </c>
       <c r="C93" t="n">
-        <v>79.4019</v>
+        <v>29.9107</v>
       </c>
       <c r="D93" t="n">
-        <v>177.142</v>
+        <v>180.452</v>
       </c>
       <c r="E93" t="n">
-        <v>30.8823</v>
+        <v>32.2038</v>
       </c>
       <c r="F93" t="n">
-        <v>62.6769</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>38.817</v>
+        <v>43.2167</v>
       </c>
       <c r="C94" t="n">
-        <v>79.26179999999999</v>
+        <v>62.4657</v>
       </c>
       <c r="D94" t="n">
-        <v>175.953</v>
+        <v>179.915</v>
       </c>
       <c r="E94" t="n">
-        <v>51.8733</v>
+        <v>64.2071</v>
       </c>
       <c r="F94" t="n">
-        <v>109.987</v>
+        <v>124.32</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>62.3975</v>
+        <v>72.0638</v>
       </c>
       <c r="C95" t="n">
-        <v>123.224</v>
+        <v>61.6013</v>
       </c>
       <c r="D95" t="n">
-        <v>174.791</v>
+        <v>178.758</v>
       </c>
       <c r="E95" t="n">
-        <v>50.8392</v>
+        <v>63.0844</v>
       </c>
       <c r="F95" t="n">
-        <v>110.121</v>
+        <v>123.036</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>61.191</v>
+        <v>74.9072</v>
       </c>
       <c r="C96" t="n">
-        <v>123.354</v>
+        <v>60.168</v>
       </c>
       <c r="D96" t="n">
-        <v>174.083</v>
+        <v>178.29</v>
       </c>
       <c r="E96" t="n">
-        <v>49.6132</v>
+        <v>61.2464</v>
       </c>
       <c r="F96" t="n">
-        <v>109.502</v>
+        <v>120.561</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>60.6249</v>
+        <v>72.03830000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>123.564</v>
+        <v>58.6293</v>
       </c>
       <c r="D97" t="n">
-        <v>173.458</v>
+        <v>177.569</v>
       </c>
       <c r="E97" t="n">
-        <v>48.426</v>
+        <v>59.5701</v>
       </c>
       <c r="F97" t="n">
-        <v>108.012</v>
+        <v>118.153</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>59.637</v>
+        <v>70.24550000000001</v>
       </c>
       <c r="C98" t="n">
-        <v>121.529</v>
+        <v>57.2868</v>
       </c>
       <c r="D98" t="n">
-        <v>173.239</v>
+        <v>177.491</v>
       </c>
       <c r="E98" t="n">
-        <v>47.1224</v>
+        <v>57.8365</v>
       </c>
       <c r="F98" t="n">
-        <v>103.956</v>
+        <v>115.193</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>57.4519</v>
+        <v>68.9559</v>
       </c>
       <c r="C99" t="n">
-        <v>120.437</v>
+        <v>56.0684</v>
       </c>
       <c r="D99" t="n">
-        <v>173.097</v>
+        <v>177.408</v>
       </c>
       <c r="E99" t="n">
-        <v>45.7086</v>
+        <v>55.8697</v>
       </c>
       <c r="F99" t="n">
-        <v>105.092</v>
+        <v>111.729</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>56.8392</v>
+        <v>68.9755</v>
       </c>
       <c r="C100" t="n">
-        <v>118.925</v>
+        <v>54.8574</v>
       </c>
       <c r="D100" t="n">
-        <v>173.806</v>
+        <v>178.274</v>
       </c>
       <c r="E100" t="n">
-        <v>44.6145</v>
+        <v>54.1745</v>
       </c>
       <c r="F100" t="n">
-        <v>103.408</v>
+        <v>111.636</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>56.5361</v>
+        <v>66.3352</v>
       </c>
       <c r="C101" t="n">
-        <v>118.928</v>
+        <v>53.651</v>
       </c>
       <c r="D101" t="n">
-        <v>173.588</v>
+        <v>178.014</v>
       </c>
       <c r="E101" t="n">
-        <v>43.5462</v>
+        <v>52.6099</v>
       </c>
       <c r="F101" t="n">
-        <v>102.205</v>
+        <v>108.461</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>56.7446</v>
+        <v>65.5108</v>
       </c>
       <c r="C102" t="n">
-        <v>116.606</v>
+        <v>52.4849</v>
       </c>
       <c r="D102" t="n">
-        <v>175.237</v>
+        <v>179.117</v>
       </c>
       <c r="E102" t="n">
-        <v>42.4266</v>
+        <v>51.2349</v>
       </c>
       <c r="F102" t="n">
-        <v>99.90940000000001</v>
+        <v>109.009</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>55.8942</v>
+        <v>63.6934</v>
       </c>
       <c r="C103" t="n">
-        <v>115.632</v>
+        <v>51.3016</v>
       </c>
       <c r="D103" t="n">
-        <v>175.921</v>
+        <v>180.066</v>
       </c>
       <c r="E103" t="n">
-        <v>41.4673</v>
+        <v>49.7826</v>
       </c>
       <c r="F103" t="n">
-        <v>99.5226</v>
+        <v>107.898</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>54.8364</v>
+        <v>62.555</v>
       </c>
       <c r="C104" t="n">
-        <v>115.06</v>
+        <v>50.313</v>
       </c>
       <c r="D104" t="n">
-        <v>177.735</v>
+        <v>181.998</v>
       </c>
       <c r="E104" t="n">
-        <v>40.614</v>
+        <v>48.4886</v>
       </c>
       <c r="F104" t="n">
-        <v>97.904</v>
+        <v>102.149</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>54.1132</v>
+        <v>63.9461</v>
       </c>
       <c r="C105" t="n">
-        <v>112.548</v>
+        <v>49.4873</v>
       </c>
       <c r="D105" t="n">
-        <v>179.448</v>
+        <v>183.571</v>
       </c>
       <c r="E105" t="n">
-        <v>39.8539</v>
+        <v>47.3145</v>
       </c>
       <c r="F105" t="n">
-        <v>95.3793</v>
+        <v>101.44</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>53.5834</v>
+        <v>62.8891</v>
       </c>
       <c r="C106" t="n">
-        <v>111.66</v>
+        <v>48.5178</v>
       </c>
       <c r="D106" t="n">
-        <v>181.468</v>
+        <v>185.834</v>
       </c>
       <c r="E106" t="n">
-        <v>39.1451</v>
+        <v>46.4647</v>
       </c>
       <c r="F106" t="n">
-        <v>96.1138</v>
+        <v>102.434</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>53.2636</v>
+        <v>61.8161</v>
       </c>
       <c r="C107" t="n">
-        <v>113.669</v>
+        <v>47.7247</v>
       </c>
       <c r="D107" t="n">
-        <v>241.372</v>
+        <v>249.903</v>
       </c>
       <c r="E107" t="n">
-        <v>34.8493</v>
+        <v>45.2857</v>
       </c>
       <c r="F107" t="n">
-        <v>95.8039</v>
+        <v>104.663</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>52.2077</v>
+        <v>60.292</v>
       </c>
       <c r="C108" t="n">
-        <v>109.938</v>
+        <v>82.1861</v>
       </c>
       <c r="D108" t="n">
-        <v>238.494</v>
+        <v>246.976</v>
       </c>
       <c r="E108" t="n">
-        <v>60.3866</v>
+        <v>79.09010000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>251.22</v>
+        <v>260.31</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>54.3801</v>
+        <v>61.0077</v>
       </c>
       <c r="C109" t="n">
-        <v>111.089</v>
+        <v>80.35380000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>237.015</v>
+        <v>244.627</v>
       </c>
       <c r="E109" t="n">
-        <v>59.6643</v>
+        <v>67.2303</v>
       </c>
       <c r="F109" t="n">
-        <v>251.511</v>
+        <v>260.849</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>72.8835</v>
+        <v>92.76690000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>281.127</v>
+        <v>78.9233</v>
       </c>
       <c r="D110" t="n">
-        <v>235.14</v>
+        <v>242.721</v>
       </c>
       <c r="E110" t="n">
-        <v>58.3813</v>
+        <v>75.8593</v>
       </c>
       <c r="F110" t="n">
-        <v>251.715</v>
+        <v>260.123</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>72.5526</v>
+        <v>91.9658</v>
       </c>
       <c r="C111" t="n">
-        <v>281.76</v>
+        <v>76.9723</v>
       </c>
       <c r="D111" t="n">
-        <v>234.393</v>
+        <v>243.386</v>
       </c>
       <c r="E111" t="n">
-        <v>52.7421</v>
+        <v>73.188</v>
       </c>
       <c r="F111" t="n">
-        <v>253.903</v>
+        <v>260.554</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>70.5682</v>
+        <v>83.6494</v>
       </c>
       <c r="C112" t="n">
-        <v>282.031</v>
+        <v>63.0933</v>
       </c>
       <c r="D112" t="n">
-        <v>232.418</v>
+        <v>240.032</v>
       </c>
       <c r="E112" t="n">
-        <v>55.4704</v>
+        <v>62.421</v>
       </c>
       <c r="F112" t="n">
-        <v>255.064</v>
+        <v>260.134</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>70.8274</v>
+        <v>87.85980000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>281.945</v>
+        <v>72.9579</v>
       </c>
       <c r="D113" t="n">
-        <v>233.411</v>
+        <v>239.111</v>
       </c>
       <c r="E113" t="n">
-        <v>54.172</v>
+        <v>69.26600000000001</v>
       </c>
       <c r="F113" t="n">
-        <v>257.015</v>
+        <v>259.653</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>67.1224</v>
+        <v>86.2367</v>
       </c>
       <c r="C114" t="n">
-        <v>281.01</v>
+        <v>71.22580000000001</v>
       </c>
       <c r="D114" t="n">
-        <v>236.961</v>
+        <v>245.359</v>
       </c>
       <c r="E114" t="n">
-        <v>52.9914</v>
+        <v>58.9915</v>
       </c>
       <c r="F114" t="n">
-        <v>256.651</v>
+        <v>259.859</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>68.9217</v>
+        <v>84.9306</v>
       </c>
       <c r="C115" t="n">
-        <v>282.404</v>
+        <v>69.4867</v>
       </c>
       <c r="D115" t="n">
-        <v>237.18</v>
+        <v>248.436</v>
       </c>
       <c r="E115" t="n">
-        <v>51.6194</v>
+        <v>65.4658</v>
       </c>
       <c r="F115" t="n">
-        <v>258.13</v>
+        <v>259.715</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>68.3035</v>
+        <v>77.1447</v>
       </c>
       <c r="C116" t="n">
-        <v>282.093</v>
+        <v>58.4015</v>
       </c>
       <c r="D116" t="n">
-        <v>235.254</v>
+        <v>254.096</v>
       </c>
       <c r="E116" t="n">
-        <v>50.6712</v>
+        <v>63.7318</v>
       </c>
       <c r="F116" t="n">
-        <v>257.975</v>
+        <v>259.274</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>66.7186</v>
+        <v>80.6007</v>
       </c>
       <c r="C117" t="n">
-        <v>281.896</v>
+        <v>66.2574</v>
       </c>
       <c r="D117" t="n">
-        <v>236.794</v>
+        <v>249.709</v>
       </c>
       <c r="E117" t="n">
-        <v>46.611</v>
+        <v>62.0132</v>
       </c>
       <c r="F117" t="n">
-        <v>259.231</v>
+        <v>259.482</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>62.9548</v>
+        <v>79.0634</v>
       </c>
       <c r="C118" t="n">
-        <v>284.244</v>
+        <v>65.08799999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>232.639</v>
+        <v>239.174</v>
       </c>
       <c r="E118" t="n">
-        <v>45.6448</v>
+        <v>53.8471</v>
       </c>
       <c r="F118" t="n">
-        <v>260.719</v>
+        <v>238.831</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>64.53830000000001</v>
+        <v>74.3721</v>
       </c>
       <c r="C119" t="n">
-        <v>171.143</v>
+        <v>55.4997</v>
       </c>
       <c r="D119" t="n">
-        <v>233.437</v>
+        <v>240.161</v>
       </c>
       <c r="E119" t="n">
-        <v>45.0347</v>
+        <v>52.7995</v>
       </c>
       <c r="F119" t="n">
-        <v>237.966</v>
+        <v>236.281</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>64.9194</v>
+        <v>76.88039999999999</v>
       </c>
       <c r="C120" t="n">
-        <v>285.066</v>
+        <v>62.4466</v>
       </c>
       <c r="D120" t="n">
-        <v>235.09</v>
+        <v>241.468</v>
       </c>
       <c r="E120" t="n">
-        <v>44.3472</v>
+        <v>51.8122</v>
       </c>
       <c r="F120" t="n">
-        <v>120.134</v>
+        <v>260.807</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>59.3355</v>
+        <v>71.08329999999999</v>
       </c>
       <c r="C121" t="n">
-        <v>172.993</v>
+        <v>53.6864</v>
       </c>
       <c r="D121" t="n">
-        <v>302.73</v>
+        <v>316.808</v>
       </c>
       <c r="E121" t="n">
-        <v>43.8079</v>
+        <v>51.1864</v>
       </c>
       <c r="F121" t="n">
-        <v>119.916</v>
+        <v>212.742</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>64.92619999999999</v>
+        <v>73.53919999999999</v>
       </c>
       <c r="C122" t="n">
-        <v>286.144</v>
+        <v>95.3884</v>
       </c>
       <c r="D122" t="n">
-        <v>299.173</v>
+        <v>312.1</v>
       </c>
       <c r="E122" t="n">
-        <v>43.4248</v>
+        <v>50.5326</v>
       </c>
       <c r="F122" t="n">
-        <v>216.494</v>
+        <v>212.189</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>63.6594</v>
+        <v>68.5518</v>
       </c>
       <c r="C123" t="n">
-        <v>286.76</v>
+        <v>86.7204</v>
       </c>
       <c r="D123" t="n">
-        <v>295.103</v>
+        <v>308.027</v>
       </c>
       <c r="E123" t="n">
-        <v>65.00830000000001</v>
+        <v>83.3287</v>
       </c>
       <c r="F123" t="n">
-        <v>310.1</v>
+        <v>314.511</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>82.9901</v>
+        <v>104.915</v>
       </c>
       <c r="C124" t="n">
-        <v>346.547</v>
+        <v>92.3871</v>
       </c>
       <c r="D124" t="n">
-        <v>291.919</v>
+        <v>304.555</v>
       </c>
       <c r="E124" t="n">
-        <v>63.8381</v>
+        <v>81.77970000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>310.256</v>
+        <v>313.018</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>82.60290000000001</v>
+        <v>100.163</v>
       </c>
       <c r="C125" t="n">
-        <v>344.232</v>
+        <v>84.28279999999999</v>
       </c>
       <c r="D125" t="n">
-        <v>288.899</v>
+        <v>301.034</v>
       </c>
       <c r="E125" t="n">
-        <v>62.977</v>
+        <v>85.02</v>
       </c>
       <c r="F125" t="n">
-        <v>309.708</v>
+        <v>312.186</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>81.9226</v>
+        <v>97.8852</v>
       </c>
       <c r="C126" t="n">
-        <v>344.003</v>
+        <v>82.76479999999999</v>
       </c>
       <c r="D126" t="n">
-        <v>286.595</v>
+        <v>298.534</v>
       </c>
       <c r="E126" t="n">
-        <v>62.1521</v>
+        <v>78.3702</v>
       </c>
       <c r="F126" t="n">
-        <v>309.741</v>
+        <v>310.59</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>79.2159</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>343.139</v>
+        <v>81.45650000000001</v>
       </c>
       <c r="D127" t="n">
-        <v>284.331</v>
+        <v>295.931</v>
       </c>
       <c r="E127" t="n">
-        <v>61.3136</v>
+        <v>76.9438</v>
       </c>
       <c r="F127" t="n">
-        <v>308.678</v>
+        <v>309.913</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>79.5921</v>
+        <v>94.789</v>
       </c>
       <c r="C128" t="n">
-        <v>341.14</v>
+        <v>80.15519999999999</v>
       </c>
       <c r="D128" t="n">
-        <v>282.708</v>
+        <v>294.096</v>
       </c>
       <c r="E128" t="n">
-        <v>62.1799</v>
+        <v>75.4706</v>
       </c>
       <c r="F128" t="n">
-        <v>309.001</v>
+        <v>308.357</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>77.39319999999999</v>
+        <v>92.8815</v>
       </c>
       <c r="C129" t="n">
-        <v>340.649</v>
+        <v>78.807</v>
       </c>
       <c r="D129" t="n">
-        <v>281.367</v>
+        <v>292.313</v>
       </c>
       <c r="E129" t="n">
-        <v>59.7599</v>
+        <v>74.2154</v>
       </c>
       <c r="F129" t="n">
-        <v>308.387</v>
+        <v>308.438</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>78.07729999999999</v>
+        <v>95.2084</v>
       </c>
       <c r="C130" t="n">
-        <v>338.644</v>
+        <v>82.4246</v>
       </c>
       <c r="D130" t="n">
-        <v>280.371</v>
+        <v>291.119</v>
       </c>
       <c r="E130" t="n">
-        <v>59.0348</v>
+        <v>72.8048</v>
       </c>
       <c r="F130" t="n">
-        <v>308.066</v>
+        <v>307.366</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>76.5532</v>
+        <v>90.4483</v>
       </c>
       <c r="C131" t="n">
-        <v>339.061</v>
+        <v>76.4539</v>
       </c>
       <c r="D131" t="n">
-        <v>279.563</v>
+        <v>290.041</v>
       </c>
       <c r="E131" t="n">
-        <v>58.5144</v>
+        <v>71.75839999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>308.276</v>
+        <v>306.107</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>76.458</v>
+        <v>88.857</v>
       </c>
       <c r="C132" t="n">
-        <v>337.461</v>
+        <v>75.446</v>
       </c>
       <c r="D132" t="n">
-        <v>279.181</v>
+        <v>289.69</v>
       </c>
       <c r="E132" t="n">
-        <v>57.6924</v>
+        <v>70.3184</v>
       </c>
       <c r="F132" t="n">
-        <v>309.917</v>
+        <v>306.232</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>75.4944</v>
+        <v>88.5633</v>
       </c>
       <c r="C133" t="n">
-        <v>336.53</v>
+        <v>74.47150000000001</v>
       </c>
       <c r="D133" t="n">
-        <v>276.457</v>
+        <v>289.439</v>
       </c>
       <c r="E133" t="n">
-        <v>57.1087</v>
+        <v>69.60420000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>310.419</v>
+        <v>305.788</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>75.0106</v>
+        <v>87.5886</v>
       </c>
       <c r="C134" t="n">
-        <v>336.593</v>
+        <v>73.5042</v>
       </c>
       <c r="D134" t="n">
-        <v>278.191</v>
+        <v>286.921</v>
       </c>
       <c r="E134" t="n">
-        <v>53.9845</v>
+        <v>62.3944</v>
       </c>
       <c r="F134" t="n">
-        <v>258.91</v>
+        <v>278.758</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>74.46720000000001</v>
+        <v>85.8085</v>
       </c>
       <c r="C135" t="n">
-        <v>336.785</v>
+        <v>72.7813</v>
       </c>
       <c r="D135" t="n">
-        <v>347.641</v>
+        <v>363.268</v>
       </c>
       <c r="E135" t="n">
-        <v>53.816</v>
+        <v>61.8921</v>
       </c>
       <c r="F135" t="n">
-        <v>310.294</v>
+        <v>250.71</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>74.5055</v>
+        <v>82.0585</v>
       </c>
       <c r="C136" t="n">
-        <v>336.725</v>
+        <v>99.5774</v>
       </c>
       <c r="D136" t="n">
-        <v>343.24</v>
+        <v>356.898</v>
       </c>
       <c r="E136" t="n">
-        <v>53.4084</v>
+        <v>61.4915</v>
       </c>
       <c r="F136" t="n">
-        <v>309.844</v>
+        <v>304.417</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>72.8125</v>
+        <v>85.7457</v>
       </c>
       <c r="C137" t="n">
-        <v>336.514</v>
+        <v>104.872</v>
       </c>
       <c r="D137" t="n">
-        <v>337.092</v>
+        <v>351.456</v>
       </c>
       <c r="E137" t="n">
-        <v>74.5406</v>
+        <v>94.5133</v>
       </c>
       <c r="F137" t="n">
-        <v>356.895</v>
+        <v>344.875</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>94.3165</v>
+        <v>114.305</v>
       </c>
       <c r="C138" t="n">
-        <v>389.85</v>
+        <v>102.154</v>
       </c>
       <c r="D138" t="n">
-        <v>332.258</v>
+        <v>333.49</v>
       </c>
       <c r="E138" t="n">
-        <v>73.6572</v>
+        <v>91.09180000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>355.189</v>
+        <v>342.631</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>91.8673</v>
+        <v>107.681</v>
       </c>
       <c r="C139" t="n">
-        <v>385.63</v>
+        <v>93.943</v>
       </c>
       <c r="D139" t="n">
-        <v>327.92</v>
+        <v>328.68</v>
       </c>
       <c r="E139" t="n">
-        <v>72.8262</v>
+        <v>89.3175</v>
       </c>
       <c r="F139" t="n">
-        <v>353.724</v>
+        <v>342.101</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>91.3228</v>
+        <v>107.042</v>
       </c>
       <c r="C140" t="n">
-        <v>382.456</v>
+        <v>92.67619999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>324.672</v>
+        <v>325.388</v>
       </c>
       <c r="E140" t="n">
-        <v>71.6636</v>
+        <v>87.9893</v>
       </c>
       <c r="F140" t="n">
-        <v>352.439</v>
+        <v>339.313</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>92.4301</v>
+        <v>105.808</v>
       </c>
       <c r="C141" t="n">
-        <v>382.189</v>
+        <v>91.5377</v>
       </c>
       <c r="D141" t="n">
-        <v>321.99</v>
+        <v>323.616</v>
       </c>
       <c r="E141" t="n">
-        <v>71.1746</v>
+        <v>86.2002</v>
       </c>
       <c r="F141" t="n">
-        <v>351.722</v>
+        <v>338.552</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>89.6835</v>
+        <v>105.105</v>
       </c>
       <c r="C142" t="n">
-        <v>380.093</v>
+        <v>90.2217</v>
       </c>
       <c r="D142" t="n">
-        <v>320.277</v>
+        <v>322.364</v>
       </c>
       <c r="E142" t="n">
-        <v>70.73390000000001</v>
+        <v>85.1972</v>
       </c>
       <c r="F142" t="n">
-        <v>350.147</v>
+        <v>335.692</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>89.64060000000001</v>
+        <v>106.644</v>
       </c>
       <c r="C143" t="n">
-        <v>379.018</v>
+        <v>94.69499999999999</v>
       </c>
       <c r="D143" t="n">
-        <v>317.708</v>
+        <v>320.569</v>
       </c>
       <c r="E143" t="n">
-        <v>71.29000000000001</v>
+        <v>84.22790000000001</v>
       </c>
       <c r="F143" t="n">
-        <v>348.377</v>
+        <v>335.791</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.1099</v>
+        <v>24.1291</v>
       </c>
       <c r="C2" t="n">
-        <v>20.2956</v>
+        <v>20.2971</v>
       </c>
       <c r="D2" t="n">
-        <v>53.5753</v>
+        <v>53.6152</v>
       </c>
       <c r="E2" t="n">
-        <v>19.6994</v>
+        <v>18.187</v>
       </c>
       <c r="F2" t="n">
-        <v>35.955</v>
+        <v>33.6247</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.2416</v>
+        <v>23.1503</v>
       </c>
       <c r="C3" t="n">
-        <v>19.7931</v>
+        <v>19.708</v>
       </c>
       <c r="D3" t="n">
-        <v>52.941</v>
+        <v>52.9132</v>
       </c>
       <c r="E3" t="n">
-        <v>18.7835</v>
+        <v>17.6511</v>
       </c>
       <c r="F3" t="n">
-        <v>35.3819</v>
+        <v>33.1703</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>23.0334</v>
+        <v>22.8648</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2655</v>
+        <v>19.3731</v>
       </c>
       <c r="D4" t="n">
-        <v>52.3902</v>
+        <v>52.3852</v>
       </c>
       <c r="E4" t="n">
-        <v>18.5277</v>
+        <v>17.2028</v>
       </c>
       <c r="F4" t="n">
-        <v>34.8911</v>
+        <v>32.7912</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.3993</v>
+        <v>22.6073</v>
       </c>
       <c r="C5" t="n">
-        <v>18.801</v>
+        <v>18.8012</v>
       </c>
       <c r="D5" t="n">
-        <v>51.8961</v>
+        <v>51.9774</v>
       </c>
       <c r="E5" t="n">
-        <v>18.0738</v>
+        <v>16.7247</v>
       </c>
       <c r="F5" t="n">
-        <v>34.5221</v>
+        <v>32.5109</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.0642</v>
+        <v>22.1106</v>
       </c>
       <c r="C6" t="n">
-        <v>18.4389</v>
+        <v>18.4779</v>
       </c>
       <c r="D6" t="n">
-        <v>51.4998</v>
+        <v>51.5936</v>
       </c>
       <c r="E6" t="n">
-        <v>17.8355</v>
+        <v>16.4652</v>
       </c>
       <c r="F6" t="n">
-        <v>34.2708</v>
+        <v>32.342</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.7322</v>
+        <v>21.7064</v>
       </c>
       <c r="C7" t="n">
-        <v>18.1469</v>
+        <v>18.2443</v>
       </c>
       <c r="D7" t="n">
-        <v>65.6343</v>
+        <v>65.4721</v>
       </c>
       <c r="E7" t="n">
-        <v>17.6907</v>
+        <v>25.6983</v>
       </c>
       <c r="F7" t="n">
-        <v>34.2317</v>
+        <v>40.7713</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.158</v>
+        <v>21.3093</v>
       </c>
       <c r="C8" t="n">
-        <v>27.1543</v>
+        <v>26.866</v>
       </c>
       <c r="D8" t="n">
-        <v>64.0778</v>
+        <v>63.8976</v>
       </c>
       <c r="E8" t="n">
-        <v>18.0488</v>
+        <v>24.7244</v>
       </c>
       <c r="F8" t="n">
-        <v>34.543</v>
+        <v>39.8242</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.5823</v>
+        <v>21.7547</v>
       </c>
       <c r="C9" t="n">
-        <v>25.9694</v>
+        <v>26.0051</v>
       </c>
       <c r="D9" t="n">
-        <v>62.7093</v>
+        <v>62.5168</v>
       </c>
       <c r="E9" t="n">
-        <v>26.9839</v>
+        <v>24.048</v>
       </c>
       <c r="F9" t="n">
-        <v>42.899</v>
+        <v>38.8718</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>29.8766</v>
+        <v>29.9731</v>
       </c>
       <c r="C10" t="n">
-        <v>25.1303</v>
+        <v>25.1833</v>
       </c>
       <c r="D10" t="n">
-        <v>61.5599</v>
+        <v>61.2869</v>
       </c>
       <c r="E10" t="n">
-        <v>25.9424</v>
+        <v>23.1349</v>
       </c>
       <c r="F10" t="n">
-        <v>41.8416</v>
+        <v>38.2685</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>28.937</v>
+        <v>28.7553</v>
       </c>
       <c r="C11" t="n">
-        <v>24.4396</v>
+        <v>24.3618</v>
       </c>
       <c r="D11" t="n">
-        <v>60.5663</v>
+        <v>60.2287</v>
       </c>
       <c r="E11" t="n">
-        <v>25.5051</v>
+        <v>22.3862</v>
       </c>
       <c r="F11" t="n">
-        <v>40.8769</v>
+        <v>37.3701</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>28.7567</v>
+        <v>28.2316</v>
       </c>
       <c r="C12" t="n">
-        <v>23.583</v>
+        <v>23.6075</v>
       </c>
       <c r="D12" t="n">
-        <v>59.4271</v>
+        <v>59.1155</v>
       </c>
       <c r="E12" t="n">
-        <v>24.5114</v>
+        <v>21.6398</v>
       </c>
       <c r="F12" t="n">
-        <v>39.917</v>
+        <v>36.6322</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>27.8914</v>
+        <v>27.7049</v>
       </c>
       <c r="C13" t="n">
-        <v>22.865</v>
+        <v>22.856</v>
       </c>
       <c r="D13" t="n">
-        <v>58.598</v>
+        <v>58.1202</v>
       </c>
       <c r="E13" t="n">
-        <v>23.6104</v>
+        <v>21.004</v>
       </c>
       <c r="F13" t="n">
-        <v>39.057</v>
+        <v>35.9255</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>26.7096</v>
+        <v>26.4454</v>
       </c>
       <c r="C14" t="n">
-        <v>22.3444</v>
+        <v>22.1672</v>
       </c>
       <c r="D14" t="n">
-        <v>57.8156</v>
+        <v>57.3847</v>
       </c>
       <c r="E14" t="n">
-        <v>22.881</v>
+        <v>20.4128</v>
       </c>
       <c r="F14" t="n">
-        <v>38.0856</v>
+        <v>35.2178</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>25.8592</v>
+        <v>26.2821</v>
       </c>
       <c r="C15" t="n">
-        <v>21.5498</v>
+        <v>21.5144</v>
       </c>
       <c r="D15" t="n">
-        <v>57.1989</v>
+        <v>56.6946</v>
       </c>
       <c r="E15" t="n">
-        <v>22.301</v>
+        <v>20.304</v>
       </c>
       <c r="F15" t="n">
-        <v>37.484</v>
+        <v>34.7013</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>25.2193</v>
+        <v>25.2769</v>
       </c>
       <c r="C16" t="n">
-        <v>20.9661</v>
+        <v>20.9538</v>
       </c>
       <c r="D16" t="n">
-        <v>56.5342</v>
+        <v>56.5031</v>
       </c>
       <c r="E16" t="n">
-        <v>21.5152</v>
+        <v>19.2914</v>
       </c>
       <c r="F16" t="n">
-        <v>36.879</v>
+        <v>34.1307</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>24.8818</v>
+        <v>24.7408</v>
       </c>
       <c r="C17" t="n">
-        <v>20.3718</v>
+        <v>20.3788</v>
       </c>
       <c r="D17" t="n">
-        <v>55.891</v>
+        <v>55.8208</v>
       </c>
       <c r="E17" t="n">
-        <v>20.9463</v>
+        <v>18.8083</v>
       </c>
       <c r="F17" t="n">
-        <v>36.0803</v>
+        <v>33.6506</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.3568</v>
+        <v>24.0519</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8431</v>
+        <v>19.8401</v>
       </c>
       <c r="D18" t="n">
-        <v>55.2233</v>
+        <v>55.2042</v>
       </c>
       <c r="E18" t="n">
-        <v>20.4458</v>
+        <v>18.4125</v>
       </c>
       <c r="F18" t="n">
-        <v>35.6583</v>
+        <v>33.1793</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.2506</v>
+        <v>23.8277</v>
       </c>
       <c r="C19" t="n">
-        <v>19.4128</v>
+        <v>19.339</v>
       </c>
       <c r="D19" t="n">
-        <v>54.4662</v>
+        <v>54.272</v>
       </c>
       <c r="E19" t="n">
-        <v>20.0152</v>
+        <v>17.9793</v>
       </c>
       <c r="F19" t="n">
-        <v>35.1816</v>
+        <v>32.8128</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.0663</v>
+        <v>23.4937</v>
       </c>
       <c r="C20" t="n">
-        <v>19.3436</v>
+        <v>18.9527</v>
       </c>
       <c r="D20" t="n">
-        <v>54.0316</v>
+        <v>53.9015</v>
       </c>
       <c r="E20" t="n">
-        <v>19.8748</v>
+        <v>17.7387</v>
       </c>
       <c r="F20" t="n">
-        <v>34.838</v>
+        <v>32.6255</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>23.1321</v>
+        <v>22.8872</v>
       </c>
       <c r="C21" t="n">
-        <v>18.6617</v>
+        <v>18.6598</v>
       </c>
       <c r="D21" t="n">
-        <v>71.5296</v>
+        <v>71.4996</v>
       </c>
       <c r="E21" t="n">
-        <v>19.6561</v>
+        <v>26.9188</v>
       </c>
       <c r="F21" t="n">
-        <v>34.7026</v>
+        <v>42.9598</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.4925</v>
+        <v>22.522</v>
       </c>
       <c r="C22" t="n">
-        <v>27.3791</v>
+        <v>27.3835</v>
       </c>
       <c r="D22" t="n">
-        <v>70.0202</v>
+        <v>69.7325</v>
       </c>
       <c r="E22" t="n">
-        <v>19.5668</v>
+        <v>25.9674</v>
       </c>
       <c r="F22" t="n">
-        <v>34.7801</v>
+        <v>41.5989</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.4987</v>
+        <v>22.2303</v>
       </c>
       <c r="C23" t="n">
-        <v>26.5731</v>
+        <v>26.6174</v>
       </c>
       <c r="D23" t="n">
-        <v>68.57769999999999</v>
+        <v>68.2717</v>
       </c>
       <c r="E23" t="n">
-        <v>28.4472</v>
+        <v>25.1525</v>
       </c>
       <c r="F23" t="n">
-        <v>43.1992</v>
+        <v>40.8687</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>30.7329</v>
+        <v>30.688</v>
       </c>
       <c r="C24" t="n">
-        <v>25.7459</v>
+        <v>25.673</v>
       </c>
       <c r="D24" t="n">
-        <v>67.2636</v>
+        <v>67.0389</v>
       </c>
       <c r="E24" t="n">
-        <v>27.4961</v>
+        <v>24.3212</v>
       </c>
       <c r="F24" t="n">
-        <v>42.1406</v>
+        <v>39.9906</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>29.8227</v>
+        <v>30.0936</v>
       </c>
       <c r="C25" t="n">
-        <v>25.0009</v>
+        <v>24.9464</v>
       </c>
       <c r="D25" t="n">
-        <v>66.0253</v>
+        <v>65.91</v>
       </c>
       <c r="E25" t="n">
-        <v>26.5291</v>
+        <v>23.5545</v>
       </c>
       <c r="F25" t="n">
-        <v>41.1309</v>
+        <v>39.0769</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>28.961</v>
+        <v>29.3367</v>
       </c>
       <c r="C26" t="n">
-        <v>24.2035</v>
+        <v>24.1367</v>
       </c>
       <c r="D26" t="n">
-        <v>64.5761</v>
+        <v>64.4619</v>
       </c>
       <c r="E26" t="n">
-        <v>25.6993</v>
+        <v>22.821</v>
       </c>
       <c r="F26" t="n">
-        <v>40.6505</v>
+        <v>37.4512</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.1122</v>
+        <v>28.6303</v>
       </c>
       <c r="C27" t="n">
-        <v>23.5759</v>
+        <v>23.399</v>
       </c>
       <c r="D27" t="n">
-        <v>63.5603</v>
+        <v>63.5281</v>
       </c>
       <c r="E27" t="n">
-        <v>24.93</v>
+        <v>22.1243</v>
       </c>
       <c r="F27" t="n">
-        <v>39.7538</v>
+        <v>36.7853</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>27.2319</v>
+        <v>27.3354</v>
       </c>
       <c r="C28" t="n">
-        <v>22.8022</v>
+        <v>22.763</v>
       </c>
       <c r="D28" t="n">
-        <v>62.7156</v>
+        <v>62.5339</v>
       </c>
       <c r="E28" t="n">
-        <v>24.073</v>
+        <v>21.5035</v>
       </c>
       <c r="F28" t="n">
-        <v>39.0091</v>
+        <v>36.0304</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>26.77</v>
+        <v>26.5783</v>
       </c>
       <c r="C29" t="n">
-        <v>22.1625</v>
+        <v>22.109</v>
       </c>
       <c r="D29" t="n">
-        <v>61.9535</v>
+        <v>61.7965</v>
       </c>
       <c r="E29" t="n">
-        <v>23.3531</v>
+        <v>20.7819</v>
       </c>
       <c r="F29" t="n">
-        <v>38.2019</v>
+        <v>35.5107</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>25.7638</v>
+        <v>25.8814</v>
       </c>
       <c r="C30" t="n">
-        <v>21.5488</v>
+        <v>21.4989</v>
       </c>
       <c r="D30" t="n">
-        <v>61.1337</v>
+        <v>60.9603</v>
       </c>
       <c r="E30" t="n">
-        <v>22.6867</v>
+        <v>20.2154</v>
       </c>
       <c r="F30" t="n">
-        <v>37.576</v>
+        <v>34.8547</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.5109</v>
+        <v>25.6979</v>
       </c>
       <c r="C31" t="n">
-        <v>20.9134</v>
+        <v>20.8764</v>
       </c>
       <c r="D31" t="n">
-        <v>60.5197</v>
+        <v>60.4445</v>
       </c>
       <c r="E31" t="n">
-        <v>21.9776</v>
+        <v>19.6754</v>
       </c>
       <c r="F31" t="n">
-        <v>36.4743</v>
+        <v>35.3788</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.3396</v>
+        <v>25.36</v>
       </c>
       <c r="C32" t="n">
-        <v>20.3784</v>
+        <v>20.3204</v>
       </c>
       <c r="D32" t="n">
-        <v>60.0582</v>
+        <v>59.9086</v>
       </c>
       <c r="E32" t="n">
-        <v>21.3893</v>
+        <v>19.2145</v>
       </c>
       <c r="F32" t="n">
-        <v>36.1887</v>
+        <v>34.9453</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>24.0809</v>
+        <v>25.2231</v>
       </c>
       <c r="C33" t="n">
-        <v>19.9098</v>
+        <v>19.9074</v>
       </c>
       <c r="D33" t="n">
-        <v>59.6821</v>
+        <v>59.5281</v>
       </c>
       <c r="E33" t="n">
-        <v>21.0263</v>
+        <v>18.8657</v>
       </c>
       <c r="F33" t="n">
-        <v>35.691</v>
+        <v>33.4596</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>24.082</v>
+        <v>24.0894</v>
       </c>
       <c r="C34" t="n">
-        <v>19.4773</v>
+        <v>19.4275</v>
       </c>
       <c r="D34" t="n">
-        <v>58.8873</v>
+        <v>58.7796</v>
       </c>
       <c r="E34" t="n">
-        <v>20.8829</v>
+        <v>18.4322</v>
       </c>
       <c r="F34" t="n">
-        <v>35.2591</v>
+        <v>33.1628</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.3289</v>
+        <v>23.3483</v>
       </c>
       <c r="C35" t="n">
-        <v>19.124</v>
+        <v>19.0943</v>
       </c>
       <c r="D35" t="n">
-        <v>77.1769</v>
+        <v>76.9859</v>
       </c>
       <c r="E35" t="n">
-        <v>20.1912</v>
+        <v>27.8236</v>
       </c>
       <c r="F35" t="n">
-        <v>34.9995</v>
+        <v>42.273</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.0148</v>
+        <v>23.7777</v>
       </c>
       <c r="C36" t="n">
-        <v>18.7389</v>
+        <v>18.7889</v>
       </c>
       <c r="D36" t="n">
-        <v>75.417</v>
+        <v>75.2478</v>
       </c>
       <c r="E36" t="n">
-        <v>20.0692</v>
+        <v>26.8732</v>
       </c>
       <c r="F36" t="n">
-        <v>34.8886</v>
+        <v>41.3759</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.3369</v>
+        <v>23.3163</v>
       </c>
       <c r="C37" t="n">
-        <v>27.1163</v>
+        <v>27.0671</v>
       </c>
       <c r="D37" t="n">
-        <v>73.8074</v>
+        <v>73.6795</v>
       </c>
       <c r="E37" t="n">
-        <v>29.1793</v>
+        <v>26.0077</v>
       </c>
       <c r="F37" t="n">
-        <v>43.6697</v>
+        <v>40.5812</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>31.2632</v>
+        <v>31.6999</v>
       </c>
       <c r="C38" t="n">
-        <v>26.347</v>
+        <v>26.3012</v>
       </c>
       <c r="D38" t="n">
-        <v>72.39319999999999</v>
+        <v>72.217</v>
       </c>
       <c r="E38" t="n">
-        <v>28.2684</v>
+        <v>25.1667</v>
       </c>
       <c r="F38" t="n">
-        <v>43.0505</v>
+        <v>39.818</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>30.5372</v>
+        <v>30.8033</v>
       </c>
       <c r="C39" t="n">
-        <v>25.5345</v>
+        <v>25.6016</v>
       </c>
       <c r="D39" t="n">
-        <v>71.01430000000001</v>
+        <v>70.84739999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>27.2872</v>
+        <v>24.6453</v>
       </c>
       <c r="F39" t="n">
-        <v>42.1872</v>
+        <v>38.9676</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>29.947</v>
+        <v>29.6</v>
       </c>
       <c r="C40" t="n">
-        <v>24.8216</v>
+        <v>24.8249</v>
       </c>
       <c r="D40" t="n">
-        <v>69.7632</v>
+        <v>69.572</v>
       </c>
       <c r="E40" t="n">
-        <v>26.4775</v>
+        <v>23.7633</v>
       </c>
       <c r="F40" t="n">
-        <v>41.1865</v>
+        <v>38.2805</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>28.7301</v>
+        <v>28.8756</v>
       </c>
       <c r="C41" t="n">
-        <v>24.1119</v>
+        <v>24.1348</v>
       </c>
       <c r="D41" t="n">
-        <v>68.59990000000001</v>
+        <v>68.4046</v>
       </c>
       <c r="E41" t="n">
-        <v>25.5613</v>
+        <v>23.0451</v>
       </c>
       <c r="F41" t="n">
-        <v>40.4306</v>
+        <v>37.6023</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>27.7833</v>
+        <v>28.45</v>
       </c>
       <c r="C42" t="n">
-        <v>23.4213</v>
+        <v>23.3666</v>
       </c>
       <c r="D42" t="n">
-        <v>67.7805</v>
+        <v>67.44540000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>24.8242</v>
+        <v>22.4651</v>
       </c>
       <c r="F42" t="n">
-        <v>39.6986</v>
+        <v>37.0262</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>27.2257</v>
+        <v>27.2509</v>
       </c>
       <c r="C43" t="n">
-        <v>22.8148</v>
+        <v>22.7597</v>
       </c>
       <c r="D43" t="n">
-        <v>66.51260000000001</v>
+        <v>66.3394</v>
       </c>
       <c r="E43" t="n">
-        <v>24.2742</v>
+        <v>21.6688</v>
       </c>
       <c r="F43" t="n">
-        <v>39.0023</v>
+        <v>36.4493</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>26.7935</v>
+        <v>26.8996</v>
       </c>
       <c r="C44" t="n">
-        <v>22.2035</v>
+        <v>22.1327</v>
       </c>
       <c r="D44" t="n">
-        <v>65.6551</v>
+        <v>65.4665</v>
       </c>
       <c r="E44" t="n">
-        <v>23.3792</v>
+        <v>21.1517</v>
       </c>
       <c r="F44" t="n">
-        <v>38.4006</v>
+        <v>35.957</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>26.1941</v>
+        <v>25.8455</v>
       </c>
       <c r="C45" t="n">
-        <v>21.6514</v>
+        <v>21.6343</v>
       </c>
       <c r="D45" t="n">
-        <v>64.9969</v>
+        <v>64.87779999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>22.9205</v>
+        <v>20.6888</v>
       </c>
       <c r="F45" t="n">
-        <v>37.8515</v>
+        <v>35.4761</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>25.8312</v>
+        <v>25.331</v>
       </c>
       <c r="C46" t="n">
-        <v>21.1141</v>
+        <v>21.1631</v>
       </c>
       <c r="D46" t="n">
-        <v>64.4383</v>
+        <v>64.2234</v>
       </c>
       <c r="E46" t="n">
-        <v>22.0652</v>
+        <v>20.0754</v>
       </c>
       <c r="F46" t="n">
-        <v>37.3244</v>
+        <v>35.0654</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>24.9532</v>
+        <v>24.755</v>
       </c>
       <c r="C47" t="n">
-        <v>20.6094</v>
+        <v>20.6417</v>
       </c>
       <c r="D47" t="n">
-        <v>63.9526</v>
+        <v>63.8032</v>
       </c>
       <c r="E47" t="n">
-        <v>21.6785</v>
+        <v>19.6919</v>
       </c>
       <c r="F47" t="n">
-        <v>36.8186</v>
+        <v>34.7442</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>24.3007</v>
+        <v>24.503</v>
       </c>
       <c r="C48" t="n">
-        <v>20.2126</v>
+        <v>20.1632</v>
       </c>
       <c r="D48" t="n">
-        <v>63.191</v>
+        <v>63.0071</v>
       </c>
       <c r="E48" t="n">
-        <v>21.1814</v>
+        <v>19.4383</v>
       </c>
       <c r="F48" t="n">
-        <v>36.4702</v>
+        <v>34.4762</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>23.9184</v>
+        <v>23.5908</v>
       </c>
       <c r="C49" t="n">
-        <v>19.842</v>
+        <v>19.7734</v>
       </c>
       <c r="D49" t="n">
-        <v>62.8523</v>
+        <v>62.6158</v>
       </c>
       <c r="E49" t="n">
-        <v>20.7778</v>
+        <v>19.1069</v>
       </c>
       <c r="F49" t="n">
-        <v>36.219</v>
+        <v>34.3247</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>23.5997</v>
+        <v>23.5616</v>
       </c>
       <c r="C50" t="n">
-        <v>19.5506</v>
+        <v>19.4972</v>
       </c>
       <c r="D50" t="n">
-        <v>80.15000000000001</v>
+        <v>79.8353</v>
       </c>
       <c r="E50" t="n">
-        <v>20.5787</v>
+        <v>28.0224</v>
       </c>
       <c r="F50" t="n">
-        <v>36.1561</v>
+        <v>43.493</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>23.502</v>
+        <v>23.5722</v>
       </c>
       <c r="C51" t="n">
-        <v>27.9206</v>
+        <v>27.9136</v>
       </c>
       <c r="D51" t="n">
-        <v>78.4242</v>
+        <v>78.212</v>
       </c>
       <c r="E51" t="n">
-        <v>30.2818</v>
+        <v>27.2917</v>
       </c>
       <c r="F51" t="n">
-        <v>46.4103</v>
+        <v>42.0257</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>24.0337</v>
+        <v>23.3127</v>
       </c>
       <c r="C52" t="n">
-        <v>27.2807</v>
+        <v>27.2316</v>
       </c>
       <c r="D52" t="n">
-        <v>76.6952</v>
+        <v>76.5834</v>
       </c>
       <c r="E52" t="n">
-        <v>29.3422</v>
+        <v>26.3299</v>
       </c>
       <c r="F52" t="n">
-        <v>45.1809</v>
+        <v>41.4183</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>32.0368</v>
+        <v>31.7528</v>
       </c>
       <c r="C53" t="n">
-        <v>26.6105</v>
+        <v>26.4399</v>
       </c>
       <c r="D53" t="n">
-        <v>75.1846</v>
+        <v>75.0197</v>
       </c>
       <c r="E53" t="n">
-        <v>28.2875</v>
+        <v>25.5839</v>
       </c>
       <c r="F53" t="n">
-        <v>44.2811</v>
+        <v>40.6493</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>31.0132</v>
+        <v>31.2706</v>
       </c>
       <c r="C54" t="n">
-        <v>25.8717</v>
+        <v>25.6362</v>
       </c>
       <c r="D54" t="n">
-        <v>73.7745</v>
+        <v>73.6343</v>
       </c>
       <c r="E54" t="n">
-        <v>27.6194</v>
+        <v>24.9578</v>
       </c>
       <c r="F54" t="n">
-        <v>43.5</v>
+        <v>39.9899</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>30.1415</v>
+        <v>30.0525</v>
       </c>
       <c r="C55" t="n">
-        <v>25.1299</v>
+        <v>24.9788</v>
       </c>
       <c r="D55" t="n">
-        <v>72.5962</v>
+        <v>72.4528</v>
       </c>
       <c r="E55" t="n">
-        <v>26.5937</v>
+        <v>24.2029</v>
       </c>
       <c r="F55" t="n">
-        <v>42.7411</v>
+        <v>39.3562</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>29.8811</v>
+        <v>28.9137</v>
       </c>
       <c r="C56" t="n">
-        <v>24.5686</v>
+        <v>24.3785</v>
       </c>
       <c r="D56" t="n">
-        <v>71.4307</v>
+        <v>71.3368</v>
       </c>
       <c r="E56" t="n">
-        <v>26.0806</v>
+        <v>23.7419</v>
       </c>
       <c r="F56" t="n">
-        <v>42.024</v>
+        <v>38.9406</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>28.7763</v>
+        <v>28.7167</v>
       </c>
       <c r="C57" t="n">
-        <v>23.944</v>
+        <v>23.6768</v>
       </c>
       <c r="D57" t="n">
-        <v>70.2903</v>
+        <v>70.1309</v>
       </c>
       <c r="E57" t="n">
-        <v>25.1105</v>
+        <v>22.866</v>
       </c>
       <c r="F57" t="n">
-        <v>41.3039</v>
+        <v>38.393</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.4703</v>
+        <v>27.8405</v>
       </c>
       <c r="C58" t="n">
-        <v>23.3886</v>
+        <v>23.1313</v>
       </c>
       <c r="D58" t="n">
-        <v>69.3822</v>
+        <v>69.2886</v>
       </c>
       <c r="E58" t="n">
-        <v>24.5371</v>
+        <v>22.4793</v>
       </c>
       <c r="F58" t="n">
-        <v>40.7279</v>
+        <v>37.9412</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.871</v>
+        <v>27.5232</v>
       </c>
       <c r="C59" t="n">
-        <v>22.8725</v>
+        <v>22.6043</v>
       </c>
       <c r="D59" t="n">
-        <v>68.5514</v>
+        <v>68.3965</v>
       </c>
       <c r="E59" t="n">
-        <v>23.766</v>
+        <v>21.8944</v>
       </c>
       <c r="F59" t="n">
-        <v>40.1628</v>
+        <v>37.5722</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>27.0838</v>
+        <v>27.0207</v>
       </c>
       <c r="C60" t="n">
-        <v>22.3255</v>
+        <v>22.1364</v>
       </c>
       <c r="D60" t="n">
-        <v>67.84950000000001</v>
+        <v>67.78870000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>23.1648</v>
+        <v>21.4085</v>
       </c>
       <c r="F60" t="n">
-        <v>39.6803</v>
+        <v>37.1671</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.4644</v>
+        <v>26.1725</v>
       </c>
       <c r="C61" t="n">
-        <v>21.8756</v>
+        <v>21.6786</v>
       </c>
       <c r="D61" t="n">
-        <v>67.10299999999999</v>
+        <v>67.0557</v>
       </c>
       <c r="E61" t="n">
-        <v>22.6247</v>
+        <v>20.8417</v>
       </c>
       <c r="F61" t="n">
-        <v>39.2527</v>
+        <v>36.8581</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>26.0665</v>
+        <v>26.0612</v>
       </c>
       <c r="C62" t="n">
-        <v>21.4328</v>
+        <v>21.2058</v>
       </c>
       <c r="D62" t="n">
-        <v>66.45999999999999</v>
+        <v>66.36369999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>22.2272</v>
+        <v>20.6569</v>
       </c>
       <c r="F62" t="n">
-        <v>38.9024</v>
+        <v>36.6785</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>25.5061</v>
+        <v>25.5542</v>
       </c>
       <c r="C63" t="n">
-        <v>21.0659</v>
+        <v>20.8532</v>
       </c>
       <c r="D63" t="n">
-        <v>66.0813</v>
+        <v>65.9509</v>
       </c>
       <c r="E63" t="n">
-        <v>21.9586</v>
+        <v>20.2674</v>
       </c>
       <c r="F63" t="n">
-        <v>38.6094</v>
+        <v>36.3404</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.1734</v>
+        <v>25.1044</v>
       </c>
       <c r="C64" t="n">
-        <v>20.7839</v>
+        <v>20.5377</v>
       </c>
       <c r="D64" t="n">
-        <v>87.2312</v>
+        <v>86.7308</v>
       </c>
       <c r="E64" t="n">
-        <v>21.6953</v>
+        <v>33.1416</v>
       </c>
       <c r="F64" t="n">
-        <v>38.552</v>
+        <v>46.4254</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>24.9662</v>
+        <v>25.1815</v>
       </c>
       <c r="C65" t="n">
-        <v>29.7041</v>
+        <v>29.94</v>
       </c>
       <c r="D65" t="n">
-        <v>85.1191</v>
+        <v>84.57340000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>21.6185</v>
+        <v>31.3769</v>
       </c>
       <c r="F65" t="n">
-        <v>38.707</v>
+        <v>45.8165</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.0257</v>
+        <v>24.7235</v>
       </c>
       <c r="C66" t="n">
-        <v>29.0393</v>
+        <v>28.974</v>
       </c>
       <c r="D66" t="n">
-        <v>83.32210000000001</v>
+        <v>82.6889</v>
       </c>
       <c r="E66" t="n">
-        <v>34.1827</v>
+        <v>31.2058</v>
       </c>
       <c r="F66" t="n">
-        <v>48.7125</v>
+        <v>45.1956</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>41.8759</v>
+        <v>41.6241</v>
       </c>
       <c r="C67" t="n">
-        <v>28.4088</v>
+        <v>28.4196</v>
       </c>
       <c r="D67" t="n">
-        <v>81.6444</v>
+        <v>81.06319999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>33.3719</v>
+        <v>30.3834</v>
       </c>
       <c r="F67" t="n">
-        <v>48.0691</v>
+        <v>44.6318</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>41.279</v>
+        <v>39.5999</v>
       </c>
       <c r="C68" t="n">
-        <v>27.8353</v>
+        <v>27.849</v>
       </c>
       <c r="D68" t="n">
-        <v>80.1104</v>
+        <v>79.4297</v>
       </c>
       <c r="E68" t="n">
-        <v>32.6694</v>
+        <v>28.9286</v>
       </c>
       <c r="F68" t="n">
-        <v>47.4978</v>
+        <v>44.0249</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>40.461</v>
+        <v>38.4394</v>
       </c>
       <c r="C69" t="n">
-        <v>27.3015</v>
+        <v>27.2852</v>
       </c>
       <c r="D69" t="n">
-        <v>78.6392</v>
+        <v>78.07769999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>31.414</v>
+        <v>28.8029</v>
       </c>
       <c r="F69" t="n">
-        <v>46.9115</v>
+        <v>43.4828</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>40.2708</v>
+        <v>39.2717</v>
       </c>
       <c r="C70" t="n">
-        <v>26.8319</v>
+        <v>26.7818</v>
       </c>
       <c r="D70" t="n">
-        <v>77.6262</v>
+        <v>77.01309999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>30.8975</v>
+        <v>27.6247</v>
       </c>
       <c r="F70" t="n">
-        <v>46.2604</v>
+        <v>42.9344</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>39.2503</v>
+        <v>37.8411</v>
       </c>
       <c r="C71" t="n">
-        <v>26.2812</v>
+        <v>26.2835</v>
       </c>
       <c r="D71" t="n">
-        <v>76.95489999999999</v>
+        <v>76.184</v>
       </c>
       <c r="E71" t="n">
-        <v>30.2278</v>
+        <v>27.3793</v>
       </c>
       <c r="F71" t="n">
-        <v>45.6165</v>
+        <v>42.4489</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>37.6866</v>
+        <v>36.9076</v>
       </c>
       <c r="C72" t="n">
-        <v>25.808</v>
+        <v>25.8488</v>
       </c>
       <c r="D72" t="n">
-        <v>76.5073</v>
+        <v>75.524</v>
       </c>
       <c r="E72" t="n">
-        <v>29.3244</v>
+        <v>26.8277</v>
       </c>
       <c r="F72" t="n">
-        <v>45.0846</v>
+        <v>42.0286</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>37.7862</v>
+        <v>37.7828</v>
       </c>
       <c r="C73" t="n">
-        <v>25.4346</v>
+        <v>25.4294</v>
       </c>
       <c r="D73" t="n">
-        <v>76.1494</v>
+        <v>75.1965</v>
       </c>
       <c r="E73" t="n">
-        <v>28.936</v>
+        <v>25.5601</v>
       </c>
       <c r="F73" t="n">
-        <v>44.5782</v>
+        <v>41.6541</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>37.7215</v>
+        <v>35.3237</v>
       </c>
       <c r="C74" t="n">
-        <v>24.9498</v>
+        <v>24.9381</v>
       </c>
       <c r="D74" t="n">
-        <v>75.6096</v>
+        <v>74.5735</v>
       </c>
       <c r="E74" t="n">
-        <v>28.0904</v>
+        <v>25.2151</v>
       </c>
       <c r="F74" t="n">
-        <v>44.1982</v>
+        <v>41.2348</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>35.4782</v>
+        <v>35.6201</v>
       </c>
       <c r="C75" t="n">
-        <v>24.5951</v>
+        <v>24.5977</v>
       </c>
       <c r="D75" t="n">
-        <v>74.5431</v>
+        <v>73.8464</v>
       </c>
       <c r="E75" t="n">
-        <v>27.7877</v>
+        <v>25.1117</v>
       </c>
       <c r="F75" t="n">
-        <v>43.7461</v>
+        <v>41.035</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>34.7979</v>
+        <v>34.1523</v>
       </c>
       <c r="C76" t="n">
-        <v>24.2508</v>
+        <v>24.2772</v>
       </c>
       <c r="D76" t="n">
-        <v>74.5271</v>
+        <v>73.94459999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>27.107</v>
+        <v>24.2509</v>
       </c>
       <c r="F76" t="n">
-        <v>43.417</v>
+        <v>40.7895</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>34.0107</v>
+        <v>33.4088</v>
       </c>
       <c r="C77" t="n">
-        <v>23.872</v>
+        <v>23.832</v>
       </c>
       <c r="D77" t="n">
-        <v>74.73909999999999</v>
+        <v>74.2838</v>
       </c>
       <c r="E77" t="n">
-        <v>26.9211</v>
+        <v>23.8049</v>
       </c>
       <c r="F77" t="n">
-        <v>43.2621</v>
+        <v>40.7117</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>34.6433</v>
+        <v>33.6802</v>
       </c>
       <c r="C78" t="n">
-        <v>23.6204</v>
+        <v>23.5071</v>
       </c>
       <c r="D78" t="n">
-        <v>123.696</v>
+        <v>121.877</v>
       </c>
       <c r="E78" t="n">
-        <v>26.4231</v>
+        <v>41.018</v>
       </c>
       <c r="F78" t="n">
-        <v>43.2214</v>
+        <v>64.2058</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>35.3925</v>
+        <v>35.5842</v>
       </c>
       <c r="C79" t="n">
-        <v>33.3872</v>
+        <v>33.0569</v>
       </c>
       <c r="D79" t="n">
-        <v>121.771</v>
+        <v>117.708</v>
       </c>
       <c r="E79" t="n">
-        <v>26.2826</v>
+        <v>40.1781</v>
       </c>
       <c r="F79" t="n">
-        <v>43.3608</v>
+        <v>64.3711</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>34.1518</v>
+        <v>33.6556</v>
       </c>
       <c r="C80" t="n">
-        <v>33.22</v>
+        <v>32.7818</v>
       </c>
       <c r="D80" t="n">
-        <v>120.231</v>
+        <v>116.006</v>
       </c>
       <c r="E80" t="n">
-        <v>42.7187</v>
+        <v>39.3234</v>
       </c>
       <c r="F80" t="n">
-        <v>70.4513</v>
+        <v>64.4593</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>52.1379</v>
+        <v>46.1682</v>
       </c>
       <c r="C81" t="n">
-        <v>32.9748</v>
+        <v>32.6728</v>
       </c>
       <c r="D81" t="n">
-        <v>118.511</v>
+        <v>114.422</v>
       </c>
       <c r="E81" t="n">
-        <v>41.7021</v>
+        <v>38.5889</v>
       </c>
       <c r="F81" t="n">
-        <v>70.6127</v>
+        <v>63.6284</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>44.9282</v>
+        <v>51.036</v>
       </c>
       <c r="C82" t="n">
-        <v>32.6897</v>
+        <v>32.0714</v>
       </c>
       <c r="D82" t="n">
-        <v>117.308</v>
+        <v>113.293</v>
       </c>
       <c r="E82" t="n">
-        <v>40.6962</v>
+        <v>37.6357</v>
       </c>
       <c r="F82" t="n">
-        <v>70.46469999999999</v>
+        <v>63.1701</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>51.3159</v>
+        <v>49.6112</v>
       </c>
       <c r="C83" t="n">
-        <v>32.2703</v>
+        <v>31.7687</v>
       </c>
       <c r="D83" t="n">
-        <v>116.652</v>
+        <v>112.447</v>
       </c>
       <c r="E83" t="n">
-        <v>38.2868</v>
+        <v>36.6981</v>
       </c>
       <c r="F83" t="n">
-        <v>68.41200000000001</v>
+        <v>62.3808</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>49.194</v>
+        <v>47.7007</v>
       </c>
       <c r="C84" t="n">
-        <v>31.5491</v>
+        <v>31.4542</v>
       </c>
       <c r="D84" t="n">
-        <v>114.645</v>
+        <v>112.044</v>
       </c>
       <c r="E84" t="n">
-        <v>37.2089</v>
+        <v>35.8053</v>
       </c>
       <c r="F84" t="n">
-        <v>67.48820000000001</v>
+        <v>61.3812</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>45.6169</v>
+        <v>46.5434</v>
       </c>
       <c r="C85" t="n">
-        <v>31.2189</v>
+        <v>31.1074</v>
       </c>
       <c r="D85" t="n">
-        <v>114.673</v>
+        <v>111.908</v>
       </c>
       <c r="E85" t="n">
-        <v>36.3155</v>
+        <v>34.8477</v>
       </c>
       <c r="F85" t="n">
-        <v>64.8524</v>
+        <v>60.6301</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>47.0406</v>
+        <v>47.3537</v>
       </c>
       <c r="C86" t="n">
-        <v>30.8064</v>
+        <v>30.7884</v>
       </c>
       <c r="D86" t="n">
-        <v>113.469</v>
+        <v>112.164</v>
       </c>
       <c r="E86" t="n">
-        <v>35.3347</v>
+        <v>34.2248</v>
       </c>
       <c r="F86" t="n">
-        <v>63.7078</v>
+        <v>59.8352</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>47.074</v>
+        <v>46.8794</v>
       </c>
       <c r="C87" t="n">
-        <v>30.5064</v>
+        <v>30.4069</v>
       </c>
       <c r="D87" t="n">
-        <v>113.845</v>
+        <v>112.381</v>
       </c>
       <c r="E87" t="n">
-        <v>34.5089</v>
+        <v>33.1988</v>
       </c>
       <c r="F87" t="n">
-        <v>63.1549</v>
+        <v>58.8754</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>41.2153</v>
+        <v>47.1406</v>
       </c>
       <c r="C88" t="n">
-        <v>30.1101</v>
+        <v>30.0834</v>
       </c>
       <c r="D88" t="n">
-        <v>114.606</v>
+        <v>113.14</v>
       </c>
       <c r="E88" t="n">
-        <v>33.7724</v>
+        <v>32.5302</v>
       </c>
       <c r="F88" t="n">
-        <v>62.9388</v>
+        <v>58.1178</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>42.9418</v>
+        <v>44.5286</v>
       </c>
       <c r="C89" t="n">
-        <v>29.83</v>
+        <v>29.7943</v>
       </c>
       <c r="D89" t="n">
-        <v>114.738</v>
+        <v>113.453</v>
       </c>
       <c r="E89" t="n">
-        <v>33.1489</v>
+        <v>31.8029</v>
       </c>
       <c r="F89" t="n">
-        <v>61.112</v>
+        <v>58.3629</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>42.6532</v>
+        <v>39.8837</v>
       </c>
       <c r="C90" t="n">
-        <v>29.4491</v>
+        <v>29.5443</v>
       </c>
       <c r="D90" t="n">
-        <v>116.223</v>
+        <v>115.915</v>
       </c>
       <c r="E90" t="n">
-        <v>32.4168</v>
+        <v>31.2913</v>
       </c>
       <c r="F90" t="n">
-        <v>60.2017</v>
+        <v>57.7959</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>43.4652</v>
+        <v>42.3535</v>
       </c>
       <c r="C91" t="n">
-        <v>29.2146</v>
+        <v>29.3546</v>
       </c>
       <c r="D91" t="n">
-        <v>118.014</v>
+        <v>117.826</v>
       </c>
       <c r="E91" t="n">
-        <v>31.7232</v>
+        <v>30.6008</v>
       </c>
       <c r="F91" t="n">
-        <v>59.5625</v>
+        <v>57.1691</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>40.1702</v>
+        <v>43.3111</v>
       </c>
       <c r="C92" t="n">
-        <v>28.8801</v>
+        <v>28.8821</v>
       </c>
       <c r="D92" t="n">
-        <v>176.1</v>
+        <v>175.865</v>
       </c>
       <c r="E92" t="n">
-        <v>31.2195</v>
+        <v>64.8764</v>
       </c>
       <c r="F92" t="n">
-        <v>59.4655</v>
+        <v>88.8297</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>41.4687</v>
+        <v>44.46</v>
       </c>
       <c r="C93" t="n">
-        <v>28.785</v>
+        <v>28.695</v>
       </c>
       <c r="D93" t="n">
-        <v>175.538</v>
+        <v>174.88</v>
       </c>
       <c r="E93" t="n">
-        <v>30.9232</v>
+        <v>63.7594</v>
       </c>
       <c r="F93" t="n">
-        <v>59.033</v>
+        <v>88.8408</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>41.5495</v>
+        <v>43.4507</v>
       </c>
       <c r="C94" t="n">
-        <v>61.3218</v>
+        <v>61.8105</v>
       </c>
       <c r="D94" t="n">
-        <v>174.345</v>
+        <v>173.853</v>
       </c>
       <c r="E94" t="n">
-        <v>62.3688</v>
+        <v>61.7724</v>
       </c>
       <c r="F94" t="n">
-        <v>90.25190000000001</v>
+        <v>87.6198</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>74.16200000000001</v>
+        <v>77.80880000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>60.2074</v>
+        <v>60.673</v>
       </c>
       <c r="D95" t="n">
-        <v>173.298</v>
+        <v>172.791</v>
       </c>
       <c r="E95" t="n">
-        <v>61.0429</v>
+        <v>59.9461</v>
       </c>
       <c r="F95" t="n">
-        <v>89.5167</v>
+        <v>88.5616</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>73.0154</v>
+        <v>76.00490000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>58.5523</v>
+        <v>59.4941</v>
       </c>
       <c r="D96" t="n">
-        <v>172.579</v>
+        <v>175.73</v>
       </c>
       <c r="E96" t="n">
-        <v>59.5051</v>
+        <v>59.0721</v>
       </c>
       <c r="F96" t="n">
-        <v>89.2717</v>
+        <v>89.4051</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>72.0659</v>
+        <v>75.19199999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>57.2593</v>
+        <v>58.1685</v>
       </c>
       <c r="D97" t="n">
-        <v>172.136</v>
+        <v>175.466</v>
       </c>
       <c r="E97" t="n">
-        <v>57.7158</v>
+        <v>57.2589</v>
       </c>
       <c r="F97" t="n">
-        <v>88.437</v>
+        <v>86.1447</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>71.9971</v>
+        <v>74.22280000000001</v>
       </c>
       <c r="C98" t="n">
-        <v>55.8496</v>
+        <v>56.6715</v>
       </c>
       <c r="D98" t="n">
-        <v>171.626</v>
+        <v>175.621</v>
       </c>
       <c r="E98" t="n">
-        <v>55.924</v>
+        <v>55.6438</v>
       </c>
       <c r="F98" t="n">
-        <v>87.1195</v>
+        <v>84.4007</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>72.0633</v>
+        <v>71.4372</v>
       </c>
       <c r="C99" t="n">
-        <v>54.4924</v>
+        <v>55.417</v>
       </c>
       <c r="D99" t="n">
-        <v>172.018</v>
+        <v>175.721</v>
       </c>
       <c r="E99" t="n">
-        <v>54.3378</v>
+        <v>53.9201</v>
       </c>
       <c r="F99" t="n">
-        <v>86.4181</v>
+        <v>84.8574</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>68.4178</v>
+        <v>67.5475</v>
       </c>
       <c r="C100" t="n">
-        <v>53.3962</v>
+        <v>54.1132</v>
       </c>
       <c r="D100" t="n">
-        <v>172.818</v>
+        <v>176.536</v>
       </c>
       <c r="E100" t="n">
-        <v>52.7084</v>
+        <v>52.4643</v>
       </c>
       <c r="F100" t="n">
-        <v>86.0531</v>
+        <v>83.2972</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.96510000000001</v>
+        <v>68.9555</v>
       </c>
       <c r="C101" t="n">
-        <v>52.0992</v>
+        <v>53.0769</v>
       </c>
       <c r="D101" t="n">
-        <v>172.971</v>
+        <v>176.896</v>
       </c>
       <c r="E101" t="n">
-        <v>51.3006</v>
+        <v>51.0588</v>
       </c>
       <c r="F101" t="n">
-        <v>82.8506</v>
+        <v>87.6632</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>66.7307</v>
+        <v>67.1918</v>
       </c>
       <c r="C102" t="n">
-        <v>51.0939</v>
+        <v>51.9517</v>
       </c>
       <c r="D102" t="n">
-        <v>173.64</v>
+        <v>177.681</v>
       </c>
       <c r="E102" t="n">
-        <v>49.8147</v>
+        <v>49.7127</v>
       </c>
       <c r="F102" t="n">
-        <v>85.70569999999999</v>
+        <v>83.1358</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>63.102</v>
+        <v>66.2867</v>
       </c>
       <c r="C103" t="n">
-        <v>50.0812</v>
+        <v>50.9142</v>
       </c>
       <c r="D103" t="n">
-        <v>175.01</v>
+        <v>179.144</v>
       </c>
       <c r="E103" t="n">
-        <v>48.5621</v>
+        <v>48.3147</v>
       </c>
       <c r="F103" t="n">
-        <v>82.6705</v>
+        <v>83.1773</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>63.6894</v>
+        <v>65.37130000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>49.0443</v>
+        <v>49.8595</v>
       </c>
       <c r="D104" t="n">
-        <v>176.246</v>
+        <v>180.742</v>
       </c>
       <c r="E104" t="n">
-        <v>47.3513</v>
+        <v>47.2282</v>
       </c>
       <c r="F104" t="n">
-        <v>82.4054</v>
+        <v>81.40560000000001</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>62.5753</v>
+        <v>64.53959999999999</v>
       </c>
       <c r="C105" t="n">
-        <v>48.1168</v>
+        <v>48.9699</v>
       </c>
       <c r="D105" t="n">
-        <v>177.921</v>
+        <v>182.543</v>
       </c>
       <c r="E105" t="n">
-        <v>46.4016</v>
+        <v>46.2069</v>
       </c>
       <c r="F105" t="n">
-        <v>81.1412</v>
+        <v>91.1134</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>62.0725</v>
+        <v>65.6413</v>
       </c>
       <c r="C106" t="n">
-        <v>47.2892</v>
+        <v>48.0484</v>
       </c>
       <c r="D106" t="n">
-        <v>180.074</v>
+        <v>184.263</v>
       </c>
       <c r="E106" t="n">
-        <v>45.3614</v>
+        <v>45.2097</v>
       </c>
       <c r="F106" t="n">
-        <v>91.3143</v>
+        <v>90.8193</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>59.9731</v>
+        <v>61.407</v>
       </c>
       <c r="C107" t="n">
-        <v>46.4698</v>
+        <v>47.3331</v>
       </c>
       <c r="D107" t="n">
-        <v>240.648</v>
+        <v>248.142</v>
       </c>
       <c r="E107" t="n">
-        <v>44.2271</v>
+        <v>79.69</v>
       </c>
       <c r="F107" t="n">
-        <v>79.95999999999999</v>
+        <v>245.96</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>59.147</v>
+        <v>60.4479</v>
       </c>
       <c r="C108" t="n">
-        <v>80.5448</v>
+        <v>81.67610000000001</v>
       </c>
       <c r="D108" t="n">
-        <v>238.016</v>
+        <v>245.683</v>
       </c>
       <c r="E108" t="n">
-        <v>66.8995</v>
+        <v>77.72620000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>245.026</v>
+        <v>246.128</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>58.097</v>
+        <v>56.1741</v>
       </c>
       <c r="C109" t="n">
-        <v>78.69370000000001</v>
+        <v>66.5069</v>
       </c>
       <c r="D109" t="n">
-        <v>235.855</v>
+        <v>243.289</v>
       </c>
       <c r="E109" t="n">
-        <v>75.88890000000001</v>
+        <v>75.4049</v>
       </c>
       <c r="F109" t="n">
-        <v>245.829</v>
+        <v>246.463</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>88.65689999999999</v>
+        <v>92.7264</v>
       </c>
       <c r="C110" t="n">
-        <v>77.2012</v>
+        <v>78.48699999999999</v>
       </c>
       <c r="D110" t="n">
-        <v>234.179</v>
+        <v>241.749</v>
       </c>
       <c r="E110" t="n">
-        <v>64.232</v>
+        <v>63.9247</v>
       </c>
       <c r="F110" t="n">
-        <v>245.666</v>
+        <v>246.444</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>80.7594</v>
+        <v>91.2683</v>
       </c>
       <c r="C111" t="n">
-        <v>62.9893</v>
+        <v>76.3947</v>
       </c>
       <c r="D111" t="n">
-        <v>232.801</v>
+        <v>240.533</v>
       </c>
       <c r="E111" t="n">
-        <v>71.6896</v>
+        <v>71.4517</v>
       </c>
       <c r="F111" t="n">
-        <v>244.5</v>
+        <v>247.209</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>86.2564</v>
+        <v>87.61360000000001</v>
       </c>
       <c r="C112" t="n">
-        <v>73.1052</v>
+        <v>74.4564</v>
       </c>
       <c r="D112" t="n">
-        <v>231.057</v>
+        <v>241.021</v>
       </c>
       <c r="E112" t="n">
-        <v>69.512</v>
+        <v>60.3955</v>
       </c>
       <c r="F112" t="n">
-        <v>244.787</v>
+        <v>247.37</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>83.9884</v>
+        <v>85.76260000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>71.3086</v>
+        <v>72.5057</v>
       </c>
       <c r="D113" t="n">
-        <v>231.972</v>
+        <v>238.154</v>
       </c>
       <c r="E113" t="n">
-        <v>67.7531</v>
+        <v>58.8138</v>
       </c>
       <c r="F113" t="n">
-        <v>244.52</v>
+        <v>247.272</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.4374</v>
+        <v>84.4898</v>
       </c>
       <c r="C114" t="n">
-        <v>69.5179</v>
+        <v>70.7692</v>
       </c>
       <c r="D114" t="n">
-        <v>235.848</v>
+        <v>249.236</v>
       </c>
       <c r="E114" t="n">
-        <v>65.8781</v>
+        <v>65.49890000000001</v>
       </c>
       <c r="F114" t="n">
-        <v>246.11</v>
+        <v>248.277</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>83.227</v>
+        <v>83.2089</v>
       </c>
       <c r="C115" t="n">
-        <v>67.90300000000001</v>
+        <v>69.0106</v>
       </c>
       <c r="D115" t="n">
-        <v>235.854</v>
+        <v>251.808</v>
       </c>
       <c r="E115" t="n">
-        <v>64.1692</v>
+        <v>63.9062</v>
       </c>
       <c r="F115" t="n">
-        <v>244.427</v>
+        <v>248.335</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>80.80240000000001</v>
+        <v>82.3319</v>
       </c>
       <c r="C116" t="n">
-        <v>66.29040000000001</v>
+        <v>67.51260000000001</v>
       </c>
       <c r="D116" t="n">
-        <v>242.304</v>
+        <v>244.519</v>
       </c>
       <c r="E116" t="n">
-        <v>62.3465</v>
+        <v>62.3292</v>
       </c>
       <c r="F116" t="n">
-        <v>244.242</v>
+        <v>248.419</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>74.2068</v>
+        <v>80.38290000000001</v>
       </c>
       <c r="C117" t="n">
-        <v>55.3523</v>
+        <v>65.95399999999999</v>
       </c>
       <c r="D117" t="n">
-        <v>242.936</v>
+        <v>247.785</v>
       </c>
       <c r="E117" t="n">
-        <v>60.8067</v>
+        <v>60.5484</v>
       </c>
       <c r="F117" t="n">
-        <v>247.062</v>
+        <v>248.97</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>73.89490000000001</v>
+        <v>77.98090000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>54.3922</v>
+        <v>64.4727</v>
       </c>
       <c r="D118" t="n">
-        <v>230.395</v>
+        <v>237.78</v>
       </c>
       <c r="E118" t="n">
-        <v>59.3648</v>
+        <v>52.6112</v>
       </c>
       <c r="F118" t="n">
-        <v>245.59</v>
+        <v>250.648</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>75.23990000000001</v>
+        <v>73.62569999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>61.9598</v>
+        <v>54.7433</v>
       </c>
       <c r="D119" t="n">
-        <v>231.295</v>
+        <v>238.712</v>
       </c>
       <c r="E119" t="n">
-        <v>51.8184</v>
+        <v>51.6767</v>
       </c>
       <c r="F119" t="n">
-        <v>153.041</v>
+        <v>102.857</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>74.5211</v>
+        <v>76.1893</v>
       </c>
       <c r="C120" t="n">
-        <v>60.6084</v>
+        <v>61.9748</v>
       </c>
       <c r="D120" t="n">
-        <v>232.301</v>
+        <v>239.876</v>
       </c>
       <c r="E120" t="n">
-        <v>50.7333</v>
+        <v>50.7829</v>
       </c>
       <c r="F120" t="n">
-        <v>223.319</v>
+        <v>179.574</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>71.95869999999999</v>
+        <v>70.3498</v>
       </c>
       <c r="C121" t="n">
-        <v>59.4342</v>
+        <v>53.1816</v>
       </c>
       <c r="D121" t="n">
-        <v>304.413</v>
+        <v>314.927</v>
       </c>
       <c r="E121" t="n">
-        <v>49.992</v>
+        <v>85.8364</v>
       </c>
       <c r="F121" t="n">
-        <v>102.5</v>
+        <v>299.235</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>69.0757</v>
+        <v>72.5354</v>
       </c>
       <c r="C122" t="n">
-        <v>86.18389999999999</v>
+        <v>95.09950000000001</v>
       </c>
       <c r="D122" t="n">
-        <v>300.015</v>
+        <v>309.9</v>
       </c>
       <c r="E122" t="n">
-        <v>49.4536</v>
+        <v>83.98269999999999</v>
       </c>
       <c r="F122" t="n">
-        <v>177.196</v>
+        <v>298.997</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>68.7103</v>
+        <v>68.3327</v>
       </c>
       <c r="C123" t="n">
-        <v>84.6553</v>
+        <v>86.24339999999999</v>
       </c>
       <c r="D123" t="n">
-        <v>296.087</v>
+        <v>305.866</v>
       </c>
       <c r="E123" t="n">
-        <v>81.43210000000001</v>
+        <v>82.1131</v>
       </c>
       <c r="F123" t="n">
-        <v>292.924</v>
+        <v>297.848</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>98.10899999999999</v>
+        <v>98.0968</v>
       </c>
       <c r="C124" t="n">
-        <v>83.5861</v>
+        <v>85.3939</v>
       </c>
       <c r="D124" t="n">
-        <v>292.792</v>
+        <v>302.351</v>
       </c>
       <c r="E124" t="n">
-        <v>79.7835</v>
+        <v>80.43810000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>292.143</v>
+        <v>295.856</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>96.4366</v>
+        <v>99.1073</v>
       </c>
       <c r="C125" t="n">
-        <v>81.9311</v>
+        <v>83.71259999999999</v>
       </c>
       <c r="D125" t="n">
-        <v>289.566</v>
+        <v>299.214</v>
       </c>
       <c r="E125" t="n">
-        <v>78.1204</v>
+        <v>78.9152</v>
       </c>
       <c r="F125" t="n">
-        <v>290.298</v>
+        <v>296.722</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>95.2971</v>
+        <v>97.31480000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>80.4658</v>
+        <v>82.262</v>
       </c>
       <c r="D126" t="n">
-        <v>287.265</v>
+        <v>296.457</v>
       </c>
       <c r="E126" t="n">
-        <v>76.4372</v>
+        <v>77.2432</v>
       </c>
       <c r="F126" t="n">
-        <v>289.686</v>
+        <v>295.734</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>97.9676</v>
+        <v>95.639</v>
       </c>
       <c r="C127" t="n">
-        <v>84.7419</v>
+        <v>80.90179999999999</v>
       </c>
       <c r="D127" t="n">
-        <v>284.269</v>
+        <v>294.17</v>
       </c>
       <c r="E127" t="n">
-        <v>75.1748</v>
+        <v>75.7838</v>
       </c>
       <c r="F127" t="n">
-        <v>290.057</v>
+        <v>295.564</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>92.6807</v>
+        <v>93.9631</v>
       </c>
       <c r="C128" t="n">
-        <v>77.4194</v>
+        <v>79.5943</v>
       </c>
       <c r="D128" t="n">
-        <v>282.597</v>
+        <v>292.245</v>
       </c>
       <c r="E128" t="n">
-        <v>73.631</v>
+        <v>74.2732</v>
       </c>
       <c r="F128" t="n">
-        <v>289.312</v>
+        <v>295.462</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>89.7436</v>
+        <v>96.19929999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>76.29040000000001</v>
+        <v>83.48</v>
       </c>
       <c r="D129" t="n">
-        <v>280.935</v>
+        <v>290.336</v>
       </c>
       <c r="E129" t="n">
-        <v>72.28870000000001</v>
+        <v>73.1914</v>
       </c>
       <c r="F129" t="n">
-        <v>288.732</v>
+        <v>295.105</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>90.15309999999999</v>
+        <v>94.4183</v>
       </c>
       <c r="C130" t="n">
-        <v>75.133</v>
+        <v>82.0814</v>
       </c>
       <c r="D130" t="n">
-        <v>279.74</v>
+        <v>289.098</v>
       </c>
       <c r="E130" t="n">
-        <v>70.97410000000001</v>
+        <v>71.8736</v>
       </c>
       <c r="F130" t="n">
-        <v>288.413</v>
+        <v>294.388</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>87.50109999999999</v>
+        <v>90.8173</v>
       </c>
       <c r="C131" t="n">
-        <v>73.9648</v>
+        <v>75.95189999999999</v>
       </c>
       <c r="D131" t="n">
-        <v>278.79</v>
+        <v>288.186</v>
       </c>
       <c r="E131" t="n">
-        <v>69.7012</v>
+        <v>70.785</v>
       </c>
       <c r="F131" t="n">
-        <v>287.475</v>
+        <v>294.44</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>86.6777</v>
+        <v>91.4941</v>
       </c>
       <c r="C132" t="n">
-        <v>72.693</v>
+        <v>79.4149</v>
       </c>
       <c r="D132" t="n">
-        <v>278.423</v>
+        <v>287.633</v>
       </c>
       <c r="E132" t="n">
-        <v>68.8189</v>
+        <v>69.6683</v>
       </c>
       <c r="F132" t="n">
-        <v>287.953</v>
+        <v>294.155</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>85.0429</v>
+        <v>88.4609</v>
       </c>
       <c r="C133" t="n">
-        <v>71.73009999999999</v>
+        <v>74.1426</v>
       </c>
       <c r="D133" t="n">
-        <v>278.164</v>
+        <v>287.645</v>
       </c>
       <c r="E133" t="n">
-        <v>67.63</v>
+        <v>68.7424</v>
       </c>
       <c r="F133" t="n">
-        <v>287.339</v>
+        <v>291.148</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>85.59950000000001</v>
+        <v>84.8891</v>
       </c>
       <c r="C134" t="n">
-        <v>70.6604</v>
+        <v>70.8282</v>
       </c>
       <c r="D134" t="n">
-        <v>273.798</v>
+        <v>275.634</v>
       </c>
       <c r="E134" t="n">
-        <v>60.7998</v>
+        <v>60.7004</v>
       </c>
       <c r="F134" t="n">
-        <v>284.462</v>
+        <v>238.191</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>83.8706</v>
+        <v>85.3519</v>
       </c>
       <c r="C135" t="n">
-        <v>69.9524</v>
+        <v>72.2479</v>
       </c>
       <c r="D135" t="n">
-        <v>348.561</v>
+        <v>361.517</v>
       </c>
       <c r="E135" t="n">
-        <v>60.2995</v>
+        <v>97.241</v>
       </c>
       <c r="F135" t="n">
-        <v>234.702</v>
+        <v>339.058</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>77.6871</v>
+        <v>85.532</v>
       </c>
       <c r="C136" t="n">
-        <v>96.4796</v>
+        <v>105.519</v>
       </c>
       <c r="D136" t="n">
-        <v>343.592</v>
+        <v>354.125</v>
       </c>
       <c r="E136" t="n">
-        <v>59.7715</v>
+        <v>95.28400000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>285.661</v>
+        <v>338.941</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>78.172</v>
+        <v>84.6939</v>
       </c>
       <c r="C137" t="n">
-        <v>94.8496</v>
+        <v>104.596</v>
       </c>
       <c r="D137" t="n">
-        <v>337.367</v>
+        <v>348.998</v>
       </c>
       <c r="E137" t="n">
-        <v>92.0168</v>
+        <v>93.9546</v>
       </c>
       <c r="F137" t="n">
-        <v>329.804</v>
+        <v>339.251</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>111.166</v>
+        <v>118.093</v>
       </c>
       <c r="C138" t="n">
-        <v>94.4657</v>
+        <v>104.19</v>
       </c>
       <c r="D138" t="n">
-        <v>332.943</v>
+        <v>344.324</v>
       </c>
       <c r="E138" t="n">
-        <v>90.57940000000001</v>
+        <v>92.1046</v>
       </c>
       <c r="F138" t="n">
-        <v>327.843</v>
+        <v>335.833</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>107.983</v>
+        <v>109.259</v>
       </c>
       <c r="C139" t="n">
-        <v>93.047</v>
+        <v>95.69929999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>328.126</v>
+        <v>340.108</v>
       </c>
       <c r="E139" t="n">
-        <v>89.1357</v>
+        <v>90.72190000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>326.491</v>
+        <v>335.711</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>112.748</v>
+        <v>111.548</v>
       </c>
       <c r="C140" t="n">
-        <v>100.154</v>
+        <v>94.5214</v>
       </c>
       <c r="D140" t="n">
-        <v>325.684</v>
+        <v>335.345</v>
       </c>
       <c r="E140" t="n">
-        <v>87.6052</v>
+        <v>93.77509999999999</v>
       </c>
       <c r="F140" t="n">
-        <v>327.227</v>
+        <v>334.82</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>109.234</v>
+        <v>108.196</v>
       </c>
       <c r="C141" t="n">
-        <v>96.5331</v>
+        <v>93.4055</v>
       </c>
       <c r="D141" t="n">
-        <v>322.304</v>
+        <v>334.066</v>
       </c>
       <c r="E141" t="n">
-        <v>86.0397</v>
+        <v>87.979</v>
       </c>
       <c r="F141" t="n">
-        <v>325.9</v>
+        <v>334.819</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>107.884</v>
+        <v>108.039</v>
       </c>
       <c r="C142" t="n">
-        <v>94.8099</v>
+        <v>92.2621</v>
       </c>
       <c r="D142" t="n">
-        <v>321.969</v>
+        <v>333.114</v>
       </c>
       <c r="E142" t="n">
-        <v>88.1966</v>
+        <v>86.8386</v>
       </c>
       <c r="F142" t="n">
-        <v>325.749</v>
+        <v>333.998</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>106.345</v>
+        <v>106.275</v>
       </c>
       <c r="C143" t="n">
-        <v>93.83750000000001</v>
+        <v>91.3912</v>
       </c>
       <c r="D143" t="n">
-        <v>320.442</v>
+        <v>332.661</v>
       </c>
       <c r="E143" t="n">
-        <v>86.82769999999999</v>
+        <v>85.5389</v>
       </c>
       <c r="F143" t="n">
-        <v>324.241</v>
+        <v>332.291</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.1291</v>
+        <v>24.0817</v>
       </c>
       <c r="C2" t="n">
-        <v>20.2971</v>
+        <v>20.3052</v>
       </c>
       <c r="D2" t="n">
-        <v>53.6152</v>
+        <v>53.8151</v>
       </c>
       <c r="E2" t="n">
-        <v>18.187</v>
+        <v>18.2367</v>
       </c>
       <c r="F2" t="n">
-        <v>33.6247</v>
+        <v>33.6327</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.1503</v>
+        <v>23.0477</v>
       </c>
       <c r="C3" t="n">
-        <v>19.708</v>
+        <v>19.8011</v>
       </c>
       <c r="D3" t="n">
-        <v>52.9132</v>
+        <v>53.188</v>
       </c>
       <c r="E3" t="n">
-        <v>17.6511</v>
+        <v>18.0573</v>
       </c>
       <c r="F3" t="n">
-        <v>33.1703</v>
+        <v>33.1646</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8648</v>
+        <v>22.7917</v>
       </c>
       <c r="C4" t="n">
-        <v>19.3731</v>
+        <v>19.2575</v>
       </c>
       <c r="D4" t="n">
-        <v>52.3852</v>
+        <v>52.6546</v>
       </c>
       <c r="E4" t="n">
-        <v>17.2028</v>
+        <v>17.1726</v>
       </c>
       <c r="F4" t="n">
-        <v>32.7912</v>
+        <v>32.7394</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.6073</v>
+        <v>22.4807</v>
       </c>
       <c r="C5" t="n">
-        <v>18.8012</v>
+        <v>18.8694</v>
       </c>
       <c r="D5" t="n">
-        <v>51.9774</v>
+        <v>52.1702</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7247</v>
+        <v>16.7364</v>
       </c>
       <c r="F5" t="n">
-        <v>32.5109</v>
+        <v>32.519</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.1106</v>
+        <v>22.0116</v>
       </c>
       <c r="C6" t="n">
-        <v>18.4779</v>
+        <v>18.4702</v>
       </c>
       <c r="D6" t="n">
-        <v>51.5936</v>
+        <v>51.7844</v>
       </c>
       <c r="E6" t="n">
-        <v>16.4652</v>
+        <v>16.3482</v>
       </c>
       <c r="F6" t="n">
-        <v>32.342</v>
+        <v>32.3477</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.7064</v>
+        <v>21.6989</v>
       </c>
       <c r="C7" t="n">
-        <v>18.2443</v>
+        <v>18.201</v>
       </c>
       <c r="D7" t="n">
-        <v>65.4721</v>
+        <v>66.0284</v>
       </c>
       <c r="E7" t="n">
-        <v>25.6983</v>
+        <v>26.2462</v>
       </c>
       <c r="F7" t="n">
-        <v>40.7713</v>
+        <v>40.6746</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.3093</v>
+        <v>21.4622</v>
       </c>
       <c r="C8" t="n">
-        <v>26.866</v>
+        <v>26.8669</v>
       </c>
       <c r="D8" t="n">
-        <v>63.8976</v>
+        <v>64.4469</v>
       </c>
       <c r="E8" t="n">
-        <v>24.7244</v>
+        <v>24.5427</v>
       </c>
       <c r="F8" t="n">
-        <v>39.8242</v>
+        <v>39.7916</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.7547</v>
+        <v>21.3615</v>
       </c>
       <c r="C9" t="n">
-        <v>26.0051</v>
+        <v>26.0089</v>
       </c>
       <c r="D9" t="n">
-        <v>62.5168</v>
+        <v>63.0379</v>
       </c>
       <c r="E9" t="n">
-        <v>24.048</v>
+        <v>23.7337</v>
       </c>
       <c r="F9" t="n">
-        <v>38.8718</v>
+        <v>39.0724</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>29.9731</v>
+        <v>30.4063</v>
       </c>
       <c r="C10" t="n">
-        <v>25.1833</v>
+        <v>25.1699</v>
       </c>
       <c r="D10" t="n">
-        <v>61.2869</v>
+        <v>61.8264</v>
       </c>
       <c r="E10" t="n">
-        <v>23.1349</v>
+        <v>23.7755</v>
       </c>
       <c r="F10" t="n">
-        <v>38.2685</v>
+        <v>38.0659</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>28.7553</v>
+        <v>29.4594</v>
       </c>
       <c r="C11" t="n">
-        <v>24.3618</v>
+        <v>24.4138</v>
       </c>
       <c r="D11" t="n">
-        <v>60.2287</v>
+        <v>60.6827</v>
       </c>
       <c r="E11" t="n">
-        <v>22.3862</v>
+        <v>22.7107</v>
       </c>
       <c r="F11" t="n">
-        <v>37.3701</v>
+        <v>37.4017</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>28.2316</v>
+        <v>28.2029</v>
       </c>
       <c r="C12" t="n">
-        <v>23.6075</v>
+        <v>23.6331</v>
       </c>
       <c r="D12" t="n">
-        <v>59.1155</v>
+        <v>59.582</v>
       </c>
       <c r="E12" t="n">
-        <v>21.6398</v>
+        <v>21.7549</v>
       </c>
       <c r="F12" t="n">
-        <v>36.6322</v>
+        <v>36.6515</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>27.7049</v>
+        <v>27.8901</v>
       </c>
       <c r="C13" t="n">
-        <v>22.856</v>
+        <v>22.9196</v>
       </c>
       <c r="D13" t="n">
-        <v>58.1202</v>
+        <v>58.6881</v>
       </c>
       <c r="E13" t="n">
-        <v>21.004</v>
+        <v>21.0794</v>
       </c>
       <c r="F13" t="n">
-        <v>35.9255</v>
+        <v>35.9509</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>26.4454</v>
+        <v>26.9475</v>
       </c>
       <c r="C14" t="n">
-        <v>22.1672</v>
+        <v>22.2402</v>
       </c>
       <c r="D14" t="n">
-        <v>57.3847</v>
+        <v>58.0809</v>
       </c>
       <c r="E14" t="n">
-        <v>20.4128</v>
+        <v>20.2664</v>
       </c>
       <c r="F14" t="n">
-        <v>35.2178</v>
+        <v>35.3284</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>26.2821</v>
+        <v>25.9779</v>
       </c>
       <c r="C15" t="n">
-        <v>21.5144</v>
+        <v>21.5716</v>
       </c>
       <c r="D15" t="n">
-        <v>56.6946</v>
+        <v>57.3021</v>
       </c>
       <c r="E15" t="n">
-        <v>20.304</v>
+        <v>19.6476</v>
       </c>
       <c r="F15" t="n">
-        <v>34.7013</v>
+        <v>34.7092</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>25.2769</v>
+        <v>25.4537</v>
       </c>
       <c r="C16" t="n">
-        <v>20.9538</v>
+        <v>21.0022</v>
       </c>
       <c r="D16" t="n">
-        <v>56.5031</v>
+        <v>56.6796</v>
       </c>
       <c r="E16" t="n">
-        <v>19.2914</v>
+        <v>19.1401</v>
       </c>
       <c r="F16" t="n">
-        <v>34.1307</v>
+        <v>34.1553</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>24.7408</v>
+        <v>25.0395</v>
       </c>
       <c r="C17" t="n">
-        <v>20.3788</v>
+        <v>20.3926</v>
       </c>
       <c r="D17" t="n">
-        <v>55.8208</v>
+        <v>56.0761</v>
       </c>
       <c r="E17" t="n">
-        <v>18.8083</v>
+        <v>18.5932</v>
       </c>
       <c r="F17" t="n">
-        <v>33.6506</v>
+        <v>33.6658</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.0519</v>
+        <v>24.0357</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8401</v>
+        <v>19.8768</v>
       </c>
       <c r="D18" t="n">
-        <v>55.2042</v>
+        <v>55.2573</v>
       </c>
       <c r="E18" t="n">
-        <v>18.4125</v>
+        <v>18.1127</v>
       </c>
       <c r="F18" t="n">
-        <v>33.1793</v>
+        <v>33.1928</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.8277</v>
+        <v>23.4434</v>
       </c>
       <c r="C19" t="n">
-        <v>19.339</v>
+        <v>19.4152</v>
       </c>
       <c r="D19" t="n">
-        <v>54.272</v>
+        <v>54.7147</v>
       </c>
       <c r="E19" t="n">
-        <v>17.9793</v>
+        <v>18.2788</v>
       </c>
       <c r="F19" t="n">
-        <v>32.8128</v>
+        <v>32.8457</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.4937</v>
+        <v>22.9774</v>
       </c>
       <c r="C20" t="n">
-        <v>18.9527</v>
+        <v>18.9911</v>
       </c>
       <c r="D20" t="n">
-        <v>53.9015</v>
+        <v>54.284</v>
       </c>
       <c r="E20" t="n">
-        <v>17.7387</v>
+        <v>17.5259</v>
       </c>
       <c r="F20" t="n">
-        <v>32.6255</v>
+        <v>32.6432</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.8872</v>
+        <v>23.1233</v>
       </c>
       <c r="C21" t="n">
-        <v>18.6598</v>
+        <v>18.6796</v>
       </c>
       <c r="D21" t="n">
-        <v>71.4996</v>
+        <v>71.77549999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>26.9188</v>
+        <v>26.9865</v>
       </c>
       <c r="F21" t="n">
-        <v>42.9598</v>
+        <v>41.1976</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.522</v>
+        <v>22.5844</v>
       </c>
       <c r="C22" t="n">
-        <v>27.3835</v>
+        <v>27.6218</v>
       </c>
       <c r="D22" t="n">
-        <v>69.7325</v>
+        <v>70.1782</v>
       </c>
       <c r="E22" t="n">
-        <v>25.9674</v>
+        <v>25.8092</v>
       </c>
       <c r="F22" t="n">
-        <v>41.5989</v>
+        <v>40.4459</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.2303</v>
+        <v>22.5431</v>
       </c>
       <c r="C23" t="n">
-        <v>26.6174</v>
+        <v>26.527</v>
       </c>
       <c r="D23" t="n">
-        <v>68.2717</v>
+        <v>68.7419</v>
       </c>
       <c r="E23" t="n">
-        <v>25.1525</v>
+        <v>24.9969</v>
       </c>
       <c r="F23" t="n">
-        <v>40.8687</v>
+        <v>39.5387</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>30.688</v>
+        <v>30.8951</v>
       </c>
       <c r="C24" t="n">
-        <v>25.673</v>
+        <v>25.7402</v>
       </c>
       <c r="D24" t="n">
-        <v>67.0389</v>
+        <v>67.4723</v>
       </c>
       <c r="E24" t="n">
-        <v>24.3212</v>
+        <v>24.1253</v>
       </c>
       <c r="F24" t="n">
-        <v>39.9906</v>
+        <v>38.7647</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>30.0936</v>
+        <v>29.7946</v>
       </c>
       <c r="C25" t="n">
-        <v>24.9464</v>
+        <v>24.9368</v>
       </c>
       <c r="D25" t="n">
-        <v>65.91</v>
+        <v>66.1925</v>
       </c>
       <c r="E25" t="n">
-        <v>23.5545</v>
+        <v>23.3252</v>
       </c>
       <c r="F25" t="n">
-        <v>39.0769</v>
+        <v>37.8509</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>29.3367</v>
+        <v>29.146</v>
       </c>
       <c r="C26" t="n">
-        <v>24.1367</v>
+        <v>24.1807</v>
       </c>
       <c r="D26" t="n">
-        <v>64.4619</v>
+        <v>64.759</v>
       </c>
       <c r="E26" t="n">
-        <v>22.821</v>
+        <v>22.5875</v>
       </c>
       <c r="F26" t="n">
-        <v>37.4512</v>
+        <v>37.0151</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.6303</v>
+        <v>28.1374</v>
       </c>
       <c r="C27" t="n">
-        <v>23.399</v>
+        <v>23.4787</v>
       </c>
       <c r="D27" t="n">
-        <v>63.5281</v>
+        <v>63.7923</v>
       </c>
       <c r="E27" t="n">
-        <v>22.1243</v>
+        <v>21.8717</v>
       </c>
       <c r="F27" t="n">
-        <v>36.7853</v>
+        <v>36.4066</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>27.3354</v>
+        <v>27.8162</v>
       </c>
       <c r="C28" t="n">
-        <v>22.763</v>
+        <v>22.7916</v>
       </c>
       <c r="D28" t="n">
-        <v>62.5339</v>
+        <v>62.902</v>
       </c>
       <c r="E28" t="n">
-        <v>21.5035</v>
+        <v>21.4799</v>
       </c>
       <c r="F28" t="n">
-        <v>36.0304</v>
+        <v>35.7422</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>26.5783</v>
+        <v>27.0427</v>
       </c>
       <c r="C29" t="n">
-        <v>22.109</v>
+        <v>22.1418</v>
       </c>
       <c r="D29" t="n">
-        <v>61.7965</v>
+        <v>62.1815</v>
       </c>
       <c r="E29" t="n">
-        <v>20.7819</v>
+        <v>20.658</v>
       </c>
       <c r="F29" t="n">
-        <v>35.5107</v>
+        <v>35.1616</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>25.8814</v>
+        <v>26.3864</v>
       </c>
       <c r="C30" t="n">
-        <v>21.4989</v>
+        <v>21.5325</v>
       </c>
       <c r="D30" t="n">
-        <v>60.9603</v>
+        <v>61.2783</v>
       </c>
       <c r="E30" t="n">
-        <v>20.2154</v>
+        <v>20.1037</v>
       </c>
       <c r="F30" t="n">
-        <v>34.8547</v>
+        <v>34.6291</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.6979</v>
+        <v>25.7684</v>
       </c>
       <c r="C31" t="n">
-        <v>20.8764</v>
+        <v>20.9605</v>
       </c>
       <c r="D31" t="n">
-        <v>60.4445</v>
+        <v>60.737</v>
       </c>
       <c r="E31" t="n">
-        <v>19.6754</v>
+        <v>19.4893</v>
       </c>
       <c r="F31" t="n">
-        <v>35.3788</v>
+        <v>34.1083</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.36</v>
+        <v>25.8553</v>
       </c>
       <c r="C32" t="n">
-        <v>20.3204</v>
+        <v>20.425</v>
       </c>
       <c r="D32" t="n">
-        <v>59.9086</v>
+        <v>60.2687</v>
       </c>
       <c r="E32" t="n">
-        <v>19.2145</v>
+        <v>19.0234</v>
       </c>
       <c r="F32" t="n">
-        <v>34.9453</v>
+        <v>33.6794</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>25.2231</v>
+        <v>24.8321</v>
       </c>
       <c r="C33" t="n">
-        <v>19.9074</v>
+        <v>19.9291</v>
       </c>
       <c r="D33" t="n">
-        <v>59.5281</v>
+        <v>59.8334</v>
       </c>
       <c r="E33" t="n">
-        <v>18.8657</v>
+        <v>18.6591</v>
       </c>
       <c r="F33" t="n">
-        <v>33.4596</v>
+        <v>33.4008</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>24.0894</v>
+        <v>23.8711</v>
       </c>
       <c r="C34" t="n">
-        <v>19.4275</v>
+        <v>19.554</v>
       </c>
       <c r="D34" t="n">
-        <v>58.7796</v>
+        <v>59.0594</v>
       </c>
       <c r="E34" t="n">
-        <v>18.4322</v>
+        <v>18.3556</v>
       </c>
       <c r="F34" t="n">
-        <v>33.1628</v>
+        <v>33.1723</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.3483</v>
+        <v>23.7799</v>
       </c>
       <c r="C35" t="n">
-        <v>19.0943</v>
+        <v>19.153</v>
       </c>
       <c r="D35" t="n">
-        <v>76.9859</v>
+        <v>77.4252</v>
       </c>
       <c r="E35" t="n">
-        <v>27.8236</v>
+        <v>27.6383</v>
       </c>
       <c r="F35" t="n">
-        <v>42.273</v>
+        <v>42.2501</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.7777</v>
+        <v>23.2414</v>
       </c>
       <c r="C36" t="n">
-        <v>18.7889</v>
+        <v>18.9564</v>
       </c>
       <c r="D36" t="n">
-        <v>75.2478</v>
+        <v>75.652</v>
       </c>
       <c r="E36" t="n">
-        <v>26.8732</v>
+        <v>26.7451</v>
       </c>
       <c r="F36" t="n">
-        <v>41.3759</v>
+        <v>41.4088</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.3163</v>
+        <v>23.0804</v>
       </c>
       <c r="C37" t="n">
-        <v>27.0671</v>
+        <v>27.3217</v>
       </c>
       <c r="D37" t="n">
-        <v>73.6795</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>26.0077</v>
+        <v>25.8348</v>
       </c>
       <c r="F37" t="n">
-        <v>40.5812</v>
+        <v>40.596</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>31.6999</v>
+        <v>31.0794</v>
       </c>
       <c r="C38" t="n">
-        <v>26.3012</v>
+        <v>26.4253</v>
       </c>
       <c r="D38" t="n">
-        <v>72.217</v>
+        <v>72.5483</v>
       </c>
       <c r="E38" t="n">
-        <v>25.1667</v>
+        <v>25.0729</v>
       </c>
       <c r="F38" t="n">
-        <v>39.818</v>
+        <v>40.2141</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>30.8033</v>
+        <v>30.4929</v>
       </c>
       <c r="C39" t="n">
-        <v>25.6016</v>
+        <v>25.9863</v>
       </c>
       <c r="D39" t="n">
-        <v>70.84739999999999</v>
+        <v>71.1944</v>
       </c>
       <c r="E39" t="n">
-        <v>24.6453</v>
+        <v>24.4991</v>
       </c>
       <c r="F39" t="n">
-        <v>38.9676</v>
+        <v>39.1743</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>29.6</v>
+        <v>29.9824</v>
       </c>
       <c r="C40" t="n">
-        <v>24.8249</v>
+        <v>24.8894</v>
       </c>
       <c r="D40" t="n">
-        <v>69.572</v>
+        <v>69.92919999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>23.7633</v>
+        <v>23.6755</v>
       </c>
       <c r="F40" t="n">
-        <v>38.2805</v>
+        <v>38.5977</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>28.8756</v>
+        <v>28.8379</v>
       </c>
       <c r="C41" t="n">
-        <v>24.1348</v>
+        <v>24.1768</v>
       </c>
       <c r="D41" t="n">
-        <v>68.4046</v>
+        <v>68.70959999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>23.0451</v>
+        <v>22.81</v>
       </c>
       <c r="F41" t="n">
-        <v>37.6023</v>
+        <v>37.8042</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>28.45</v>
+        <v>28.0606</v>
       </c>
       <c r="C42" t="n">
-        <v>23.3666</v>
+        <v>23.4986</v>
       </c>
       <c r="D42" t="n">
-        <v>67.44540000000001</v>
+        <v>67.8172</v>
       </c>
       <c r="E42" t="n">
-        <v>22.4651</v>
+        <v>22.5737</v>
       </c>
       <c r="F42" t="n">
-        <v>37.0262</v>
+        <v>37.3102</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>27.2509</v>
+        <v>27.492</v>
       </c>
       <c r="C43" t="n">
-        <v>22.7597</v>
+        <v>22.8697</v>
       </c>
       <c r="D43" t="n">
-        <v>66.3394</v>
+        <v>66.6324</v>
       </c>
       <c r="E43" t="n">
-        <v>21.6688</v>
+        <v>21.53</v>
       </c>
       <c r="F43" t="n">
-        <v>36.4493</v>
+        <v>36.7312</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>26.8996</v>
+        <v>27.002</v>
       </c>
       <c r="C44" t="n">
-        <v>22.1327</v>
+        <v>22.3372</v>
       </c>
       <c r="D44" t="n">
-        <v>65.4665</v>
+        <v>65.79689999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>21.1517</v>
+        <v>20.9664</v>
       </c>
       <c r="F44" t="n">
-        <v>35.957</v>
+        <v>36.1936</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>25.8455</v>
+        <v>25.9061</v>
       </c>
       <c r="C45" t="n">
-        <v>21.6343</v>
+        <v>21.7096</v>
       </c>
       <c r="D45" t="n">
-        <v>64.87779999999999</v>
+        <v>65.15779999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>20.6888</v>
+        <v>20.6173</v>
       </c>
       <c r="F45" t="n">
-        <v>35.4761</v>
+        <v>35.7588</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>25.331</v>
+        <v>25.8017</v>
       </c>
       <c r="C46" t="n">
-        <v>21.1631</v>
+        <v>21.1777</v>
       </c>
       <c r="D46" t="n">
-        <v>64.2234</v>
+        <v>64.569</v>
       </c>
       <c r="E46" t="n">
-        <v>20.0754</v>
+        <v>20.0727</v>
       </c>
       <c r="F46" t="n">
-        <v>35.0654</v>
+        <v>35.3352</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>24.755</v>
+        <v>24.8432</v>
       </c>
       <c r="C47" t="n">
-        <v>20.6417</v>
+        <v>20.6996</v>
       </c>
       <c r="D47" t="n">
-        <v>63.8032</v>
+        <v>64.1002</v>
       </c>
       <c r="E47" t="n">
-        <v>19.6919</v>
+        <v>19.5144</v>
       </c>
       <c r="F47" t="n">
-        <v>34.7442</v>
+        <v>35.0097</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>24.503</v>
+        <v>24.7619</v>
       </c>
       <c r="C48" t="n">
-        <v>20.1632</v>
+        <v>20.2551</v>
       </c>
       <c r="D48" t="n">
-        <v>63.0071</v>
+        <v>63.3745</v>
       </c>
       <c r="E48" t="n">
-        <v>19.4383</v>
+        <v>19.1797</v>
       </c>
       <c r="F48" t="n">
-        <v>34.4762</v>
+        <v>34.7341</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>23.5908</v>
+        <v>24.1862</v>
       </c>
       <c r="C49" t="n">
-        <v>19.7734</v>
+        <v>19.953</v>
       </c>
       <c r="D49" t="n">
-        <v>62.6158</v>
+        <v>63.0087</v>
       </c>
       <c r="E49" t="n">
-        <v>19.1069</v>
+        <v>18.9968</v>
       </c>
       <c r="F49" t="n">
-        <v>34.3247</v>
+        <v>34.5763</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>23.5616</v>
+        <v>23.6513</v>
       </c>
       <c r="C50" t="n">
-        <v>19.4972</v>
+        <v>19.6036</v>
       </c>
       <c r="D50" t="n">
-        <v>79.8353</v>
+        <v>80.3629</v>
       </c>
       <c r="E50" t="n">
-        <v>28.0224</v>
+        <v>28.0147</v>
       </c>
       <c r="F50" t="n">
-        <v>43.493</v>
+        <v>42.9235</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>23.5722</v>
+        <v>24.1336</v>
       </c>
       <c r="C51" t="n">
-        <v>27.9136</v>
+        <v>28.1348</v>
       </c>
       <c r="D51" t="n">
-        <v>78.212</v>
+        <v>78.63160000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>27.2917</v>
+        <v>27.1807</v>
       </c>
       <c r="F51" t="n">
-        <v>42.0257</v>
+        <v>42.346</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>23.3127</v>
+        <v>23.8338</v>
       </c>
       <c r="C52" t="n">
-        <v>27.2316</v>
+        <v>27.31</v>
       </c>
       <c r="D52" t="n">
-        <v>76.5834</v>
+        <v>76.94110000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>26.3299</v>
+        <v>26.4255</v>
       </c>
       <c r="F52" t="n">
-        <v>41.4183</v>
+        <v>41.6124</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>31.7528</v>
+        <v>31.743</v>
       </c>
       <c r="C53" t="n">
-        <v>26.4399</v>
+        <v>26.7017</v>
       </c>
       <c r="D53" t="n">
-        <v>75.0197</v>
+        <v>75.38979999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>25.5839</v>
+        <v>25.7086</v>
       </c>
       <c r="F53" t="n">
-        <v>40.6493</v>
+        <v>40.9324</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>31.2706</v>
+        <v>31.7519</v>
       </c>
       <c r="C54" t="n">
-        <v>25.6362</v>
+        <v>25.8386</v>
       </c>
       <c r="D54" t="n">
-        <v>73.6343</v>
+        <v>74.0142</v>
       </c>
       <c r="E54" t="n">
-        <v>24.9578</v>
+        <v>24.7902</v>
       </c>
       <c r="F54" t="n">
-        <v>39.9899</v>
+        <v>40.319</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>30.0525</v>
+        <v>30.2471</v>
       </c>
       <c r="C55" t="n">
-        <v>24.9788</v>
+        <v>25.2229</v>
       </c>
       <c r="D55" t="n">
-        <v>72.4528</v>
+        <v>72.78100000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>24.2029</v>
+        <v>24.1149</v>
       </c>
       <c r="F55" t="n">
-        <v>39.3562</v>
+        <v>39.6991</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>28.9137</v>
+        <v>29.4972</v>
       </c>
       <c r="C56" t="n">
-        <v>24.3785</v>
+        <v>24.5267</v>
       </c>
       <c r="D56" t="n">
-        <v>71.3368</v>
+        <v>71.67189999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>23.7419</v>
+        <v>23.3956</v>
       </c>
       <c r="F56" t="n">
-        <v>38.9406</v>
+        <v>39.086</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>28.7167</v>
+        <v>28.833</v>
       </c>
       <c r="C57" t="n">
-        <v>23.6768</v>
+        <v>23.961</v>
       </c>
       <c r="D57" t="n">
-        <v>70.1309</v>
+        <v>70.44670000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>22.866</v>
+        <v>22.9112</v>
       </c>
       <c r="F57" t="n">
-        <v>38.393</v>
+        <v>38.6376</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>27.8405</v>
+        <v>28.2352</v>
       </c>
       <c r="C58" t="n">
-        <v>23.1313</v>
+        <v>23.3068</v>
       </c>
       <c r="D58" t="n">
-        <v>69.2886</v>
+        <v>69.6345</v>
       </c>
       <c r="E58" t="n">
-        <v>22.4793</v>
+        <v>22.1645</v>
       </c>
       <c r="F58" t="n">
-        <v>37.9412</v>
+        <v>38.1315</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.5232</v>
+        <v>27.6198</v>
       </c>
       <c r="C59" t="n">
-        <v>22.6043</v>
+        <v>22.7279</v>
       </c>
       <c r="D59" t="n">
-        <v>68.3965</v>
+        <v>68.77679999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>21.8944</v>
+        <v>21.8429</v>
       </c>
       <c r="F59" t="n">
-        <v>37.5722</v>
+        <v>37.7302</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>27.0207</v>
+        <v>26.9309</v>
       </c>
       <c r="C60" t="n">
-        <v>22.1364</v>
+        <v>22.3569</v>
       </c>
       <c r="D60" t="n">
-        <v>67.78870000000001</v>
+        <v>68.10809999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>21.4085</v>
+        <v>21.3319</v>
       </c>
       <c r="F60" t="n">
-        <v>37.1671</v>
+        <v>37.244</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.1725</v>
+        <v>26.7836</v>
       </c>
       <c r="C61" t="n">
-        <v>21.6786</v>
+        <v>21.8893</v>
       </c>
       <c r="D61" t="n">
-        <v>67.0557</v>
+        <v>67.34610000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>20.8417</v>
+        <v>20.577</v>
       </c>
       <c r="F61" t="n">
-        <v>36.8581</v>
+        <v>37.0484</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>26.0612</v>
+        <v>25.8127</v>
       </c>
       <c r="C62" t="n">
-        <v>21.2058</v>
+        <v>21.4505</v>
       </c>
       <c r="D62" t="n">
-        <v>66.36369999999999</v>
+        <v>66.60809999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>20.6569</v>
+        <v>20.5489</v>
       </c>
       <c r="F62" t="n">
-        <v>36.6785</v>
+        <v>36.8207</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>25.5542</v>
+        <v>25.9398</v>
       </c>
       <c r="C63" t="n">
-        <v>20.8532</v>
+        <v>21.0027</v>
       </c>
       <c r="D63" t="n">
-        <v>65.9509</v>
+        <v>66.2843</v>
       </c>
       <c r="E63" t="n">
-        <v>20.2674</v>
+        <v>19.9973</v>
       </c>
       <c r="F63" t="n">
-        <v>36.3404</v>
+        <v>36.5367</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.1044</v>
+        <v>25.2256</v>
       </c>
       <c r="C64" t="n">
-        <v>20.5377</v>
+        <v>20.7889</v>
       </c>
       <c r="D64" t="n">
-        <v>86.7308</v>
+        <v>87.8121</v>
       </c>
       <c r="E64" t="n">
-        <v>33.1416</v>
+        <v>32.7254</v>
       </c>
       <c r="F64" t="n">
-        <v>46.4254</v>
+        <v>46.4582</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.1815</v>
+        <v>25.8488</v>
       </c>
       <c r="C65" t="n">
-        <v>29.94</v>
+        <v>29.6768</v>
       </c>
       <c r="D65" t="n">
-        <v>84.57340000000001</v>
+        <v>85.38330000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>31.3769</v>
+        <v>31.8037</v>
       </c>
       <c r="F65" t="n">
-        <v>45.8165</v>
+        <v>45.9279</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>24.7235</v>
+        <v>24.9427</v>
       </c>
       <c r="C66" t="n">
-        <v>28.974</v>
+        <v>29.0745</v>
       </c>
       <c r="D66" t="n">
-        <v>82.6889</v>
+        <v>83.6422</v>
       </c>
       <c r="E66" t="n">
-        <v>31.2058</v>
+        <v>30.5571</v>
       </c>
       <c r="F66" t="n">
-        <v>45.1956</v>
+        <v>45.3677</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>41.6241</v>
+        <v>39.8556</v>
       </c>
       <c r="C67" t="n">
-        <v>28.4196</v>
+        <v>28.389</v>
       </c>
       <c r="D67" t="n">
-        <v>81.06319999999999</v>
+        <v>81.9036</v>
       </c>
       <c r="E67" t="n">
-        <v>30.3834</v>
+        <v>29.4749</v>
       </c>
       <c r="F67" t="n">
-        <v>44.6318</v>
+        <v>44.7906</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>39.5999</v>
+        <v>39.4342</v>
       </c>
       <c r="C68" t="n">
-        <v>27.849</v>
+        <v>27.8149</v>
       </c>
       <c r="D68" t="n">
-        <v>79.4297</v>
+        <v>80.3385</v>
       </c>
       <c r="E68" t="n">
-        <v>28.9286</v>
+        <v>28.7444</v>
       </c>
       <c r="F68" t="n">
-        <v>44.0249</v>
+        <v>44.2797</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>38.4394</v>
+        <v>39.0533</v>
       </c>
       <c r="C69" t="n">
-        <v>27.2852</v>
+        <v>27.2526</v>
       </c>
       <c r="D69" t="n">
-        <v>78.07769999999999</v>
+        <v>79.0527</v>
       </c>
       <c r="E69" t="n">
-        <v>28.8029</v>
+        <v>28.5308</v>
       </c>
       <c r="F69" t="n">
-        <v>43.4828</v>
+        <v>43.6386</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>39.2717</v>
+        <v>38.5596</v>
       </c>
       <c r="C70" t="n">
-        <v>26.7818</v>
+        <v>26.7636</v>
       </c>
       <c r="D70" t="n">
-        <v>77.01309999999999</v>
+        <v>78.0545</v>
       </c>
       <c r="E70" t="n">
-        <v>27.6247</v>
+        <v>27.8891</v>
       </c>
       <c r="F70" t="n">
-        <v>42.9344</v>
+        <v>43.1178</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>37.8411</v>
+        <v>37.6501</v>
       </c>
       <c r="C71" t="n">
-        <v>26.2835</v>
+        <v>26.2727</v>
       </c>
       <c r="D71" t="n">
-        <v>76.184</v>
+        <v>77.3796</v>
       </c>
       <c r="E71" t="n">
-        <v>27.3793</v>
+        <v>26.4895</v>
       </c>
       <c r="F71" t="n">
-        <v>42.4489</v>
+        <v>42.7557</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.9076</v>
+        <v>36.2692</v>
       </c>
       <c r="C72" t="n">
-        <v>25.8488</v>
+        <v>25.8157</v>
       </c>
       <c r="D72" t="n">
-        <v>75.524</v>
+        <v>76.6116</v>
       </c>
       <c r="E72" t="n">
-        <v>26.8277</v>
+        <v>26.5074</v>
       </c>
       <c r="F72" t="n">
-        <v>42.0286</v>
+        <v>42.3185</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>37.7828</v>
+        <v>35.8616</v>
       </c>
       <c r="C73" t="n">
-        <v>25.4294</v>
+        <v>25.3273</v>
       </c>
       <c r="D73" t="n">
-        <v>75.1965</v>
+        <v>76.12269999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>25.5601</v>
+        <v>25.9764</v>
       </c>
       <c r="F73" t="n">
-        <v>41.6541</v>
+        <v>41.8678</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>35.3237</v>
+        <v>36.8522</v>
       </c>
       <c r="C74" t="n">
-        <v>24.9381</v>
+        <v>24.9603</v>
       </c>
       <c r="D74" t="n">
-        <v>74.5735</v>
+        <v>75.7741</v>
       </c>
       <c r="E74" t="n">
-        <v>25.2151</v>
+        <v>24.9315</v>
       </c>
       <c r="F74" t="n">
-        <v>41.2348</v>
+        <v>41.5259</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>35.6201</v>
+        <v>35.6227</v>
       </c>
       <c r="C75" t="n">
-        <v>24.5977</v>
+        <v>24.4754</v>
       </c>
       <c r="D75" t="n">
-        <v>73.8464</v>
+        <v>75.00149999999999</v>
       </c>
       <c r="E75" t="n">
-        <v>25.1117</v>
+        <v>24.4764</v>
       </c>
       <c r="F75" t="n">
-        <v>41.035</v>
+        <v>41.2266</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>34.1523</v>
+        <v>34.4219</v>
       </c>
       <c r="C76" t="n">
-        <v>24.2772</v>
+        <v>24.1243</v>
       </c>
       <c r="D76" t="n">
-        <v>73.94459999999999</v>
+        <v>75.1794</v>
       </c>
       <c r="E76" t="n">
-        <v>24.2509</v>
+        <v>24.7147</v>
       </c>
       <c r="F76" t="n">
-        <v>40.7895</v>
+        <v>41.0585</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>33.4088</v>
+        <v>34.3416</v>
       </c>
       <c r="C77" t="n">
-        <v>23.832</v>
+        <v>23.8883</v>
       </c>
       <c r="D77" t="n">
-        <v>74.2838</v>
+        <v>75.3605</v>
       </c>
       <c r="E77" t="n">
-        <v>23.8049</v>
+        <v>23.7291</v>
       </c>
       <c r="F77" t="n">
-        <v>40.7117</v>
+        <v>41.0463</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>33.6802</v>
+        <v>33.5502</v>
       </c>
       <c r="C78" t="n">
-        <v>23.5071</v>
+        <v>23.4537</v>
       </c>
       <c r="D78" t="n">
-        <v>121.877</v>
+        <v>123.174</v>
       </c>
       <c r="E78" t="n">
-        <v>41.018</v>
+        <v>41.3328</v>
       </c>
       <c r="F78" t="n">
-        <v>64.2058</v>
+        <v>65.1384</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>35.5842</v>
+        <v>35.846</v>
       </c>
       <c r="C79" t="n">
-        <v>33.0569</v>
+        <v>33.2626</v>
       </c>
       <c r="D79" t="n">
-        <v>117.708</v>
+        <v>120.64</v>
       </c>
       <c r="E79" t="n">
-        <v>40.1781</v>
+        <v>40.3023</v>
       </c>
       <c r="F79" t="n">
-        <v>64.3711</v>
+        <v>65.1816</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>33.6556</v>
+        <v>36.2829</v>
       </c>
       <c r="C80" t="n">
-        <v>32.7818</v>
+        <v>33.0737</v>
       </c>
       <c r="D80" t="n">
-        <v>116.006</v>
+        <v>119.067</v>
       </c>
       <c r="E80" t="n">
-        <v>39.3234</v>
+        <v>39.1926</v>
       </c>
       <c r="F80" t="n">
-        <v>64.4593</v>
+        <v>65.256</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>46.1682</v>
+        <v>46.2864</v>
       </c>
       <c r="C81" t="n">
-        <v>32.6728</v>
+        <v>32.7514</v>
       </c>
       <c r="D81" t="n">
-        <v>114.422</v>
+        <v>117.631</v>
       </c>
       <c r="E81" t="n">
-        <v>38.5889</v>
+        <v>38.9274</v>
       </c>
       <c r="F81" t="n">
-        <v>63.6284</v>
+        <v>64.8954</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>51.036</v>
+        <v>45.3029</v>
       </c>
       <c r="C82" t="n">
-        <v>32.0714</v>
+        <v>31.9795</v>
       </c>
       <c r="D82" t="n">
-        <v>113.293</v>
+        <v>116.081</v>
       </c>
       <c r="E82" t="n">
-        <v>37.6357</v>
+        <v>37.5952</v>
       </c>
       <c r="F82" t="n">
-        <v>63.1701</v>
+        <v>64.5586</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>49.6112</v>
+        <v>49.2652</v>
       </c>
       <c r="C83" t="n">
-        <v>31.7687</v>
+        <v>31.9759</v>
       </c>
       <c r="D83" t="n">
-        <v>112.447</v>
+        <v>115.344</v>
       </c>
       <c r="E83" t="n">
-        <v>36.6981</v>
+        <v>37.1102</v>
       </c>
       <c r="F83" t="n">
-        <v>62.3808</v>
+        <v>63.3162</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>47.7007</v>
+        <v>43.8249</v>
       </c>
       <c r="C84" t="n">
-        <v>31.4542</v>
+        <v>31.5302</v>
       </c>
       <c r="D84" t="n">
-        <v>112.044</v>
+        <v>114.993</v>
       </c>
       <c r="E84" t="n">
-        <v>35.8053</v>
+        <v>35.8723</v>
       </c>
       <c r="F84" t="n">
-        <v>61.3812</v>
+        <v>62.5463</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>46.5434</v>
+        <v>42.9986</v>
       </c>
       <c r="C85" t="n">
-        <v>31.1074</v>
+        <v>31.1796</v>
       </c>
       <c r="D85" t="n">
-        <v>111.908</v>
+        <v>114.694</v>
       </c>
       <c r="E85" t="n">
-        <v>34.8477</v>
+        <v>35.0601</v>
       </c>
       <c r="F85" t="n">
-        <v>60.6301</v>
+        <v>62.0859</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>47.3537</v>
+        <v>47.3209</v>
       </c>
       <c r="C86" t="n">
-        <v>30.7884</v>
+        <v>31.0432</v>
       </c>
       <c r="D86" t="n">
-        <v>112.164</v>
+        <v>115.57</v>
       </c>
       <c r="E86" t="n">
-        <v>34.2248</v>
+        <v>34.3861</v>
       </c>
       <c r="F86" t="n">
-        <v>59.8352</v>
+        <v>61.0782</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>46.8794</v>
+        <v>43.0289</v>
       </c>
       <c r="C87" t="n">
-        <v>30.4069</v>
+        <v>30.3042</v>
       </c>
       <c r="D87" t="n">
-        <v>112.381</v>
+        <v>115.912</v>
       </c>
       <c r="E87" t="n">
-        <v>33.1988</v>
+        <v>33.2758</v>
       </c>
       <c r="F87" t="n">
-        <v>58.8754</v>
+        <v>60.4425</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>47.1406</v>
+        <v>42.8388</v>
       </c>
       <c r="C88" t="n">
-        <v>30.0834</v>
+        <v>30.2959</v>
       </c>
       <c r="D88" t="n">
-        <v>113.14</v>
+        <v>116.607</v>
       </c>
       <c r="E88" t="n">
-        <v>32.5302</v>
+        <v>32.7966</v>
       </c>
       <c r="F88" t="n">
-        <v>58.1178</v>
+        <v>59.6647</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>44.5286</v>
+        <v>45.8324</v>
       </c>
       <c r="C89" t="n">
-        <v>29.7943</v>
+        <v>29.7583</v>
       </c>
       <c r="D89" t="n">
-        <v>113.453</v>
+        <v>116.825</v>
       </c>
       <c r="E89" t="n">
-        <v>31.8029</v>
+        <v>31.7595</v>
       </c>
       <c r="F89" t="n">
-        <v>58.3629</v>
+        <v>58.9351</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>39.8837</v>
+        <v>44.0784</v>
       </c>
       <c r="C90" t="n">
-        <v>29.5443</v>
+        <v>29.6094</v>
       </c>
       <c r="D90" t="n">
-        <v>115.915</v>
+        <v>117.975</v>
       </c>
       <c r="E90" t="n">
-        <v>31.2913</v>
+        <v>31.538</v>
       </c>
       <c r="F90" t="n">
-        <v>57.7959</v>
+        <v>58.568</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>42.3535</v>
+        <v>43.3384</v>
       </c>
       <c r="C91" t="n">
-        <v>29.3546</v>
+        <v>29.2359</v>
       </c>
       <c r="D91" t="n">
-        <v>117.826</v>
+        <v>119.551</v>
       </c>
       <c r="E91" t="n">
-        <v>30.6008</v>
+        <v>30.6678</v>
       </c>
       <c r="F91" t="n">
-        <v>57.1691</v>
+        <v>57.9741</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>43.3111</v>
+        <v>42.4978</v>
       </c>
       <c r="C92" t="n">
-        <v>28.8821</v>
+        <v>29.1897</v>
       </c>
       <c r="D92" t="n">
-        <v>175.865</v>
+        <v>179.215</v>
       </c>
       <c r="E92" t="n">
-        <v>64.8764</v>
+        <v>64.486</v>
       </c>
       <c r="F92" t="n">
-        <v>88.8297</v>
+        <v>88.6481</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>44.46</v>
+        <v>44.6331</v>
       </c>
       <c r="C93" t="n">
-        <v>28.695</v>
+        <v>29.0307</v>
       </c>
       <c r="D93" t="n">
-        <v>174.88</v>
+        <v>178.811</v>
       </c>
       <c r="E93" t="n">
-        <v>63.7594</v>
+        <v>62.9828</v>
       </c>
       <c r="F93" t="n">
-        <v>88.8408</v>
+        <v>89.9136</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>43.4507</v>
+        <v>44.7761</v>
       </c>
       <c r="C94" t="n">
-        <v>61.8105</v>
+        <v>61.6776</v>
       </c>
       <c r="D94" t="n">
-        <v>173.853</v>
+        <v>177.325</v>
       </c>
       <c r="E94" t="n">
-        <v>61.7724</v>
+        <v>61.7352</v>
       </c>
       <c r="F94" t="n">
-        <v>87.6198</v>
+        <v>88.6781</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>77.80880000000001</v>
+        <v>74.93810000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>60.673</v>
+        <v>60.3986</v>
       </c>
       <c r="D95" t="n">
-        <v>172.791</v>
+        <v>176.167</v>
       </c>
       <c r="E95" t="n">
-        <v>59.9461</v>
+        <v>59.5128</v>
       </c>
       <c r="F95" t="n">
-        <v>88.5616</v>
+        <v>87.5607</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>76.00490000000001</v>
+        <v>75.0568</v>
       </c>
       <c r="C96" t="n">
-        <v>59.4941</v>
+        <v>59.0837</v>
       </c>
       <c r="D96" t="n">
-        <v>175.73</v>
+        <v>174.514</v>
       </c>
       <c r="E96" t="n">
-        <v>59.0721</v>
+        <v>57.7606</v>
       </c>
       <c r="F96" t="n">
-        <v>89.4051</v>
+        <v>87.04170000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>75.19199999999999</v>
+        <v>73.6747</v>
       </c>
       <c r="C97" t="n">
-        <v>58.1685</v>
+        <v>57.4064</v>
       </c>
       <c r="D97" t="n">
-        <v>175.466</v>
+        <v>174.406</v>
       </c>
       <c r="E97" t="n">
-        <v>57.2589</v>
+        <v>55.789</v>
       </c>
       <c r="F97" t="n">
-        <v>86.1447</v>
+        <v>85.7397</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>74.22280000000001</v>
+        <v>71.6833</v>
       </c>
       <c r="C98" t="n">
-        <v>56.6715</v>
+        <v>56.113</v>
       </c>
       <c r="D98" t="n">
-        <v>175.621</v>
+        <v>173.889</v>
       </c>
       <c r="E98" t="n">
-        <v>55.6438</v>
+        <v>53.9228</v>
       </c>
       <c r="F98" t="n">
-        <v>84.4007</v>
+        <v>84.7685</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>71.4372</v>
+        <v>70.0917</v>
       </c>
       <c r="C99" t="n">
-        <v>55.417</v>
+        <v>54.5825</v>
       </c>
       <c r="D99" t="n">
-        <v>175.721</v>
+        <v>174.342</v>
       </c>
       <c r="E99" t="n">
-        <v>53.9201</v>
+        <v>52.7323</v>
       </c>
       <c r="F99" t="n">
-        <v>84.8574</v>
+        <v>84.36490000000001</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>67.5475</v>
+        <v>67.5146</v>
       </c>
       <c r="C100" t="n">
-        <v>54.1132</v>
+        <v>53.6986</v>
       </c>
       <c r="D100" t="n">
-        <v>176.536</v>
+        <v>174.981</v>
       </c>
       <c r="E100" t="n">
-        <v>52.4643</v>
+        <v>51.0791</v>
       </c>
       <c r="F100" t="n">
-        <v>83.2972</v>
+        <v>83.67310000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>68.9555</v>
+        <v>67.4311</v>
       </c>
       <c r="C101" t="n">
-        <v>53.0769</v>
+        <v>52.4312</v>
       </c>
       <c r="D101" t="n">
-        <v>176.896</v>
+        <v>175.345</v>
       </c>
       <c r="E101" t="n">
-        <v>51.0588</v>
+        <v>49.6049</v>
       </c>
       <c r="F101" t="n">
-        <v>87.6632</v>
+        <v>82.4705</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>67.1918</v>
+        <v>66.2873</v>
       </c>
       <c r="C102" t="n">
-        <v>51.9517</v>
+        <v>51.3471</v>
       </c>
       <c r="D102" t="n">
-        <v>177.681</v>
+        <v>176.252</v>
       </c>
       <c r="E102" t="n">
-        <v>49.7127</v>
+        <v>48.3935</v>
       </c>
       <c r="F102" t="n">
-        <v>83.1358</v>
+        <v>82.67100000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>66.2867</v>
+        <v>65.31319999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>50.9142</v>
+        <v>50.3354</v>
       </c>
       <c r="D103" t="n">
-        <v>179.144</v>
+        <v>178.056</v>
       </c>
       <c r="E103" t="n">
-        <v>48.3147</v>
+        <v>47.1904</v>
       </c>
       <c r="F103" t="n">
-        <v>83.1773</v>
+        <v>82.02160000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>65.37130000000001</v>
+        <v>64.48820000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>49.8595</v>
+        <v>49.2562</v>
       </c>
       <c r="D104" t="n">
-        <v>180.742</v>
+        <v>179.393</v>
       </c>
       <c r="E104" t="n">
-        <v>47.2282</v>
+        <v>45.7529</v>
       </c>
       <c r="F104" t="n">
-        <v>81.40560000000001</v>
+        <v>79.5548</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>64.53959999999999</v>
+        <v>63.866</v>
       </c>
       <c r="C105" t="n">
-        <v>48.9699</v>
+        <v>48.6026</v>
       </c>
       <c r="D105" t="n">
-        <v>182.543</v>
+        <v>180.682</v>
       </c>
       <c r="E105" t="n">
-        <v>46.2069</v>
+        <v>44.7798</v>
       </c>
       <c r="F105" t="n">
-        <v>91.1134</v>
+        <v>89.9538</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>65.6413</v>
+        <v>64.6726</v>
       </c>
       <c r="C106" t="n">
-        <v>48.0484</v>
+        <v>47.5915</v>
       </c>
       <c r="D106" t="n">
-        <v>184.263</v>
+        <v>182.374</v>
       </c>
       <c r="E106" t="n">
-        <v>45.2097</v>
+        <v>44.0417</v>
       </c>
       <c r="F106" t="n">
-        <v>90.8193</v>
+        <v>90.5612</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>61.407</v>
+        <v>60.6711</v>
       </c>
       <c r="C107" t="n">
-        <v>47.3331</v>
+        <v>46.7065</v>
       </c>
       <c r="D107" t="n">
-        <v>248.142</v>
+        <v>245.146</v>
       </c>
       <c r="E107" t="n">
-        <v>79.69</v>
+        <v>79.15179999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>245.96</v>
+        <v>242.223</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>60.4479</v>
+        <v>60.1491</v>
       </c>
       <c r="C108" t="n">
-        <v>81.67610000000001</v>
+        <v>81.1808</v>
       </c>
       <c r="D108" t="n">
-        <v>245.683</v>
+        <v>242.745</v>
       </c>
       <c r="E108" t="n">
-        <v>77.72620000000001</v>
+        <v>76.5577</v>
       </c>
       <c r="F108" t="n">
-        <v>246.128</v>
+        <v>244.622</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>56.1741</v>
+        <v>55.5031</v>
       </c>
       <c r="C109" t="n">
-        <v>66.5069</v>
+        <v>65.2313</v>
       </c>
       <c r="D109" t="n">
-        <v>243.289</v>
+        <v>240.923</v>
       </c>
       <c r="E109" t="n">
-        <v>75.4049</v>
+        <v>74.2135</v>
       </c>
       <c r="F109" t="n">
-        <v>246.463</v>
+        <v>244.119</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>92.7264</v>
+        <v>91.6241</v>
       </c>
       <c r="C110" t="n">
-        <v>78.48699999999999</v>
+        <v>77.8989</v>
       </c>
       <c r="D110" t="n">
-        <v>241.749</v>
+        <v>238.317</v>
       </c>
       <c r="E110" t="n">
-        <v>63.9247</v>
+        <v>62.1977</v>
       </c>
       <c r="F110" t="n">
-        <v>246.444</v>
+        <v>244.635</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>91.2683</v>
+        <v>90.6272</v>
       </c>
       <c r="C111" t="n">
-        <v>76.3947</v>
+        <v>76.1219</v>
       </c>
       <c r="D111" t="n">
-        <v>240.533</v>
+        <v>236.9</v>
       </c>
       <c r="E111" t="n">
-        <v>71.4517</v>
+        <v>69.895</v>
       </c>
       <c r="F111" t="n">
-        <v>247.209</v>
+        <v>246.369</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>87.61360000000001</v>
+        <v>87.0887</v>
       </c>
       <c r="C112" t="n">
-        <v>74.4564</v>
+        <v>74.2666</v>
       </c>
       <c r="D112" t="n">
-        <v>241.021</v>
+        <v>238.712</v>
       </c>
       <c r="E112" t="n">
-        <v>60.3955</v>
+        <v>59.2474</v>
       </c>
       <c r="F112" t="n">
-        <v>247.37</v>
+        <v>246.43</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>85.76260000000001</v>
+        <v>85.4692</v>
       </c>
       <c r="C113" t="n">
-        <v>72.5057</v>
+        <v>72.0791</v>
       </c>
       <c r="D113" t="n">
-        <v>238.154</v>
+        <v>236.635</v>
       </c>
       <c r="E113" t="n">
-        <v>58.8138</v>
+        <v>57.4708</v>
       </c>
       <c r="F113" t="n">
-        <v>247.272</v>
+        <v>245.625</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.4898</v>
+        <v>84.21599999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>70.7692</v>
+        <v>70.2906</v>
       </c>
       <c r="D114" t="n">
-        <v>249.236</v>
+        <v>245.523</v>
       </c>
       <c r="E114" t="n">
-        <v>65.49890000000001</v>
+        <v>64.645</v>
       </c>
       <c r="F114" t="n">
-        <v>248.277</v>
+        <v>248.749</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>83.2089</v>
+        <v>82.4148</v>
       </c>
       <c r="C115" t="n">
-        <v>69.0106</v>
+        <v>68.7804</v>
       </c>
       <c r="D115" t="n">
-        <v>251.808</v>
+        <v>248.144</v>
       </c>
       <c r="E115" t="n">
-        <v>63.9062</v>
+        <v>62.837</v>
       </c>
       <c r="F115" t="n">
-        <v>248.335</v>
+        <v>248.331</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>82.3319</v>
+        <v>81.6403</v>
       </c>
       <c r="C116" t="n">
-        <v>67.51260000000001</v>
+        <v>67.3716</v>
       </c>
       <c r="D116" t="n">
-        <v>244.519</v>
+        <v>242.121</v>
       </c>
       <c r="E116" t="n">
-        <v>62.3292</v>
+        <v>61.6019</v>
       </c>
       <c r="F116" t="n">
-        <v>248.419</v>
+        <v>245.854</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>80.38290000000001</v>
+        <v>81.0757</v>
       </c>
       <c r="C117" t="n">
-        <v>65.95399999999999</v>
+        <v>65.4461</v>
       </c>
       <c r="D117" t="n">
-        <v>247.785</v>
+        <v>244.306</v>
       </c>
       <c r="E117" t="n">
-        <v>60.5484</v>
+        <v>60.1397</v>
       </c>
       <c r="F117" t="n">
-        <v>248.97</v>
+        <v>247.861</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>77.98090000000001</v>
+        <v>77.6238</v>
       </c>
       <c r="C118" t="n">
-        <v>64.4727</v>
+        <v>64.2252</v>
       </c>
       <c r="D118" t="n">
-        <v>237.78</v>
+        <v>234.92</v>
       </c>
       <c r="E118" t="n">
-        <v>52.6112</v>
+        <v>51.7475</v>
       </c>
       <c r="F118" t="n">
-        <v>250.648</v>
+        <v>246.563</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>73.62569999999999</v>
+        <v>71.91679999999999</v>
       </c>
       <c r="C119" t="n">
-        <v>54.7433</v>
+        <v>53.3194</v>
       </c>
       <c r="D119" t="n">
-        <v>238.712</v>
+        <v>231.842</v>
       </c>
       <c r="E119" t="n">
-        <v>51.6767</v>
+        <v>49.8381</v>
       </c>
       <c r="F119" t="n">
-        <v>102.857</v>
+        <v>100.14</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>76.1893</v>
+        <v>74.67270000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>61.9748</v>
+        <v>60.5299</v>
       </c>
       <c r="D120" t="n">
-        <v>239.876</v>
+        <v>233.265</v>
       </c>
       <c r="E120" t="n">
-        <v>50.7829</v>
+        <v>49.0234</v>
       </c>
       <c r="F120" t="n">
-        <v>179.574</v>
+        <v>173.989</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>70.3498</v>
+        <v>68.1397</v>
       </c>
       <c r="C121" t="n">
-        <v>53.1816</v>
+        <v>51.402</v>
       </c>
       <c r="D121" t="n">
-        <v>314.927</v>
+        <v>305.208</v>
       </c>
       <c r="E121" t="n">
-        <v>85.8364</v>
+        <v>83.63809999999999</v>
       </c>
       <c r="F121" t="n">
-        <v>299.235</v>
+        <v>290.903</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>72.5354</v>
+        <v>70.8888</v>
       </c>
       <c r="C122" t="n">
-        <v>95.09950000000001</v>
+        <v>93.6049</v>
       </c>
       <c r="D122" t="n">
-        <v>309.9</v>
+        <v>300.832</v>
       </c>
       <c r="E122" t="n">
-        <v>83.98269999999999</v>
+        <v>81.77760000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>298.997</v>
+        <v>290.739</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>68.3327</v>
+        <v>66.8057</v>
       </c>
       <c r="C123" t="n">
-        <v>86.24339999999999</v>
+        <v>84.51819999999999</v>
       </c>
       <c r="D123" t="n">
-        <v>305.866</v>
+        <v>296.885</v>
       </c>
       <c r="E123" t="n">
-        <v>82.1131</v>
+        <v>80.0277</v>
       </c>
       <c r="F123" t="n">
-        <v>297.848</v>
+        <v>289.795</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>98.0968</v>
+        <v>96.2882</v>
       </c>
       <c r="C124" t="n">
-        <v>85.3939</v>
+        <v>83.3995</v>
       </c>
       <c r="D124" t="n">
-        <v>302.351</v>
+        <v>293.336</v>
       </c>
       <c r="E124" t="n">
-        <v>80.43810000000001</v>
+        <v>78.2043</v>
       </c>
       <c r="F124" t="n">
-        <v>295.856</v>
+        <v>288.047</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>99.1073</v>
+        <v>97.17529999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>83.71259999999999</v>
+        <v>81.804</v>
       </c>
       <c r="D125" t="n">
-        <v>299.214</v>
+        <v>290.154</v>
       </c>
       <c r="E125" t="n">
-        <v>78.9152</v>
+        <v>76.68980000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>296.722</v>
+        <v>289.026</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>97.31480000000001</v>
+        <v>95.2467</v>
       </c>
       <c r="C126" t="n">
-        <v>82.262</v>
+        <v>80.3356</v>
       </c>
       <c r="D126" t="n">
-        <v>296.457</v>
+        <v>287.718</v>
       </c>
       <c r="E126" t="n">
-        <v>77.2432</v>
+        <v>74.9376</v>
       </c>
       <c r="F126" t="n">
-        <v>295.734</v>
+        <v>286.993</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>95.639</v>
+        <v>93.8167</v>
       </c>
       <c r="C127" t="n">
-        <v>80.90179999999999</v>
+        <v>78.6682</v>
       </c>
       <c r="D127" t="n">
-        <v>294.17</v>
+        <v>285.255</v>
       </c>
       <c r="E127" t="n">
-        <v>75.7838</v>
+        <v>73.6129</v>
       </c>
       <c r="F127" t="n">
-        <v>295.564</v>
+        <v>286.717</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>93.9631</v>
+        <v>91.9539</v>
       </c>
       <c r="C128" t="n">
-        <v>79.5943</v>
+        <v>77.4423</v>
       </c>
       <c r="D128" t="n">
-        <v>292.245</v>
+        <v>283.434</v>
       </c>
       <c r="E128" t="n">
-        <v>74.2732</v>
+        <v>71.98569999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>295.462</v>
+        <v>287.303</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>96.19929999999999</v>
+        <v>94.36409999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>83.48</v>
+        <v>81.2351</v>
       </c>
       <c r="D129" t="n">
-        <v>290.336</v>
+        <v>281.759</v>
       </c>
       <c r="E129" t="n">
-        <v>73.1914</v>
+        <v>70.7795</v>
       </c>
       <c r="F129" t="n">
-        <v>295.105</v>
+        <v>286.238</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>94.4183</v>
+        <v>92.5425</v>
       </c>
       <c r="C130" t="n">
-        <v>82.0814</v>
+        <v>79.8152</v>
       </c>
       <c r="D130" t="n">
-        <v>289.098</v>
+        <v>280.606</v>
       </c>
       <c r="E130" t="n">
-        <v>71.8736</v>
+        <v>69.6216</v>
       </c>
       <c r="F130" t="n">
-        <v>294.388</v>
+        <v>285.273</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>90.8173</v>
+        <v>88.79170000000001</v>
       </c>
       <c r="C131" t="n">
-        <v>75.95189999999999</v>
+        <v>73.4997</v>
       </c>
       <c r="D131" t="n">
-        <v>288.186</v>
+        <v>279.616</v>
       </c>
       <c r="E131" t="n">
-        <v>70.785</v>
+        <v>68.48990000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>294.44</v>
+        <v>285.406</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>91.4941</v>
+        <v>89.5498</v>
       </c>
       <c r="C132" t="n">
-        <v>79.4149</v>
+        <v>77.02979999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>287.633</v>
+        <v>279.021</v>
       </c>
       <c r="E132" t="n">
-        <v>69.6683</v>
+        <v>67.2518</v>
       </c>
       <c r="F132" t="n">
-        <v>294.155</v>
+        <v>285.251</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>88.4609</v>
+        <v>85.9186</v>
       </c>
       <c r="C133" t="n">
-        <v>74.1426</v>
+        <v>71.4222</v>
       </c>
       <c r="D133" t="n">
-        <v>287.645</v>
+        <v>278.859</v>
       </c>
       <c r="E133" t="n">
-        <v>68.7424</v>
+        <v>66.2651</v>
       </c>
       <c r="F133" t="n">
-        <v>291.148</v>
+        <v>285.089</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>84.8891</v>
+        <v>84.9825</v>
       </c>
       <c r="C134" t="n">
-        <v>70.8282</v>
+        <v>70.45699999999999</v>
       </c>
       <c r="D134" t="n">
-        <v>275.634</v>
+        <v>274.551</v>
       </c>
       <c r="E134" t="n">
-        <v>60.7004</v>
+        <v>59.3514</v>
       </c>
       <c r="F134" t="n">
-        <v>238.191</v>
+        <v>234.761</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>85.3519</v>
+        <v>83.15009999999999</v>
       </c>
       <c r="C135" t="n">
-        <v>72.2479</v>
+        <v>69.4696</v>
       </c>
       <c r="D135" t="n">
-        <v>361.517</v>
+        <v>350.252</v>
       </c>
       <c r="E135" t="n">
-        <v>97.241</v>
+        <v>94.66679999999999</v>
       </c>
       <c r="F135" t="n">
-        <v>339.058</v>
+        <v>329.478</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>85.532</v>
+        <v>83.16459999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>105.519</v>
+        <v>103.024</v>
       </c>
       <c r="D136" t="n">
-        <v>354.125</v>
+        <v>343.414</v>
       </c>
       <c r="E136" t="n">
-        <v>95.28400000000001</v>
+        <v>92.8642</v>
       </c>
       <c r="F136" t="n">
-        <v>338.941</v>
+        <v>328.901</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>84.6939</v>
+        <v>82.0279</v>
       </c>
       <c r="C137" t="n">
-        <v>104.596</v>
+        <v>102.085</v>
       </c>
       <c r="D137" t="n">
-        <v>348.998</v>
+        <v>338.201</v>
       </c>
       <c r="E137" t="n">
-        <v>93.9546</v>
+        <v>90.9259</v>
       </c>
       <c r="F137" t="n">
-        <v>339.251</v>
+        <v>328.401</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>118.093</v>
+        <v>115.414</v>
       </c>
       <c r="C138" t="n">
-        <v>104.19</v>
+        <v>101.468</v>
       </c>
       <c r="D138" t="n">
-        <v>344.324</v>
+        <v>333.57</v>
       </c>
       <c r="E138" t="n">
-        <v>92.1046</v>
+        <v>89.43980000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>335.833</v>
+        <v>326.173</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>109.259</v>
+        <v>106.442</v>
       </c>
       <c r="C139" t="n">
-        <v>95.69929999999999</v>
+        <v>93.25490000000001</v>
       </c>
       <c r="D139" t="n">
-        <v>340.108</v>
+        <v>329.444</v>
       </c>
       <c r="E139" t="n">
-        <v>90.72190000000001</v>
+        <v>87.74509999999999</v>
       </c>
       <c r="F139" t="n">
-        <v>335.711</v>
+        <v>325.685</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>111.548</v>
+        <v>108.535</v>
       </c>
       <c r="C140" t="n">
-        <v>94.5214</v>
+        <v>92.0652</v>
       </c>
       <c r="D140" t="n">
-        <v>335.345</v>
+        <v>325.146</v>
       </c>
       <c r="E140" t="n">
-        <v>93.77509999999999</v>
+        <v>90.6545</v>
       </c>
       <c r="F140" t="n">
-        <v>334.82</v>
+        <v>324.825</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>108.196</v>
+        <v>105.348</v>
       </c>
       <c r="C141" t="n">
-        <v>93.4055</v>
+        <v>90.797</v>
       </c>
       <c r="D141" t="n">
-        <v>334.066</v>
+        <v>323.464</v>
       </c>
       <c r="E141" t="n">
-        <v>87.979</v>
+        <v>84.703</v>
       </c>
       <c r="F141" t="n">
-        <v>334.819</v>
+        <v>324.681</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>108.039</v>
+        <v>104.815</v>
       </c>
       <c r="C142" t="n">
-        <v>92.2621</v>
+        <v>89.54649999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>333.114</v>
+        <v>322.501</v>
       </c>
       <c r="E142" t="n">
-        <v>86.8386</v>
+        <v>83.4662</v>
       </c>
       <c r="F142" t="n">
-        <v>333.998</v>
+        <v>323.62</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>106.275</v>
+        <v>103.358</v>
       </c>
       <c r="C143" t="n">
-        <v>91.3912</v>
+        <v>88.5763</v>
       </c>
       <c r="D143" t="n">
-        <v>332.661</v>
+        <v>321.554</v>
       </c>
       <c r="E143" t="n">
-        <v>85.5389</v>
+        <v>82.2366</v>
       </c>
       <c r="F143" t="n">
-        <v>332.291</v>
+        <v>322.002</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.0817</v>
+        <v>24.0328</v>
       </c>
       <c r="C2" t="n">
-        <v>20.3052</v>
+        <v>20.2969</v>
       </c>
       <c r="D2" t="n">
-        <v>53.8151</v>
+        <v>53.5667</v>
       </c>
       <c r="E2" t="n">
-        <v>18.2367</v>
+        <v>18.2169</v>
       </c>
       <c r="F2" t="n">
-        <v>33.6327</v>
+        <v>33.522</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.0477</v>
+        <v>23.4401</v>
       </c>
       <c r="C3" t="n">
-        <v>19.8011</v>
+        <v>19.7451</v>
       </c>
       <c r="D3" t="n">
-        <v>53.188</v>
+        <v>52.9331</v>
       </c>
       <c r="E3" t="n">
-        <v>18.0573</v>
+        <v>17.6696</v>
       </c>
       <c r="F3" t="n">
-        <v>33.1646</v>
+        <v>33.0777</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.7917</v>
+        <v>22.7611</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2575</v>
+        <v>19.2846</v>
       </c>
       <c r="D4" t="n">
-        <v>52.6546</v>
+        <v>52.3889</v>
       </c>
       <c r="E4" t="n">
-        <v>17.1726</v>
+        <v>17.615</v>
       </c>
       <c r="F4" t="n">
-        <v>32.7394</v>
+        <v>32.6718</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.4807</v>
+        <v>22.2211</v>
       </c>
       <c r="C5" t="n">
-        <v>18.8694</v>
+        <v>18.8463</v>
       </c>
       <c r="D5" t="n">
-        <v>52.1702</v>
+        <v>52.0289</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7364</v>
+        <v>17.1409</v>
       </c>
       <c r="F5" t="n">
-        <v>32.519</v>
+        <v>32.402</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.0116</v>
+        <v>21.9959</v>
       </c>
       <c r="C6" t="n">
-        <v>18.4702</v>
+        <v>18.3918</v>
       </c>
       <c r="D6" t="n">
-        <v>51.7844</v>
+        <v>51.5758</v>
       </c>
       <c r="E6" t="n">
-        <v>16.3482</v>
+        <v>16.2925</v>
       </c>
       <c r="F6" t="n">
-        <v>32.3477</v>
+        <v>32.2972</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.6989</v>
+        <v>21.555</v>
       </c>
       <c r="C7" t="n">
-        <v>18.201</v>
+        <v>18.1703</v>
       </c>
       <c r="D7" t="n">
-        <v>66.0284</v>
+        <v>65.7706</v>
       </c>
       <c r="E7" t="n">
-        <v>26.2462</v>
+        <v>25.4814</v>
       </c>
       <c r="F7" t="n">
-        <v>40.6746</v>
+        <v>40.579</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.4622</v>
+        <v>21.2862</v>
       </c>
       <c r="C8" t="n">
-        <v>26.8669</v>
+        <v>26.8603</v>
       </c>
       <c r="D8" t="n">
-        <v>64.4469</v>
+        <v>64.2745</v>
       </c>
       <c r="E8" t="n">
-        <v>24.5427</v>
+        <v>24.5618</v>
       </c>
       <c r="F8" t="n">
-        <v>39.7916</v>
+        <v>39.6937</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.3615</v>
+        <v>21.1869</v>
       </c>
       <c r="C9" t="n">
-        <v>26.0089</v>
+        <v>25.9761</v>
       </c>
       <c r="D9" t="n">
-        <v>63.0379</v>
+        <v>62.8207</v>
       </c>
       <c r="E9" t="n">
-        <v>23.7337</v>
+        <v>23.6848</v>
       </c>
       <c r="F9" t="n">
-        <v>39.0724</v>
+        <v>38.827</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>30.4063</v>
+        <v>30.2007</v>
       </c>
       <c r="C10" t="n">
-        <v>25.1699</v>
+        <v>25.1221</v>
       </c>
       <c r="D10" t="n">
-        <v>61.8264</v>
+        <v>61.6257</v>
       </c>
       <c r="E10" t="n">
-        <v>23.7755</v>
+        <v>22.8075</v>
       </c>
       <c r="F10" t="n">
-        <v>38.0659</v>
+        <v>38.0027</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>29.4594</v>
+        <v>28.7639</v>
       </c>
       <c r="C11" t="n">
-        <v>24.4138</v>
+        <v>24.3316</v>
       </c>
       <c r="D11" t="n">
-        <v>60.6827</v>
+        <v>60.5482</v>
       </c>
       <c r="E11" t="n">
-        <v>22.7107</v>
+        <v>22.4693</v>
       </c>
       <c r="F11" t="n">
-        <v>37.4017</v>
+        <v>37.2386</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>28.2029</v>
+        <v>28.4271</v>
       </c>
       <c r="C12" t="n">
-        <v>23.6331</v>
+        <v>23.4771</v>
       </c>
       <c r="D12" t="n">
-        <v>59.582</v>
+        <v>59.4691</v>
       </c>
       <c r="E12" t="n">
-        <v>21.7549</v>
+        <v>21.3895</v>
       </c>
       <c r="F12" t="n">
-        <v>36.6515</v>
+        <v>36.4229</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>27.8901</v>
+        <v>27.605</v>
       </c>
       <c r="C13" t="n">
-        <v>22.9196</v>
+        <v>22.8534</v>
       </c>
       <c r="D13" t="n">
-        <v>58.6881</v>
+        <v>58.5887</v>
       </c>
       <c r="E13" t="n">
-        <v>21.0794</v>
+        <v>20.6328</v>
       </c>
       <c r="F13" t="n">
-        <v>35.9509</v>
+        <v>35.7406</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>26.9475</v>
+        <v>26.8164</v>
       </c>
       <c r="C14" t="n">
-        <v>22.2402</v>
+        <v>22.1094</v>
       </c>
       <c r="D14" t="n">
-        <v>58.0809</v>
+        <v>57.7943</v>
       </c>
       <c r="E14" t="n">
-        <v>20.2664</v>
+        <v>20.0227</v>
       </c>
       <c r="F14" t="n">
-        <v>35.3284</v>
+        <v>35.1207</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>25.9779</v>
+        <v>26.0136</v>
       </c>
       <c r="C15" t="n">
-        <v>21.5716</v>
+        <v>21.4203</v>
       </c>
       <c r="D15" t="n">
-        <v>57.3021</v>
+        <v>56.9578</v>
       </c>
       <c r="E15" t="n">
-        <v>19.6476</v>
+        <v>19.3934</v>
       </c>
       <c r="F15" t="n">
-        <v>34.7092</v>
+        <v>34.5229</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>25.4537</v>
+        <v>25.4195</v>
       </c>
       <c r="C16" t="n">
-        <v>21.0022</v>
+        <v>20.8603</v>
       </c>
       <c r="D16" t="n">
-        <v>56.6796</v>
+        <v>56.4764</v>
       </c>
       <c r="E16" t="n">
-        <v>19.1401</v>
+        <v>18.8275</v>
       </c>
       <c r="F16" t="n">
-        <v>34.1553</v>
+        <v>33.9486</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>25.0395</v>
+        <v>24.5343</v>
       </c>
       <c r="C17" t="n">
-        <v>20.3926</v>
+        <v>20.2798</v>
       </c>
       <c r="D17" t="n">
-        <v>56.0761</v>
+        <v>55.9477</v>
       </c>
       <c r="E17" t="n">
-        <v>18.5932</v>
+        <v>18.2932</v>
       </c>
       <c r="F17" t="n">
-        <v>33.6658</v>
+        <v>33.4718</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.0357</v>
+        <v>24.5291</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8768</v>
+        <v>19.7494</v>
       </c>
       <c r="D18" t="n">
-        <v>55.2573</v>
+        <v>55.0055</v>
       </c>
       <c r="E18" t="n">
-        <v>18.1127</v>
+        <v>17.8278</v>
       </c>
       <c r="F18" t="n">
-        <v>33.1928</v>
+        <v>33.0558</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.4434</v>
+        <v>23.6917</v>
       </c>
       <c r="C19" t="n">
-        <v>19.4152</v>
+        <v>19.2691</v>
       </c>
       <c r="D19" t="n">
-        <v>54.7147</v>
+        <v>54.4484</v>
       </c>
       <c r="E19" t="n">
-        <v>18.2788</v>
+        <v>17.4829</v>
       </c>
       <c r="F19" t="n">
-        <v>32.8457</v>
+        <v>32.6925</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>22.9774</v>
+        <v>23.46</v>
       </c>
       <c r="C20" t="n">
-        <v>18.9911</v>
+        <v>18.8423</v>
       </c>
       <c r="D20" t="n">
-        <v>54.284</v>
+        <v>54.0108</v>
       </c>
       <c r="E20" t="n">
-        <v>17.5259</v>
+        <v>17.3661</v>
       </c>
       <c r="F20" t="n">
-        <v>32.6432</v>
+        <v>32.5076</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>23.1233</v>
+        <v>22.7325</v>
       </c>
       <c r="C21" t="n">
-        <v>18.6796</v>
+        <v>18.5208</v>
       </c>
       <c r="D21" t="n">
-        <v>71.77549999999999</v>
+        <v>71.1858</v>
       </c>
       <c r="E21" t="n">
-        <v>26.9865</v>
+        <v>26.566</v>
       </c>
       <c r="F21" t="n">
-        <v>41.1976</v>
+        <v>41.0188</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.5844</v>
+        <v>22.5452</v>
       </c>
       <c r="C22" t="n">
-        <v>27.6218</v>
+        <v>27.2185</v>
       </c>
       <c r="D22" t="n">
-        <v>70.1782</v>
+        <v>69.66889999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>25.8092</v>
+        <v>25.551</v>
       </c>
       <c r="F22" t="n">
-        <v>40.4459</v>
+        <v>40.1649</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.5431</v>
+        <v>22.4674</v>
       </c>
       <c r="C23" t="n">
-        <v>26.527</v>
+        <v>26.3656</v>
       </c>
       <c r="D23" t="n">
-        <v>68.7419</v>
+        <v>68.2586</v>
       </c>
       <c r="E23" t="n">
-        <v>24.9969</v>
+        <v>24.7287</v>
       </c>
       <c r="F23" t="n">
-        <v>39.5387</v>
+        <v>39.2806</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>30.8951</v>
+        <v>30.8921</v>
       </c>
       <c r="C24" t="n">
-        <v>25.7402</v>
+        <v>25.5604</v>
       </c>
       <c r="D24" t="n">
-        <v>67.4723</v>
+        <v>66.83710000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>24.1253</v>
+        <v>23.871</v>
       </c>
       <c r="F24" t="n">
-        <v>38.7647</v>
+        <v>38.4697</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>29.7946</v>
+        <v>30.0075</v>
       </c>
       <c r="C25" t="n">
-        <v>24.9368</v>
+        <v>24.7832</v>
       </c>
       <c r="D25" t="n">
-        <v>66.1925</v>
+        <v>65.57859999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3252</v>
+        <v>23.082</v>
       </c>
       <c r="F25" t="n">
-        <v>37.8509</v>
+        <v>37.6783</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>29.146</v>
+        <v>29.0711</v>
       </c>
       <c r="C26" t="n">
-        <v>24.1807</v>
+        <v>23.999</v>
       </c>
       <c r="D26" t="n">
-        <v>64.759</v>
+        <v>64.13590000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>22.5875</v>
+        <v>22.3907</v>
       </c>
       <c r="F26" t="n">
-        <v>37.0151</v>
+        <v>36.8522</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.1374</v>
+        <v>28.6555</v>
       </c>
       <c r="C27" t="n">
-        <v>23.4787</v>
+        <v>23.2627</v>
       </c>
       <c r="D27" t="n">
-        <v>63.7923</v>
+        <v>63.1203</v>
       </c>
       <c r="E27" t="n">
-        <v>21.8717</v>
+        <v>21.7074</v>
       </c>
       <c r="F27" t="n">
-        <v>36.4066</v>
+        <v>36.1725</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>27.8162</v>
+        <v>27.3139</v>
       </c>
       <c r="C28" t="n">
-        <v>22.7916</v>
+        <v>22.6157</v>
       </c>
       <c r="D28" t="n">
-        <v>62.902</v>
+        <v>62.2232</v>
       </c>
       <c r="E28" t="n">
-        <v>21.4799</v>
+        <v>21.0204</v>
       </c>
       <c r="F28" t="n">
-        <v>35.7422</v>
+        <v>35.5506</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>27.0427</v>
+        <v>27.0744</v>
       </c>
       <c r="C29" t="n">
-        <v>22.1418</v>
+        <v>21.915</v>
       </c>
       <c r="D29" t="n">
-        <v>62.1815</v>
+        <v>61.5084</v>
       </c>
       <c r="E29" t="n">
-        <v>20.658</v>
+        <v>20.3607</v>
       </c>
       <c r="F29" t="n">
-        <v>35.1616</v>
+        <v>34.9175</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>26.3864</v>
+        <v>26.3768</v>
       </c>
       <c r="C30" t="n">
-        <v>21.5325</v>
+        <v>21.3172</v>
       </c>
       <c r="D30" t="n">
-        <v>61.2783</v>
+        <v>60.5863</v>
       </c>
       <c r="E30" t="n">
-        <v>20.1037</v>
+        <v>20.2393</v>
       </c>
       <c r="F30" t="n">
-        <v>34.6291</v>
+        <v>34.3652</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.7684</v>
+        <v>25.2249</v>
       </c>
       <c r="C31" t="n">
-        <v>20.9605</v>
+        <v>20.7795</v>
       </c>
       <c r="D31" t="n">
-        <v>60.737</v>
+        <v>60.0682</v>
       </c>
       <c r="E31" t="n">
-        <v>19.4893</v>
+        <v>19.4037</v>
       </c>
       <c r="F31" t="n">
-        <v>34.1083</v>
+        <v>33.844</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.8553</v>
+        <v>25.3452</v>
       </c>
       <c r="C32" t="n">
-        <v>20.425</v>
+        <v>20.2726</v>
       </c>
       <c r="D32" t="n">
-        <v>60.2687</v>
+        <v>59.5861</v>
       </c>
       <c r="E32" t="n">
-        <v>19.0234</v>
+        <v>18.8507</v>
       </c>
       <c r="F32" t="n">
-        <v>33.6794</v>
+        <v>33.5662</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>24.8321</v>
+        <v>24.6225</v>
       </c>
       <c r="C33" t="n">
-        <v>19.9291</v>
+        <v>19.7737</v>
       </c>
       <c r="D33" t="n">
-        <v>59.8334</v>
+        <v>59.1393</v>
       </c>
       <c r="E33" t="n">
-        <v>18.6591</v>
+        <v>18.423</v>
       </c>
       <c r="F33" t="n">
-        <v>33.4008</v>
+        <v>33.2135</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>23.8711</v>
+        <v>24.3706</v>
       </c>
       <c r="C34" t="n">
-        <v>19.554</v>
+        <v>19.3714</v>
       </c>
       <c r="D34" t="n">
-        <v>59.0594</v>
+        <v>58.2573</v>
       </c>
       <c r="E34" t="n">
-        <v>18.3556</v>
+        <v>18.228</v>
       </c>
       <c r="F34" t="n">
-        <v>33.1723</v>
+        <v>32.9307</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.7799</v>
+        <v>23.9001</v>
       </c>
       <c r="C35" t="n">
-        <v>19.153</v>
+        <v>19.0482</v>
       </c>
       <c r="D35" t="n">
-        <v>77.4252</v>
+        <v>76.6164</v>
       </c>
       <c r="E35" t="n">
-        <v>27.6383</v>
+        <v>27.5741</v>
       </c>
       <c r="F35" t="n">
-        <v>42.2501</v>
+        <v>42.0166</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.2414</v>
+        <v>23.0636</v>
       </c>
       <c r="C36" t="n">
-        <v>18.9564</v>
+        <v>18.7558</v>
       </c>
       <c r="D36" t="n">
-        <v>75.652</v>
+        <v>74.9162</v>
       </c>
       <c r="E36" t="n">
-        <v>26.7451</v>
+        <v>26.6103</v>
       </c>
       <c r="F36" t="n">
-        <v>41.4088</v>
+        <v>41.3295</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.0804</v>
+        <v>22.9154</v>
       </c>
       <c r="C37" t="n">
-        <v>27.3217</v>
+        <v>27.1279</v>
       </c>
       <c r="D37" t="n">
-        <v>74.06999999999999</v>
+        <v>73.2988</v>
       </c>
       <c r="E37" t="n">
-        <v>25.8348</v>
+        <v>26.0245</v>
       </c>
       <c r="F37" t="n">
-        <v>40.596</v>
+        <v>40.4606</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>31.0794</v>
+        <v>31.4058</v>
       </c>
       <c r="C38" t="n">
-        <v>26.4253</v>
+        <v>26.2852</v>
       </c>
       <c r="D38" t="n">
-        <v>72.5483</v>
+        <v>71.7814</v>
       </c>
       <c r="E38" t="n">
-        <v>25.0729</v>
+        <v>24.9707</v>
       </c>
       <c r="F38" t="n">
-        <v>40.2141</v>
+        <v>39.8642</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>30.4929</v>
+        <v>30.3387</v>
       </c>
       <c r="C39" t="n">
-        <v>25.9863</v>
+        <v>25.5321</v>
       </c>
       <c r="D39" t="n">
-        <v>71.1944</v>
+        <v>70.4867</v>
       </c>
       <c r="E39" t="n">
-        <v>24.4991</v>
+        <v>24.178</v>
       </c>
       <c r="F39" t="n">
-        <v>39.1743</v>
+        <v>38.905</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>29.9824</v>
+        <v>30.0087</v>
       </c>
       <c r="C40" t="n">
-        <v>24.8894</v>
+        <v>24.8601</v>
       </c>
       <c r="D40" t="n">
-        <v>69.92919999999999</v>
+        <v>69.2625</v>
       </c>
       <c r="E40" t="n">
-        <v>23.6755</v>
+        <v>23.6734</v>
       </c>
       <c r="F40" t="n">
-        <v>38.5977</v>
+        <v>38.2749</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>28.8379</v>
+        <v>28.8647</v>
       </c>
       <c r="C41" t="n">
-        <v>24.1768</v>
+        <v>24.1568</v>
       </c>
       <c r="D41" t="n">
-        <v>68.70959999999999</v>
+        <v>68.0586</v>
       </c>
       <c r="E41" t="n">
-        <v>22.81</v>
+        <v>22.7037</v>
       </c>
       <c r="F41" t="n">
-        <v>37.8042</v>
+        <v>37.5935</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>28.0606</v>
+        <v>28.1976</v>
       </c>
       <c r="C42" t="n">
-        <v>23.4986</v>
+        <v>23.4691</v>
       </c>
       <c r="D42" t="n">
-        <v>67.8172</v>
+        <v>67.1374</v>
       </c>
       <c r="E42" t="n">
-        <v>22.5737</v>
+        <v>22.0059</v>
       </c>
       <c r="F42" t="n">
-        <v>37.3102</v>
+        <v>37.0167</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>27.492</v>
+        <v>27.0088</v>
       </c>
       <c r="C43" t="n">
-        <v>22.8697</v>
+        <v>22.8168</v>
       </c>
       <c r="D43" t="n">
-        <v>66.6324</v>
+        <v>65.98260000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>21.53</v>
+        <v>21.4298</v>
       </c>
       <c r="F43" t="n">
-        <v>36.7312</v>
+        <v>36.4287</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>27.002</v>
+        <v>26.4825</v>
       </c>
       <c r="C44" t="n">
-        <v>22.3372</v>
+        <v>22.1612</v>
       </c>
       <c r="D44" t="n">
-        <v>65.79689999999999</v>
+        <v>65.2242</v>
       </c>
       <c r="E44" t="n">
-        <v>20.9664</v>
+        <v>20.7767</v>
       </c>
       <c r="F44" t="n">
-        <v>36.1936</v>
+        <v>35.9133</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>25.9061</v>
+        <v>25.9471</v>
       </c>
       <c r="C45" t="n">
-        <v>21.7096</v>
+        <v>21.5703</v>
       </c>
       <c r="D45" t="n">
-        <v>65.15779999999999</v>
+        <v>64.563</v>
       </c>
       <c r="E45" t="n">
-        <v>20.6173</v>
+        <v>20.2468</v>
       </c>
       <c r="F45" t="n">
-        <v>35.7588</v>
+        <v>35.4705</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>25.8017</v>
+        <v>25.6698</v>
       </c>
       <c r="C46" t="n">
-        <v>21.1777</v>
+        <v>21.0739</v>
       </c>
       <c r="D46" t="n">
-        <v>64.569</v>
+        <v>64.01479999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>20.0727</v>
+        <v>19.8217</v>
       </c>
       <c r="F46" t="n">
-        <v>35.3352</v>
+        <v>35.0583</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>24.8432</v>
+        <v>24.6273</v>
       </c>
       <c r="C47" t="n">
-        <v>20.6996</v>
+        <v>20.7677</v>
       </c>
       <c r="D47" t="n">
-        <v>64.1002</v>
+        <v>63.5325</v>
       </c>
       <c r="E47" t="n">
-        <v>19.5144</v>
+        <v>19.3037</v>
       </c>
       <c r="F47" t="n">
-        <v>35.0097</v>
+        <v>34.7105</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>24.7619</v>
+        <v>24.2204</v>
       </c>
       <c r="C48" t="n">
-        <v>20.2551</v>
+        <v>20.1787</v>
       </c>
       <c r="D48" t="n">
-        <v>63.3745</v>
+        <v>62.8496</v>
       </c>
       <c r="E48" t="n">
-        <v>19.1797</v>
+        <v>18.9942</v>
       </c>
       <c r="F48" t="n">
-        <v>34.7341</v>
+        <v>34.4572</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>24.1862</v>
+        <v>23.9418</v>
       </c>
       <c r="C49" t="n">
-        <v>19.953</v>
+        <v>19.7772</v>
       </c>
       <c r="D49" t="n">
-        <v>63.0087</v>
+        <v>62.4766</v>
       </c>
       <c r="E49" t="n">
-        <v>18.9968</v>
+        <v>18.7048</v>
       </c>
       <c r="F49" t="n">
-        <v>34.5763</v>
+        <v>34.3225</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>23.6513</v>
+        <v>23.7193</v>
       </c>
       <c r="C50" t="n">
-        <v>19.6036</v>
+        <v>19.7215</v>
       </c>
       <c r="D50" t="n">
-        <v>80.3629</v>
+        <v>79.8715</v>
       </c>
       <c r="E50" t="n">
-        <v>28.0147</v>
+        <v>27.7268</v>
       </c>
       <c r="F50" t="n">
-        <v>42.9235</v>
+        <v>43.7537</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>24.1336</v>
+        <v>24.5003</v>
       </c>
       <c r="C51" t="n">
-        <v>28.1348</v>
+        <v>28.0175</v>
       </c>
       <c r="D51" t="n">
-        <v>78.63160000000001</v>
+        <v>78.07510000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>27.1807</v>
+        <v>27.0584</v>
       </c>
       <c r="F51" t="n">
-        <v>42.346</v>
+        <v>42.3824</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>23.8338</v>
+        <v>23.7063</v>
       </c>
       <c r="C52" t="n">
-        <v>27.31</v>
+        <v>27.1645</v>
       </c>
       <c r="D52" t="n">
-        <v>76.94110000000001</v>
+        <v>76.3797</v>
       </c>
       <c r="E52" t="n">
-        <v>26.4255</v>
+        <v>26.2453</v>
       </c>
       <c r="F52" t="n">
-        <v>41.6124</v>
+        <v>41.5024</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>31.743</v>
+        <v>31.4661</v>
       </c>
       <c r="C53" t="n">
-        <v>26.7017</v>
+        <v>26.5125</v>
       </c>
       <c r="D53" t="n">
-        <v>75.38979999999999</v>
+        <v>74.9033</v>
       </c>
       <c r="E53" t="n">
-        <v>25.7086</v>
+        <v>25.3218</v>
       </c>
       <c r="F53" t="n">
-        <v>40.9324</v>
+        <v>40.8266</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>31.7519</v>
+        <v>30.7233</v>
       </c>
       <c r="C54" t="n">
-        <v>25.8386</v>
+        <v>25.7909</v>
       </c>
       <c r="D54" t="n">
-        <v>74.0142</v>
+        <v>73.4902</v>
       </c>
       <c r="E54" t="n">
-        <v>24.7902</v>
+        <v>24.5324</v>
       </c>
       <c r="F54" t="n">
-        <v>40.319</v>
+        <v>40.1732</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>30.2471</v>
+        <v>30.1017</v>
       </c>
       <c r="C55" t="n">
-        <v>25.2229</v>
+        <v>25.1147</v>
       </c>
       <c r="D55" t="n">
-        <v>72.78100000000001</v>
+        <v>72.348</v>
       </c>
       <c r="E55" t="n">
-        <v>24.1149</v>
+        <v>23.9404</v>
       </c>
       <c r="F55" t="n">
-        <v>39.6991</v>
+        <v>39.5809</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>29.4972</v>
+        <v>29.2157</v>
       </c>
       <c r="C56" t="n">
-        <v>24.5267</v>
+        <v>24.4203</v>
       </c>
       <c r="D56" t="n">
-        <v>71.67189999999999</v>
+        <v>71.26260000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>23.3956</v>
+        <v>23.1846</v>
       </c>
       <c r="F56" t="n">
-        <v>39.086</v>
+        <v>39.032</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>28.833</v>
+        <v>28.7565</v>
       </c>
       <c r="C57" t="n">
-        <v>23.961</v>
+        <v>24.0072</v>
       </c>
       <c r="D57" t="n">
-        <v>70.44670000000001</v>
+        <v>70.08369999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>22.9112</v>
+        <v>22.4854</v>
       </c>
       <c r="F57" t="n">
-        <v>38.6376</v>
+        <v>38.4705</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.2352</v>
+        <v>28.5616</v>
       </c>
       <c r="C58" t="n">
-        <v>23.3068</v>
+        <v>23.253</v>
       </c>
       <c r="D58" t="n">
-        <v>69.6345</v>
+        <v>69.2448</v>
       </c>
       <c r="E58" t="n">
-        <v>22.1645</v>
+        <v>21.9336</v>
       </c>
       <c r="F58" t="n">
-        <v>38.1315</v>
+        <v>37.9939</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.6198</v>
+        <v>27.7602</v>
       </c>
       <c r="C59" t="n">
-        <v>22.7279</v>
+        <v>22.8387</v>
       </c>
       <c r="D59" t="n">
-        <v>68.77679999999999</v>
+        <v>68.3642</v>
       </c>
       <c r="E59" t="n">
-        <v>21.8429</v>
+        <v>21.4483</v>
       </c>
       <c r="F59" t="n">
-        <v>37.7302</v>
+        <v>37.6053</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>26.9309</v>
+        <v>26.9899</v>
       </c>
       <c r="C60" t="n">
-        <v>22.3569</v>
+        <v>22.3852</v>
       </c>
       <c r="D60" t="n">
-        <v>68.10809999999999</v>
+        <v>67.79689999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>21.3319</v>
+        <v>21.0421</v>
       </c>
       <c r="F60" t="n">
-        <v>37.244</v>
+        <v>37.2147</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.7836</v>
+        <v>26.8184</v>
       </c>
       <c r="C61" t="n">
-        <v>21.8893</v>
+        <v>21.7557</v>
       </c>
       <c r="D61" t="n">
-        <v>67.34610000000001</v>
+        <v>67.0235</v>
       </c>
       <c r="E61" t="n">
-        <v>20.577</v>
+        <v>20.5947</v>
       </c>
       <c r="F61" t="n">
-        <v>37.0484</v>
+        <v>36.9167</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>25.8127</v>
+        <v>26.171</v>
       </c>
       <c r="C62" t="n">
-        <v>21.4505</v>
+        <v>21.3493</v>
       </c>
       <c r="D62" t="n">
-        <v>66.60809999999999</v>
+        <v>66.386</v>
       </c>
       <c r="E62" t="n">
-        <v>20.5489</v>
+        <v>20.1115</v>
       </c>
       <c r="F62" t="n">
-        <v>36.8207</v>
+        <v>36.6956</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>25.9398</v>
+        <v>25.8415</v>
       </c>
       <c r="C63" t="n">
-        <v>21.0027</v>
+        <v>21.0337</v>
       </c>
       <c r="D63" t="n">
-        <v>66.2843</v>
+        <v>65.98399999999999</v>
       </c>
       <c r="E63" t="n">
-        <v>19.9973</v>
+        <v>20.0728</v>
       </c>
       <c r="F63" t="n">
-        <v>36.5367</v>
+        <v>36.5601</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.2256</v>
+        <v>25.505</v>
       </c>
       <c r="C64" t="n">
-        <v>20.7889</v>
+        <v>20.8282</v>
       </c>
       <c r="D64" t="n">
-        <v>87.8121</v>
+        <v>87.30929999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>32.7254</v>
+        <v>32.2756</v>
       </c>
       <c r="F64" t="n">
-        <v>46.4582</v>
+        <v>47.4864</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.8488</v>
+        <v>25.2572</v>
       </c>
       <c r="C65" t="n">
-        <v>29.6768</v>
+        <v>29.6912</v>
       </c>
       <c r="D65" t="n">
-        <v>85.38330000000001</v>
+        <v>85.1439</v>
       </c>
       <c r="E65" t="n">
-        <v>31.8037</v>
+        <v>30.5143</v>
       </c>
       <c r="F65" t="n">
-        <v>45.9279</v>
+        <v>46.9766</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>24.9427</v>
+        <v>25.4286</v>
       </c>
       <c r="C66" t="n">
-        <v>29.0745</v>
+        <v>28.9975</v>
       </c>
       <c r="D66" t="n">
-        <v>83.6422</v>
+        <v>83.3159</v>
       </c>
       <c r="E66" t="n">
-        <v>30.5571</v>
+        <v>30.9044</v>
       </c>
       <c r="F66" t="n">
-        <v>45.3677</v>
+        <v>46.2337</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>39.8556</v>
+        <v>40.3022</v>
       </c>
       <c r="C67" t="n">
-        <v>28.389</v>
+        <v>28.4097</v>
       </c>
       <c r="D67" t="n">
-        <v>81.9036</v>
+        <v>81.5748</v>
       </c>
       <c r="E67" t="n">
-        <v>29.4749</v>
+        <v>29.659</v>
       </c>
       <c r="F67" t="n">
-        <v>44.7906</v>
+        <v>45.7272</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>39.4342</v>
+        <v>38.092</v>
       </c>
       <c r="C68" t="n">
-        <v>27.8149</v>
+        <v>27.8535</v>
       </c>
       <c r="D68" t="n">
-        <v>80.3385</v>
+        <v>80.0616</v>
       </c>
       <c r="E68" t="n">
-        <v>28.7444</v>
+        <v>29.1669</v>
       </c>
       <c r="F68" t="n">
-        <v>44.2797</v>
+        <v>44.9639</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>39.0533</v>
+        <v>38.8663</v>
       </c>
       <c r="C69" t="n">
-        <v>27.2526</v>
+        <v>27.2899</v>
       </c>
       <c r="D69" t="n">
-        <v>79.0527</v>
+        <v>78.6283</v>
       </c>
       <c r="E69" t="n">
-        <v>28.5308</v>
+        <v>28.1267</v>
       </c>
       <c r="F69" t="n">
-        <v>43.6386</v>
+        <v>44.2385</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>38.5596</v>
+        <v>37.3654</v>
       </c>
       <c r="C70" t="n">
-        <v>26.7636</v>
+        <v>26.7196</v>
       </c>
       <c r="D70" t="n">
-        <v>78.0545</v>
+        <v>77.5667</v>
       </c>
       <c r="E70" t="n">
-        <v>27.8891</v>
+        <v>27.8041</v>
       </c>
       <c r="F70" t="n">
-        <v>43.1178</v>
+        <v>43.7266</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>37.6501</v>
+        <v>38.3406</v>
       </c>
       <c r="C71" t="n">
-        <v>26.2727</v>
+        <v>26.2142</v>
       </c>
       <c r="D71" t="n">
-        <v>77.3796</v>
+        <v>76.9354</v>
       </c>
       <c r="E71" t="n">
-        <v>26.4895</v>
+        <v>26.8171</v>
       </c>
       <c r="F71" t="n">
-        <v>42.7557</v>
+        <v>43.3597</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.2692</v>
+        <v>37.0268</v>
       </c>
       <c r="C72" t="n">
-        <v>25.8157</v>
+        <v>25.9843</v>
       </c>
       <c r="D72" t="n">
-        <v>76.6116</v>
+        <v>76.44710000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>26.5074</v>
+        <v>25.9861</v>
       </c>
       <c r="F72" t="n">
-        <v>42.3185</v>
+        <v>42.8402</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>35.8616</v>
+        <v>36.3382</v>
       </c>
       <c r="C73" t="n">
-        <v>25.3273</v>
+        <v>25.3606</v>
       </c>
       <c r="D73" t="n">
-        <v>76.12269999999999</v>
+        <v>76.24590000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>25.9764</v>
+        <v>25.4605</v>
       </c>
       <c r="F73" t="n">
-        <v>41.8678</v>
+        <v>42.3767</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>36.8522</v>
+        <v>36.112</v>
       </c>
       <c r="C74" t="n">
-        <v>24.9603</v>
+        <v>24.9221</v>
       </c>
       <c r="D74" t="n">
-        <v>75.7741</v>
+        <v>75.6416</v>
       </c>
       <c r="E74" t="n">
-        <v>24.9315</v>
+        <v>25.3814</v>
       </c>
       <c r="F74" t="n">
-        <v>41.5259</v>
+        <v>42.0435</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>35.6227</v>
+        <v>34.7253</v>
       </c>
       <c r="C75" t="n">
-        <v>24.4754</v>
+        <v>24.5589</v>
       </c>
       <c r="D75" t="n">
-        <v>75.00149999999999</v>
+        <v>75.1062</v>
       </c>
       <c r="E75" t="n">
-        <v>24.4764</v>
+        <v>24.2964</v>
       </c>
       <c r="F75" t="n">
-        <v>41.2266</v>
+        <v>41.7969</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>34.4219</v>
+        <v>33.4124</v>
       </c>
       <c r="C76" t="n">
-        <v>24.1243</v>
+        <v>24.3452</v>
       </c>
       <c r="D76" t="n">
-        <v>75.1794</v>
+        <v>75.15949999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>24.7147</v>
+        <v>23.7645</v>
       </c>
       <c r="F76" t="n">
-        <v>41.0585</v>
+        <v>41.4671</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>34.3416</v>
+        <v>33.6027</v>
       </c>
       <c r="C77" t="n">
-        <v>23.8883</v>
+        <v>23.8133</v>
       </c>
       <c r="D77" t="n">
-        <v>75.3605</v>
+        <v>75.5844</v>
       </c>
       <c r="E77" t="n">
-        <v>23.7291</v>
+        <v>23.9077</v>
       </c>
       <c r="F77" t="n">
-        <v>41.0463</v>
+        <v>41.2141</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>33.5502</v>
+        <v>33.5978</v>
       </c>
       <c r="C78" t="n">
-        <v>23.4537</v>
+        <v>23.5364</v>
       </c>
       <c r="D78" t="n">
-        <v>123.174</v>
+        <v>123.153</v>
       </c>
       <c r="E78" t="n">
-        <v>41.3328</v>
+        <v>40.4153</v>
       </c>
       <c r="F78" t="n">
-        <v>65.1384</v>
+        <v>65.3477</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>35.846</v>
+        <v>37.1194</v>
       </c>
       <c r="C79" t="n">
-        <v>33.2626</v>
+        <v>33.0398</v>
       </c>
       <c r="D79" t="n">
-        <v>120.64</v>
+        <v>120.874</v>
       </c>
       <c r="E79" t="n">
-        <v>40.3023</v>
+        <v>39.6654</v>
       </c>
       <c r="F79" t="n">
-        <v>65.1816</v>
+        <v>65.5497</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>36.2829</v>
+        <v>35.8362</v>
       </c>
       <c r="C80" t="n">
-        <v>33.0737</v>
+        <v>32.8253</v>
       </c>
       <c r="D80" t="n">
-        <v>119.067</v>
+        <v>119.076</v>
       </c>
       <c r="E80" t="n">
-        <v>39.1926</v>
+        <v>38.8843</v>
       </c>
       <c r="F80" t="n">
-        <v>65.256</v>
+        <v>65.44159999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>46.2864</v>
+        <v>50.0019</v>
       </c>
       <c r="C81" t="n">
-        <v>32.7514</v>
+        <v>32.5232</v>
       </c>
       <c r="D81" t="n">
-        <v>117.631</v>
+        <v>117.482</v>
       </c>
       <c r="E81" t="n">
-        <v>38.9274</v>
+        <v>37.8531</v>
       </c>
       <c r="F81" t="n">
-        <v>64.8954</v>
+        <v>64.8706</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>45.3029</v>
+        <v>49.9658</v>
       </c>
       <c r="C82" t="n">
-        <v>31.9795</v>
+        <v>32.147</v>
       </c>
       <c r="D82" t="n">
-        <v>116.081</v>
+        <v>116.121</v>
       </c>
       <c r="E82" t="n">
-        <v>37.5952</v>
+        <v>36.9116</v>
       </c>
       <c r="F82" t="n">
-        <v>64.5586</v>
+        <v>64.0031</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>49.2652</v>
+        <v>49.0894</v>
       </c>
       <c r="C83" t="n">
-        <v>31.9759</v>
+        <v>31.8411</v>
       </c>
       <c r="D83" t="n">
-        <v>115.344</v>
+        <v>115.185</v>
       </c>
       <c r="E83" t="n">
-        <v>37.1102</v>
+        <v>36.0088</v>
       </c>
       <c r="F83" t="n">
-        <v>63.3162</v>
+        <v>63.2509</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.8249</v>
+        <v>48.7549</v>
       </c>
       <c r="C84" t="n">
-        <v>31.5302</v>
+        <v>31.4558</v>
       </c>
       <c r="D84" t="n">
-        <v>114.993</v>
+        <v>114.837</v>
       </c>
       <c r="E84" t="n">
-        <v>35.8723</v>
+        <v>35.0642</v>
       </c>
       <c r="F84" t="n">
-        <v>62.5463</v>
+        <v>62.2233</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>42.9986</v>
+        <v>41.9847</v>
       </c>
       <c r="C85" t="n">
-        <v>31.1796</v>
+        <v>31.2849</v>
       </c>
       <c r="D85" t="n">
-        <v>114.694</v>
+        <v>114.664</v>
       </c>
       <c r="E85" t="n">
-        <v>35.0601</v>
+        <v>34.2178</v>
       </c>
       <c r="F85" t="n">
-        <v>62.0859</v>
+        <v>61.4038</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>47.3209</v>
+        <v>48.103</v>
       </c>
       <c r="C86" t="n">
-        <v>31.0432</v>
+        <v>30.805</v>
       </c>
       <c r="D86" t="n">
-        <v>115.57</v>
+        <v>114.904</v>
       </c>
       <c r="E86" t="n">
-        <v>34.3861</v>
+        <v>33.3343</v>
       </c>
       <c r="F86" t="n">
-        <v>61.0782</v>
+        <v>60.389</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>43.0289</v>
+        <v>44.4999</v>
       </c>
       <c r="C87" t="n">
-        <v>30.3042</v>
+        <v>30.3529</v>
       </c>
       <c r="D87" t="n">
-        <v>115.912</v>
+        <v>115.086</v>
       </c>
       <c r="E87" t="n">
-        <v>33.2758</v>
+        <v>32.4998</v>
       </c>
       <c r="F87" t="n">
-        <v>60.4425</v>
+        <v>59.6778</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>42.8388</v>
+        <v>46.0386</v>
       </c>
       <c r="C88" t="n">
-        <v>30.2959</v>
+        <v>30.2255</v>
       </c>
       <c r="D88" t="n">
-        <v>116.607</v>
+        <v>115.754</v>
       </c>
       <c r="E88" t="n">
-        <v>32.7966</v>
+        <v>31.8009</v>
       </c>
       <c r="F88" t="n">
-        <v>59.6647</v>
+        <v>58.8358</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>45.8324</v>
+        <v>45.9085</v>
       </c>
       <c r="C89" t="n">
-        <v>29.7583</v>
+        <v>29.8082</v>
       </c>
       <c r="D89" t="n">
-        <v>116.825</v>
+        <v>115.825</v>
       </c>
       <c r="E89" t="n">
-        <v>31.7595</v>
+        <v>31.0746</v>
       </c>
       <c r="F89" t="n">
-        <v>58.9351</v>
+        <v>57.6238</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>44.0784</v>
+        <v>44.9332</v>
       </c>
       <c r="C90" t="n">
-        <v>29.6094</v>
+        <v>29.5174</v>
       </c>
       <c r="D90" t="n">
-        <v>117.975</v>
+        <v>116.962</v>
       </c>
       <c r="E90" t="n">
-        <v>31.538</v>
+        <v>30.7172</v>
       </c>
       <c r="F90" t="n">
-        <v>58.568</v>
+        <v>57.1831</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>43.3384</v>
+        <v>42.2721</v>
       </c>
       <c r="C91" t="n">
-        <v>29.2359</v>
+        <v>29.3731</v>
       </c>
       <c r="D91" t="n">
-        <v>119.551</v>
+        <v>119.272</v>
       </c>
       <c r="E91" t="n">
-        <v>30.6678</v>
+        <v>30.1187</v>
       </c>
       <c r="F91" t="n">
-        <v>57.9741</v>
+        <v>57.5937</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>42.4978</v>
+        <v>41.4039</v>
       </c>
       <c r="C92" t="n">
-        <v>29.1897</v>
+        <v>28.9508</v>
       </c>
       <c r="D92" t="n">
-        <v>179.215</v>
+        <v>177.602</v>
       </c>
       <c r="E92" t="n">
-        <v>64.486</v>
+        <v>64.26949999999999</v>
       </c>
       <c r="F92" t="n">
-        <v>88.6481</v>
+        <v>89.6392</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>44.6331</v>
+        <v>41.6891</v>
       </c>
       <c r="C93" t="n">
-        <v>29.0307</v>
+        <v>28.7836</v>
       </c>
       <c r="D93" t="n">
-        <v>178.811</v>
+        <v>176.423</v>
       </c>
       <c r="E93" t="n">
-        <v>62.9828</v>
+        <v>63.1481</v>
       </c>
       <c r="F93" t="n">
-        <v>89.9136</v>
+        <v>90.8614</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>44.7761</v>
+        <v>45.037</v>
       </c>
       <c r="C94" t="n">
-        <v>61.6776</v>
+        <v>62.0875</v>
       </c>
       <c r="D94" t="n">
-        <v>177.325</v>
+        <v>175.438</v>
       </c>
       <c r="E94" t="n">
-        <v>61.7352</v>
+        <v>61.2231</v>
       </c>
       <c r="F94" t="n">
-        <v>88.6781</v>
+        <v>90.1478</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>74.93810000000001</v>
+        <v>78.501</v>
       </c>
       <c r="C95" t="n">
-        <v>60.3986</v>
+        <v>60.9268</v>
       </c>
       <c r="D95" t="n">
-        <v>176.167</v>
+        <v>174.489</v>
       </c>
       <c r="E95" t="n">
-        <v>59.5128</v>
+        <v>59.4621</v>
       </c>
       <c r="F95" t="n">
-        <v>87.5607</v>
+        <v>89.0277</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>75.0568</v>
+        <v>75.36199999999999</v>
       </c>
       <c r="C96" t="n">
-        <v>59.0837</v>
+        <v>59.4151</v>
       </c>
       <c r="D96" t="n">
-        <v>174.514</v>
+        <v>173.439</v>
       </c>
       <c r="E96" t="n">
-        <v>57.7606</v>
+        <v>57.7446</v>
       </c>
       <c r="F96" t="n">
-        <v>87.04170000000001</v>
+        <v>87.3272</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>73.6747</v>
+        <v>73.1872</v>
       </c>
       <c r="C97" t="n">
-        <v>57.4064</v>
+        <v>57.8464</v>
       </c>
       <c r="D97" t="n">
-        <v>174.406</v>
+        <v>173.084</v>
       </c>
       <c r="E97" t="n">
-        <v>55.789</v>
+        <v>55.8822</v>
       </c>
       <c r="F97" t="n">
-        <v>85.7397</v>
+        <v>85.5736</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>71.6833</v>
+        <v>67.6579</v>
       </c>
       <c r="C98" t="n">
-        <v>56.113</v>
+        <v>56.5946</v>
       </c>
       <c r="D98" t="n">
-        <v>173.889</v>
+        <v>172.801</v>
       </c>
       <c r="E98" t="n">
-        <v>53.9228</v>
+        <v>54.0618</v>
       </c>
       <c r="F98" t="n">
-        <v>84.7685</v>
+        <v>83.946</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>70.0917</v>
+        <v>71.5675</v>
       </c>
       <c r="C99" t="n">
-        <v>54.5825</v>
+        <v>55.1974</v>
       </c>
       <c r="D99" t="n">
-        <v>174.342</v>
+        <v>172.992</v>
       </c>
       <c r="E99" t="n">
-        <v>52.7323</v>
+        <v>52.7147</v>
       </c>
       <c r="F99" t="n">
-        <v>84.36490000000001</v>
+        <v>84.679</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>67.5146</v>
+        <v>68.25279999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>53.6986</v>
+        <v>53.9512</v>
       </c>
       <c r="D100" t="n">
-        <v>174.981</v>
+        <v>173.436</v>
       </c>
       <c r="E100" t="n">
-        <v>51.0791</v>
+        <v>51.1797</v>
       </c>
       <c r="F100" t="n">
-        <v>83.67310000000001</v>
+        <v>81.7315</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.4311</v>
+        <v>67.349</v>
       </c>
       <c r="C101" t="n">
-        <v>52.4312</v>
+        <v>52.6429</v>
       </c>
       <c r="D101" t="n">
-        <v>175.345</v>
+        <v>173.495</v>
       </c>
       <c r="E101" t="n">
-        <v>49.6049</v>
+        <v>49.6478</v>
       </c>
       <c r="F101" t="n">
-        <v>82.4705</v>
+        <v>85.1572</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>66.2873</v>
+        <v>67.27800000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>51.3471</v>
+        <v>51.5837</v>
       </c>
       <c r="D102" t="n">
-        <v>176.252</v>
+        <v>174.52</v>
       </c>
       <c r="E102" t="n">
-        <v>48.3935</v>
+        <v>48.2655</v>
       </c>
       <c r="F102" t="n">
-        <v>82.67100000000001</v>
+        <v>80.6007</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>65.31319999999999</v>
+        <v>65.8516</v>
       </c>
       <c r="C103" t="n">
-        <v>50.3354</v>
+        <v>50.5294</v>
       </c>
       <c r="D103" t="n">
-        <v>178.056</v>
+        <v>175.88</v>
       </c>
       <c r="E103" t="n">
-        <v>47.1904</v>
+        <v>47.146</v>
       </c>
       <c r="F103" t="n">
-        <v>82.02160000000001</v>
+        <v>80.2064</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>64.48820000000001</v>
+        <v>64.3441</v>
       </c>
       <c r="C104" t="n">
-        <v>49.2562</v>
+        <v>49.4764</v>
       </c>
       <c r="D104" t="n">
-        <v>179.393</v>
+        <v>177.141</v>
       </c>
       <c r="E104" t="n">
-        <v>45.7529</v>
+        <v>45.8672</v>
       </c>
       <c r="F104" t="n">
-        <v>79.5548</v>
+        <v>78.7829</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>63.866</v>
+        <v>63.2301</v>
       </c>
       <c r="C105" t="n">
-        <v>48.6026</v>
+        <v>48.6222</v>
       </c>
       <c r="D105" t="n">
-        <v>180.682</v>
+        <v>178.664</v>
       </c>
       <c r="E105" t="n">
-        <v>44.7798</v>
+        <v>44.8476</v>
       </c>
       <c r="F105" t="n">
-        <v>89.9538</v>
+        <v>78.5202</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>64.6726</v>
+        <v>62.7343</v>
       </c>
       <c r="C106" t="n">
-        <v>47.5915</v>
+        <v>47.7337</v>
       </c>
       <c r="D106" t="n">
-        <v>182.374</v>
+        <v>180.897</v>
       </c>
       <c r="E106" t="n">
-        <v>44.0417</v>
+        <v>43.9253</v>
       </c>
       <c r="F106" t="n">
-        <v>90.5612</v>
+        <v>78.13420000000001</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>60.6711</v>
+        <v>60.8799</v>
       </c>
       <c r="C107" t="n">
-        <v>46.7065</v>
+        <v>46.9071</v>
       </c>
       <c r="D107" t="n">
-        <v>245.146</v>
+        <v>241.547</v>
       </c>
       <c r="E107" t="n">
-        <v>79.15179999999999</v>
+        <v>78.59180000000001</v>
       </c>
       <c r="F107" t="n">
-        <v>242.223</v>
+        <v>241.864</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>60.1491</v>
+        <v>61.1168</v>
       </c>
       <c r="C108" t="n">
-        <v>81.1808</v>
+        <v>81.7547</v>
       </c>
       <c r="D108" t="n">
-        <v>242.745</v>
+        <v>238.972</v>
       </c>
       <c r="E108" t="n">
-        <v>76.5577</v>
+        <v>76.8673</v>
       </c>
       <c r="F108" t="n">
-        <v>244.622</v>
+        <v>241.009</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>55.5031</v>
+        <v>57.5658</v>
       </c>
       <c r="C109" t="n">
-        <v>65.2313</v>
+        <v>79.8257</v>
       </c>
       <c r="D109" t="n">
-        <v>240.923</v>
+        <v>236.794</v>
       </c>
       <c r="E109" t="n">
-        <v>74.2135</v>
+        <v>74.5609</v>
       </c>
       <c r="F109" t="n">
-        <v>244.119</v>
+        <v>241.71</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>91.6241</v>
+        <v>90.7773</v>
       </c>
       <c r="C110" t="n">
-        <v>77.8989</v>
+        <v>78.3652</v>
       </c>
       <c r="D110" t="n">
-        <v>238.317</v>
+        <v>234.297</v>
       </c>
       <c r="E110" t="n">
-        <v>62.1977</v>
+        <v>72.53830000000001</v>
       </c>
       <c r="F110" t="n">
-        <v>244.635</v>
+        <v>241.111</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>90.6272</v>
+        <v>78.80549999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>76.1219</v>
+        <v>63.3858</v>
       </c>
       <c r="D111" t="n">
-        <v>236.9</v>
+        <v>233.748</v>
       </c>
       <c r="E111" t="n">
-        <v>69.895</v>
+        <v>69.9864</v>
       </c>
       <c r="F111" t="n">
-        <v>246.369</v>
+        <v>242.178</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>87.0887</v>
+        <v>86.5377</v>
       </c>
       <c r="C112" t="n">
-        <v>74.2666</v>
+        <v>74.14960000000001</v>
       </c>
       <c r="D112" t="n">
-        <v>238.712</v>
+        <v>232.573</v>
       </c>
       <c r="E112" t="n">
-        <v>59.2474</v>
+        <v>59.1073</v>
       </c>
       <c r="F112" t="n">
-        <v>246.43</v>
+        <v>243.82</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>85.4692</v>
+        <v>86.17610000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>72.0791</v>
+        <v>72.1388</v>
       </c>
       <c r="D113" t="n">
-        <v>236.635</v>
+        <v>234.263</v>
       </c>
       <c r="E113" t="n">
-        <v>57.4708</v>
+        <v>66.25620000000001</v>
       </c>
       <c r="F113" t="n">
-        <v>245.625</v>
+        <v>243.517</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.21599999999999</v>
+        <v>84.114</v>
       </c>
       <c r="C114" t="n">
-        <v>70.2906</v>
+        <v>70.3711</v>
       </c>
       <c r="D114" t="n">
-        <v>245.523</v>
+        <v>240.034</v>
       </c>
       <c r="E114" t="n">
-        <v>64.645</v>
+        <v>64.31010000000001</v>
       </c>
       <c r="F114" t="n">
-        <v>248.749</v>
+        <v>241.99</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>82.4148</v>
+        <v>82.12430000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>68.7804</v>
+        <v>68.6039</v>
       </c>
       <c r="D115" t="n">
-        <v>248.144</v>
+        <v>242.344</v>
       </c>
       <c r="E115" t="n">
-        <v>62.837</v>
+        <v>62.5368</v>
       </c>
       <c r="F115" t="n">
-        <v>248.331</v>
+        <v>243.527</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>81.6403</v>
+        <v>73.48399999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>67.3716</v>
+        <v>57.0817</v>
       </c>
       <c r="D116" t="n">
-        <v>242.121</v>
+        <v>244.634</v>
       </c>
       <c r="E116" t="n">
-        <v>61.6019</v>
+        <v>53.5843</v>
       </c>
       <c r="F116" t="n">
-        <v>245.854</v>
+        <v>243.733</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>81.0757</v>
+        <v>79.2483</v>
       </c>
       <c r="C117" t="n">
-        <v>65.4461</v>
+        <v>65.42700000000001</v>
       </c>
       <c r="D117" t="n">
-        <v>244.306</v>
+        <v>245.626</v>
       </c>
       <c r="E117" t="n">
-        <v>60.1397</v>
+        <v>59.559</v>
       </c>
       <c r="F117" t="n">
-        <v>247.861</v>
+        <v>243.894</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>77.6238</v>
+        <v>71.6191</v>
       </c>
       <c r="C118" t="n">
-        <v>64.2252</v>
+        <v>54.9759</v>
       </c>
       <c r="D118" t="n">
-        <v>234.92</v>
+        <v>231.644</v>
       </c>
       <c r="E118" t="n">
-        <v>51.7475</v>
+        <v>51.2651</v>
       </c>
       <c r="F118" t="n">
-        <v>246.563</v>
+        <v>223.574</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>71.91679999999999</v>
+        <v>76.3653</v>
       </c>
       <c r="C119" t="n">
-        <v>53.3194</v>
+        <v>62.5751</v>
       </c>
       <c r="D119" t="n">
-        <v>231.842</v>
+        <v>232.585</v>
       </c>
       <c r="E119" t="n">
-        <v>49.8381</v>
+        <v>50.2321</v>
       </c>
       <c r="F119" t="n">
-        <v>100.14</v>
+        <v>174.38</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>74.67270000000001</v>
+        <v>73.79600000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>60.5299</v>
+        <v>61.2428</v>
       </c>
       <c r="D120" t="n">
-        <v>233.265</v>
+        <v>233.862</v>
       </c>
       <c r="E120" t="n">
-        <v>49.0234</v>
+        <v>49.4648</v>
       </c>
       <c r="F120" t="n">
-        <v>173.989</v>
+        <v>99.9299</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>68.1397</v>
+        <v>69.26179999999999</v>
       </c>
       <c r="C121" t="n">
-        <v>51.402</v>
+        <v>52.5626</v>
       </c>
       <c r="D121" t="n">
-        <v>305.208</v>
+        <v>306.443</v>
       </c>
       <c r="E121" t="n">
-        <v>83.63809999999999</v>
+        <v>84.7517</v>
       </c>
       <c r="F121" t="n">
-        <v>290.903</v>
+        <v>292.719</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>70.8888</v>
+        <v>68.917</v>
       </c>
       <c r="C122" t="n">
-        <v>93.6049</v>
+        <v>87.4803</v>
       </c>
       <c r="D122" t="n">
-        <v>300.832</v>
+        <v>301.984</v>
       </c>
       <c r="E122" t="n">
-        <v>81.77760000000001</v>
+        <v>82.883</v>
       </c>
       <c r="F122" t="n">
-        <v>290.739</v>
+        <v>291.435</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>66.8057</v>
+        <v>71.5859</v>
       </c>
       <c r="C123" t="n">
-        <v>84.51819999999999</v>
+        <v>92.7821</v>
       </c>
       <c r="D123" t="n">
-        <v>296.885</v>
+        <v>298.123</v>
       </c>
       <c r="E123" t="n">
-        <v>80.0277</v>
+        <v>80.9027</v>
       </c>
       <c r="F123" t="n">
-        <v>289.795</v>
+        <v>290.624</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>96.2882</v>
+        <v>100.052</v>
       </c>
       <c r="C124" t="n">
-        <v>83.3995</v>
+        <v>84.8095</v>
       </c>
       <c r="D124" t="n">
-        <v>293.336</v>
+        <v>294.591</v>
       </c>
       <c r="E124" t="n">
-        <v>78.2043</v>
+        <v>79.2568</v>
       </c>
       <c r="F124" t="n">
-        <v>288.047</v>
+        <v>291.311</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>97.17529999999999</v>
+        <v>96.76179999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>81.804</v>
+        <v>83.2242</v>
       </c>
       <c r="D125" t="n">
-        <v>290.154</v>
+        <v>291.562</v>
       </c>
       <c r="E125" t="n">
-        <v>76.68980000000001</v>
+        <v>77.5902</v>
       </c>
       <c r="F125" t="n">
-        <v>289.026</v>
+        <v>289.966</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>95.2467</v>
+        <v>100.349</v>
       </c>
       <c r="C126" t="n">
-        <v>80.3356</v>
+        <v>87.5154</v>
       </c>
       <c r="D126" t="n">
-        <v>287.718</v>
+        <v>288.886</v>
       </c>
       <c r="E126" t="n">
-        <v>74.9376</v>
+        <v>75.95140000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>286.993</v>
+        <v>290.212</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>93.8167</v>
+        <v>94.55500000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>78.6682</v>
+        <v>80.1174</v>
       </c>
       <c r="D127" t="n">
-        <v>285.255</v>
+        <v>286.667</v>
       </c>
       <c r="E127" t="n">
-        <v>73.6129</v>
+        <v>74.4744</v>
       </c>
       <c r="F127" t="n">
-        <v>286.717</v>
+        <v>288.368</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>91.9539</v>
+        <v>92.0643</v>
       </c>
       <c r="C128" t="n">
-        <v>77.4423</v>
+        <v>78.7333</v>
       </c>
       <c r="D128" t="n">
-        <v>283.434</v>
+        <v>284.8</v>
       </c>
       <c r="E128" t="n">
-        <v>71.98569999999999</v>
+        <v>77.05880000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>287.303</v>
+        <v>288.253</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>94.36409999999999</v>
+        <v>92.10550000000001</v>
       </c>
       <c r="C129" t="n">
-        <v>81.2351</v>
+        <v>77.348</v>
       </c>
       <c r="D129" t="n">
-        <v>281.759</v>
+        <v>283.095</v>
       </c>
       <c r="E129" t="n">
-        <v>70.7795</v>
+        <v>71.58199999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>286.238</v>
+        <v>288.855</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>92.5425</v>
+        <v>90.6712</v>
       </c>
       <c r="C130" t="n">
-        <v>79.8152</v>
+        <v>75.9873</v>
       </c>
       <c r="D130" t="n">
-        <v>280.606</v>
+        <v>281.872</v>
       </c>
       <c r="E130" t="n">
-        <v>69.6216</v>
+        <v>70.3027</v>
       </c>
       <c r="F130" t="n">
-        <v>285.273</v>
+        <v>288.123</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>88.79170000000001</v>
+        <v>88.896</v>
       </c>
       <c r="C131" t="n">
-        <v>73.4997</v>
+        <v>74.8254</v>
       </c>
       <c r="D131" t="n">
-        <v>279.616</v>
+        <v>281.024</v>
       </c>
       <c r="E131" t="n">
-        <v>68.48990000000001</v>
+        <v>72.6079</v>
       </c>
       <c r="F131" t="n">
-        <v>285.406</v>
+        <v>287.258</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>89.5498</v>
+        <v>88.84269999999999</v>
       </c>
       <c r="C132" t="n">
-        <v>77.02979999999999</v>
+        <v>73.5938</v>
       </c>
       <c r="D132" t="n">
-        <v>279.021</v>
+        <v>280.606</v>
       </c>
       <c r="E132" t="n">
-        <v>67.2518</v>
+        <v>67.9893</v>
       </c>
       <c r="F132" t="n">
-        <v>285.251</v>
+        <v>287.919</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>85.9186</v>
+        <v>86.7454</v>
       </c>
       <c r="C133" t="n">
-        <v>71.4222</v>
+        <v>72.7204</v>
       </c>
       <c r="D133" t="n">
-        <v>278.859</v>
+        <v>280.37</v>
       </c>
       <c r="E133" t="n">
-        <v>66.2651</v>
+        <v>66.96639999999999</v>
       </c>
       <c r="F133" t="n">
-        <v>285.089</v>
+        <v>287.668</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>84.9825</v>
+        <v>86.398</v>
       </c>
       <c r="C134" t="n">
-        <v>70.45699999999999</v>
+        <v>71.73260000000001</v>
       </c>
       <c r="D134" t="n">
-        <v>274.551</v>
+        <v>276.469</v>
       </c>
       <c r="E134" t="n">
-        <v>59.3514</v>
+        <v>59.956</v>
       </c>
       <c r="F134" t="n">
-        <v>234.761</v>
+        <v>184.05</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>83.15009999999999</v>
+        <v>76.6645</v>
       </c>
       <c r="C135" t="n">
-        <v>69.4696</v>
+        <v>62.7807</v>
       </c>
       <c r="D135" t="n">
-        <v>350.252</v>
+        <v>351.528</v>
       </c>
       <c r="E135" t="n">
-        <v>94.66679999999999</v>
+        <v>95.6018</v>
       </c>
       <c r="F135" t="n">
-        <v>329.478</v>
+        <v>331.818</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>83.16459999999999</v>
+        <v>84.11069999999999</v>
       </c>
       <c r="C136" t="n">
-        <v>103.024</v>
+        <v>105.442</v>
       </c>
       <c r="D136" t="n">
-        <v>343.414</v>
+        <v>345.225</v>
       </c>
       <c r="E136" t="n">
-        <v>92.8642</v>
+        <v>93.63630000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>328.901</v>
+        <v>329.644</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>82.0279</v>
+        <v>83.0485</v>
       </c>
       <c r="C137" t="n">
-        <v>102.085</v>
+        <v>103.167</v>
       </c>
       <c r="D137" t="n">
-        <v>338.201</v>
+        <v>340.065</v>
       </c>
       <c r="E137" t="n">
-        <v>90.9259</v>
+        <v>92.0098</v>
       </c>
       <c r="F137" t="n">
-        <v>328.401</v>
+        <v>329.24</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>115.414</v>
+        <v>110.929</v>
       </c>
       <c r="C138" t="n">
-        <v>101.468</v>
+        <v>95.63590000000001</v>
       </c>
       <c r="D138" t="n">
-        <v>333.57</v>
+        <v>337.403</v>
       </c>
       <c r="E138" t="n">
-        <v>89.43980000000001</v>
+        <v>91.0044</v>
       </c>
       <c r="F138" t="n">
-        <v>326.173</v>
+        <v>337.377</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>106.442</v>
+        <v>111.792</v>
       </c>
       <c r="C139" t="n">
-        <v>93.25490000000001</v>
+        <v>95.9341</v>
       </c>
       <c r="D139" t="n">
-        <v>329.444</v>
+        <v>341.401</v>
       </c>
       <c r="E139" t="n">
-        <v>87.74509999999999</v>
+        <v>89.0551</v>
       </c>
       <c r="F139" t="n">
-        <v>325.685</v>
+        <v>336.033</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>108.535</v>
+        <v>109.552</v>
       </c>
       <c r="C140" t="n">
-        <v>92.0652</v>
+        <v>94.29340000000001</v>
       </c>
       <c r="D140" t="n">
-        <v>325.146</v>
+        <v>336.157</v>
       </c>
       <c r="E140" t="n">
-        <v>90.6545</v>
+        <v>87.60080000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>324.825</v>
+        <v>334.67</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>105.348</v>
+        <v>109.913</v>
       </c>
       <c r="C141" t="n">
-        <v>90.797</v>
+        <v>93.2111</v>
       </c>
       <c r="D141" t="n">
-        <v>323.464</v>
+        <v>333.368</v>
       </c>
       <c r="E141" t="n">
-        <v>84.703</v>
+        <v>85.9177</v>
       </c>
       <c r="F141" t="n">
-        <v>324.681</v>
+        <v>333.685</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>104.815</v>
+        <v>107.154</v>
       </c>
       <c r="C142" t="n">
-        <v>89.54649999999999</v>
+        <v>92.08150000000001</v>
       </c>
       <c r="D142" t="n">
-        <v>322.501</v>
+        <v>333.503</v>
       </c>
       <c r="E142" t="n">
-        <v>83.4662</v>
+        <v>84.96380000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>323.62</v>
+        <v>333.913</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>103.358</v>
+        <v>106.24</v>
       </c>
       <c r="C143" t="n">
-        <v>88.5763</v>
+        <v>91.0977</v>
       </c>
       <c r="D143" t="n">
-        <v>321.554</v>
+        <v>332.655</v>
       </c>
       <c r="E143" t="n">
-        <v>82.2366</v>
+        <v>83.61709999999999</v>
       </c>
       <c r="F143" t="n">
-        <v>322.002</v>
+        <v>332.598</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.0328</v>
+        <v>24.0529</v>
       </c>
       <c r="C2" t="n">
-        <v>20.2969</v>
+        <v>20.321</v>
       </c>
       <c r="D2" t="n">
-        <v>53.5667</v>
+        <v>53.6895</v>
       </c>
       <c r="E2" t="n">
-        <v>18.2169</v>
+        <v>18.3002</v>
       </c>
       <c r="F2" t="n">
-        <v>33.522</v>
+        <v>33.5724</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.4401</v>
+        <v>23.3372</v>
       </c>
       <c r="C3" t="n">
-        <v>19.7451</v>
+        <v>19.7975</v>
       </c>
       <c r="D3" t="n">
-        <v>52.9331</v>
+        <v>53.0876</v>
       </c>
       <c r="E3" t="n">
-        <v>17.6696</v>
+        <v>17.7905</v>
       </c>
       <c r="F3" t="n">
-        <v>33.0777</v>
+        <v>33.1088</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.7611</v>
+        <v>22.905</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2846</v>
+        <v>19.3956</v>
       </c>
       <c r="D4" t="n">
-        <v>52.3889</v>
+        <v>52.5352</v>
       </c>
       <c r="E4" t="n">
-        <v>17.615</v>
+        <v>17.1959</v>
       </c>
       <c r="F4" t="n">
-        <v>32.6718</v>
+        <v>32.763</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.2211</v>
+        <v>22.0268</v>
       </c>
       <c r="C5" t="n">
-        <v>18.8463</v>
+        <v>18.8436</v>
       </c>
       <c r="D5" t="n">
-        <v>52.0289</v>
+        <v>52.0602</v>
       </c>
       <c r="E5" t="n">
-        <v>17.1409</v>
+        <v>16.7999</v>
       </c>
       <c r="F5" t="n">
-        <v>32.402</v>
+        <v>32.4812</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>21.9959</v>
+        <v>22.073</v>
       </c>
       <c r="C6" t="n">
-        <v>18.3918</v>
+        <v>18.4797</v>
       </c>
       <c r="D6" t="n">
-        <v>51.5758</v>
+        <v>51.7065</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2925</v>
+        <v>16.3331</v>
       </c>
       <c r="F6" t="n">
-        <v>32.2972</v>
+        <v>32.3422</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.555</v>
+        <v>21.6823</v>
       </c>
       <c r="C7" t="n">
-        <v>18.1703</v>
+        <v>18.2791</v>
       </c>
       <c r="D7" t="n">
-        <v>65.7706</v>
+        <v>65.8935</v>
       </c>
       <c r="E7" t="n">
-        <v>25.4814</v>
+        <v>25.4837</v>
       </c>
       <c r="F7" t="n">
-        <v>40.579</v>
+        <v>40.8426</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.2862</v>
+        <v>21.4675</v>
       </c>
       <c r="C8" t="n">
-        <v>26.8603</v>
+        <v>26.9532</v>
       </c>
       <c r="D8" t="n">
-        <v>64.2745</v>
+        <v>64.4025</v>
       </c>
       <c r="E8" t="n">
-        <v>24.5618</v>
+        <v>25.2387</v>
       </c>
       <c r="F8" t="n">
-        <v>39.6937</v>
+        <v>39.8885</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.1869</v>
+        <v>21.6433</v>
       </c>
       <c r="C9" t="n">
-        <v>25.9761</v>
+        <v>26.041</v>
       </c>
       <c r="D9" t="n">
-        <v>62.8207</v>
+        <v>62.9974</v>
       </c>
       <c r="E9" t="n">
-        <v>23.6848</v>
+        <v>23.7363</v>
       </c>
       <c r="F9" t="n">
-        <v>38.827</v>
+        <v>39.1402</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>30.2007</v>
+        <v>30.0657</v>
       </c>
       <c r="C10" t="n">
-        <v>25.1221</v>
+        <v>25.2082</v>
       </c>
       <c r="D10" t="n">
-        <v>61.6257</v>
+        <v>61.743</v>
       </c>
       <c r="E10" t="n">
-        <v>22.8075</v>
+        <v>22.9578</v>
       </c>
       <c r="F10" t="n">
-        <v>38.0027</v>
+        <v>38.2031</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>28.7639</v>
+        <v>29.3701</v>
       </c>
       <c r="C11" t="n">
-        <v>24.3316</v>
+        <v>24.4414</v>
       </c>
       <c r="D11" t="n">
-        <v>60.5482</v>
+        <v>60.7824</v>
       </c>
       <c r="E11" t="n">
-        <v>22.4693</v>
+        <v>22.2944</v>
       </c>
       <c r="F11" t="n">
-        <v>37.2386</v>
+        <v>37.3584</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>28.4271</v>
+        <v>28.0391</v>
       </c>
       <c r="C12" t="n">
-        <v>23.4771</v>
+        <v>23.6873</v>
       </c>
       <c r="D12" t="n">
-        <v>59.4691</v>
+        <v>59.6184</v>
       </c>
       <c r="E12" t="n">
-        <v>21.3895</v>
+        <v>21.5248</v>
       </c>
       <c r="F12" t="n">
-        <v>36.4229</v>
+        <v>36.5907</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>27.605</v>
+        <v>27.8077</v>
       </c>
       <c r="C13" t="n">
-        <v>22.8534</v>
+        <v>22.9044</v>
       </c>
       <c r="D13" t="n">
-        <v>58.5887</v>
+        <v>58.7861</v>
       </c>
       <c r="E13" t="n">
-        <v>20.6328</v>
+        <v>21.3147</v>
       </c>
       <c r="F13" t="n">
-        <v>35.7406</v>
+        <v>35.9034</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>26.8164</v>
+        <v>27.2746</v>
       </c>
       <c r="C14" t="n">
-        <v>22.1094</v>
+        <v>22.2133</v>
       </c>
       <c r="D14" t="n">
-        <v>57.7943</v>
+        <v>58.0021</v>
       </c>
       <c r="E14" t="n">
-        <v>20.0227</v>
+        <v>20.193</v>
       </c>
       <c r="F14" t="n">
-        <v>35.1207</v>
+        <v>35.2832</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>26.0136</v>
+        <v>25.8694</v>
       </c>
       <c r="C15" t="n">
-        <v>21.4203</v>
+        <v>21.5713</v>
       </c>
       <c r="D15" t="n">
-        <v>56.9578</v>
+        <v>57.1419</v>
       </c>
       <c r="E15" t="n">
-        <v>19.3934</v>
+        <v>19.5748</v>
       </c>
       <c r="F15" t="n">
-        <v>34.5229</v>
+        <v>34.6686</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>25.4195</v>
+        <v>25.4248</v>
       </c>
       <c r="C16" t="n">
-        <v>20.8603</v>
+        <v>20.9311</v>
       </c>
       <c r="D16" t="n">
-        <v>56.4764</v>
+        <v>56.9231</v>
       </c>
       <c r="E16" t="n">
-        <v>18.8275</v>
+        <v>19.0715</v>
       </c>
       <c r="F16" t="n">
-        <v>33.9486</v>
+        <v>34.1152</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>24.5343</v>
+        <v>24.8164</v>
       </c>
       <c r="C17" t="n">
-        <v>20.2798</v>
+        <v>20.4061</v>
       </c>
       <c r="D17" t="n">
-        <v>55.9477</v>
+        <v>56.2927</v>
       </c>
       <c r="E17" t="n">
-        <v>18.2932</v>
+        <v>18.5208</v>
       </c>
       <c r="F17" t="n">
-        <v>33.4718</v>
+        <v>33.6322</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.5291</v>
+        <v>24.2601</v>
       </c>
       <c r="C18" t="n">
-        <v>19.7494</v>
+        <v>19.8694</v>
       </c>
       <c r="D18" t="n">
-        <v>55.0055</v>
+        <v>55.2803</v>
       </c>
       <c r="E18" t="n">
-        <v>17.8278</v>
+        <v>18.0674</v>
       </c>
       <c r="F18" t="n">
-        <v>33.0558</v>
+        <v>33.2027</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.6917</v>
+        <v>23.3605</v>
       </c>
       <c r="C19" t="n">
-        <v>19.2691</v>
+        <v>19.3894</v>
       </c>
       <c r="D19" t="n">
-        <v>54.4484</v>
+        <v>54.5846</v>
       </c>
       <c r="E19" t="n">
-        <v>17.4829</v>
+        <v>17.7056</v>
       </c>
       <c r="F19" t="n">
-        <v>32.6925</v>
+        <v>32.8948</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.46</v>
+        <v>23.1522</v>
       </c>
       <c r="C20" t="n">
-        <v>18.8423</v>
+        <v>18.9616</v>
       </c>
       <c r="D20" t="n">
-        <v>54.0108</v>
+        <v>54.2011</v>
       </c>
       <c r="E20" t="n">
-        <v>17.3661</v>
+        <v>17.4897</v>
       </c>
       <c r="F20" t="n">
-        <v>32.5076</v>
+        <v>32.629</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.7325</v>
+        <v>22.7679</v>
       </c>
       <c r="C21" t="n">
-        <v>18.5208</v>
+        <v>18.6414</v>
       </c>
       <c r="D21" t="n">
-        <v>71.1858</v>
+        <v>71.6844</v>
       </c>
       <c r="E21" t="n">
-        <v>26.566</v>
+        <v>26.6486</v>
       </c>
       <c r="F21" t="n">
-        <v>41.0188</v>
+        <v>41.2147</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.5452</v>
+        <v>22.6737</v>
       </c>
       <c r="C22" t="n">
-        <v>27.2185</v>
+        <v>27.409</v>
       </c>
       <c r="D22" t="n">
-        <v>69.66889999999999</v>
+        <v>70.1587</v>
       </c>
       <c r="E22" t="n">
-        <v>25.551</v>
+        <v>26.1559</v>
       </c>
       <c r="F22" t="n">
-        <v>40.1649</v>
+        <v>40.3338</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.4674</v>
+        <v>22.4969</v>
       </c>
       <c r="C23" t="n">
-        <v>26.3656</v>
+        <v>26.734</v>
       </c>
       <c r="D23" t="n">
-        <v>68.2586</v>
+        <v>68.7538</v>
       </c>
       <c r="E23" t="n">
-        <v>24.7287</v>
+        <v>24.9094</v>
       </c>
       <c r="F23" t="n">
-        <v>39.2806</v>
+        <v>39.5191</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>30.8921</v>
+        <v>31.1323</v>
       </c>
       <c r="C24" t="n">
-        <v>25.5604</v>
+        <v>25.8016</v>
       </c>
       <c r="D24" t="n">
-        <v>66.83710000000001</v>
+        <v>67.50409999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>23.871</v>
+        <v>24.1318</v>
       </c>
       <c r="F24" t="n">
-        <v>38.4697</v>
+        <v>38.6718</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>30.0075</v>
+        <v>29.827</v>
       </c>
       <c r="C25" t="n">
-        <v>24.7832</v>
+        <v>24.9345</v>
       </c>
       <c r="D25" t="n">
-        <v>65.57859999999999</v>
+        <v>66.1328</v>
       </c>
       <c r="E25" t="n">
-        <v>23.082</v>
+        <v>23.3466</v>
       </c>
       <c r="F25" t="n">
-        <v>37.6783</v>
+        <v>37.9158</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>29.0711</v>
+        <v>29.1566</v>
       </c>
       <c r="C26" t="n">
-        <v>23.999</v>
+        <v>24.2988</v>
       </c>
       <c r="D26" t="n">
-        <v>64.13590000000001</v>
+        <v>64.6403</v>
       </c>
       <c r="E26" t="n">
-        <v>22.3907</v>
+        <v>22.6077</v>
       </c>
       <c r="F26" t="n">
-        <v>36.8522</v>
+        <v>37.0663</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.6555</v>
+        <v>28.1304</v>
       </c>
       <c r="C27" t="n">
-        <v>23.2627</v>
+        <v>23.5215</v>
       </c>
       <c r="D27" t="n">
-        <v>63.1203</v>
+        <v>63.6788</v>
       </c>
       <c r="E27" t="n">
-        <v>21.7074</v>
+        <v>21.8831</v>
       </c>
       <c r="F27" t="n">
-        <v>36.1725</v>
+        <v>36.3813</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>27.3139</v>
+        <v>27.8702</v>
       </c>
       <c r="C28" t="n">
-        <v>22.6157</v>
+        <v>22.7483</v>
       </c>
       <c r="D28" t="n">
-        <v>62.2232</v>
+        <v>62.7867</v>
       </c>
       <c r="E28" t="n">
-        <v>21.0204</v>
+        <v>21.359</v>
       </c>
       <c r="F28" t="n">
-        <v>35.5506</v>
+        <v>35.7499</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>27.0744</v>
+        <v>26.6</v>
       </c>
       <c r="C29" t="n">
-        <v>21.915</v>
+        <v>22.1747</v>
       </c>
       <c r="D29" t="n">
-        <v>61.5084</v>
+        <v>62.085</v>
       </c>
       <c r="E29" t="n">
-        <v>20.3607</v>
+        <v>20.8095</v>
       </c>
       <c r="F29" t="n">
-        <v>34.9175</v>
+        <v>35.1934</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>26.3768</v>
+        <v>26.4086</v>
       </c>
       <c r="C30" t="n">
-        <v>21.3172</v>
+        <v>21.5055</v>
       </c>
       <c r="D30" t="n">
-        <v>60.5863</v>
+        <v>61.2119</v>
       </c>
       <c r="E30" t="n">
-        <v>20.2393</v>
+        <v>20.036</v>
       </c>
       <c r="F30" t="n">
-        <v>34.3652</v>
+        <v>34.643</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.2249</v>
+        <v>25.7206</v>
       </c>
       <c r="C31" t="n">
-        <v>20.7795</v>
+        <v>20.9235</v>
       </c>
       <c r="D31" t="n">
-        <v>60.0682</v>
+        <v>60.7107</v>
       </c>
       <c r="E31" t="n">
-        <v>19.4037</v>
+        <v>19.4859</v>
       </c>
       <c r="F31" t="n">
-        <v>33.844</v>
+        <v>34.0857</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.3452</v>
+        <v>25.8709</v>
       </c>
       <c r="C32" t="n">
-        <v>20.2726</v>
+        <v>20.4221</v>
       </c>
       <c r="D32" t="n">
-        <v>59.5861</v>
+        <v>60.2198</v>
       </c>
       <c r="E32" t="n">
-        <v>18.8507</v>
+        <v>19.0407</v>
       </c>
       <c r="F32" t="n">
-        <v>33.5662</v>
+        <v>33.6376</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>24.6225</v>
+        <v>24.8374</v>
       </c>
       <c r="C33" t="n">
-        <v>19.7737</v>
+        <v>19.9635</v>
       </c>
       <c r="D33" t="n">
-        <v>59.1393</v>
+        <v>59.8665</v>
       </c>
       <c r="E33" t="n">
-        <v>18.423</v>
+        <v>18.6173</v>
       </c>
       <c r="F33" t="n">
-        <v>33.2135</v>
+        <v>33.4361</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>24.3706</v>
+        <v>23.8986</v>
       </c>
       <c r="C34" t="n">
-        <v>19.3714</v>
+        <v>19.514</v>
       </c>
       <c r="D34" t="n">
-        <v>58.2573</v>
+        <v>58.9955</v>
       </c>
       <c r="E34" t="n">
-        <v>18.228</v>
+        <v>18.309</v>
       </c>
       <c r="F34" t="n">
-        <v>32.9307</v>
+        <v>33.1727</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.9001</v>
+        <v>23.4679</v>
       </c>
       <c r="C35" t="n">
-        <v>19.0482</v>
+        <v>19.1988</v>
       </c>
       <c r="D35" t="n">
-        <v>76.6164</v>
+        <v>77.48609999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>27.5741</v>
+        <v>27.5533</v>
       </c>
       <c r="F35" t="n">
-        <v>42.0166</v>
+        <v>42.2368</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.0636</v>
+        <v>23.0229</v>
       </c>
       <c r="C36" t="n">
-        <v>18.7558</v>
+        <v>18.9201</v>
       </c>
       <c r="D36" t="n">
-        <v>74.9162</v>
+        <v>75.55500000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>26.6103</v>
+        <v>27.0151</v>
       </c>
       <c r="F36" t="n">
-        <v>41.3295</v>
+        <v>41.3944</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>22.9154</v>
+        <v>23.5061</v>
       </c>
       <c r="C37" t="n">
-        <v>27.1279</v>
+        <v>27.2532</v>
       </c>
       <c r="D37" t="n">
-        <v>73.2988</v>
+        <v>74.0068</v>
       </c>
       <c r="E37" t="n">
-        <v>26.0245</v>
+        <v>26.158</v>
       </c>
       <c r="F37" t="n">
-        <v>40.4606</v>
+        <v>40.6019</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>31.4058</v>
+        <v>30.8975</v>
       </c>
       <c r="C38" t="n">
-        <v>26.2852</v>
+        <v>26.3613</v>
       </c>
       <c r="D38" t="n">
-        <v>71.7814</v>
+        <v>72.5471</v>
       </c>
       <c r="E38" t="n">
-        <v>24.9707</v>
+        <v>25.0661</v>
       </c>
       <c r="F38" t="n">
-        <v>39.8642</v>
+        <v>39.6768</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>30.3387</v>
+        <v>30.3813</v>
       </c>
       <c r="C39" t="n">
-        <v>25.5321</v>
+        <v>25.6256</v>
       </c>
       <c r="D39" t="n">
-        <v>70.4867</v>
+        <v>71.2214</v>
       </c>
       <c r="E39" t="n">
-        <v>24.178</v>
+        <v>24.2263</v>
       </c>
       <c r="F39" t="n">
-        <v>38.905</v>
+        <v>39.1259</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>30.0087</v>
+        <v>29.6507</v>
       </c>
       <c r="C40" t="n">
-        <v>24.8601</v>
+        <v>24.85</v>
       </c>
       <c r="D40" t="n">
-        <v>69.2625</v>
+        <v>69.93859999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>23.6734</v>
+        <v>23.6118</v>
       </c>
       <c r="F40" t="n">
-        <v>38.2749</v>
+        <v>38.4545</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>28.8647</v>
+        <v>28.7207</v>
       </c>
       <c r="C41" t="n">
-        <v>24.1568</v>
+        <v>24.1433</v>
       </c>
       <c r="D41" t="n">
-        <v>68.0586</v>
+        <v>68.7822</v>
       </c>
       <c r="E41" t="n">
-        <v>22.7037</v>
+        <v>22.792</v>
       </c>
       <c r="F41" t="n">
-        <v>37.5935</v>
+        <v>37.7769</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>28.1976</v>
+        <v>28.119</v>
       </c>
       <c r="C42" t="n">
-        <v>23.4691</v>
+        <v>23.4786</v>
       </c>
       <c r="D42" t="n">
-        <v>67.1374</v>
+        <v>67.8639</v>
       </c>
       <c r="E42" t="n">
-        <v>22.0059</v>
+        <v>22.3802</v>
       </c>
       <c r="F42" t="n">
-        <v>37.0167</v>
+        <v>37.1992</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>27.0088</v>
+        <v>27.2175</v>
       </c>
       <c r="C43" t="n">
-        <v>22.8168</v>
+        <v>22.8874</v>
       </c>
       <c r="D43" t="n">
-        <v>65.98260000000001</v>
+        <v>66.6947</v>
       </c>
       <c r="E43" t="n">
-        <v>21.4298</v>
+        <v>21.7797</v>
       </c>
       <c r="F43" t="n">
-        <v>36.4287</v>
+        <v>36.6243</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>26.4825</v>
+        <v>26.741</v>
       </c>
       <c r="C44" t="n">
-        <v>22.1612</v>
+        <v>22.2622</v>
       </c>
       <c r="D44" t="n">
-        <v>65.2242</v>
+        <v>65.8781</v>
       </c>
       <c r="E44" t="n">
-        <v>20.7767</v>
+        <v>20.9438</v>
       </c>
       <c r="F44" t="n">
-        <v>35.9133</v>
+        <v>36.0871</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>25.9471</v>
+        <v>26.4632</v>
       </c>
       <c r="C45" t="n">
-        <v>21.5703</v>
+        <v>21.6995</v>
       </c>
       <c r="D45" t="n">
-        <v>64.563</v>
+        <v>65.1819</v>
       </c>
       <c r="E45" t="n">
-        <v>20.2468</v>
+        <v>20.589</v>
       </c>
       <c r="F45" t="n">
-        <v>35.4705</v>
+        <v>35.6853</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>25.6698</v>
+        <v>25.4072</v>
       </c>
       <c r="C46" t="n">
-        <v>21.0739</v>
+        <v>21.1781</v>
       </c>
       <c r="D46" t="n">
-        <v>64.01479999999999</v>
+        <v>64.61150000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>19.8217</v>
+        <v>19.8903</v>
       </c>
       <c r="F46" t="n">
-        <v>35.0583</v>
+        <v>35.2944</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>24.6273</v>
+        <v>24.7932</v>
       </c>
       <c r="C47" t="n">
-        <v>20.7677</v>
+        <v>20.7653</v>
       </c>
       <c r="D47" t="n">
-        <v>63.5325</v>
+        <v>64.2213</v>
       </c>
       <c r="E47" t="n">
-        <v>19.3037</v>
+        <v>19.5578</v>
       </c>
       <c r="F47" t="n">
-        <v>34.7105</v>
+        <v>34.9455</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>24.2204</v>
+        <v>24.5752</v>
       </c>
       <c r="C48" t="n">
-        <v>20.1787</v>
+        <v>20.2706</v>
       </c>
       <c r="D48" t="n">
-        <v>62.8496</v>
+        <v>63.4561</v>
       </c>
       <c r="E48" t="n">
-        <v>18.9942</v>
+        <v>19.1649</v>
       </c>
       <c r="F48" t="n">
-        <v>34.4572</v>
+        <v>34.7289</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>23.9418</v>
+        <v>24.126</v>
       </c>
       <c r="C49" t="n">
-        <v>19.7772</v>
+        <v>19.9062</v>
       </c>
       <c r="D49" t="n">
-        <v>62.4766</v>
+        <v>63.1111</v>
       </c>
       <c r="E49" t="n">
-        <v>18.7048</v>
+        <v>18.8568</v>
       </c>
       <c r="F49" t="n">
-        <v>34.3225</v>
+        <v>34.5593</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>23.7193</v>
+        <v>24.047</v>
       </c>
       <c r="C50" t="n">
-        <v>19.7215</v>
+        <v>19.6743</v>
       </c>
       <c r="D50" t="n">
-        <v>79.8715</v>
+        <v>80.4452</v>
       </c>
       <c r="E50" t="n">
-        <v>27.7268</v>
+        <v>28.1442</v>
       </c>
       <c r="F50" t="n">
-        <v>43.7537</v>
+        <v>43.0949</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>24.5003</v>
+        <v>23.6465</v>
       </c>
       <c r="C51" t="n">
-        <v>28.0175</v>
+        <v>27.993</v>
       </c>
       <c r="D51" t="n">
-        <v>78.07510000000001</v>
+        <v>78.6217</v>
       </c>
       <c r="E51" t="n">
-        <v>27.0584</v>
+        <v>27.0625</v>
       </c>
       <c r="F51" t="n">
-        <v>42.3824</v>
+        <v>42.2992</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>23.7063</v>
+        <v>23.7441</v>
       </c>
       <c r="C52" t="n">
-        <v>27.1645</v>
+        <v>27.296</v>
       </c>
       <c r="D52" t="n">
-        <v>76.3797</v>
+        <v>76.92189999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>26.2453</v>
+        <v>26.1142</v>
       </c>
       <c r="F52" t="n">
-        <v>41.5024</v>
+        <v>41.6036</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>31.4661</v>
+        <v>31.8388</v>
       </c>
       <c r="C53" t="n">
-        <v>26.5125</v>
+        <v>26.4825</v>
       </c>
       <c r="D53" t="n">
-        <v>74.9033</v>
+        <v>75.37</v>
       </c>
       <c r="E53" t="n">
-        <v>25.3218</v>
+        <v>25.4687</v>
       </c>
       <c r="F53" t="n">
-        <v>40.8266</v>
+        <v>40.943</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>30.7233</v>
+        <v>31.232</v>
       </c>
       <c r="C54" t="n">
-        <v>25.7909</v>
+        <v>25.7636</v>
       </c>
       <c r="D54" t="n">
-        <v>73.4902</v>
+        <v>73.9618</v>
       </c>
       <c r="E54" t="n">
-        <v>24.5324</v>
+        <v>24.6801</v>
       </c>
       <c r="F54" t="n">
-        <v>40.1732</v>
+        <v>40.2273</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>30.1017</v>
+        <v>30.7119</v>
       </c>
       <c r="C55" t="n">
-        <v>25.1147</v>
+        <v>25.2167</v>
       </c>
       <c r="D55" t="n">
-        <v>72.348</v>
+        <v>72.8116</v>
       </c>
       <c r="E55" t="n">
-        <v>23.9404</v>
+        <v>24.0369</v>
       </c>
       <c r="F55" t="n">
-        <v>39.5809</v>
+        <v>39.6166</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>29.2157</v>
+        <v>30.3734</v>
       </c>
       <c r="C56" t="n">
-        <v>24.4203</v>
+        <v>24.5938</v>
       </c>
       <c r="D56" t="n">
-        <v>71.26260000000001</v>
+        <v>71.66759999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>23.1846</v>
+        <v>23.2698</v>
       </c>
       <c r="F56" t="n">
-        <v>39.032</v>
+        <v>39.0745</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>28.7565</v>
+        <v>29.2282</v>
       </c>
       <c r="C57" t="n">
-        <v>24.0072</v>
+        <v>23.9121</v>
       </c>
       <c r="D57" t="n">
-        <v>70.08369999999999</v>
+        <v>70.45010000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>22.4854</v>
+        <v>22.7807</v>
       </c>
       <c r="F57" t="n">
-        <v>38.4705</v>
+        <v>38.5621</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.5616</v>
+        <v>28.2621</v>
       </c>
       <c r="C58" t="n">
-        <v>23.253</v>
+        <v>23.2974</v>
       </c>
       <c r="D58" t="n">
-        <v>69.2448</v>
+        <v>69.63379999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>21.9336</v>
+        <v>22.2518</v>
       </c>
       <c r="F58" t="n">
-        <v>37.9939</v>
+        <v>38.031</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.7602</v>
+        <v>27.96</v>
       </c>
       <c r="C59" t="n">
-        <v>22.8387</v>
+        <v>22.7214</v>
       </c>
       <c r="D59" t="n">
-        <v>68.3642</v>
+        <v>68.7471</v>
       </c>
       <c r="E59" t="n">
-        <v>21.4483</v>
+        <v>21.421</v>
       </c>
       <c r="F59" t="n">
-        <v>37.6053</v>
+        <v>37.6349</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>26.9899</v>
+        <v>27.1893</v>
       </c>
       <c r="C60" t="n">
-        <v>22.3852</v>
+        <v>22.3832</v>
       </c>
       <c r="D60" t="n">
-        <v>67.79689999999999</v>
+        <v>68.1589</v>
       </c>
       <c r="E60" t="n">
-        <v>21.0421</v>
+        <v>21.0845</v>
       </c>
       <c r="F60" t="n">
-        <v>37.2147</v>
+        <v>37.3055</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.8184</v>
+        <v>26.9521</v>
       </c>
       <c r="C61" t="n">
-        <v>21.7557</v>
+        <v>21.9128</v>
       </c>
       <c r="D61" t="n">
-        <v>67.0235</v>
+        <v>67.40349999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>20.5947</v>
+        <v>20.8244</v>
       </c>
       <c r="F61" t="n">
-        <v>36.9167</v>
+        <v>37.0042</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>26.171</v>
+        <v>26.0947</v>
       </c>
       <c r="C62" t="n">
-        <v>21.3493</v>
+        <v>21.5528</v>
       </c>
       <c r="D62" t="n">
-        <v>66.386</v>
+        <v>66.7358</v>
       </c>
       <c r="E62" t="n">
-        <v>20.1115</v>
+        <v>20.5095</v>
       </c>
       <c r="F62" t="n">
-        <v>36.6956</v>
+        <v>36.7475</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>25.8415</v>
+        <v>25.7044</v>
       </c>
       <c r="C63" t="n">
-        <v>21.0337</v>
+        <v>21.0723</v>
       </c>
       <c r="D63" t="n">
-        <v>65.98399999999999</v>
+        <v>66.46080000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>20.0728</v>
+        <v>20.0006</v>
       </c>
       <c r="F63" t="n">
-        <v>36.5601</v>
+        <v>36.6794</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.505</v>
+        <v>25.7744</v>
       </c>
       <c r="C64" t="n">
-        <v>20.8282</v>
+        <v>20.841</v>
       </c>
       <c r="D64" t="n">
-        <v>87.30929999999999</v>
+        <v>88.3044</v>
       </c>
       <c r="E64" t="n">
-        <v>32.2756</v>
+        <v>33.1589</v>
       </c>
       <c r="F64" t="n">
-        <v>47.4864</v>
+        <v>47.7023</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.2572</v>
+        <v>25.7644</v>
       </c>
       <c r="C65" t="n">
-        <v>29.6912</v>
+        <v>29.7217</v>
       </c>
       <c r="D65" t="n">
-        <v>85.1439</v>
+        <v>85.8402</v>
       </c>
       <c r="E65" t="n">
-        <v>30.5143</v>
+        <v>32.4596</v>
       </c>
       <c r="F65" t="n">
-        <v>46.9766</v>
+        <v>47.2121</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.4286</v>
+        <v>25.3458</v>
       </c>
       <c r="C66" t="n">
-        <v>28.9975</v>
+        <v>29.162</v>
       </c>
       <c r="D66" t="n">
-        <v>83.3159</v>
+        <v>83.9735</v>
       </c>
       <c r="E66" t="n">
-        <v>30.9044</v>
+        <v>31.2426</v>
       </c>
       <c r="F66" t="n">
-        <v>46.2337</v>
+        <v>46.5261</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>40.3022</v>
+        <v>41.6424</v>
       </c>
       <c r="C67" t="n">
-        <v>28.4097</v>
+        <v>28.4984</v>
       </c>
       <c r="D67" t="n">
-        <v>81.5748</v>
+        <v>82.3395</v>
       </c>
       <c r="E67" t="n">
-        <v>29.659</v>
+        <v>30.66</v>
       </c>
       <c r="F67" t="n">
-        <v>45.7272</v>
+        <v>45.8545</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>38.092</v>
+        <v>40.2603</v>
       </c>
       <c r="C68" t="n">
-        <v>27.8535</v>
+        <v>27.8731</v>
       </c>
       <c r="D68" t="n">
-        <v>80.0616</v>
+        <v>80.8219</v>
       </c>
       <c r="E68" t="n">
-        <v>29.1669</v>
+        <v>29.9216</v>
       </c>
       <c r="F68" t="n">
-        <v>44.9639</v>
+        <v>45.3165</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>38.8663</v>
+        <v>38.0217</v>
       </c>
       <c r="C69" t="n">
-        <v>27.2899</v>
+        <v>27.369</v>
       </c>
       <c r="D69" t="n">
-        <v>78.6283</v>
+        <v>79.4264</v>
       </c>
       <c r="E69" t="n">
-        <v>28.1267</v>
+        <v>29.3065</v>
       </c>
       <c r="F69" t="n">
-        <v>44.2385</v>
+        <v>44.7067</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>37.3654</v>
+        <v>39.0582</v>
       </c>
       <c r="C70" t="n">
-        <v>26.7196</v>
+        <v>26.8754</v>
       </c>
       <c r="D70" t="n">
-        <v>77.5667</v>
+        <v>78.4264</v>
       </c>
       <c r="E70" t="n">
-        <v>27.8041</v>
+        <v>28.2423</v>
       </c>
       <c r="F70" t="n">
-        <v>43.7266</v>
+        <v>44.0058</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>38.3406</v>
+        <v>37.6909</v>
       </c>
       <c r="C71" t="n">
-        <v>26.2142</v>
+        <v>26.36</v>
       </c>
       <c r="D71" t="n">
-        <v>76.9354</v>
+        <v>77.6626</v>
       </c>
       <c r="E71" t="n">
-        <v>26.8171</v>
+        <v>27.6965</v>
       </c>
       <c r="F71" t="n">
-        <v>43.3597</v>
+        <v>43.6136</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>37.0268</v>
+        <v>36.7375</v>
       </c>
       <c r="C72" t="n">
-        <v>25.9843</v>
+        <v>25.8998</v>
       </c>
       <c r="D72" t="n">
-        <v>76.44710000000001</v>
+        <v>77.28570000000001</v>
       </c>
       <c r="E72" t="n">
-        <v>25.9861</v>
+        <v>26.8555</v>
       </c>
       <c r="F72" t="n">
-        <v>42.8402</v>
+        <v>43.1744</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>36.3382</v>
+        <v>36.6929</v>
       </c>
       <c r="C73" t="n">
-        <v>25.3606</v>
+        <v>25.435</v>
       </c>
       <c r="D73" t="n">
-        <v>76.24590000000001</v>
+        <v>76.8781</v>
       </c>
       <c r="E73" t="n">
-        <v>25.4605</v>
+        <v>26.4819</v>
       </c>
       <c r="F73" t="n">
-        <v>42.3767</v>
+        <v>42.6706</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>36.112</v>
+        <v>35.4706</v>
       </c>
       <c r="C74" t="n">
-        <v>24.9221</v>
+        <v>25.1306</v>
       </c>
       <c r="D74" t="n">
-        <v>75.6416</v>
+        <v>76.52500000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>25.3814</v>
+        <v>25.911</v>
       </c>
       <c r="F74" t="n">
-        <v>42.0435</v>
+        <v>42.339</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>34.7253</v>
+        <v>34.5702</v>
       </c>
       <c r="C75" t="n">
-        <v>24.5589</v>
+        <v>24.6851</v>
       </c>
       <c r="D75" t="n">
-        <v>75.1062</v>
+        <v>75.6309</v>
       </c>
       <c r="E75" t="n">
-        <v>24.2964</v>
+        <v>25.3337</v>
       </c>
       <c r="F75" t="n">
-        <v>41.7969</v>
+        <v>42.1244</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>33.4124</v>
+        <v>35.757</v>
       </c>
       <c r="C76" t="n">
-        <v>24.3452</v>
+        <v>24.2518</v>
       </c>
       <c r="D76" t="n">
-        <v>75.15949999999999</v>
+        <v>75.7153</v>
       </c>
       <c r="E76" t="n">
-        <v>23.7645</v>
+        <v>25.0091</v>
       </c>
       <c r="F76" t="n">
-        <v>41.4671</v>
+        <v>41.8683</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>33.6027</v>
+        <v>34.955</v>
       </c>
       <c r="C77" t="n">
-        <v>23.8133</v>
+        <v>23.8883</v>
       </c>
       <c r="D77" t="n">
-        <v>75.5844</v>
+        <v>75.9409</v>
       </c>
       <c r="E77" t="n">
-        <v>23.9077</v>
+        <v>24.6349</v>
       </c>
       <c r="F77" t="n">
-        <v>41.2141</v>
+        <v>41.8169</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>33.5978</v>
+        <v>34.6577</v>
       </c>
       <c r="C78" t="n">
-        <v>23.5364</v>
+        <v>23.6335</v>
       </c>
       <c r="D78" t="n">
-        <v>123.153</v>
+        <v>123.824</v>
       </c>
       <c r="E78" t="n">
-        <v>40.4153</v>
+        <v>41.8151</v>
       </c>
       <c r="F78" t="n">
-        <v>65.3477</v>
+        <v>65.96129999999999</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>37.1194</v>
+        <v>36.3732</v>
       </c>
       <c r="C79" t="n">
-        <v>33.0398</v>
+        <v>33.3916</v>
       </c>
       <c r="D79" t="n">
-        <v>120.874</v>
+        <v>122.034</v>
       </c>
       <c r="E79" t="n">
-        <v>39.6654</v>
+        <v>41.0913</v>
       </c>
       <c r="F79" t="n">
-        <v>65.5497</v>
+        <v>67.3712</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>35.8362</v>
+        <v>37.4756</v>
       </c>
       <c r="C80" t="n">
-        <v>32.8253</v>
+        <v>33.2321</v>
       </c>
       <c r="D80" t="n">
-        <v>119.076</v>
+        <v>120.365</v>
       </c>
       <c r="E80" t="n">
-        <v>38.8843</v>
+        <v>40.1168</v>
       </c>
       <c r="F80" t="n">
-        <v>65.44159999999999</v>
+        <v>66.0514</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>50.0019</v>
+        <v>51.6406</v>
       </c>
       <c r="C81" t="n">
-        <v>32.5232</v>
+        <v>32.9076</v>
       </c>
       <c r="D81" t="n">
-        <v>117.482</v>
+        <v>119.186</v>
       </c>
       <c r="E81" t="n">
-        <v>37.8531</v>
+        <v>39.4833</v>
       </c>
       <c r="F81" t="n">
-        <v>64.8706</v>
+        <v>65.5956</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>49.9658</v>
+        <v>51.0368</v>
       </c>
       <c r="C82" t="n">
-        <v>32.147</v>
+        <v>32.5012</v>
       </c>
       <c r="D82" t="n">
-        <v>116.121</v>
+        <v>117.888</v>
       </c>
       <c r="E82" t="n">
-        <v>36.9116</v>
+        <v>38.2609</v>
       </c>
       <c r="F82" t="n">
-        <v>64.0031</v>
+        <v>65.1622</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>49.0894</v>
+        <v>49.9467</v>
       </c>
       <c r="C83" t="n">
-        <v>31.8411</v>
+        <v>32.1129</v>
       </c>
       <c r="D83" t="n">
-        <v>115.185</v>
+        <v>116.517</v>
       </c>
       <c r="E83" t="n">
-        <v>36.0088</v>
+        <v>37.2332</v>
       </c>
       <c r="F83" t="n">
-        <v>63.2509</v>
+        <v>64.3582</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>48.7549</v>
+        <v>47.1408</v>
       </c>
       <c r="C84" t="n">
-        <v>31.4558</v>
+        <v>31.7827</v>
       </c>
       <c r="D84" t="n">
-        <v>114.837</v>
+        <v>115.867</v>
       </c>
       <c r="E84" t="n">
-        <v>35.0642</v>
+        <v>36.3875</v>
       </c>
       <c r="F84" t="n">
-        <v>62.2233</v>
+        <v>63.1381</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>41.9847</v>
+        <v>48.8955</v>
       </c>
       <c r="C85" t="n">
-        <v>31.2849</v>
+        <v>31.4135</v>
       </c>
       <c r="D85" t="n">
-        <v>114.664</v>
+        <v>115.928</v>
       </c>
       <c r="E85" t="n">
-        <v>34.2178</v>
+        <v>35.3313</v>
       </c>
       <c r="F85" t="n">
-        <v>61.4038</v>
+        <v>62.3366</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>48.103</v>
+        <v>44.4444</v>
       </c>
       <c r="C86" t="n">
-        <v>30.805</v>
+        <v>31.1595</v>
       </c>
       <c r="D86" t="n">
-        <v>114.904</v>
+        <v>116.004</v>
       </c>
       <c r="E86" t="n">
-        <v>33.3343</v>
+        <v>34.4253</v>
       </c>
       <c r="F86" t="n">
-        <v>60.389</v>
+        <v>61.402</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>44.4999</v>
+        <v>48.3134</v>
       </c>
       <c r="C87" t="n">
-        <v>30.3529</v>
+        <v>30.7574</v>
       </c>
       <c r="D87" t="n">
-        <v>115.086</v>
+        <v>116.227</v>
       </c>
       <c r="E87" t="n">
-        <v>32.4998</v>
+        <v>33.8076</v>
       </c>
       <c r="F87" t="n">
-        <v>59.6778</v>
+        <v>60.5592</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>46.0386</v>
+        <v>47.0868</v>
       </c>
       <c r="C88" t="n">
-        <v>30.2255</v>
+        <v>30.4484</v>
       </c>
       <c r="D88" t="n">
-        <v>115.754</v>
+        <v>116.902</v>
       </c>
       <c r="E88" t="n">
-        <v>31.8009</v>
+        <v>32.9878</v>
       </c>
       <c r="F88" t="n">
-        <v>58.8358</v>
+        <v>59.5286</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>45.9085</v>
+        <v>46.2971</v>
       </c>
       <c r="C89" t="n">
-        <v>29.8082</v>
+        <v>30.0945</v>
       </c>
       <c r="D89" t="n">
-        <v>115.825</v>
+        <v>117.17</v>
       </c>
       <c r="E89" t="n">
-        <v>31.0746</v>
+        <v>32.2501</v>
       </c>
       <c r="F89" t="n">
-        <v>57.6238</v>
+        <v>58.8324</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>44.9332</v>
+        <v>42.4865</v>
       </c>
       <c r="C90" t="n">
-        <v>29.5174</v>
+        <v>29.8516</v>
       </c>
       <c r="D90" t="n">
-        <v>116.962</v>
+        <v>117.88</v>
       </c>
       <c r="E90" t="n">
-        <v>30.7172</v>
+        <v>31.5306</v>
       </c>
       <c r="F90" t="n">
-        <v>57.1831</v>
+        <v>58.475</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>42.2721</v>
+        <v>42.6712</v>
       </c>
       <c r="C91" t="n">
-        <v>29.3731</v>
+        <v>29.4766</v>
       </c>
       <c r="D91" t="n">
-        <v>119.272</v>
+        <v>119.58</v>
       </c>
       <c r="E91" t="n">
-        <v>30.1187</v>
+        <v>31.0283</v>
       </c>
       <c r="F91" t="n">
-        <v>57.5937</v>
+        <v>58.065</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>41.4039</v>
+        <v>42.9876</v>
       </c>
       <c r="C92" t="n">
-        <v>28.9508</v>
+        <v>29.165</v>
       </c>
       <c r="D92" t="n">
-        <v>177.602</v>
+        <v>179.525</v>
       </c>
       <c r="E92" t="n">
-        <v>64.26949999999999</v>
+        <v>64.8176</v>
       </c>
       <c r="F92" t="n">
-        <v>89.6392</v>
+        <v>90.99760000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>41.6891</v>
+        <v>46.5192</v>
       </c>
       <c r="C93" t="n">
-        <v>28.7836</v>
+        <v>29.1453</v>
       </c>
       <c r="D93" t="n">
-        <v>176.423</v>
+        <v>178.867</v>
       </c>
       <c r="E93" t="n">
-        <v>63.1481</v>
+        <v>63.3196</v>
       </c>
       <c r="F93" t="n">
-        <v>90.8614</v>
+        <v>91.06189999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>45.037</v>
+        <v>45.9819</v>
       </c>
       <c r="C94" t="n">
-        <v>62.0875</v>
+        <v>61.8781</v>
       </c>
       <c r="D94" t="n">
-        <v>175.438</v>
+        <v>177.979</v>
       </c>
       <c r="E94" t="n">
-        <v>61.2231</v>
+        <v>61.7618</v>
       </c>
       <c r="F94" t="n">
-        <v>90.1478</v>
+        <v>88.0025</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>78.501</v>
+        <v>74.6216</v>
       </c>
       <c r="C95" t="n">
-        <v>60.9268</v>
+        <v>60.6017</v>
       </c>
       <c r="D95" t="n">
-        <v>174.489</v>
+        <v>177.248</v>
       </c>
       <c r="E95" t="n">
-        <v>59.4621</v>
+        <v>59.8701</v>
       </c>
       <c r="F95" t="n">
-        <v>89.0277</v>
+        <v>87.6027</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>75.36199999999999</v>
+        <v>75.25700000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>59.4151</v>
+        <v>59.3946</v>
       </c>
       <c r="D96" t="n">
-        <v>173.439</v>
+        <v>176.282</v>
       </c>
       <c r="E96" t="n">
-        <v>57.7446</v>
+        <v>58.2925</v>
       </c>
       <c r="F96" t="n">
-        <v>87.3272</v>
+        <v>88.2878</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>73.1872</v>
+        <v>72.5916</v>
       </c>
       <c r="C97" t="n">
-        <v>57.8464</v>
+        <v>58.017</v>
       </c>
       <c r="D97" t="n">
-        <v>173.084</v>
+        <v>175.771</v>
       </c>
       <c r="E97" t="n">
-        <v>55.8822</v>
+        <v>56.4107</v>
       </c>
       <c r="F97" t="n">
-        <v>85.5736</v>
+        <v>87.2495</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>67.6579</v>
+        <v>73.8026</v>
       </c>
       <c r="C98" t="n">
-        <v>56.5946</v>
+        <v>56.6079</v>
       </c>
       <c r="D98" t="n">
-        <v>172.801</v>
+        <v>175.578</v>
       </c>
       <c r="E98" t="n">
-        <v>54.0618</v>
+        <v>54.6623</v>
       </c>
       <c r="F98" t="n">
-        <v>83.946</v>
+        <v>85.96899999999999</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>71.5675</v>
+        <v>69.3078</v>
       </c>
       <c r="C99" t="n">
-        <v>55.1974</v>
+        <v>55.2677</v>
       </c>
       <c r="D99" t="n">
-        <v>172.992</v>
+        <v>175.945</v>
       </c>
       <c r="E99" t="n">
-        <v>52.7147</v>
+        <v>53.1924</v>
       </c>
       <c r="F99" t="n">
-        <v>84.679</v>
+        <v>87.2084</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>68.25279999999999</v>
+        <v>68.4405</v>
       </c>
       <c r="C100" t="n">
-        <v>53.9512</v>
+        <v>54.0105</v>
       </c>
       <c r="D100" t="n">
-        <v>173.436</v>
+        <v>176.122</v>
       </c>
       <c r="E100" t="n">
-        <v>51.1797</v>
+        <v>51.5682</v>
       </c>
       <c r="F100" t="n">
-        <v>81.7315</v>
+        <v>84.2873</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.349</v>
+        <v>67.0984</v>
       </c>
       <c r="C101" t="n">
-        <v>52.6429</v>
+        <v>52.7243</v>
       </c>
       <c r="D101" t="n">
-        <v>173.495</v>
+        <v>176.481</v>
       </c>
       <c r="E101" t="n">
-        <v>49.6478</v>
+        <v>50.2269</v>
       </c>
       <c r="F101" t="n">
-        <v>85.1572</v>
+        <v>83.3712</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>67.27800000000001</v>
+        <v>67.08410000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>51.5837</v>
+        <v>51.7428</v>
       </c>
       <c r="D102" t="n">
-        <v>174.52</v>
+        <v>177.472</v>
       </c>
       <c r="E102" t="n">
-        <v>48.2655</v>
+        <v>48.7857</v>
       </c>
       <c r="F102" t="n">
-        <v>80.6007</v>
+        <v>82.32550000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>65.8516</v>
+        <v>66.12390000000001</v>
       </c>
       <c r="C103" t="n">
-        <v>50.5294</v>
+        <v>50.6951</v>
       </c>
       <c r="D103" t="n">
-        <v>175.88</v>
+        <v>178.999</v>
       </c>
       <c r="E103" t="n">
-        <v>47.146</v>
+        <v>47.3797</v>
       </c>
       <c r="F103" t="n">
-        <v>80.2064</v>
+        <v>82.47239999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>64.3441</v>
+        <v>65.2392</v>
       </c>
       <c r="C104" t="n">
-        <v>49.4764</v>
+        <v>49.6667</v>
       </c>
       <c r="D104" t="n">
-        <v>177.141</v>
+        <v>180.264</v>
       </c>
       <c r="E104" t="n">
-        <v>45.8672</v>
+        <v>46.3622</v>
       </c>
       <c r="F104" t="n">
-        <v>78.7829</v>
+        <v>81.1341</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>63.2301</v>
+        <v>64.3266</v>
       </c>
       <c r="C105" t="n">
-        <v>48.6222</v>
+        <v>48.7274</v>
       </c>
       <c r="D105" t="n">
-        <v>178.664</v>
+        <v>181.626</v>
       </c>
       <c r="E105" t="n">
-        <v>44.8476</v>
+        <v>45.2772</v>
       </c>
       <c r="F105" t="n">
-        <v>78.5202</v>
+        <v>90.3129</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>62.7343</v>
+        <v>65.4653</v>
       </c>
       <c r="C106" t="n">
-        <v>47.7337</v>
+        <v>47.8636</v>
       </c>
       <c r="D106" t="n">
-        <v>180.897</v>
+        <v>184.357</v>
       </c>
       <c r="E106" t="n">
-        <v>43.9253</v>
+        <v>44.3796</v>
       </c>
       <c r="F106" t="n">
-        <v>78.13420000000001</v>
+        <v>90.3719</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>60.8799</v>
+        <v>61.1548</v>
       </c>
       <c r="C107" t="n">
-        <v>46.9071</v>
+        <v>47.1687</v>
       </c>
       <c r="D107" t="n">
-        <v>241.547</v>
+        <v>247.544</v>
       </c>
       <c r="E107" t="n">
-        <v>78.59180000000001</v>
+        <v>78.8974</v>
       </c>
       <c r="F107" t="n">
-        <v>241.864</v>
+        <v>244.494</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>61.1168</v>
+        <v>60.4598</v>
       </c>
       <c r="C108" t="n">
-        <v>81.7547</v>
+        <v>81.58320000000001</v>
       </c>
       <c r="D108" t="n">
-        <v>238.972</v>
+        <v>244.834</v>
       </c>
       <c r="E108" t="n">
-        <v>76.8673</v>
+        <v>76.8295</v>
       </c>
       <c r="F108" t="n">
-        <v>241.009</v>
+        <v>245.934</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>57.5658</v>
+        <v>55.9517</v>
       </c>
       <c r="C109" t="n">
-        <v>79.8257</v>
+        <v>66.4229</v>
       </c>
       <c r="D109" t="n">
-        <v>236.794</v>
+        <v>242.41</v>
       </c>
       <c r="E109" t="n">
-        <v>74.5609</v>
+        <v>74.6183</v>
       </c>
       <c r="F109" t="n">
-        <v>241.71</v>
+        <v>245.813</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>90.7773</v>
+        <v>92.6544</v>
       </c>
       <c r="C110" t="n">
-        <v>78.3652</v>
+        <v>78.33629999999999</v>
       </c>
       <c r="D110" t="n">
-        <v>234.297</v>
+        <v>241.141</v>
       </c>
       <c r="E110" t="n">
-        <v>72.53830000000001</v>
+        <v>63.0675</v>
       </c>
       <c r="F110" t="n">
-        <v>241.111</v>
+        <v>246.251</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>78.80549999999999</v>
+        <v>91.1985</v>
       </c>
       <c r="C111" t="n">
-        <v>63.3858</v>
+        <v>76.3158</v>
       </c>
       <c r="D111" t="n">
-        <v>233.748</v>
+        <v>239.37</v>
       </c>
       <c r="E111" t="n">
-        <v>69.9864</v>
+        <v>70.3489</v>
       </c>
       <c r="F111" t="n">
-        <v>242.178</v>
+        <v>245.712</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>86.5377</v>
+        <v>87.6327</v>
       </c>
       <c r="C112" t="n">
-        <v>74.14960000000001</v>
+        <v>74.29430000000001</v>
       </c>
       <c r="D112" t="n">
-        <v>232.573</v>
+        <v>240.503</v>
       </c>
       <c r="E112" t="n">
-        <v>59.1073</v>
+        <v>59.5007</v>
       </c>
       <c r="F112" t="n">
-        <v>243.82</v>
+        <v>246.64</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>86.17610000000001</v>
+        <v>85.6814</v>
       </c>
       <c r="C113" t="n">
-        <v>72.1388</v>
+        <v>72.3763</v>
       </c>
       <c r="D113" t="n">
-        <v>234.263</v>
+        <v>237.594</v>
       </c>
       <c r="E113" t="n">
-        <v>66.25620000000001</v>
+        <v>57.9761</v>
       </c>
       <c r="F113" t="n">
-        <v>243.517</v>
+        <v>246.981</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.114</v>
+        <v>84.559</v>
       </c>
       <c r="C114" t="n">
-        <v>70.3711</v>
+        <v>70.693</v>
       </c>
       <c r="D114" t="n">
-        <v>240.034</v>
+        <v>248.603</v>
       </c>
       <c r="E114" t="n">
-        <v>64.31010000000001</v>
+        <v>64.5372</v>
       </c>
       <c r="F114" t="n">
-        <v>241.99</v>
+        <v>247.352</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>82.12430000000001</v>
+        <v>83.1956</v>
       </c>
       <c r="C115" t="n">
-        <v>68.6039</v>
+        <v>68.8305</v>
       </c>
       <c r="D115" t="n">
-        <v>242.344</v>
+        <v>250.966</v>
       </c>
       <c r="E115" t="n">
-        <v>62.5368</v>
+        <v>62.932</v>
       </c>
       <c r="F115" t="n">
-        <v>243.527</v>
+        <v>248.699</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>73.48399999999999</v>
+        <v>82.3165</v>
       </c>
       <c r="C116" t="n">
-        <v>57.0817</v>
+        <v>67.4213</v>
       </c>
       <c r="D116" t="n">
-        <v>244.634</v>
+        <v>244.151</v>
       </c>
       <c r="E116" t="n">
-        <v>53.5843</v>
+        <v>61.305</v>
       </c>
       <c r="F116" t="n">
-        <v>243.733</v>
+        <v>248.182</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>79.2483</v>
+        <v>80.41849999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>65.42700000000001</v>
+        <v>65.8571</v>
       </c>
       <c r="D117" t="n">
-        <v>245.626</v>
+        <v>247.804</v>
       </c>
       <c r="E117" t="n">
-        <v>59.559</v>
+        <v>59.6619</v>
       </c>
       <c r="F117" t="n">
-        <v>243.894</v>
+        <v>249.459</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>71.6191</v>
+        <v>77.9872</v>
       </c>
       <c r="C118" t="n">
-        <v>54.9759</v>
+        <v>64.4023</v>
       </c>
       <c r="D118" t="n">
-        <v>231.644</v>
+        <v>237.349</v>
       </c>
       <c r="E118" t="n">
-        <v>51.2651</v>
+        <v>51.6532</v>
       </c>
       <c r="F118" t="n">
-        <v>223.574</v>
+        <v>249.916</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>76.3653</v>
+        <v>73.69370000000001</v>
       </c>
       <c r="C119" t="n">
-        <v>62.5751</v>
+        <v>54.7361</v>
       </c>
       <c r="D119" t="n">
-        <v>232.585</v>
+        <v>238.892</v>
       </c>
       <c r="E119" t="n">
-        <v>50.2321</v>
+        <v>50.8521</v>
       </c>
       <c r="F119" t="n">
-        <v>174.38</v>
+        <v>103.008</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>73.79600000000001</v>
+        <v>76.25360000000001</v>
       </c>
       <c r="C120" t="n">
-        <v>61.2428</v>
+        <v>61.9129</v>
       </c>
       <c r="D120" t="n">
-        <v>233.862</v>
+        <v>239.718</v>
       </c>
       <c r="E120" t="n">
-        <v>49.4648</v>
+        <v>49.9706</v>
       </c>
       <c r="F120" t="n">
-        <v>99.9299</v>
+        <v>179.392</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>69.26179999999999</v>
+        <v>70.1507</v>
       </c>
       <c r="C121" t="n">
-        <v>52.5626</v>
+        <v>53.1645</v>
       </c>
       <c r="D121" t="n">
-        <v>306.443</v>
+        <v>314.252</v>
       </c>
       <c r="E121" t="n">
-        <v>84.7517</v>
+        <v>84.9743</v>
       </c>
       <c r="F121" t="n">
-        <v>292.719</v>
+        <v>298.234</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>68.917</v>
+        <v>72.5067</v>
       </c>
       <c r="C122" t="n">
-        <v>87.4803</v>
+        <v>95.0613</v>
       </c>
       <c r="D122" t="n">
-        <v>301.984</v>
+        <v>309.508</v>
       </c>
       <c r="E122" t="n">
-        <v>82.883</v>
+        <v>83.1982</v>
       </c>
       <c r="F122" t="n">
-        <v>291.435</v>
+        <v>297.628</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>71.5859</v>
+        <v>68.3331</v>
       </c>
       <c r="C123" t="n">
-        <v>92.7821</v>
+        <v>86.03570000000001</v>
       </c>
       <c r="D123" t="n">
-        <v>298.123</v>
+        <v>305.28</v>
       </c>
       <c r="E123" t="n">
-        <v>80.9027</v>
+        <v>81.2197</v>
       </c>
       <c r="F123" t="n">
-        <v>290.624</v>
+        <v>297.708</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>100.052</v>
+        <v>98.0711</v>
       </c>
       <c r="C124" t="n">
-        <v>84.8095</v>
+        <v>85.2679</v>
       </c>
       <c r="D124" t="n">
-        <v>294.591</v>
+        <v>301.793</v>
       </c>
       <c r="E124" t="n">
-        <v>79.2568</v>
+        <v>79.3184</v>
       </c>
       <c r="F124" t="n">
-        <v>291.311</v>
+        <v>296.497</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>96.76179999999999</v>
+        <v>99.2559</v>
       </c>
       <c r="C125" t="n">
-        <v>83.2242</v>
+        <v>83.6831</v>
       </c>
       <c r="D125" t="n">
-        <v>291.562</v>
+        <v>298.583</v>
       </c>
       <c r="E125" t="n">
-        <v>77.5902</v>
+        <v>77.74809999999999</v>
       </c>
       <c r="F125" t="n">
-        <v>289.966</v>
+        <v>296.296</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>100.349</v>
+        <v>97.24809999999999</v>
       </c>
       <c r="C126" t="n">
-        <v>87.5154</v>
+        <v>82.1644</v>
       </c>
       <c r="D126" t="n">
-        <v>288.886</v>
+        <v>295.791</v>
       </c>
       <c r="E126" t="n">
-        <v>75.95140000000001</v>
+        <v>76.1153</v>
       </c>
       <c r="F126" t="n">
-        <v>290.212</v>
+        <v>294.948</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>94.55500000000001</v>
+        <v>95.7396</v>
       </c>
       <c r="C127" t="n">
-        <v>80.1174</v>
+        <v>80.91</v>
       </c>
       <c r="D127" t="n">
-        <v>286.667</v>
+        <v>293.477</v>
       </c>
       <c r="E127" t="n">
-        <v>74.4744</v>
+        <v>74.5099</v>
       </c>
       <c r="F127" t="n">
-        <v>288.368</v>
+        <v>294.68</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>92.0643</v>
+        <v>93.80070000000001</v>
       </c>
       <c r="C128" t="n">
-        <v>78.7333</v>
+        <v>79.4811</v>
       </c>
       <c r="D128" t="n">
-        <v>284.8</v>
+        <v>291.629</v>
       </c>
       <c r="E128" t="n">
-        <v>77.05880000000001</v>
+        <v>73.12990000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>288.253</v>
+        <v>294.513</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>92.10550000000001</v>
+        <v>96.2199</v>
       </c>
       <c r="C129" t="n">
-        <v>77.348</v>
+        <v>83.3766</v>
       </c>
       <c r="D129" t="n">
-        <v>283.095</v>
+        <v>289.907</v>
       </c>
       <c r="E129" t="n">
-        <v>71.58199999999999</v>
+        <v>72.018</v>
       </c>
       <c r="F129" t="n">
-        <v>288.855</v>
+        <v>294.539</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>90.6712</v>
+        <v>94.3948</v>
       </c>
       <c r="C130" t="n">
-        <v>75.9873</v>
+        <v>82.0094</v>
       </c>
       <c r="D130" t="n">
-        <v>281.872</v>
+        <v>288.998</v>
       </c>
       <c r="E130" t="n">
-        <v>70.3027</v>
+        <v>70.7509</v>
       </c>
       <c r="F130" t="n">
-        <v>288.123</v>
+        <v>293.709</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>88.896</v>
+        <v>90.84439999999999</v>
       </c>
       <c r="C131" t="n">
-        <v>74.8254</v>
+        <v>75.946</v>
       </c>
       <c r="D131" t="n">
-        <v>281.024</v>
+        <v>287.767</v>
       </c>
       <c r="E131" t="n">
-        <v>72.6079</v>
+        <v>69.62309999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>287.258</v>
+        <v>293.433</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>88.84269999999999</v>
+        <v>91.41630000000001</v>
       </c>
       <c r="C132" t="n">
-        <v>73.5938</v>
+        <v>79.2762</v>
       </c>
       <c r="D132" t="n">
-        <v>280.606</v>
+        <v>287.152</v>
       </c>
       <c r="E132" t="n">
-        <v>67.9893</v>
+        <v>68.4718</v>
       </c>
       <c r="F132" t="n">
-        <v>287.919</v>
+        <v>293.319</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>86.7454</v>
+        <v>88.27979999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>72.7204</v>
+        <v>73.9297</v>
       </c>
       <c r="D133" t="n">
-        <v>280.37</v>
+        <v>287.26</v>
       </c>
       <c r="E133" t="n">
-        <v>66.96639999999999</v>
+        <v>67.4044</v>
       </c>
       <c r="F133" t="n">
-        <v>287.668</v>
+        <v>293.622</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>86.398</v>
+        <v>86.9242</v>
       </c>
       <c r="C134" t="n">
-        <v>71.73260000000001</v>
+        <v>72.8811</v>
       </c>
       <c r="D134" t="n">
-        <v>276.469</v>
+        <v>282.346</v>
       </c>
       <c r="E134" t="n">
-        <v>59.956</v>
+        <v>60.7783</v>
       </c>
       <c r="F134" t="n">
-        <v>184.05</v>
+        <v>241.901</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>76.6645</v>
+        <v>85.2966</v>
       </c>
       <c r="C135" t="n">
-        <v>62.7807</v>
+        <v>72.16419999999999</v>
       </c>
       <c r="D135" t="n">
-        <v>351.528</v>
+        <v>360.912</v>
       </c>
       <c r="E135" t="n">
-        <v>95.6018</v>
+        <v>95.5425</v>
       </c>
       <c r="F135" t="n">
-        <v>331.818</v>
+        <v>338.837</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>84.11069999999999</v>
+        <v>85.5625</v>
       </c>
       <c r="C136" t="n">
-        <v>105.442</v>
+        <v>106.415</v>
       </c>
       <c r="D136" t="n">
-        <v>345.225</v>
+        <v>353.642</v>
       </c>
       <c r="E136" t="n">
-        <v>93.63630000000001</v>
+        <v>93.6028</v>
       </c>
       <c r="F136" t="n">
-        <v>329.644</v>
+        <v>338.582</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>83.0485</v>
+        <v>84.6067</v>
       </c>
       <c r="C137" t="n">
-        <v>103.167</v>
+        <v>104.232</v>
       </c>
       <c r="D137" t="n">
-        <v>340.065</v>
+        <v>348.8</v>
       </c>
       <c r="E137" t="n">
-        <v>92.0098</v>
+        <v>92.45399999999999</v>
       </c>
       <c r="F137" t="n">
-        <v>329.24</v>
+        <v>338.459</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>110.929</v>
+        <v>118.015</v>
       </c>
       <c r="C138" t="n">
-        <v>95.63590000000001</v>
+        <v>104.106</v>
       </c>
       <c r="D138" t="n">
-        <v>337.403</v>
+        <v>343.9</v>
       </c>
       <c r="E138" t="n">
-        <v>91.0044</v>
+        <v>90.83329999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>337.377</v>
+        <v>335.896</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>111.792</v>
+        <v>109.531</v>
       </c>
       <c r="C139" t="n">
-        <v>95.9341</v>
+        <v>95.6045</v>
       </c>
       <c r="D139" t="n">
-        <v>341.401</v>
+        <v>340.089</v>
       </c>
       <c r="E139" t="n">
-        <v>89.0551</v>
+        <v>89.105</v>
       </c>
       <c r="F139" t="n">
-        <v>336.033</v>
+        <v>335.572</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>109.552</v>
+        <v>111.601</v>
       </c>
       <c r="C140" t="n">
-        <v>94.29340000000001</v>
+        <v>93.55759999999999</v>
       </c>
       <c r="D140" t="n">
-        <v>336.157</v>
+        <v>326.324</v>
       </c>
       <c r="E140" t="n">
-        <v>87.60080000000001</v>
+        <v>90.22069999999999</v>
       </c>
       <c r="F140" t="n">
-        <v>334.67</v>
+        <v>326.167</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>109.913</v>
+        <v>105.582</v>
       </c>
       <c r="C141" t="n">
-        <v>93.2111</v>
+        <v>91.1011</v>
       </c>
       <c r="D141" t="n">
-        <v>333.368</v>
+        <v>324.83</v>
       </c>
       <c r="E141" t="n">
-        <v>85.9177</v>
+        <v>84.4563</v>
       </c>
       <c r="F141" t="n">
-        <v>333.685</v>
+        <v>325.72</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>107.154</v>
+        <v>105.051</v>
       </c>
       <c r="C142" t="n">
-        <v>92.08150000000001</v>
+        <v>90.0621</v>
       </c>
       <c r="D142" t="n">
-        <v>333.503</v>
+        <v>323.983</v>
       </c>
       <c r="E142" t="n">
-        <v>84.96380000000001</v>
+        <v>83.35599999999999</v>
       </c>
       <c r="F142" t="n">
-        <v>333.913</v>
+        <v>324.276</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>106.24</v>
+        <v>103.624</v>
       </c>
       <c r="C143" t="n">
-        <v>91.0977</v>
+        <v>88.871</v>
       </c>
       <c r="D143" t="n">
-        <v>332.655</v>
+        <v>322.82</v>
       </c>
       <c r="E143" t="n">
-        <v>83.61709999999999</v>
+        <v>82.14960000000001</v>
       </c>
       <c r="F143" t="n">
-        <v>332.598</v>
+        <v>323.375</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.0529</v>
+        <v>24.0997</v>
       </c>
       <c r="C2" t="n">
-        <v>20.321</v>
+        <v>20.2892</v>
       </c>
       <c r="D2" t="n">
-        <v>53.6895</v>
+        <v>53.7108</v>
       </c>
       <c r="E2" t="n">
-        <v>18.3002</v>
+        <v>18.2422</v>
       </c>
       <c r="F2" t="n">
-        <v>33.5724</v>
+        <v>33.7082</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.3372</v>
+        <v>23.8318</v>
       </c>
       <c r="C3" t="n">
-        <v>19.7975</v>
+        <v>19.7751</v>
       </c>
       <c r="D3" t="n">
-        <v>53.0876</v>
+        <v>53.077</v>
       </c>
       <c r="E3" t="n">
-        <v>17.7905</v>
+        <v>17.6537</v>
       </c>
       <c r="F3" t="n">
-        <v>33.1088</v>
+        <v>33.2733</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>22.905</v>
+        <v>23.107</v>
       </c>
       <c r="C4" t="n">
-        <v>19.3956</v>
+        <v>19.3184</v>
       </c>
       <c r="D4" t="n">
-        <v>52.5352</v>
+        <v>52.5585</v>
       </c>
       <c r="E4" t="n">
-        <v>17.1959</v>
+        <v>17.1704</v>
       </c>
       <c r="F4" t="n">
-        <v>32.763</v>
+        <v>32.8623</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.0268</v>
+        <v>22.3517</v>
       </c>
       <c r="C5" t="n">
-        <v>18.8436</v>
+        <v>18.8693</v>
       </c>
       <c r="D5" t="n">
-        <v>52.0602</v>
+        <v>52.0827</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7999</v>
+        <v>16.7033</v>
       </c>
       <c r="F5" t="n">
-        <v>32.4812</v>
+        <v>32.576</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.073</v>
+        <v>22.1431</v>
       </c>
       <c r="C6" t="n">
-        <v>18.4797</v>
+        <v>18.4611</v>
       </c>
       <c r="D6" t="n">
-        <v>51.7065</v>
+        <v>51.664</v>
       </c>
       <c r="E6" t="n">
-        <v>16.3331</v>
+        <v>16.3192</v>
       </c>
       <c r="F6" t="n">
-        <v>32.3422</v>
+        <v>32.4015</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.6823</v>
+        <v>21.6312</v>
       </c>
       <c r="C7" t="n">
-        <v>18.2791</v>
+        <v>18.1576</v>
       </c>
       <c r="D7" t="n">
-        <v>65.8935</v>
+        <v>65.9472</v>
       </c>
       <c r="E7" t="n">
-        <v>25.4837</v>
+        <v>25.4818</v>
       </c>
       <c r="F7" t="n">
-        <v>40.8426</v>
+        <v>40.9916</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.4675</v>
+        <v>21.4042</v>
       </c>
       <c r="C8" t="n">
-        <v>26.9532</v>
+        <v>26.8684</v>
       </c>
       <c r="D8" t="n">
-        <v>64.4025</v>
+        <v>64.2693</v>
       </c>
       <c r="E8" t="n">
-        <v>25.2387</v>
+        <v>24.6652</v>
       </c>
       <c r="F8" t="n">
-        <v>39.8885</v>
+        <v>40.1215</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.6433</v>
+        <v>21.458</v>
       </c>
       <c r="C9" t="n">
-        <v>26.041</v>
+        <v>26.0327</v>
       </c>
       <c r="D9" t="n">
-        <v>62.9974</v>
+        <v>62.9736</v>
       </c>
       <c r="E9" t="n">
-        <v>23.7363</v>
+        <v>23.8285</v>
       </c>
       <c r="F9" t="n">
-        <v>39.1402</v>
+        <v>39.2185</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>30.0657</v>
+        <v>30.1671</v>
       </c>
       <c r="C10" t="n">
-        <v>25.2082</v>
+        <v>25.1664</v>
       </c>
       <c r="D10" t="n">
-        <v>61.743</v>
+        <v>61.7838</v>
       </c>
       <c r="E10" t="n">
-        <v>22.9578</v>
+        <v>23.0394</v>
       </c>
       <c r="F10" t="n">
-        <v>38.2031</v>
+        <v>38.3855</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>29.3701</v>
+        <v>29.1165</v>
       </c>
       <c r="C11" t="n">
-        <v>24.4414</v>
+        <v>24.3545</v>
       </c>
       <c r="D11" t="n">
-        <v>60.7824</v>
+        <v>60.7229</v>
       </c>
       <c r="E11" t="n">
-        <v>22.2944</v>
+        <v>22.2199</v>
       </c>
       <c r="F11" t="n">
-        <v>37.3584</v>
+        <v>37.5083</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>28.0391</v>
+        <v>28.3418</v>
       </c>
       <c r="C12" t="n">
-        <v>23.6873</v>
+        <v>23.6525</v>
       </c>
       <c r="D12" t="n">
-        <v>59.6184</v>
+        <v>59.5929</v>
       </c>
       <c r="E12" t="n">
-        <v>21.5248</v>
+        <v>21.5111</v>
       </c>
       <c r="F12" t="n">
-        <v>36.5907</v>
+        <v>36.7663</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>27.8077</v>
+        <v>27.5911</v>
       </c>
       <c r="C13" t="n">
-        <v>22.9044</v>
+        <v>22.8959</v>
       </c>
       <c r="D13" t="n">
-        <v>58.7861</v>
+        <v>58.7376</v>
       </c>
       <c r="E13" t="n">
-        <v>21.3147</v>
+        <v>20.7831</v>
       </c>
       <c r="F13" t="n">
-        <v>35.9034</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>27.2746</v>
+        <v>26.8857</v>
       </c>
       <c r="C14" t="n">
-        <v>22.2133</v>
+        <v>22.1935</v>
       </c>
       <c r="D14" t="n">
-        <v>58.0021</v>
+        <v>57.8923</v>
       </c>
       <c r="E14" t="n">
-        <v>20.193</v>
+        <v>20.285</v>
       </c>
       <c r="F14" t="n">
-        <v>35.2832</v>
+        <v>35.3952</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>25.8694</v>
+        <v>25.8832</v>
       </c>
       <c r="C15" t="n">
-        <v>21.5713</v>
+        <v>21.5895</v>
       </c>
       <c r="D15" t="n">
-        <v>57.1419</v>
+        <v>57.3754</v>
       </c>
       <c r="E15" t="n">
-        <v>19.5748</v>
+        <v>19.6626</v>
       </c>
       <c r="F15" t="n">
-        <v>34.6686</v>
+        <v>34.782</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>25.4248</v>
+        <v>25.7508</v>
       </c>
       <c r="C16" t="n">
-        <v>20.9311</v>
+        <v>20.9431</v>
       </c>
       <c r="D16" t="n">
-        <v>56.9231</v>
+        <v>56.6722</v>
       </c>
       <c r="E16" t="n">
-        <v>19.0715</v>
+        <v>19.0296</v>
       </c>
       <c r="F16" t="n">
-        <v>34.1152</v>
+        <v>34.2293</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>24.8164</v>
+        <v>24.6859</v>
       </c>
       <c r="C17" t="n">
-        <v>20.4061</v>
+        <v>20.5342</v>
       </c>
       <c r="D17" t="n">
-        <v>56.2927</v>
+        <v>56.2596</v>
       </c>
       <c r="E17" t="n">
-        <v>18.5208</v>
+        <v>18.4983</v>
       </c>
       <c r="F17" t="n">
-        <v>33.6322</v>
+        <v>33.7361</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.2601</v>
+        <v>24.0451</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8694</v>
+        <v>19.8465</v>
       </c>
       <c r="D18" t="n">
-        <v>55.2803</v>
+        <v>55.2909</v>
       </c>
       <c r="E18" t="n">
-        <v>18.0674</v>
+        <v>18.0792</v>
       </c>
       <c r="F18" t="n">
-        <v>33.2027</v>
+        <v>33.3062</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.3605</v>
+        <v>23.4923</v>
       </c>
       <c r="C19" t="n">
-        <v>19.3894</v>
+        <v>19.4026</v>
       </c>
       <c r="D19" t="n">
-        <v>54.5846</v>
+        <v>54.6871</v>
       </c>
       <c r="E19" t="n">
-        <v>17.7056</v>
+        <v>17.6582</v>
       </c>
       <c r="F19" t="n">
-        <v>32.8948</v>
+        <v>32.9381</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.1522</v>
+        <v>23.2438</v>
       </c>
       <c r="C20" t="n">
-        <v>18.9616</v>
+        <v>18.9556</v>
       </c>
       <c r="D20" t="n">
-        <v>54.2011</v>
+        <v>54.0547</v>
       </c>
       <c r="E20" t="n">
-        <v>17.4897</v>
+        <v>17.461</v>
       </c>
       <c r="F20" t="n">
-        <v>32.629</v>
+        <v>32.7028</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.7679</v>
+        <v>22.7387</v>
       </c>
       <c r="C21" t="n">
-        <v>18.6414</v>
+        <v>18.656</v>
       </c>
       <c r="D21" t="n">
-        <v>71.6844</v>
+        <v>71.93219999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>26.6486</v>
+        <v>26.6821</v>
       </c>
       <c r="F21" t="n">
-        <v>41.2147</v>
+        <v>41.1678</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.6737</v>
+        <v>22.6916</v>
       </c>
       <c r="C22" t="n">
-        <v>27.409</v>
+        <v>27.3272</v>
       </c>
       <c r="D22" t="n">
-        <v>70.1587</v>
+        <v>70.2497</v>
       </c>
       <c r="E22" t="n">
-        <v>26.1559</v>
+        <v>25.7925</v>
       </c>
       <c r="F22" t="n">
-        <v>40.3338</v>
+        <v>40.3247</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.4969</v>
+        <v>22.6129</v>
       </c>
       <c r="C23" t="n">
-        <v>26.734</v>
+        <v>26.5179</v>
       </c>
       <c r="D23" t="n">
-        <v>68.7538</v>
+        <v>68.72799999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>24.9094</v>
+        <v>24.8838</v>
       </c>
       <c r="F23" t="n">
-        <v>39.5191</v>
+        <v>39.4914</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>31.1323</v>
+        <v>30.8111</v>
       </c>
       <c r="C24" t="n">
-        <v>25.8016</v>
+        <v>25.6967</v>
       </c>
       <c r="D24" t="n">
-        <v>67.50409999999999</v>
+        <v>67.57769999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>24.1318</v>
+        <v>24.1733</v>
       </c>
       <c r="F24" t="n">
-        <v>38.6718</v>
+        <v>38.704</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>29.827</v>
+        <v>29.8224</v>
       </c>
       <c r="C25" t="n">
-        <v>24.9345</v>
+        <v>24.9157</v>
       </c>
       <c r="D25" t="n">
-        <v>66.1328</v>
+        <v>66.24550000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3466</v>
+        <v>23.3599</v>
       </c>
       <c r="F25" t="n">
-        <v>37.9158</v>
+        <v>37.8627</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>29.1566</v>
+        <v>28.8342</v>
       </c>
       <c r="C26" t="n">
-        <v>24.2988</v>
+        <v>24.1639</v>
       </c>
       <c r="D26" t="n">
-        <v>64.6403</v>
+        <v>64.8035</v>
       </c>
       <c r="E26" t="n">
-        <v>22.6077</v>
+        <v>22.4705</v>
       </c>
       <c r="F26" t="n">
-        <v>37.0663</v>
+        <v>38.4673</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.1304</v>
+        <v>28.6855</v>
       </c>
       <c r="C27" t="n">
-        <v>23.5215</v>
+        <v>23.4328</v>
       </c>
       <c r="D27" t="n">
-        <v>63.6788</v>
+        <v>63.7868</v>
       </c>
       <c r="E27" t="n">
-        <v>21.8831</v>
+        <v>21.7954</v>
       </c>
       <c r="F27" t="n">
-        <v>36.3813</v>
+        <v>37.8537</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>27.8702</v>
+        <v>27.8801</v>
       </c>
       <c r="C28" t="n">
-        <v>22.7483</v>
+        <v>22.7025</v>
       </c>
       <c r="D28" t="n">
-        <v>62.7867</v>
+        <v>62.813</v>
       </c>
       <c r="E28" t="n">
-        <v>21.359</v>
+        <v>21.2766</v>
       </c>
       <c r="F28" t="n">
-        <v>35.7499</v>
+        <v>37.0343</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>26.6</v>
+        <v>26.5869</v>
       </c>
       <c r="C29" t="n">
-        <v>22.1747</v>
+        <v>22.0826</v>
       </c>
       <c r="D29" t="n">
-        <v>62.085</v>
+        <v>62.0742</v>
       </c>
       <c r="E29" t="n">
-        <v>20.8095</v>
+        <v>20.5485</v>
       </c>
       <c r="F29" t="n">
-        <v>35.1934</v>
+        <v>36.2927</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>26.4086</v>
+        <v>26.4437</v>
       </c>
       <c r="C30" t="n">
-        <v>21.5055</v>
+        <v>21.4836</v>
       </c>
       <c r="D30" t="n">
-        <v>61.2119</v>
+        <v>61.1748</v>
       </c>
       <c r="E30" t="n">
-        <v>20.036</v>
+        <v>19.9142</v>
       </c>
       <c r="F30" t="n">
-        <v>34.643</v>
+        <v>35.7451</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.7206</v>
+        <v>25.7509</v>
       </c>
       <c r="C31" t="n">
-        <v>20.9235</v>
+        <v>20.88</v>
       </c>
       <c r="D31" t="n">
-        <v>60.7107</v>
+        <v>60.6823</v>
       </c>
       <c r="E31" t="n">
-        <v>19.4859</v>
+        <v>19.4272</v>
       </c>
       <c r="F31" t="n">
-        <v>34.0857</v>
+        <v>33.9965</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.8709</v>
+        <v>25.8588</v>
       </c>
       <c r="C32" t="n">
-        <v>20.4221</v>
+        <v>20.3926</v>
       </c>
       <c r="D32" t="n">
-        <v>60.2198</v>
+        <v>60.1624</v>
       </c>
       <c r="E32" t="n">
-        <v>19.0407</v>
+        <v>18.9392</v>
       </c>
       <c r="F32" t="n">
-        <v>33.6376</v>
+        <v>33.5701</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>24.8374</v>
+        <v>25.298</v>
       </c>
       <c r="C33" t="n">
-        <v>19.9635</v>
+        <v>19.8985</v>
       </c>
       <c r="D33" t="n">
-        <v>59.8665</v>
+        <v>59.7807</v>
       </c>
       <c r="E33" t="n">
-        <v>18.6173</v>
+        <v>18.5996</v>
       </c>
       <c r="F33" t="n">
-        <v>33.4361</v>
+        <v>33.392</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>23.8986</v>
+        <v>23.9293</v>
       </c>
       <c r="C34" t="n">
-        <v>19.514</v>
+        <v>19.511</v>
       </c>
       <c r="D34" t="n">
-        <v>58.9955</v>
+        <v>58.9502</v>
       </c>
       <c r="E34" t="n">
-        <v>18.309</v>
+        <v>18.2916</v>
       </c>
       <c r="F34" t="n">
-        <v>33.1727</v>
+        <v>33.0832</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.4679</v>
+        <v>23.6303</v>
       </c>
       <c r="C35" t="n">
-        <v>19.1988</v>
+        <v>19.1431</v>
       </c>
       <c r="D35" t="n">
-        <v>77.48609999999999</v>
+        <v>77.1601</v>
       </c>
       <c r="E35" t="n">
-        <v>27.5533</v>
+        <v>27.4924</v>
       </c>
       <c r="F35" t="n">
-        <v>42.2368</v>
+        <v>42.0726</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.0229</v>
+        <v>23.6239</v>
       </c>
       <c r="C36" t="n">
-        <v>18.9201</v>
+        <v>18.8823</v>
       </c>
       <c r="D36" t="n">
-        <v>75.55500000000001</v>
+        <v>75.4222</v>
       </c>
       <c r="E36" t="n">
-        <v>27.0151</v>
+        <v>26.6964</v>
       </c>
       <c r="F36" t="n">
-        <v>41.3944</v>
+        <v>41.1676</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.5061</v>
+        <v>23.2556</v>
       </c>
       <c r="C37" t="n">
-        <v>27.2532</v>
+        <v>27.0637</v>
       </c>
       <c r="D37" t="n">
-        <v>74.0068</v>
+        <v>73.938</v>
       </c>
       <c r="E37" t="n">
-        <v>26.158</v>
+        <v>25.7461</v>
       </c>
       <c r="F37" t="n">
-        <v>40.6019</v>
+        <v>40.2028</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>30.8975</v>
+        <v>31.2231</v>
       </c>
       <c r="C38" t="n">
-        <v>26.3613</v>
+        <v>26.2593</v>
       </c>
       <c r="D38" t="n">
-        <v>72.5471</v>
+        <v>72.3948</v>
       </c>
       <c r="E38" t="n">
-        <v>25.0661</v>
+        <v>24.9302</v>
       </c>
       <c r="F38" t="n">
-        <v>39.6768</v>
+        <v>39.4102</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>30.3813</v>
+        <v>30.4325</v>
       </c>
       <c r="C39" t="n">
-        <v>25.6256</v>
+        <v>25.477</v>
       </c>
       <c r="D39" t="n">
-        <v>71.2214</v>
+        <v>71.0321</v>
       </c>
       <c r="E39" t="n">
-        <v>24.2263</v>
+        <v>24.1716</v>
       </c>
       <c r="F39" t="n">
-        <v>39.1259</v>
+        <v>38.8551</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>29.6507</v>
+        <v>29.971</v>
       </c>
       <c r="C40" t="n">
-        <v>24.85</v>
+        <v>24.7515</v>
       </c>
       <c r="D40" t="n">
-        <v>69.93859999999999</v>
+        <v>69.8198</v>
       </c>
       <c r="E40" t="n">
-        <v>23.6118</v>
+        <v>23.4152</v>
       </c>
       <c r="F40" t="n">
-        <v>38.4545</v>
+        <v>38.1147</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>28.7207</v>
+        <v>29.1978</v>
       </c>
       <c r="C41" t="n">
-        <v>24.1433</v>
+        <v>23.9957</v>
       </c>
       <c r="D41" t="n">
-        <v>68.7822</v>
+        <v>68.73269999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>22.792</v>
+        <v>22.9513</v>
       </c>
       <c r="F41" t="n">
-        <v>37.7769</v>
+        <v>37.4374</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>28.119</v>
+        <v>28.0456</v>
       </c>
       <c r="C42" t="n">
-        <v>23.4786</v>
+        <v>23.2982</v>
       </c>
       <c r="D42" t="n">
-        <v>67.8639</v>
+        <v>67.6249</v>
       </c>
       <c r="E42" t="n">
-        <v>22.3802</v>
+        <v>22.063</v>
       </c>
       <c r="F42" t="n">
-        <v>37.1992</v>
+        <v>36.8235</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>27.2175</v>
+        <v>27.3928</v>
       </c>
       <c r="C43" t="n">
-        <v>22.8874</v>
+        <v>22.7219</v>
       </c>
       <c r="D43" t="n">
-        <v>66.6947</v>
+        <v>66.42700000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>21.7797</v>
+        <v>21.3776</v>
       </c>
       <c r="F43" t="n">
-        <v>36.6243</v>
+        <v>36.2669</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>26.741</v>
+        <v>26.8187</v>
       </c>
       <c r="C44" t="n">
-        <v>22.2622</v>
+        <v>22.1397</v>
       </c>
       <c r="D44" t="n">
-        <v>65.8781</v>
+        <v>65.6048</v>
       </c>
       <c r="E44" t="n">
-        <v>20.9438</v>
+        <v>20.8332</v>
       </c>
       <c r="F44" t="n">
-        <v>36.0871</v>
+        <v>35.7892</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>26.4632</v>
+        <v>25.7901</v>
       </c>
       <c r="C45" t="n">
-        <v>21.6995</v>
+        <v>21.6019</v>
       </c>
       <c r="D45" t="n">
-        <v>65.1819</v>
+        <v>64.9923</v>
       </c>
       <c r="E45" t="n">
-        <v>20.589</v>
+        <v>20.2689</v>
       </c>
       <c r="F45" t="n">
-        <v>35.6853</v>
+        <v>35.2382</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>25.4072</v>
+        <v>25.6657</v>
       </c>
       <c r="C46" t="n">
-        <v>21.1781</v>
+        <v>21.0399</v>
       </c>
       <c r="D46" t="n">
-        <v>64.61150000000001</v>
+        <v>64.40009999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>19.8903</v>
+        <v>19.8244</v>
       </c>
       <c r="F46" t="n">
-        <v>35.2944</v>
+        <v>34.7286</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>24.7932</v>
+        <v>24.597</v>
       </c>
       <c r="C47" t="n">
-        <v>20.7653</v>
+        <v>20.6813</v>
       </c>
       <c r="D47" t="n">
-        <v>64.2213</v>
+        <v>63.9273</v>
       </c>
       <c r="E47" t="n">
-        <v>19.5578</v>
+        <v>19.4116</v>
       </c>
       <c r="F47" t="n">
-        <v>34.9455</v>
+        <v>34.5806</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>24.5752</v>
+        <v>24.3928</v>
       </c>
       <c r="C48" t="n">
-        <v>20.2706</v>
+        <v>20.2182</v>
       </c>
       <c r="D48" t="n">
-        <v>63.4561</v>
+        <v>63.2166</v>
       </c>
       <c r="E48" t="n">
-        <v>19.1649</v>
+        <v>19.3779</v>
       </c>
       <c r="F48" t="n">
-        <v>34.7289</v>
+        <v>34.2558</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>24.126</v>
+        <v>24.3107</v>
       </c>
       <c r="C49" t="n">
-        <v>19.9062</v>
+        <v>19.7242</v>
       </c>
       <c r="D49" t="n">
-        <v>63.1111</v>
+        <v>62.8555</v>
       </c>
       <c r="E49" t="n">
-        <v>18.8568</v>
+        <v>18.9339</v>
       </c>
       <c r="F49" t="n">
-        <v>34.5593</v>
+        <v>33.9317</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>24.047</v>
+        <v>23.5676</v>
       </c>
       <c r="C50" t="n">
-        <v>19.6743</v>
+        <v>19.5348</v>
       </c>
       <c r="D50" t="n">
-        <v>80.4452</v>
+        <v>80.16240000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>28.1442</v>
+        <v>27.5932</v>
       </c>
       <c r="F50" t="n">
-        <v>43.0949</v>
+        <v>42.877</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>23.6465</v>
+        <v>23.5118</v>
       </c>
       <c r="C51" t="n">
-        <v>27.993</v>
+        <v>28.0706</v>
       </c>
       <c r="D51" t="n">
-        <v>78.6217</v>
+        <v>78.3943</v>
       </c>
       <c r="E51" t="n">
-        <v>27.0625</v>
+        <v>27.177</v>
       </c>
       <c r="F51" t="n">
-        <v>42.2992</v>
+        <v>42.1253</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>23.7441</v>
+        <v>23.6498</v>
       </c>
       <c r="C52" t="n">
-        <v>27.296</v>
+        <v>27.2211</v>
       </c>
       <c r="D52" t="n">
-        <v>76.92189999999999</v>
+        <v>76.7452</v>
       </c>
       <c r="E52" t="n">
-        <v>26.1142</v>
+        <v>26.1823</v>
       </c>
       <c r="F52" t="n">
-        <v>41.6036</v>
+        <v>41.4218</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>31.8388</v>
+        <v>31.3421</v>
       </c>
       <c r="C53" t="n">
-        <v>26.4825</v>
+        <v>26.377</v>
       </c>
       <c r="D53" t="n">
-        <v>75.37</v>
+        <v>75.19450000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>25.4687</v>
+        <v>25.4319</v>
       </c>
       <c r="F53" t="n">
-        <v>40.943</v>
+        <v>40.6623</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>31.232</v>
+        <v>30.6736</v>
       </c>
       <c r="C54" t="n">
-        <v>25.7636</v>
+        <v>25.6668</v>
       </c>
       <c r="D54" t="n">
-        <v>73.9618</v>
+        <v>73.7756</v>
       </c>
       <c r="E54" t="n">
-        <v>24.6801</v>
+        <v>24.5594</v>
       </c>
       <c r="F54" t="n">
-        <v>40.2273</v>
+        <v>40.1027</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>30.7119</v>
+        <v>30.1671</v>
       </c>
       <c r="C55" t="n">
-        <v>25.2167</v>
+        <v>24.9905</v>
       </c>
       <c r="D55" t="n">
-        <v>72.8116</v>
+        <v>72.58410000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>24.0369</v>
+        <v>23.7797</v>
       </c>
       <c r="F55" t="n">
-        <v>39.6166</v>
+        <v>39.5106</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>30.3734</v>
+        <v>29.1309</v>
       </c>
       <c r="C56" t="n">
-        <v>24.5938</v>
+        <v>24.3205</v>
       </c>
       <c r="D56" t="n">
-        <v>71.66759999999999</v>
+        <v>71.4877</v>
       </c>
       <c r="E56" t="n">
-        <v>23.2698</v>
+        <v>23.097</v>
       </c>
       <c r="F56" t="n">
-        <v>39.0745</v>
+        <v>38.8857</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>29.2282</v>
+        <v>28.9579</v>
       </c>
       <c r="C57" t="n">
-        <v>23.9121</v>
+        <v>23.7598</v>
       </c>
       <c r="D57" t="n">
-        <v>70.45010000000001</v>
+        <v>70.2591</v>
       </c>
       <c r="E57" t="n">
-        <v>22.7807</v>
+        <v>22.3198</v>
       </c>
       <c r="F57" t="n">
-        <v>38.5621</v>
+        <v>38.2099</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.2621</v>
+        <v>28.4861</v>
       </c>
       <c r="C58" t="n">
-        <v>23.2974</v>
+        <v>23.1619</v>
       </c>
       <c r="D58" t="n">
-        <v>69.63379999999999</v>
+        <v>69.43300000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>22.2518</v>
+        <v>21.8077</v>
       </c>
       <c r="F58" t="n">
-        <v>38.031</v>
+        <v>37.7582</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.96</v>
+        <v>27.1852</v>
       </c>
       <c r="C59" t="n">
-        <v>22.7214</v>
+        <v>22.7269</v>
       </c>
       <c r="D59" t="n">
-        <v>68.7471</v>
+        <v>68.5539</v>
       </c>
       <c r="E59" t="n">
-        <v>21.421</v>
+        <v>21.6002</v>
       </c>
       <c r="F59" t="n">
-        <v>37.6349</v>
+        <v>37.4814</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>27.1893</v>
+        <v>26.8433</v>
       </c>
       <c r="C60" t="n">
-        <v>22.3832</v>
+        <v>22.2997</v>
       </c>
       <c r="D60" t="n">
-        <v>68.1589</v>
+        <v>67.9404</v>
       </c>
       <c r="E60" t="n">
-        <v>21.0845</v>
+        <v>20.9715</v>
       </c>
       <c r="F60" t="n">
-        <v>37.3055</v>
+        <v>37.1387</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.9521</v>
+        <v>26.5531</v>
       </c>
       <c r="C61" t="n">
-        <v>21.9128</v>
+        <v>21.9234</v>
       </c>
       <c r="D61" t="n">
-        <v>67.40349999999999</v>
+        <v>67.2124</v>
       </c>
       <c r="E61" t="n">
-        <v>20.8244</v>
+        <v>20.5938</v>
       </c>
       <c r="F61" t="n">
-        <v>37.0042</v>
+        <v>36.8207</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>26.0947</v>
+        <v>25.9667</v>
       </c>
       <c r="C62" t="n">
-        <v>21.5528</v>
+        <v>21.4044</v>
       </c>
       <c r="D62" t="n">
-        <v>66.7358</v>
+        <v>66.5365</v>
       </c>
       <c r="E62" t="n">
-        <v>20.5095</v>
+        <v>20.1708</v>
       </c>
       <c r="F62" t="n">
-        <v>36.7475</v>
+        <v>36.6554</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>25.7044</v>
+        <v>25.386</v>
       </c>
       <c r="C63" t="n">
-        <v>21.0723</v>
+        <v>21.057</v>
       </c>
       <c r="D63" t="n">
-        <v>66.46080000000001</v>
+        <v>66.1189</v>
       </c>
       <c r="E63" t="n">
-        <v>20.0006</v>
+        <v>19.8672</v>
       </c>
       <c r="F63" t="n">
-        <v>36.6794</v>
+        <v>36.5308</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.7744</v>
+        <v>25.2635</v>
       </c>
       <c r="C64" t="n">
-        <v>20.841</v>
+        <v>20.7509</v>
       </c>
       <c r="D64" t="n">
-        <v>88.3044</v>
+        <v>86.97799999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>33.1589</v>
+        <v>32.4914</v>
       </c>
       <c r="F64" t="n">
-        <v>47.7023</v>
+        <v>46.6227</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.7644</v>
+        <v>25.0237</v>
       </c>
       <c r="C65" t="n">
-        <v>29.7217</v>
+        <v>29.5784</v>
       </c>
       <c r="D65" t="n">
-        <v>85.8402</v>
+        <v>84.7928</v>
       </c>
       <c r="E65" t="n">
-        <v>32.4596</v>
+        <v>31.5361</v>
       </c>
       <c r="F65" t="n">
-        <v>47.2121</v>
+        <v>46.051</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.3458</v>
+        <v>25.0173</v>
       </c>
       <c r="C66" t="n">
-        <v>29.162</v>
+        <v>29.0005</v>
       </c>
       <c r="D66" t="n">
-        <v>83.9735</v>
+        <v>83.01139999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>31.2426</v>
+        <v>29.8578</v>
       </c>
       <c r="F66" t="n">
-        <v>46.5261</v>
+        <v>45.3623</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>41.6424</v>
+        <v>39.7823</v>
       </c>
       <c r="C67" t="n">
-        <v>28.4984</v>
+        <v>28.4083</v>
       </c>
       <c r="D67" t="n">
-        <v>82.3395</v>
+        <v>81.3373</v>
       </c>
       <c r="E67" t="n">
-        <v>30.66</v>
+        <v>29.1083</v>
       </c>
       <c r="F67" t="n">
-        <v>45.8545</v>
+        <v>44.8375</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>40.2603</v>
+        <v>39.6109</v>
       </c>
       <c r="C68" t="n">
-        <v>27.8731</v>
+        <v>27.6701</v>
       </c>
       <c r="D68" t="n">
-        <v>80.8219</v>
+        <v>79.8571</v>
       </c>
       <c r="E68" t="n">
-        <v>29.9216</v>
+        <v>28.4742</v>
       </c>
       <c r="F68" t="n">
-        <v>45.3165</v>
+        <v>44.2123</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>38.0217</v>
+        <v>38.8491</v>
       </c>
       <c r="C69" t="n">
-        <v>27.369</v>
+        <v>27.2157</v>
       </c>
       <c r="D69" t="n">
-        <v>79.4264</v>
+        <v>78.5275</v>
       </c>
       <c r="E69" t="n">
-        <v>29.3065</v>
+        <v>28.3375</v>
       </c>
       <c r="F69" t="n">
-        <v>44.7067</v>
+        <v>43.4254</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>39.0582</v>
+        <v>38.2291</v>
       </c>
       <c r="C70" t="n">
-        <v>26.8754</v>
+        <v>26.5954</v>
       </c>
       <c r="D70" t="n">
-        <v>78.4264</v>
+        <v>77.5993</v>
       </c>
       <c r="E70" t="n">
-        <v>28.2423</v>
+        <v>27.6998</v>
       </c>
       <c r="F70" t="n">
-        <v>44.0058</v>
+        <v>42.9693</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>37.6909</v>
+        <v>35.7942</v>
       </c>
       <c r="C71" t="n">
-        <v>26.36</v>
+        <v>26.1654</v>
       </c>
       <c r="D71" t="n">
-        <v>77.6626</v>
+        <v>76.813</v>
       </c>
       <c r="E71" t="n">
-        <v>27.6965</v>
+        <v>26.3495</v>
       </c>
       <c r="F71" t="n">
-        <v>43.6136</v>
+        <v>42.4521</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.7375</v>
+        <v>36.8912</v>
       </c>
       <c r="C72" t="n">
-        <v>25.8998</v>
+        <v>25.7295</v>
       </c>
       <c r="D72" t="n">
-        <v>77.28570000000001</v>
+        <v>76.1987</v>
       </c>
       <c r="E72" t="n">
-        <v>26.8555</v>
+        <v>26.2832</v>
       </c>
       <c r="F72" t="n">
-        <v>43.1744</v>
+        <v>42.1306</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>36.6929</v>
+        <v>35.3885</v>
       </c>
       <c r="C73" t="n">
-        <v>25.435</v>
+        <v>25.2043</v>
       </c>
       <c r="D73" t="n">
-        <v>76.8781</v>
+        <v>75.7355</v>
       </c>
       <c r="E73" t="n">
-        <v>26.4819</v>
+        <v>26.0089</v>
       </c>
       <c r="F73" t="n">
-        <v>42.6706</v>
+        <v>41.8499</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>35.4706</v>
+        <v>35.6344</v>
       </c>
       <c r="C74" t="n">
-        <v>25.1306</v>
+        <v>24.8008</v>
       </c>
       <c r="D74" t="n">
-        <v>76.52500000000001</v>
+        <v>75.26090000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>25.911</v>
+        <v>24.7531</v>
       </c>
       <c r="F74" t="n">
-        <v>42.339</v>
+        <v>41.4987</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>34.5702</v>
+        <v>33.7643</v>
       </c>
       <c r="C75" t="n">
-        <v>24.6851</v>
+        <v>24.3865</v>
       </c>
       <c r="D75" t="n">
-        <v>75.6309</v>
+        <v>74.4302</v>
       </c>
       <c r="E75" t="n">
-        <v>25.3337</v>
+        <v>24.2109</v>
       </c>
       <c r="F75" t="n">
-        <v>42.1244</v>
+        <v>41.1009</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>35.757</v>
+        <v>34.3579</v>
       </c>
       <c r="C76" t="n">
-        <v>24.2518</v>
+        <v>24.1056</v>
       </c>
       <c r="D76" t="n">
-        <v>75.7153</v>
+        <v>74.4314</v>
       </c>
       <c r="E76" t="n">
-        <v>25.0091</v>
+        <v>23.8221</v>
       </c>
       <c r="F76" t="n">
-        <v>41.8683</v>
+        <v>41.0325</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>34.955</v>
+        <v>33.9932</v>
       </c>
       <c r="C77" t="n">
-        <v>23.8883</v>
+        <v>23.6554</v>
       </c>
       <c r="D77" t="n">
-        <v>75.9409</v>
+        <v>74.8462</v>
       </c>
       <c r="E77" t="n">
-        <v>24.6349</v>
+        <v>23.8233</v>
       </c>
       <c r="F77" t="n">
-        <v>41.8169</v>
+        <v>40.9487</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>34.6577</v>
+        <v>33.8442</v>
       </c>
       <c r="C78" t="n">
-        <v>23.6335</v>
+        <v>23.3963</v>
       </c>
       <c r="D78" t="n">
-        <v>123.824</v>
+        <v>122.275</v>
       </c>
       <c r="E78" t="n">
-        <v>41.8151</v>
+        <v>40.272</v>
       </c>
       <c r="F78" t="n">
-        <v>65.96129999999999</v>
+        <v>65.5094</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>36.3732</v>
+        <v>34.695</v>
       </c>
       <c r="C79" t="n">
-        <v>33.3916</v>
+        <v>33.0865</v>
       </c>
       <c r="D79" t="n">
-        <v>122.034</v>
+        <v>120.014</v>
       </c>
       <c r="E79" t="n">
-        <v>41.0913</v>
+        <v>40.0336</v>
       </c>
       <c r="F79" t="n">
-        <v>67.3712</v>
+        <v>65.8711</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>37.4756</v>
+        <v>34.8599</v>
       </c>
       <c r="C80" t="n">
-        <v>33.2321</v>
+        <v>32.8168</v>
       </c>
       <c r="D80" t="n">
-        <v>120.365</v>
+        <v>118.308</v>
       </c>
       <c r="E80" t="n">
-        <v>40.1168</v>
+        <v>38.7408</v>
       </c>
       <c r="F80" t="n">
-        <v>66.0514</v>
+        <v>65.53149999999999</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>51.6406</v>
+        <v>48.6928</v>
       </c>
       <c r="C81" t="n">
-        <v>32.9076</v>
+        <v>32.5064</v>
       </c>
       <c r="D81" t="n">
-        <v>119.186</v>
+        <v>116.705</v>
       </c>
       <c r="E81" t="n">
-        <v>39.4833</v>
+        <v>38.0436</v>
       </c>
       <c r="F81" t="n">
-        <v>65.5956</v>
+        <v>64.8702</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>51.0368</v>
+        <v>51.0567</v>
       </c>
       <c r="C82" t="n">
-        <v>32.5012</v>
+        <v>32.2249</v>
       </c>
       <c r="D82" t="n">
-        <v>117.888</v>
+        <v>115.41</v>
       </c>
       <c r="E82" t="n">
-        <v>38.2609</v>
+        <v>37.0063</v>
       </c>
       <c r="F82" t="n">
-        <v>65.1622</v>
+        <v>64.0866</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>49.9467</v>
+        <v>47.8144</v>
       </c>
       <c r="C83" t="n">
-        <v>32.1129</v>
+        <v>31.8858</v>
       </c>
       <c r="D83" t="n">
-        <v>116.517</v>
+        <v>114.069</v>
       </c>
       <c r="E83" t="n">
-        <v>37.2332</v>
+        <v>36.0568</v>
       </c>
       <c r="F83" t="n">
-        <v>64.3582</v>
+        <v>62.8072</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>47.1408</v>
+        <v>43.03</v>
       </c>
       <c r="C84" t="n">
-        <v>31.7827</v>
+        <v>31.5399</v>
       </c>
       <c r="D84" t="n">
-        <v>115.867</v>
+        <v>113.704</v>
       </c>
       <c r="E84" t="n">
-        <v>36.3875</v>
+        <v>34.893</v>
       </c>
       <c r="F84" t="n">
-        <v>63.1381</v>
+        <v>62.132</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>48.8955</v>
+        <v>44.0107</v>
       </c>
       <c r="C85" t="n">
-        <v>31.4135</v>
+        <v>31.1535</v>
       </c>
       <c r="D85" t="n">
-        <v>115.928</v>
+        <v>113.605</v>
       </c>
       <c r="E85" t="n">
-        <v>35.3313</v>
+        <v>34.3023</v>
       </c>
       <c r="F85" t="n">
-        <v>62.3366</v>
+        <v>61.1425</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>44.4444</v>
+        <v>43.5224</v>
       </c>
       <c r="C86" t="n">
-        <v>31.1595</v>
+        <v>30.8098</v>
       </c>
       <c r="D86" t="n">
-        <v>116.004</v>
+        <v>113.796</v>
       </c>
       <c r="E86" t="n">
-        <v>34.4253</v>
+        <v>33.3348</v>
       </c>
       <c r="F86" t="n">
-        <v>61.402</v>
+        <v>60.3445</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>48.3134</v>
+        <v>45.0531</v>
       </c>
       <c r="C87" t="n">
-        <v>30.7574</v>
+        <v>30.5355</v>
       </c>
       <c r="D87" t="n">
-        <v>116.227</v>
+        <v>113.944</v>
       </c>
       <c r="E87" t="n">
-        <v>33.8076</v>
+        <v>32.5799</v>
       </c>
       <c r="F87" t="n">
-        <v>60.5592</v>
+        <v>59.338</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>47.0868</v>
+        <v>44.0017</v>
       </c>
       <c r="C88" t="n">
-        <v>30.4484</v>
+        <v>30.1399</v>
       </c>
       <c r="D88" t="n">
-        <v>116.902</v>
+        <v>114.885</v>
       </c>
       <c r="E88" t="n">
-        <v>32.9878</v>
+        <v>31.8961</v>
       </c>
       <c r="F88" t="n">
-        <v>59.5286</v>
+        <v>58.7536</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>46.2971</v>
+        <v>45.6421</v>
       </c>
       <c r="C89" t="n">
-        <v>30.0945</v>
+        <v>29.8797</v>
       </c>
       <c r="D89" t="n">
-        <v>117.17</v>
+        <v>114.934</v>
       </c>
       <c r="E89" t="n">
-        <v>32.2501</v>
+        <v>31.1385</v>
       </c>
       <c r="F89" t="n">
-        <v>58.8324</v>
+        <v>58.3767</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>42.4865</v>
+        <v>42.1805</v>
       </c>
       <c r="C90" t="n">
-        <v>29.8516</v>
+        <v>29.5208</v>
       </c>
       <c r="D90" t="n">
-        <v>117.88</v>
+        <v>116.678</v>
       </c>
       <c r="E90" t="n">
-        <v>31.5306</v>
+        <v>30.6076</v>
       </c>
       <c r="F90" t="n">
-        <v>58.475</v>
+        <v>57.6616</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>42.6712</v>
+        <v>44.0537</v>
       </c>
       <c r="C91" t="n">
-        <v>29.4766</v>
+        <v>29.2868</v>
       </c>
       <c r="D91" t="n">
-        <v>119.58</v>
+        <v>118.012</v>
       </c>
       <c r="E91" t="n">
-        <v>31.0283</v>
+        <v>30.1008</v>
       </c>
       <c r="F91" t="n">
-        <v>58.065</v>
+        <v>56.962</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>42.9876</v>
+        <v>42.0445</v>
       </c>
       <c r="C92" t="n">
-        <v>29.165</v>
+        <v>29.0301</v>
       </c>
       <c r="D92" t="n">
-        <v>179.525</v>
+        <v>176.436</v>
       </c>
       <c r="E92" t="n">
-        <v>64.8176</v>
+        <v>64.0582</v>
       </c>
       <c r="F92" t="n">
-        <v>90.99760000000001</v>
+        <v>89.11190000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>46.5192</v>
+        <v>40.8764</v>
       </c>
       <c r="C93" t="n">
-        <v>29.1453</v>
+        <v>28.6488</v>
       </c>
       <c r="D93" t="n">
-        <v>178.867</v>
+        <v>175.986</v>
       </c>
       <c r="E93" t="n">
-        <v>63.3196</v>
+        <v>62.8586</v>
       </c>
       <c r="F93" t="n">
-        <v>91.06189999999999</v>
+        <v>88.3254</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>45.9819</v>
+        <v>45.0404</v>
       </c>
       <c r="C94" t="n">
-        <v>61.8781</v>
+        <v>61.7203</v>
       </c>
       <c r="D94" t="n">
-        <v>177.979</v>
+        <v>174.847</v>
       </c>
       <c r="E94" t="n">
-        <v>61.7618</v>
+        <v>61.1153</v>
       </c>
       <c r="F94" t="n">
-        <v>88.0025</v>
+        <v>86.98050000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>74.6216</v>
+        <v>76.3813</v>
       </c>
       <c r="C95" t="n">
-        <v>60.6017</v>
+        <v>60.6309</v>
       </c>
       <c r="D95" t="n">
-        <v>177.248</v>
+        <v>173.861</v>
       </c>
       <c r="E95" t="n">
-        <v>59.8701</v>
+        <v>59.1808</v>
       </c>
       <c r="F95" t="n">
-        <v>87.6027</v>
+        <v>86.9233</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>75.25700000000001</v>
+        <v>75.5757</v>
       </c>
       <c r="C96" t="n">
-        <v>59.3946</v>
+        <v>59.0884</v>
       </c>
       <c r="D96" t="n">
-        <v>176.282</v>
+        <v>173.058</v>
       </c>
       <c r="E96" t="n">
-        <v>58.2925</v>
+        <v>57.4206</v>
       </c>
       <c r="F96" t="n">
-        <v>88.2878</v>
+        <v>85.3309</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>72.5916</v>
+        <v>75.459</v>
       </c>
       <c r="C97" t="n">
-        <v>58.017</v>
+        <v>57.7262</v>
       </c>
       <c r="D97" t="n">
-        <v>175.771</v>
+        <v>172.38</v>
       </c>
       <c r="E97" t="n">
-        <v>56.4107</v>
+        <v>55.5482</v>
       </c>
       <c r="F97" t="n">
-        <v>87.2495</v>
+        <v>83.96040000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>73.8026</v>
+        <v>71.3771</v>
       </c>
       <c r="C98" t="n">
-        <v>56.6079</v>
+        <v>56.2855</v>
       </c>
       <c r="D98" t="n">
-        <v>175.578</v>
+        <v>172.128</v>
       </c>
       <c r="E98" t="n">
-        <v>54.6623</v>
+        <v>53.7922</v>
       </c>
       <c r="F98" t="n">
-        <v>85.96899999999999</v>
+        <v>82.8356</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>69.3078</v>
+        <v>68.6409</v>
       </c>
       <c r="C99" t="n">
-        <v>55.2677</v>
+        <v>55.0402</v>
       </c>
       <c r="D99" t="n">
-        <v>175.945</v>
+        <v>172.228</v>
       </c>
       <c r="E99" t="n">
-        <v>53.1924</v>
+        <v>52.354</v>
       </c>
       <c r="F99" t="n">
-        <v>87.2084</v>
+        <v>83.0048</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>68.4405</v>
+        <v>66.7229</v>
       </c>
       <c r="C100" t="n">
-        <v>54.0105</v>
+        <v>53.76</v>
       </c>
       <c r="D100" t="n">
-        <v>176.122</v>
+        <v>172.995</v>
       </c>
       <c r="E100" t="n">
-        <v>51.5682</v>
+        <v>50.8531</v>
       </c>
       <c r="F100" t="n">
-        <v>84.2873</v>
+        <v>83.0654</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.0984</v>
+        <v>67.97539999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>52.7243</v>
+        <v>52.6378</v>
       </c>
       <c r="D101" t="n">
-        <v>176.481</v>
+        <v>172.609</v>
       </c>
       <c r="E101" t="n">
-        <v>50.2269</v>
+        <v>49.489</v>
       </c>
       <c r="F101" t="n">
-        <v>83.3712</v>
+        <v>83.10290000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>67.08410000000001</v>
+        <v>66.52979999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>51.7428</v>
+        <v>51.4743</v>
       </c>
       <c r="D102" t="n">
-        <v>177.472</v>
+        <v>173.716</v>
       </c>
       <c r="E102" t="n">
-        <v>48.7857</v>
+        <v>48.1197</v>
       </c>
       <c r="F102" t="n">
-        <v>82.32550000000001</v>
+        <v>79.8886</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>66.12390000000001</v>
+        <v>65.21129999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>50.6951</v>
+        <v>50.3573</v>
       </c>
       <c r="D103" t="n">
-        <v>178.999</v>
+        <v>175.612</v>
       </c>
       <c r="E103" t="n">
-        <v>47.3797</v>
+        <v>46.8815</v>
       </c>
       <c r="F103" t="n">
-        <v>82.47239999999999</v>
+        <v>78.77500000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>65.2392</v>
+        <v>64.15779999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>49.6667</v>
+        <v>49.3873</v>
       </c>
       <c r="D104" t="n">
-        <v>180.264</v>
+        <v>177.312</v>
       </c>
       <c r="E104" t="n">
-        <v>46.3622</v>
+        <v>45.6269</v>
       </c>
       <c r="F104" t="n">
-        <v>81.1341</v>
+        <v>77.9122</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>64.3266</v>
+        <v>63.0275</v>
       </c>
       <c r="C105" t="n">
-        <v>48.7274</v>
+        <v>48.3987</v>
       </c>
       <c r="D105" t="n">
-        <v>181.626</v>
+        <v>177.32</v>
       </c>
       <c r="E105" t="n">
-        <v>45.2772</v>
+        <v>44.5922</v>
       </c>
       <c r="F105" t="n">
-        <v>90.3129</v>
+        <v>78.1538</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>65.4653</v>
+        <v>62.4536</v>
       </c>
       <c r="C106" t="n">
-        <v>47.8636</v>
+        <v>47.5397</v>
       </c>
       <c r="D106" t="n">
-        <v>184.357</v>
+        <v>179.991</v>
       </c>
       <c r="E106" t="n">
-        <v>44.3796</v>
+        <v>43.7577</v>
       </c>
       <c r="F106" t="n">
-        <v>90.3719</v>
+        <v>78.2422</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>61.1548</v>
+        <v>60.5865</v>
       </c>
       <c r="C107" t="n">
-        <v>47.1687</v>
+        <v>46.75</v>
       </c>
       <c r="D107" t="n">
-        <v>247.544</v>
+        <v>240.54</v>
       </c>
       <c r="E107" t="n">
-        <v>78.8974</v>
+        <v>78.485</v>
       </c>
       <c r="F107" t="n">
-        <v>244.494</v>
+        <v>240.57</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>60.4598</v>
+        <v>60.5475</v>
       </c>
       <c r="C108" t="n">
-        <v>81.58320000000001</v>
+        <v>81.5801</v>
       </c>
       <c r="D108" t="n">
-        <v>244.834</v>
+        <v>237.822</v>
       </c>
       <c r="E108" t="n">
-        <v>76.8295</v>
+        <v>65.70610000000001</v>
       </c>
       <c r="F108" t="n">
-        <v>245.934</v>
+        <v>240.352</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>55.9517</v>
+        <v>51.6102</v>
       </c>
       <c r="C109" t="n">
-        <v>66.4229</v>
+        <v>65.84269999999999</v>
       </c>
       <c r="D109" t="n">
-        <v>242.41</v>
+        <v>235.927</v>
       </c>
       <c r="E109" t="n">
-        <v>74.6183</v>
+        <v>74.28619999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>245.813</v>
+        <v>241.684</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>92.6544</v>
+        <v>84.595</v>
       </c>
       <c r="C110" t="n">
-        <v>78.33629999999999</v>
+        <v>64.31140000000001</v>
       </c>
       <c r="D110" t="n">
-        <v>241.141</v>
+        <v>234.518</v>
       </c>
       <c r="E110" t="n">
-        <v>63.0675</v>
+        <v>72.2672</v>
       </c>
       <c r="F110" t="n">
-        <v>246.251</v>
+        <v>240.314</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>91.1985</v>
+        <v>88.94</v>
       </c>
       <c r="C111" t="n">
-        <v>76.3158</v>
+        <v>76.05329999999999</v>
       </c>
       <c r="D111" t="n">
-        <v>239.37</v>
+        <v>232.837</v>
       </c>
       <c r="E111" t="n">
-        <v>70.3489</v>
+        <v>60.6395</v>
       </c>
       <c r="F111" t="n">
-        <v>245.712</v>
+        <v>241.683</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>87.6327</v>
+        <v>80.7248</v>
       </c>
       <c r="C112" t="n">
-        <v>74.29430000000001</v>
+        <v>61.4045</v>
       </c>
       <c r="D112" t="n">
-        <v>240.503</v>
+        <v>231.866</v>
       </c>
       <c r="E112" t="n">
-        <v>59.5007</v>
+        <v>59.0014</v>
       </c>
       <c r="F112" t="n">
-        <v>246.64</v>
+        <v>241.542</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>85.6814</v>
+        <v>78.1902</v>
       </c>
       <c r="C113" t="n">
-        <v>72.3763</v>
+        <v>59.9867</v>
       </c>
       <c r="D113" t="n">
-        <v>237.594</v>
+        <v>233.337</v>
       </c>
       <c r="E113" t="n">
-        <v>57.9761</v>
+        <v>66.1057</v>
       </c>
       <c r="F113" t="n">
-        <v>246.981</v>
+        <v>241.061</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.559</v>
+        <v>83.31950000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>70.693</v>
+        <v>70.24039999999999</v>
       </c>
       <c r="D114" t="n">
-        <v>248.603</v>
+        <v>243.823</v>
       </c>
       <c r="E114" t="n">
-        <v>64.5372</v>
+        <v>64.3182</v>
       </c>
       <c r="F114" t="n">
-        <v>247.352</v>
+        <v>244.236</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>83.1956</v>
+        <v>83.2235</v>
       </c>
       <c r="C115" t="n">
-        <v>68.8305</v>
+        <v>68.6237</v>
       </c>
       <c r="D115" t="n">
-        <v>250.966</v>
+        <v>240.392</v>
       </c>
       <c r="E115" t="n">
-        <v>62.932</v>
+        <v>62.7491</v>
       </c>
       <c r="F115" t="n">
-        <v>248.699</v>
+        <v>244.576</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>82.3165</v>
+        <v>80.29259999999999</v>
       </c>
       <c r="C116" t="n">
-        <v>67.4213</v>
+        <v>66.9267</v>
       </c>
       <c r="D116" t="n">
-        <v>244.151</v>
+        <v>246.008</v>
       </c>
       <c r="E116" t="n">
-        <v>61.305</v>
+        <v>61.1097</v>
       </c>
       <c r="F116" t="n">
-        <v>248.182</v>
+        <v>244.678</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>80.41849999999999</v>
+        <v>77.8856</v>
       </c>
       <c r="C117" t="n">
-        <v>65.8571</v>
+        <v>65.3883</v>
       </c>
       <c r="D117" t="n">
-        <v>247.804</v>
+        <v>245.839</v>
       </c>
       <c r="E117" t="n">
-        <v>59.6619</v>
+        <v>59.4744</v>
       </c>
       <c r="F117" t="n">
-        <v>249.459</v>
+        <v>245.396</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>77.9872</v>
+        <v>71.54349999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>64.4023</v>
+        <v>54.5512</v>
       </c>
       <c r="D118" t="n">
-        <v>237.349</v>
+        <v>232.438</v>
       </c>
       <c r="E118" t="n">
-        <v>51.6532</v>
+        <v>51.4298</v>
       </c>
       <c r="F118" t="n">
-        <v>249.916</v>
+        <v>245.165</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>73.69370000000001</v>
+        <v>76.42400000000001</v>
       </c>
       <c r="C119" t="n">
-        <v>54.7361</v>
+        <v>62.5714</v>
       </c>
       <c r="D119" t="n">
-        <v>238.892</v>
+        <v>233.628</v>
       </c>
       <c r="E119" t="n">
-        <v>50.8521</v>
+        <v>50.418</v>
       </c>
       <c r="F119" t="n">
-        <v>103.008</v>
+        <v>152.924</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>76.25360000000001</v>
+        <v>76.0106</v>
       </c>
       <c r="C120" t="n">
-        <v>61.9129</v>
+        <v>61.3225</v>
       </c>
       <c r="D120" t="n">
-        <v>239.718</v>
+        <v>234.319</v>
       </c>
       <c r="E120" t="n">
-        <v>49.9706</v>
+        <v>49.5099</v>
       </c>
       <c r="F120" t="n">
-        <v>179.392</v>
+        <v>246.7</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>70.1507</v>
+        <v>68.645</v>
       </c>
       <c r="C121" t="n">
-        <v>53.1645</v>
+        <v>52.0142</v>
       </c>
       <c r="D121" t="n">
-        <v>314.252</v>
+        <v>307.425</v>
       </c>
       <c r="E121" t="n">
-        <v>84.9743</v>
+        <v>84.9609</v>
       </c>
       <c r="F121" t="n">
-        <v>298.234</v>
+        <v>294.76</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>72.5067</v>
+        <v>73.1198</v>
       </c>
       <c r="C122" t="n">
-        <v>95.0613</v>
+        <v>94.9576</v>
       </c>
       <c r="D122" t="n">
-        <v>309.508</v>
+        <v>302.816</v>
       </c>
       <c r="E122" t="n">
-        <v>83.1982</v>
+        <v>83.0749</v>
       </c>
       <c r="F122" t="n">
-        <v>297.628</v>
+        <v>293.313</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>68.3331</v>
+        <v>71.5792</v>
       </c>
       <c r="C123" t="n">
-        <v>86.03570000000001</v>
+        <v>93.0206</v>
       </c>
       <c r="D123" t="n">
-        <v>305.28</v>
+        <v>298.96</v>
       </c>
       <c r="E123" t="n">
-        <v>81.2197</v>
+        <v>81.15219999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>297.708</v>
+        <v>292.559</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>98.0711</v>
+        <v>97.53700000000001</v>
       </c>
       <c r="C124" t="n">
-        <v>85.2679</v>
+        <v>84.3425</v>
       </c>
       <c r="D124" t="n">
-        <v>301.793</v>
+        <v>295.548</v>
       </c>
       <c r="E124" t="n">
-        <v>79.3184</v>
+        <v>79.20099999999999</v>
       </c>
       <c r="F124" t="n">
-        <v>296.497</v>
+        <v>291.401</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>99.2559</v>
+        <v>98.6819</v>
       </c>
       <c r="C125" t="n">
-        <v>83.6831</v>
+        <v>82.8291</v>
       </c>
       <c r="D125" t="n">
-        <v>298.583</v>
+        <v>292.328</v>
       </c>
       <c r="E125" t="n">
-        <v>77.74809999999999</v>
+        <v>77.66540000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>296.296</v>
+        <v>291.954</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>97.24809999999999</v>
+        <v>95.22410000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>82.1644</v>
+        <v>81.233</v>
       </c>
       <c r="D126" t="n">
-        <v>295.791</v>
+        <v>290.044</v>
       </c>
       <c r="E126" t="n">
-        <v>76.1153</v>
+        <v>76.0039</v>
       </c>
       <c r="F126" t="n">
-        <v>294.948</v>
+        <v>290.314</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>95.7396</v>
+        <v>98.68040000000001</v>
       </c>
       <c r="C127" t="n">
-        <v>80.91</v>
+        <v>85.75879999999999</v>
       </c>
       <c r="D127" t="n">
-        <v>293.477</v>
+        <v>288.06</v>
       </c>
       <c r="E127" t="n">
-        <v>74.5099</v>
+        <v>78.6982</v>
       </c>
       <c r="F127" t="n">
-        <v>294.68</v>
+        <v>290.451</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>93.80070000000001</v>
+        <v>97.05889999999999</v>
       </c>
       <c r="C128" t="n">
-        <v>79.4811</v>
+        <v>84.12779999999999</v>
       </c>
       <c r="D128" t="n">
-        <v>291.629</v>
+        <v>286.048</v>
       </c>
       <c r="E128" t="n">
-        <v>73.12990000000001</v>
+        <v>72.42529999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>294.513</v>
+        <v>289.779</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>96.2199</v>
+        <v>90.6807</v>
       </c>
       <c r="C129" t="n">
-        <v>83.3766</v>
+        <v>76.3815</v>
       </c>
       <c r="D129" t="n">
-        <v>289.907</v>
+        <v>283.881</v>
       </c>
       <c r="E129" t="n">
-        <v>72.018</v>
+        <v>71.0282</v>
       </c>
       <c r="F129" t="n">
-        <v>294.539</v>
+        <v>289.048</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>94.3948</v>
+        <v>89.53449999999999</v>
       </c>
       <c r="C130" t="n">
-        <v>82.0094</v>
+        <v>75.21729999999999</v>
       </c>
       <c r="D130" t="n">
-        <v>288.998</v>
+        <v>282.815</v>
       </c>
       <c r="E130" t="n">
-        <v>70.7509</v>
+        <v>69.65900000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>293.709</v>
+        <v>288.947</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>90.84439999999999</v>
+        <v>87.8655</v>
       </c>
       <c r="C131" t="n">
-        <v>75.946</v>
+        <v>74.0615</v>
       </c>
       <c r="D131" t="n">
-        <v>287.767</v>
+        <v>281.949</v>
       </c>
       <c r="E131" t="n">
-        <v>69.62309999999999</v>
+        <v>68.5438</v>
       </c>
       <c r="F131" t="n">
-        <v>293.433</v>
+        <v>288.321</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>91.41630000000001</v>
+        <v>88.1395</v>
       </c>
       <c r="C132" t="n">
-        <v>79.2762</v>
+        <v>72.9385</v>
       </c>
       <c r="D132" t="n">
-        <v>287.152</v>
+        <v>281.278</v>
       </c>
       <c r="E132" t="n">
-        <v>68.4718</v>
+        <v>67.47790000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>293.319</v>
+        <v>288.003</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>88.27979999999999</v>
+        <v>85.7328</v>
       </c>
       <c r="C133" t="n">
-        <v>73.9297</v>
+        <v>71.9868</v>
       </c>
       <c r="D133" t="n">
-        <v>287.26</v>
+        <v>281.344</v>
       </c>
       <c r="E133" t="n">
-        <v>67.4044</v>
+        <v>66.52500000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>293.622</v>
+        <v>288.287</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>86.9242</v>
+        <v>84.63339999999999</v>
       </c>
       <c r="C134" t="n">
-        <v>72.8811</v>
+        <v>71.14749999999999</v>
       </c>
       <c r="D134" t="n">
-        <v>282.346</v>
+        <v>278.286</v>
       </c>
       <c r="E134" t="n">
-        <v>60.7783</v>
+        <v>65.5814</v>
       </c>
       <c r="F134" t="n">
-        <v>241.901</v>
+        <v>288.032</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>85.2966</v>
+        <v>83.47490000000001</v>
       </c>
       <c r="C135" t="n">
-        <v>72.16419999999999</v>
+        <v>70.3847</v>
       </c>
       <c r="D135" t="n">
-        <v>360.912</v>
+        <v>352.957</v>
       </c>
       <c r="E135" t="n">
-        <v>95.5425</v>
+        <v>94.9192</v>
       </c>
       <c r="F135" t="n">
-        <v>338.837</v>
+        <v>331.93</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>85.5625</v>
+        <v>79.93340000000001</v>
       </c>
       <c r="C136" t="n">
-        <v>106.415</v>
+        <v>97.34139999999999</v>
       </c>
       <c r="D136" t="n">
-        <v>353.642</v>
+        <v>346.682</v>
       </c>
       <c r="E136" t="n">
-        <v>93.6028</v>
+        <v>92.9413</v>
       </c>
       <c r="F136" t="n">
-        <v>338.582</v>
+        <v>332.036</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>84.6067</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="C137" t="n">
-        <v>104.232</v>
+        <v>102.374</v>
       </c>
       <c r="D137" t="n">
-        <v>348.8</v>
+        <v>341.154</v>
       </c>
       <c r="E137" t="n">
-        <v>92.45399999999999</v>
+        <v>91.1343</v>
       </c>
       <c r="F137" t="n">
-        <v>338.459</v>
+        <v>331.502</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>118.015</v>
+        <v>108.866</v>
       </c>
       <c r="C138" t="n">
-        <v>104.106</v>
+        <v>94.80710000000001</v>
       </c>
       <c r="D138" t="n">
-        <v>343.9</v>
+        <v>336.325</v>
       </c>
       <c r="E138" t="n">
-        <v>90.83329999999999</v>
+        <v>89.42570000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>335.896</v>
+        <v>327.259</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>109.531</v>
+        <v>110.761</v>
       </c>
       <c r="C139" t="n">
-        <v>95.6045</v>
+        <v>93.80159999999999</v>
       </c>
       <c r="D139" t="n">
-        <v>340.089</v>
+        <v>332.082</v>
       </c>
       <c r="E139" t="n">
-        <v>89.105</v>
+        <v>87.9837</v>
       </c>
       <c r="F139" t="n">
-        <v>335.572</v>
+        <v>328.233</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>111.601</v>
+        <v>108.307</v>
       </c>
       <c r="C140" t="n">
-        <v>93.55759999999999</v>
+        <v>92.60980000000001</v>
       </c>
       <c r="D140" t="n">
-        <v>326.324</v>
+        <v>330.169</v>
       </c>
       <c r="E140" t="n">
-        <v>90.22069999999999</v>
+        <v>90.7924</v>
       </c>
       <c r="F140" t="n">
-        <v>326.167</v>
+        <v>327.857</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>105.582</v>
+        <v>110.197</v>
       </c>
       <c r="C141" t="n">
-        <v>91.1011</v>
+        <v>97.28100000000001</v>
       </c>
       <c r="D141" t="n">
-        <v>324.83</v>
+        <v>326.275</v>
       </c>
       <c r="E141" t="n">
-        <v>84.4563</v>
+        <v>88.9188</v>
       </c>
       <c r="F141" t="n">
-        <v>325.72</v>
+        <v>327.186</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>105.051</v>
+        <v>108.638</v>
       </c>
       <c r="C142" t="n">
-        <v>90.0621</v>
+        <v>95.89579999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>323.983</v>
+        <v>325.625</v>
       </c>
       <c r="E142" t="n">
-        <v>83.35599999999999</v>
+        <v>83.3389</v>
       </c>
       <c r="F142" t="n">
-        <v>324.276</v>
+        <v>325.938</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>103.624</v>
+        <v>102.362</v>
       </c>
       <c r="C143" t="n">
-        <v>88.871</v>
+        <v>89.0467</v>
       </c>
       <c r="D143" t="n">
-        <v>322.82</v>
+        <v>323.932</v>
       </c>
       <c r="E143" t="n">
-        <v>82.14960000000001</v>
+        <v>82.4897</v>
       </c>
       <c r="F143" t="n">
-        <v>323.375</v>
+        <v>324.278</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.0997</v>
+        <v>24.0762</v>
       </c>
       <c r="C2" t="n">
-        <v>20.2892</v>
+        <v>20.2937</v>
       </c>
       <c r="D2" t="n">
-        <v>53.7108</v>
+        <v>53.5625</v>
       </c>
       <c r="E2" t="n">
-        <v>18.2422</v>
+        <v>17.5561</v>
       </c>
       <c r="F2" t="n">
-        <v>33.7082</v>
+        <v>32.3824</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.8318</v>
+        <v>23.3991</v>
       </c>
       <c r="C3" t="n">
-        <v>19.7751</v>
+        <v>19.7694</v>
       </c>
       <c r="D3" t="n">
-        <v>53.077</v>
+        <v>52.9713</v>
       </c>
       <c r="E3" t="n">
-        <v>17.6537</v>
+        <v>17.0435</v>
       </c>
       <c r="F3" t="n">
-        <v>33.2733</v>
+        <v>32.005</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>23.107</v>
+        <v>23.3284</v>
       </c>
       <c r="C4" t="n">
-        <v>19.3184</v>
+        <v>19.2641</v>
       </c>
       <c r="D4" t="n">
-        <v>52.5585</v>
+        <v>52.4426</v>
       </c>
       <c r="E4" t="n">
-        <v>17.1704</v>
+        <v>16.5624</v>
       </c>
       <c r="F4" t="n">
-        <v>32.8623</v>
+        <v>31.6943</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.3517</v>
+        <v>22.4221</v>
       </c>
       <c r="C5" t="n">
-        <v>18.8693</v>
+        <v>18.8614</v>
       </c>
       <c r="D5" t="n">
-        <v>52.0827</v>
+        <v>52.0225</v>
       </c>
       <c r="E5" t="n">
-        <v>16.7033</v>
+        <v>25.9546</v>
       </c>
       <c r="F5" t="n">
-        <v>32.576</v>
+        <v>40.5426</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.1431</v>
+        <v>22.5631</v>
       </c>
       <c r="C6" t="n">
-        <v>18.4611</v>
+        <v>18.4948</v>
       </c>
       <c r="D6" t="n">
-        <v>51.664</v>
+        <v>51.5592</v>
       </c>
       <c r="E6" t="n">
-        <v>16.3192</v>
+        <v>24.9427</v>
       </c>
       <c r="F6" t="n">
-        <v>32.4015</v>
+        <v>39.8663</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>21.6312</v>
+        <v>22.2089</v>
       </c>
       <c r="C7" t="n">
-        <v>18.1576</v>
+        <v>18.1848</v>
       </c>
       <c r="D7" t="n">
-        <v>65.9472</v>
+        <v>66.07380000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>25.4818</v>
+        <v>24.105</v>
       </c>
       <c r="F7" t="n">
-        <v>40.9916</v>
+        <v>38.9797</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.4042</v>
+        <v>21.3702</v>
       </c>
       <c r="C8" t="n">
-        <v>26.8684</v>
+        <v>26.934</v>
       </c>
       <c r="D8" t="n">
-        <v>64.2693</v>
+        <v>64.36790000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>24.6652</v>
+        <v>23.3028</v>
       </c>
       <c r="F8" t="n">
-        <v>40.1215</v>
+        <v>38.0439</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.458</v>
+        <v>21.3489</v>
       </c>
       <c r="C9" t="n">
-        <v>26.0327</v>
+        <v>26.0584</v>
       </c>
       <c r="D9" t="n">
-        <v>62.9736</v>
+        <v>63.0016</v>
       </c>
       <c r="E9" t="n">
-        <v>23.8285</v>
+        <v>22.6059</v>
       </c>
       <c r="F9" t="n">
-        <v>39.2185</v>
+        <v>37.241</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>30.1671</v>
+        <v>30.5578</v>
       </c>
       <c r="C10" t="n">
-        <v>25.1664</v>
+        <v>25.2347</v>
       </c>
       <c r="D10" t="n">
-        <v>61.7838</v>
+        <v>61.7734</v>
       </c>
       <c r="E10" t="n">
-        <v>23.0394</v>
+        <v>21.7992</v>
       </c>
       <c r="F10" t="n">
-        <v>38.3855</v>
+        <v>36.4906</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>29.1165</v>
+        <v>29.5858</v>
       </c>
       <c r="C11" t="n">
-        <v>24.3545</v>
+        <v>24.4212</v>
       </c>
       <c r="D11" t="n">
-        <v>60.7229</v>
+        <v>60.65</v>
       </c>
       <c r="E11" t="n">
-        <v>22.2199</v>
+        <v>21.0353</v>
       </c>
       <c r="F11" t="n">
-        <v>37.5083</v>
+        <v>35.7642</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>28.3418</v>
+        <v>28.1558</v>
       </c>
       <c r="C12" t="n">
-        <v>23.6525</v>
+        <v>23.6978</v>
       </c>
       <c r="D12" t="n">
-        <v>59.5929</v>
+        <v>59.5896</v>
       </c>
       <c r="E12" t="n">
-        <v>21.5111</v>
+        <v>20.4105</v>
       </c>
       <c r="F12" t="n">
-        <v>36.7663</v>
+        <v>35.063</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>27.5911</v>
+        <v>27.2384</v>
       </c>
       <c r="C13" t="n">
-        <v>22.8959</v>
+        <v>22.9332</v>
       </c>
       <c r="D13" t="n">
-        <v>58.7376</v>
+        <v>58.6892</v>
       </c>
       <c r="E13" t="n">
-        <v>20.7831</v>
+        <v>19.8083</v>
       </c>
       <c r="F13" t="n">
-        <v>36.04</v>
+        <v>34.4232</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>26.8857</v>
+        <v>26.9471</v>
       </c>
       <c r="C14" t="n">
-        <v>22.1935</v>
+        <v>22.2069</v>
       </c>
       <c r="D14" t="n">
-        <v>57.8923</v>
+        <v>57.9107</v>
       </c>
       <c r="E14" t="n">
-        <v>20.285</v>
+        <v>19.1675</v>
       </c>
       <c r="F14" t="n">
-        <v>35.3952</v>
+        <v>33.888</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>25.8832</v>
+        <v>25.9565</v>
       </c>
       <c r="C15" t="n">
-        <v>21.5895</v>
+        <v>21.5411</v>
       </c>
       <c r="D15" t="n">
-        <v>57.3754</v>
+        <v>57.2786</v>
       </c>
       <c r="E15" t="n">
-        <v>19.6626</v>
+        <v>18.8442</v>
       </c>
       <c r="F15" t="n">
-        <v>34.782</v>
+        <v>33.3254</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>25.7508</v>
+        <v>25.5557</v>
       </c>
       <c r="C16" t="n">
-        <v>20.9431</v>
+        <v>20.9228</v>
       </c>
       <c r="D16" t="n">
-        <v>56.6722</v>
+        <v>57.012</v>
       </c>
       <c r="E16" t="n">
-        <v>19.0296</v>
+        <v>18.5295</v>
       </c>
       <c r="F16" t="n">
-        <v>34.2293</v>
+        <v>32.8585</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>24.6859</v>
+        <v>25.1532</v>
       </c>
       <c r="C17" t="n">
-        <v>20.5342</v>
+        <v>20.4046</v>
       </c>
       <c r="D17" t="n">
-        <v>56.2596</v>
+        <v>56.1807</v>
       </c>
       <c r="E17" t="n">
-        <v>18.4983</v>
+        <v>17.7892</v>
       </c>
       <c r="F17" t="n">
-        <v>33.7361</v>
+        <v>32.4439</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>24.0451</v>
+        <v>23.9048</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8465</v>
+        <v>19.8742</v>
       </c>
       <c r="D18" t="n">
-        <v>55.2909</v>
+        <v>55.5338</v>
       </c>
       <c r="E18" t="n">
-        <v>18.0792</v>
+        <v>17.2327</v>
       </c>
       <c r="F18" t="n">
-        <v>33.3062</v>
+        <v>32.0827</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.4923</v>
+        <v>23.7658</v>
       </c>
       <c r="C19" t="n">
-        <v>19.4026</v>
+        <v>19.3599</v>
       </c>
       <c r="D19" t="n">
-        <v>54.6871</v>
+        <v>54.7333</v>
       </c>
       <c r="E19" t="n">
-        <v>17.6582</v>
+        <v>16.7687</v>
       </c>
       <c r="F19" t="n">
-        <v>32.9381</v>
+        <v>31.7034</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.2438</v>
+        <v>23.0896</v>
       </c>
       <c r="C20" t="n">
-        <v>18.9556</v>
+        <v>18.9722</v>
       </c>
       <c r="D20" t="n">
-        <v>54.0547</v>
+        <v>54.0915</v>
       </c>
       <c r="E20" t="n">
-        <v>17.461</v>
+        <v>26.607</v>
       </c>
       <c r="F20" t="n">
-        <v>32.7028</v>
+        <v>40.3236</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>22.7387</v>
+        <v>23.3263</v>
       </c>
       <c r="C21" t="n">
-        <v>18.656</v>
+        <v>18.7154</v>
       </c>
       <c r="D21" t="n">
-        <v>71.93219999999999</v>
+        <v>71.8643</v>
       </c>
       <c r="E21" t="n">
-        <v>26.6821</v>
+        <v>25.1581</v>
       </c>
       <c r="F21" t="n">
-        <v>41.1678</v>
+        <v>39.5304</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.6916</v>
+        <v>22.491</v>
       </c>
       <c r="C22" t="n">
-        <v>27.3272</v>
+        <v>27.3646</v>
       </c>
       <c r="D22" t="n">
-        <v>70.2497</v>
+        <v>70.2925</v>
       </c>
       <c r="E22" t="n">
-        <v>25.7925</v>
+        <v>24.8955</v>
       </c>
       <c r="F22" t="n">
-        <v>40.3247</v>
+        <v>38.7298</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.6129</v>
+        <v>22.6151</v>
       </c>
       <c r="C23" t="n">
-        <v>26.5179</v>
+        <v>26.5407</v>
       </c>
       <c r="D23" t="n">
-        <v>68.72799999999999</v>
+        <v>68.7546</v>
       </c>
       <c r="E23" t="n">
-        <v>24.8838</v>
+        <v>23.6585</v>
       </c>
       <c r="F23" t="n">
-        <v>39.4914</v>
+        <v>37.9413</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>30.8111</v>
+        <v>30.7411</v>
       </c>
       <c r="C24" t="n">
-        <v>25.6967</v>
+        <v>25.7136</v>
       </c>
       <c r="D24" t="n">
-        <v>67.57769999999999</v>
+        <v>67.5917</v>
       </c>
       <c r="E24" t="n">
-        <v>24.1733</v>
+        <v>22.8941</v>
       </c>
       <c r="F24" t="n">
-        <v>38.704</v>
+        <v>37.1976</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>29.8224</v>
+        <v>29.6767</v>
       </c>
       <c r="C25" t="n">
-        <v>24.9157</v>
+        <v>24.9351</v>
       </c>
       <c r="D25" t="n">
-        <v>66.24550000000001</v>
+        <v>66.2912</v>
       </c>
       <c r="E25" t="n">
-        <v>23.3599</v>
+        <v>22.1509</v>
       </c>
       <c r="F25" t="n">
-        <v>37.8627</v>
+        <v>36.5025</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>28.8342</v>
+        <v>29.2466</v>
       </c>
       <c r="C26" t="n">
-        <v>24.1639</v>
+        <v>24.1903</v>
       </c>
       <c r="D26" t="n">
-        <v>64.8035</v>
+        <v>64.81740000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>22.4705</v>
+        <v>21.2756</v>
       </c>
       <c r="F26" t="n">
-        <v>38.4673</v>
+        <v>35.8221</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.6855</v>
+        <v>28.6266</v>
       </c>
       <c r="C27" t="n">
-        <v>23.4328</v>
+        <v>23.4537</v>
       </c>
       <c r="D27" t="n">
-        <v>63.7868</v>
+        <v>63.8404</v>
       </c>
       <c r="E27" t="n">
-        <v>21.7954</v>
+        <v>20.722</v>
       </c>
       <c r="F27" t="n">
-        <v>37.8537</v>
+        <v>35.1682</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>27.8801</v>
+        <v>27.9216</v>
       </c>
       <c r="C28" t="n">
-        <v>22.7025</v>
+        <v>22.7711</v>
       </c>
       <c r="D28" t="n">
-        <v>62.813</v>
+        <v>62.8472</v>
       </c>
       <c r="E28" t="n">
-        <v>21.2766</v>
+        <v>20.1535</v>
       </c>
       <c r="F28" t="n">
-        <v>37.0343</v>
+        <v>34.5064</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>26.5869</v>
+        <v>26.961</v>
       </c>
       <c r="C29" t="n">
-        <v>22.0826</v>
+        <v>22.1214</v>
       </c>
       <c r="D29" t="n">
-        <v>62.0742</v>
+        <v>62.146</v>
       </c>
       <c r="E29" t="n">
-        <v>20.5485</v>
+        <v>19.497</v>
       </c>
       <c r="F29" t="n">
-        <v>36.2927</v>
+        <v>33.9807</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>26.4437</v>
+        <v>26.2767</v>
       </c>
       <c r="C30" t="n">
-        <v>21.4836</v>
+        <v>21.4847</v>
       </c>
       <c r="D30" t="n">
-        <v>61.1748</v>
+        <v>61.2473</v>
       </c>
       <c r="E30" t="n">
-        <v>19.9142</v>
+        <v>19.0767</v>
       </c>
       <c r="F30" t="n">
-        <v>35.7451</v>
+        <v>33.5035</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.7509</v>
+        <v>25.7473</v>
       </c>
       <c r="C31" t="n">
-        <v>20.88</v>
+        <v>20.9139</v>
       </c>
       <c r="D31" t="n">
-        <v>60.6823</v>
+        <v>60.7258</v>
       </c>
       <c r="E31" t="n">
-        <v>19.4272</v>
+        <v>18.5601</v>
       </c>
       <c r="F31" t="n">
-        <v>33.9965</v>
+        <v>32.9061</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.8588</v>
+        <v>25.0886</v>
       </c>
       <c r="C32" t="n">
-        <v>20.3926</v>
+        <v>20.4114</v>
       </c>
       <c r="D32" t="n">
-        <v>60.1624</v>
+        <v>60.2534</v>
       </c>
       <c r="E32" t="n">
-        <v>18.9392</v>
+        <v>18.1611</v>
       </c>
       <c r="F32" t="n">
-        <v>33.5701</v>
+        <v>32.5312</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>25.298</v>
+        <v>24.3918</v>
       </c>
       <c r="C33" t="n">
-        <v>19.8985</v>
+        <v>19.9047</v>
       </c>
       <c r="D33" t="n">
-        <v>59.7807</v>
+        <v>59.8176</v>
       </c>
       <c r="E33" t="n">
-        <v>18.5996</v>
+        <v>17.6036</v>
       </c>
       <c r="F33" t="n">
-        <v>33.392</v>
+        <v>32.3218</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>23.9293</v>
+        <v>24.0062</v>
       </c>
       <c r="C34" t="n">
-        <v>19.511</v>
+        <v>19.5554</v>
       </c>
       <c r="D34" t="n">
-        <v>58.9502</v>
+        <v>58.9791</v>
       </c>
       <c r="E34" t="n">
-        <v>18.2916</v>
+        <v>26.9116</v>
       </c>
       <c r="F34" t="n">
-        <v>33.0832</v>
+        <v>41.0996</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.6303</v>
+        <v>23.9854</v>
       </c>
       <c r="C35" t="n">
-        <v>19.1431</v>
+        <v>19.151</v>
       </c>
       <c r="D35" t="n">
-        <v>77.1601</v>
+        <v>77.29559999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>27.4924</v>
+        <v>26.3316</v>
       </c>
       <c r="F35" t="n">
-        <v>42.0726</v>
+        <v>40.361</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>23.6239</v>
+        <v>22.9529</v>
       </c>
       <c r="C36" t="n">
-        <v>18.8823</v>
+        <v>18.8577</v>
       </c>
       <c r="D36" t="n">
-        <v>75.4222</v>
+        <v>75.5151</v>
       </c>
       <c r="E36" t="n">
-        <v>26.6964</v>
+        <v>25.2655</v>
       </c>
       <c r="F36" t="n">
-        <v>41.1676</v>
+        <v>39.5804</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.2556</v>
+        <v>23.2329</v>
       </c>
       <c r="C37" t="n">
-        <v>27.0637</v>
+        <v>27.1329</v>
       </c>
       <c r="D37" t="n">
-        <v>73.938</v>
+        <v>73.92789999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>25.7461</v>
+        <v>24.3547</v>
       </c>
       <c r="F37" t="n">
-        <v>40.2028</v>
+        <v>38.8171</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>31.2231</v>
+        <v>31.8479</v>
       </c>
       <c r="C38" t="n">
-        <v>26.2593</v>
+        <v>26.3408</v>
       </c>
       <c r="D38" t="n">
-        <v>72.3948</v>
+        <v>72.4299</v>
       </c>
       <c r="E38" t="n">
-        <v>24.9302</v>
+        <v>23.557</v>
       </c>
       <c r="F38" t="n">
-        <v>39.4102</v>
+        <v>38.112</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>30.4325</v>
+        <v>30.3005</v>
       </c>
       <c r="C39" t="n">
-        <v>25.477</v>
+        <v>25.5297</v>
       </c>
       <c r="D39" t="n">
-        <v>71.0321</v>
+        <v>71.08369999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>24.1716</v>
+        <v>22.9431</v>
       </c>
       <c r="F39" t="n">
-        <v>38.8551</v>
+        <v>37.4496</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>29.971</v>
+        <v>29.4707</v>
       </c>
       <c r="C40" t="n">
-        <v>24.7515</v>
+        <v>24.7896</v>
       </c>
       <c r="D40" t="n">
-        <v>69.8198</v>
+        <v>69.7805</v>
       </c>
       <c r="E40" t="n">
-        <v>23.4152</v>
+        <v>22.1858</v>
       </c>
       <c r="F40" t="n">
-        <v>38.1147</v>
+        <v>36.8474</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>29.1978</v>
+        <v>28.9336</v>
       </c>
       <c r="C41" t="n">
-        <v>23.9957</v>
+        <v>24.0674</v>
       </c>
       <c r="D41" t="n">
-        <v>68.73269999999999</v>
+        <v>68.64149999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>22.9513</v>
+        <v>21.4557</v>
       </c>
       <c r="F41" t="n">
-        <v>37.4374</v>
+        <v>36.2496</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>28.0456</v>
+        <v>28.1275</v>
       </c>
       <c r="C42" t="n">
-        <v>23.2982</v>
+        <v>23.4199</v>
       </c>
       <c r="D42" t="n">
-        <v>67.6249</v>
+        <v>67.8552</v>
       </c>
       <c r="E42" t="n">
-        <v>22.063</v>
+        <v>20.8871</v>
       </c>
       <c r="F42" t="n">
-        <v>36.8235</v>
+        <v>35.6083</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>27.3928</v>
+        <v>27.6371</v>
       </c>
       <c r="C43" t="n">
-        <v>22.7219</v>
+        <v>22.7436</v>
       </c>
       <c r="D43" t="n">
-        <v>66.42700000000001</v>
+        <v>66.50149999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>21.3776</v>
+        <v>20.402</v>
       </c>
       <c r="F43" t="n">
-        <v>36.2669</v>
+        <v>35.1086</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>26.8187</v>
+        <v>26.4792</v>
       </c>
       <c r="C44" t="n">
         <v>22.1397</v>
       </c>
       <c r="D44" t="n">
-        <v>65.6048</v>
+        <v>65.7462</v>
       </c>
       <c r="E44" t="n">
-        <v>20.8332</v>
+        <v>19.8575</v>
       </c>
       <c r="F44" t="n">
-        <v>35.7892</v>
+        <v>34.626</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>25.7901</v>
+        <v>26.2942</v>
       </c>
       <c r="C45" t="n">
-        <v>21.6019</v>
+        <v>21.6532</v>
       </c>
       <c r="D45" t="n">
-        <v>64.9923</v>
+        <v>65.0877</v>
       </c>
       <c r="E45" t="n">
-        <v>20.2689</v>
+        <v>19.3197</v>
       </c>
       <c r="F45" t="n">
-        <v>35.2382</v>
+        <v>34.3202</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>25.6657</v>
+        <v>25.1811</v>
       </c>
       <c r="C46" t="n">
-        <v>21.0399</v>
+        <v>21.0334</v>
       </c>
       <c r="D46" t="n">
-        <v>64.40009999999999</v>
+        <v>64.50239999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>19.8244</v>
+        <v>18.8857</v>
       </c>
       <c r="F46" t="n">
-        <v>34.7286</v>
+        <v>33.8437</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>24.597</v>
+        <v>24.7107</v>
       </c>
       <c r="C47" t="n">
-        <v>20.6813</v>
+        <v>20.6063</v>
       </c>
       <c r="D47" t="n">
-        <v>63.9273</v>
+        <v>63.9867</v>
       </c>
       <c r="E47" t="n">
-        <v>19.4116</v>
+        <v>18.4859</v>
       </c>
       <c r="F47" t="n">
-        <v>34.5806</v>
+        <v>33.5445</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>24.3928</v>
+        <v>24.2738</v>
       </c>
       <c r="C48" t="n">
-        <v>20.2182</v>
+        <v>20.1252</v>
       </c>
       <c r="D48" t="n">
-        <v>63.2166</v>
+        <v>63.2576</v>
       </c>
       <c r="E48" t="n">
-        <v>19.3779</v>
+        <v>27.5997</v>
       </c>
       <c r="F48" t="n">
-        <v>34.2558</v>
+        <v>42.8668</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>24.3107</v>
+        <v>24.2417</v>
       </c>
       <c r="C49" t="n">
-        <v>19.7242</v>
+        <v>19.6563</v>
       </c>
       <c r="D49" t="n">
-        <v>62.8555</v>
+        <v>62.8759</v>
       </c>
       <c r="E49" t="n">
-        <v>18.9339</v>
+        <v>26.8585</v>
       </c>
       <c r="F49" t="n">
-        <v>33.9317</v>
+        <v>42.0282</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>23.5676</v>
+        <v>23.5271</v>
       </c>
       <c r="C50" t="n">
-        <v>19.5348</v>
+        <v>19.5526</v>
       </c>
       <c r="D50" t="n">
-        <v>80.16240000000001</v>
+        <v>80.1726</v>
       </c>
       <c r="E50" t="n">
-        <v>27.5932</v>
+        <v>26.1561</v>
       </c>
       <c r="F50" t="n">
-        <v>42.877</v>
+        <v>41.4184</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>23.5118</v>
+        <v>23.6218</v>
       </c>
       <c r="C51" t="n">
-        <v>28.0706</v>
+        <v>27.9094</v>
       </c>
       <c r="D51" t="n">
-        <v>78.3943</v>
+        <v>78.4057</v>
       </c>
       <c r="E51" t="n">
-        <v>27.177</v>
+        <v>25.2029</v>
       </c>
       <c r="F51" t="n">
-        <v>42.1253</v>
+        <v>40.4936</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>23.6498</v>
+        <v>23.6655</v>
       </c>
       <c r="C52" t="n">
-        <v>27.2211</v>
+        <v>27.0727</v>
       </c>
       <c r="D52" t="n">
-        <v>76.7452</v>
+        <v>76.67359999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>26.1823</v>
+        <v>24.502</v>
       </c>
       <c r="F52" t="n">
-        <v>41.4218</v>
+        <v>39.931</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>31.3421</v>
+        <v>32.6294</v>
       </c>
       <c r="C53" t="n">
-        <v>26.377</v>
+        <v>26.4093</v>
       </c>
       <c r="D53" t="n">
-        <v>75.19450000000001</v>
+        <v>75.15479999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>25.4319</v>
+        <v>24.0073</v>
       </c>
       <c r="F53" t="n">
-        <v>40.6623</v>
+        <v>39.273</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>30.6736</v>
+        <v>30.4206</v>
       </c>
       <c r="C54" t="n">
-        <v>25.6668</v>
+        <v>25.6122</v>
       </c>
       <c r="D54" t="n">
-        <v>73.7756</v>
+        <v>73.73569999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>24.5594</v>
+        <v>23.0126</v>
       </c>
       <c r="F54" t="n">
-        <v>40.1027</v>
+        <v>38.6649</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>30.1671</v>
+        <v>29.6119</v>
       </c>
       <c r="C55" t="n">
-        <v>24.9905</v>
+        <v>24.9705</v>
       </c>
       <c r="D55" t="n">
-        <v>72.58410000000001</v>
+        <v>72.54519999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>23.7797</v>
+        <v>22.4696</v>
       </c>
       <c r="F55" t="n">
-        <v>39.5106</v>
+        <v>38.0273</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>29.1309</v>
+        <v>28.8312</v>
       </c>
       <c r="C56" t="n">
-        <v>24.3205</v>
+        <v>24.2916</v>
       </c>
       <c r="D56" t="n">
-        <v>71.4877</v>
+        <v>71.4648</v>
       </c>
       <c r="E56" t="n">
-        <v>23.097</v>
+        <v>21.8255</v>
       </c>
       <c r="F56" t="n">
-        <v>38.8857</v>
+        <v>37.5298</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>28.9579</v>
+        <v>28.3599</v>
       </c>
       <c r="C57" t="n">
-        <v>23.7598</v>
+        <v>23.8208</v>
       </c>
       <c r="D57" t="n">
-        <v>70.2591</v>
+        <v>70.2402</v>
       </c>
       <c r="E57" t="n">
-        <v>22.3198</v>
+        <v>21.4215</v>
       </c>
       <c r="F57" t="n">
-        <v>38.2099</v>
+        <v>37.2157</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>28.4861</v>
+        <v>27.9324</v>
       </c>
       <c r="C58" t="n">
-        <v>23.1619</v>
+        <v>23.1472</v>
       </c>
       <c r="D58" t="n">
-        <v>69.43300000000001</v>
+        <v>69.378</v>
       </c>
       <c r="E58" t="n">
-        <v>21.8077</v>
+        <v>20.7993</v>
       </c>
       <c r="F58" t="n">
-        <v>37.7582</v>
+        <v>36.7401</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.1852</v>
+        <v>27.6105</v>
       </c>
       <c r="C59" t="n">
-        <v>22.7269</v>
+        <v>22.5827</v>
       </c>
       <c r="D59" t="n">
-        <v>68.5539</v>
+        <v>68.5183</v>
       </c>
       <c r="E59" t="n">
-        <v>21.6002</v>
+        <v>20.2516</v>
       </c>
       <c r="F59" t="n">
-        <v>37.4814</v>
+        <v>36.4165</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>26.8433</v>
+        <v>26.3892</v>
       </c>
       <c r="C60" t="n">
-        <v>22.2997</v>
+        <v>22.089</v>
       </c>
       <c r="D60" t="n">
-        <v>67.9404</v>
+        <v>67.875</v>
       </c>
       <c r="E60" t="n">
-        <v>20.9715</v>
+        <v>19.8803</v>
       </c>
       <c r="F60" t="n">
-        <v>37.1387</v>
+        <v>36.0734</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.5531</v>
+        <v>26.1055</v>
       </c>
       <c r="C61" t="n">
-        <v>21.9234</v>
+        <v>21.8322</v>
       </c>
       <c r="D61" t="n">
-        <v>67.2124</v>
+        <v>67.1026</v>
       </c>
       <c r="E61" t="n">
-        <v>20.5938</v>
+        <v>19.4198</v>
       </c>
       <c r="F61" t="n">
-        <v>36.8207</v>
+        <v>35.8239</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>25.9667</v>
+        <v>25.88</v>
       </c>
       <c r="C62" t="n">
-        <v>21.4044</v>
+        <v>21.2073</v>
       </c>
       <c r="D62" t="n">
-        <v>66.5365</v>
+        <v>66.422</v>
       </c>
       <c r="E62" t="n">
-        <v>20.1708</v>
+        <v>19.3797</v>
       </c>
       <c r="F62" t="n">
-        <v>36.6554</v>
+        <v>35.6392</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>25.386</v>
+        <v>25.026</v>
       </c>
       <c r="C63" t="n">
-        <v>21.057</v>
+        <v>20.8573</v>
       </c>
       <c r="D63" t="n">
-        <v>66.1189</v>
+        <v>66.0592</v>
       </c>
       <c r="E63" t="n">
-        <v>19.8672</v>
+        <v>31.8285</v>
       </c>
       <c r="F63" t="n">
-        <v>36.5308</v>
+        <v>44.8794</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.2635</v>
+        <v>25.3795</v>
       </c>
       <c r="C64" t="n">
-        <v>20.7509</v>
+        <v>20.6199</v>
       </c>
       <c r="D64" t="n">
-        <v>86.97799999999999</v>
+        <v>87.3933</v>
       </c>
       <c r="E64" t="n">
-        <v>32.4914</v>
+        <v>31.0475</v>
       </c>
       <c r="F64" t="n">
-        <v>46.6227</v>
+        <v>44.3309</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.0237</v>
+        <v>25.5167</v>
       </c>
       <c r="C65" t="n">
-        <v>29.5784</v>
+        <v>29.5778</v>
       </c>
       <c r="D65" t="n">
-        <v>84.7928</v>
+        <v>85.3502</v>
       </c>
       <c r="E65" t="n">
-        <v>31.5361</v>
+        <v>30.239</v>
       </c>
       <c r="F65" t="n">
-        <v>46.051</v>
+        <v>43.6903</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.0173</v>
+        <v>25.1907</v>
       </c>
       <c r="C66" t="n">
-        <v>29.0005</v>
+        <v>28.9279</v>
       </c>
       <c r="D66" t="n">
-        <v>83.01139999999999</v>
+        <v>83.5467</v>
       </c>
       <c r="E66" t="n">
-        <v>29.8578</v>
+        <v>30.0125</v>
       </c>
       <c r="F66" t="n">
-        <v>45.3623</v>
+        <v>43.2531</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>39.7823</v>
+        <v>39.134</v>
       </c>
       <c r="C67" t="n">
-        <v>28.4083</v>
+        <v>28.3137</v>
       </c>
       <c r="D67" t="n">
-        <v>81.3373</v>
+        <v>81.84950000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>29.1083</v>
+        <v>28.6058</v>
       </c>
       <c r="F67" t="n">
-        <v>44.8375</v>
+        <v>42.6353</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>39.6109</v>
+        <v>39.0131</v>
       </c>
       <c r="C68" t="n">
-        <v>27.6701</v>
+        <v>27.7161</v>
       </c>
       <c r="D68" t="n">
-        <v>79.8571</v>
+        <v>80.36020000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>28.4742</v>
+        <v>27.9622</v>
       </c>
       <c r="F68" t="n">
-        <v>44.2123</v>
+        <v>42.1286</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>38.8491</v>
+        <v>39.326</v>
       </c>
       <c r="C69" t="n">
-        <v>27.2157</v>
+        <v>27.1728</v>
       </c>
       <c r="D69" t="n">
-        <v>78.5275</v>
+        <v>78.84829999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>28.3375</v>
+        <v>27.2149</v>
       </c>
       <c r="F69" t="n">
-        <v>43.4254</v>
+        <v>41.4738</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>38.2291</v>
+        <v>40.0769</v>
       </c>
       <c r="C70" t="n">
-        <v>26.5954</v>
+        <v>26.6548</v>
       </c>
       <c r="D70" t="n">
-        <v>77.5993</v>
+        <v>77.81399999999999</v>
       </c>
       <c r="E70" t="n">
-        <v>27.6998</v>
+        <v>26.6976</v>
       </c>
       <c r="F70" t="n">
-        <v>42.9693</v>
+        <v>41.1459</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>35.7942</v>
+        <v>37.9637</v>
       </c>
       <c r="C71" t="n">
-        <v>26.1654</v>
+        <v>26.2514</v>
       </c>
       <c r="D71" t="n">
-        <v>76.813</v>
+        <v>76.9646</v>
       </c>
       <c r="E71" t="n">
-        <v>26.3495</v>
+        <v>26.4489</v>
       </c>
       <c r="F71" t="n">
-        <v>42.4521</v>
+        <v>40.6885</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>36.8912</v>
+        <v>35.8097</v>
       </c>
       <c r="C72" t="n">
-        <v>25.7295</v>
+        <v>25.8109</v>
       </c>
       <c r="D72" t="n">
-        <v>76.1987</v>
+        <v>76.30419999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>26.2832</v>
+        <v>26.0261</v>
       </c>
       <c r="F72" t="n">
-        <v>42.1306</v>
+        <v>40.4058</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>35.3885</v>
+        <v>35.4461</v>
       </c>
       <c r="C73" t="n">
-        <v>25.2043</v>
+        <v>25.2981</v>
       </c>
       <c r="D73" t="n">
-        <v>75.7355</v>
+        <v>75.8505</v>
       </c>
       <c r="E73" t="n">
-        <v>26.0089</v>
+        <v>25.373</v>
       </c>
       <c r="F73" t="n">
-        <v>41.8499</v>
+        <v>40.0744</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>35.6344</v>
+        <v>35.5404</v>
       </c>
       <c r="C74" t="n">
-        <v>24.8008</v>
+        <v>24.8689</v>
       </c>
       <c r="D74" t="n">
-        <v>75.26090000000001</v>
+        <v>75.2004</v>
       </c>
       <c r="E74" t="n">
-        <v>24.7531</v>
+        <v>24.4834</v>
       </c>
       <c r="F74" t="n">
-        <v>41.4987</v>
+        <v>39.885</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>33.7643</v>
+        <v>34.8649</v>
       </c>
       <c r="C75" t="n">
-        <v>24.3865</v>
+        <v>24.4466</v>
       </c>
       <c r="D75" t="n">
-        <v>74.4302</v>
+        <v>74.3292</v>
       </c>
       <c r="E75" t="n">
-        <v>24.2109</v>
+        <v>24.4719</v>
       </c>
       <c r="F75" t="n">
-        <v>41.1009</v>
+        <v>39.7365</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>34.3579</v>
+        <v>34.7823</v>
       </c>
       <c r="C76" t="n">
-        <v>24.1056</v>
+        <v>24.1226</v>
       </c>
       <c r="D76" t="n">
-        <v>74.4314</v>
+        <v>74.3672</v>
       </c>
       <c r="E76" t="n">
-        <v>23.8221</v>
+        <v>23.6087</v>
       </c>
       <c r="F76" t="n">
-        <v>41.0325</v>
+        <v>39.5765</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>33.9932</v>
+        <v>34.1382</v>
       </c>
       <c r="C77" t="n">
-        <v>23.6554</v>
+        <v>23.7208</v>
       </c>
       <c r="D77" t="n">
-        <v>74.8462</v>
+        <v>74.7081</v>
       </c>
       <c r="E77" t="n">
-        <v>23.8233</v>
+        <v>41.6825</v>
       </c>
       <c r="F77" t="n">
-        <v>40.9487</v>
+        <v>65.5616</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>33.8442</v>
+        <v>36.7127</v>
       </c>
       <c r="C78" t="n">
-        <v>23.3963</v>
+        <v>23.4252</v>
       </c>
       <c r="D78" t="n">
-        <v>122.275</v>
+        <v>122.05</v>
       </c>
       <c r="E78" t="n">
-        <v>40.272</v>
+        <v>41.0421</v>
       </c>
       <c r="F78" t="n">
-        <v>65.5094</v>
+        <v>65.34350000000001</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>34.695</v>
+        <v>36.2767</v>
       </c>
       <c r="C79" t="n">
-        <v>33.0865</v>
+        <v>33.1348</v>
       </c>
       <c r="D79" t="n">
-        <v>120.014</v>
+        <v>119.865</v>
       </c>
       <c r="E79" t="n">
-        <v>40.0336</v>
+        <v>40.0376</v>
       </c>
       <c r="F79" t="n">
-        <v>65.8711</v>
+        <v>65.0672</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>34.8599</v>
+        <v>32.8032</v>
       </c>
       <c r="C80" t="n">
-        <v>32.8168</v>
+        <v>32.8778</v>
       </c>
       <c r="D80" t="n">
-        <v>118.308</v>
+        <v>118.507</v>
       </c>
       <c r="E80" t="n">
-        <v>38.7408</v>
+        <v>39.1223</v>
       </c>
       <c r="F80" t="n">
-        <v>65.53149999999999</v>
+        <v>64.4175</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>48.6928</v>
+        <v>51.677</v>
       </c>
       <c r="C81" t="n">
-        <v>32.5064</v>
+        <v>32.5286</v>
       </c>
       <c r="D81" t="n">
-        <v>116.705</v>
+        <v>116.721</v>
       </c>
       <c r="E81" t="n">
-        <v>38.0436</v>
+        <v>38.1324</v>
       </c>
       <c r="F81" t="n">
-        <v>64.8702</v>
+        <v>63.8556</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>51.0567</v>
+        <v>49.9434</v>
       </c>
       <c r="C82" t="n">
-        <v>32.2249</v>
+        <v>32.1367</v>
       </c>
       <c r="D82" t="n">
-        <v>115.41</v>
+        <v>115.408</v>
       </c>
       <c r="E82" t="n">
-        <v>37.0063</v>
+        <v>36.9392</v>
       </c>
       <c r="F82" t="n">
-        <v>64.0866</v>
+        <v>62.8588</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>47.8144</v>
+        <v>45.8548</v>
       </c>
       <c r="C83" t="n">
-        <v>31.8858</v>
+        <v>31.8391</v>
       </c>
       <c r="D83" t="n">
-        <v>114.069</v>
+        <v>114.565</v>
       </c>
       <c r="E83" t="n">
-        <v>36.0568</v>
+        <v>36.1082</v>
       </c>
       <c r="F83" t="n">
-        <v>62.8072</v>
+        <v>62.0767</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.03</v>
+        <v>43.1052</v>
       </c>
       <c r="C84" t="n">
-        <v>31.5399</v>
+        <v>31.4963</v>
       </c>
       <c r="D84" t="n">
-        <v>113.704</v>
+        <v>114.177</v>
       </c>
       <c r="E84" t="n">
-        <v>34.893</v>
+        <v>35.182</v>
       </c>
       <c r="F84" t="n">
-        <v>62.132</v>
+        <v>60.8396</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>44.0107</v>
+        <v>47.7361</v>
       </c>
       <c r="C85" t="n">
-        <v>31.1535</v>
+        <v>31.08</v>
       </c>
       <c r="D85" t="n">
-        <v>113.605</v>
+        <v>114.075</v>
       </c>
       <c r="E85" t="n">
-        <v>34.3023</v>
+        <v>34.3344</v>
       </c>
       <c r="F85" t="n">
-        <v>61.1425</v>
+        <v>60.3703</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>43.5224</v>
+        <v>45.3631</v>
       </c>
       <c r="C86" t="n">
-        <v>30.8098</v>
+        <v>30.8341</v>
       </c>
       <c r="D86" t="n">
-        <v>113.796</v>
+        <v>114.136</v>
       </c>
       <c r="E86" t="n">
-        <v>33.3348</v>
+        <v>33.2669</v>
       </c>
       <c r="F86" t="n">
-        <v>60.3445</v>
+        <v>59.3206</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>45.0531</v>
+        <v>46.8204</v>
       </c>
       <c r="C87" t="n">
-        <v>30.5355</v>
+        <v>30.4186</v>
       </c>
       <c r="D87" t="n">
-        <v>113.944</v>
+        <v>114.376</v>
       </c>
       <c r="E87" t="n">
-        <v>32.5799</v>
+        <v>32.5555</v>
       </c>
       <c r="F87" t="n">
-        <v>59.338</v>
+        <v>58.4144</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>44.0017</v>
+        <v>46.0722</v>
       </c>
       <c r="C88" t="n">
-        <v>30.1399</v>
+        <v>30.0782</v>
       </c>
       <c r="D88" t="n">
-        <v>114.885</v>
+        <v>115.238</v>
       </c>
       <c r="E88" t="n">
-        <v>31.8961</v>
+        <v>31.8454</v>
       </c>
       <c r="F88" t="n">
-        <v>58.7536</v>
+        <v>57.5472</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>45.6421</v>
+        <v>44.4402</v>
       </c>
       <c r="C89" t="n">
-        <v>29.8797</v>
+        <v>29.8421</v>
       </c>
       <c r="D89" t="n">
-        <v>114.934</v>
+        <v>115.851</v>
       </c>
       <c r="E89" t="n">
-        <v>31.1385</v>
+        <v>31.2186</v>
       </c>
       <c r="F89" t="n">
-        <v>58.3767</v>
+        <v>56.6829</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>42.1805</v>
+        <v>43.1161</v>
       </c>
       <c r="C90" t="n">
-        <v>29.5208</v>
+        <v>29.5669</v>
       </c>
       <c r="D90" t="n">
-        <v>116.678</v>
+        <v>117.606</v>
       </c>
       <c r="E90" t="n">
-        <v>30.6076</v>
+        <v>30.6061</v>
       </c>
       <c r="F90" t="n">
-        <v>57.6616</v>
+        <v>56.2776</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>44.0537</v>
+        <v>42.8381</v>
       </c>
       <c r="C91" t="n">
-        <v>29.2868</v>
+        <v>29.2566</v>
       </c>
       <c r="D91" t="n">
-        <v>118.012</v>
+        <v>118.353</v>
       </c>
       <c r="E91" t="n">
-        <v>30.1008</v>
+        <v>66.0938</v>
       </c>
       <c r="F91" t="n">
-        <v>56.962</v>
+        <v>87.71080000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>42.0445</v>
+        <v>45.4307</v>
       </c>
       <c r="C92" t="n">
-        <v>29.0301</v>
+        <v>28.8908</v>
       </c>
       <c r="D92" t="n">
-        <v>176.436</v>
+        <v>177.156</v>
       </c>
       <c r="E92" t="n">
-        <v>64.0582</v>
+        <v>64.61190000000001</v>
       </c>
       <c r="F92" t="n">
-        <v>89.11190000000001</v>
+        <v>87.73390000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>40.8764</v>
+        <v>48.3555</v>
       </c>
       <c r="C93" t="n">
-        <v>28.6488</v>
+        <v>28.8852</v>
       </c>
       <c r="D93" t="n">
-        <v>175.986</v>
+        <v>176.99</v>
       </c>
       <c r="E93" t="n">
-        <v>62.8586</v>
+        <v>62.5363</v>
       </c>
       <c r="F93" t="n">
-        <v>88.3254</v>
+        <v>86.2398</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>45.0404</v>
+        <v>45.5429</v>
       </c>
       <c r="C94" t="n">
-        <v>61.7203</v>
+        <v>61.932</v>
       </c>
       <c r="D94" t="n">
-        <v>174.847</v>
+        <v>175.757</v>
       </c>
       <c r="E94" t="n">
-        <v>61.1153</v>
+        <v>60.8163</v>
       </c>
       <c r="F94" t="n">
-        <v>86.98050000000001</v>
+        <v>85.43640000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>76.3813</v>
+        <v>76.8952</v>
       </c>
       <c r="C95" t="n">
-        <v>60.6309</v>
+        <v>60.759</v>
       </c>
       <c r="D95" t="n">
-        <v>173.861</v>
+        <v>174.538</v>
       </c>
       <c r="E95" t="n">
-        <v>59.1808</v>
+        <v>58.8653</v>
       </c>
       <c r="F95" t="n">
-        <v>86.9233</v>
+        <v>85.54510000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>75.5757</v>
+        <v>74.7257</v>
       </c>
       <c r="C96" t="n">
-        <v>59.0884</v>
+        <v>59.3094</v>
       </c>
       <c r="D96" t="n">
-        <v>173.058</v>
+        <v>173.901</v>
       </c>
       <c r="E96" t="n">
-        <v>57.4206</v>
+        <v>56.9874</v>
       </c>
       <c r="F96" t="n">
-        <v>85.3309</v>
+        <v>84.2993</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>75.459</v>
+        <v>72.59610000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>57.7262</v>
+        <v>57.7918</v>
       </c>
       <c r="D97" t="n">
-        <v>172.38</v>
+        <v>173.317</v>
       </c>
       <c r="E97" t="n">
-        <v>55.5482</v>
+        <v>55.1056</v>
       </c>
       <c r="F97" t="n">
-        <v>83.96040000000001</v>
+        <v>83.61960000000001</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>71.3771</v>
+        <v>72.8045</v>
       </c>
       <c r="C98" t="n">
-        <v>56.2855</v>
+        <v>56.4035</v>
       </c>
       <c r="D98" t="n">
-        <v>172.128</v>
+        <v>173.091</v>
       </c>
       <c r="E98" t="n">
-        <v>53.7922</v>
+        <v>53.4947</v>
       </c>
       <c r="F98" t="n">
-        <v>82.8356</v>
+        <v>81.7564</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>68.6409</v>
+        <v>70.0684</v>
       </c>
       <c r="C99" t="n">
-        <v>55.0402</v>
+        <v>55.1271</v>
       </c>
       <c r="D99" t="n">
-        <v>172.228</v>
+        <v>172.914</v>
       </c>
       <c r="E99" t="n">
-        <v>52.354</v>
+        <v>51.8871</v>
       </c>
       <c r="F99" t="n">
-        <v>83.0048</v>
+        <v>81.2115</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>66.7229</v>
+        <v>69.3828</v>
       </c>
       <c r="C100" t="n">
-        <v>53.76</v>
+        <v>53.8696</v>
       </c>
       <c r="D100" t="n">
-        <v>172.995</v>
+        <v>173.276</v>
       </c>
       <c r="E100" t="n">
-        <v>50.8531</v>
+        <v>50.388</v>
       </c>
       <c r="F100" t="n">
-        <v>83.0654</v>
+        <v>80.16030000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>67.97539999999999</v>
+        <v>68.1828</v>
       </c>
       <c r="C101" t="n">
-        <v>52.6378</v>
+        <v>52.6317</v>
       </c>
       <c r="D101" t="n">
-        <v>172.609</v>
+        <v>172.787</v>
       </c>
       <c r="E101" t="n">
-        <v>49.489</v>
+        <v>48.9883</v>
       </c>
       <c r="F101" t="n">
-        <v>83.10290000000001</v>
+        <v>80.4567</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>66.52979999999999</v>
+        <v>66.9671</v>
       </c>
       <c r="C102" t="n">
-        <v>51.4743</v>
+        <v>51.4586</v>
       </c>
       <c r="D102" t="n">
-        <v>173.716</v>
+        <v>174.47</v>
       </c>
       <c r="E102" t="n">
-        <v>48.1197</v>
+        <v>47.7139</v>
       </c>
       <c r="F102" t="n">
-        <v>79.8886</v>
+        <v>79.2975</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>65.21129999999999</v>
+        <v>66.771</v>
       </c>
       <c r="C103" t="n">
-        <v>50.3573</v>
+        <v>50.4832</v>
       </c>
       <c r="D103" t="n">
-        <v>175.612</v>
+        <v>176.448</v>
       </c>
       <c r="E103" t="n">
-        <v>46.8815</v>
+        <v>46.3921</v>
       </c>
       <c r="F103" t="n">
-        <v>78.77500000000001</v>
+        <v>78.4718</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>64.15779999999999</v>
+        <v>63.4577</v>
       </c>
       <c r="C104" t="n">
-        <v>49.3873</v>
+        <v>49.4771</v>
       </c>
       <c r="D104" t="n">
-        <v>177.312</v>
+        <v>177.091</v>
       </c>
       <c r="E104" t="n">
-        <v>45.6269</v>
+        <v>45.2715</v>
       </c>
       <c r="F104" t="n">
-        <v>77.9122</v>
+        <v>77.2139</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>63.0275</v>
+        <v>63.2704</v>
       </c>
       <c r="C105" t="n">
-        <v>48.3987</v>
+        <v>48.5191</v>
       </c>
       <c r="D105" t="n">
-        <v>177.32</v>
+        <v>179.168</v>
       </c>
       <c r="E105" t="n">
-        <v>44.5922</v>
+        <v>82.7152</v>
       </c>
       <c r="F105" t="n">
-        <v>78.1538</v>
+        <v>238.436</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>62.4536</v>
+        <v>60.7328</v>
       </c>
       <c r="C106" t="n">
-        <v>47.5397</v>
+        <v>47.5931</v>
       </c>
       <c r="D106" t="n">
-        <v>179.991</v>
+        <v>180.156</v>
       </c>
       <c r="E106" t="n">
-        <v>43.7577</v>
+        <v>80.6306</v>
       </c>
       <c r="F106" t="n">
-        <v>78.2422</v>
+        <v>240.857</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>60.5865</v>
+        <v>61.6603</v>
       </c>
       <c r="C107" t="n">
-        <v>46.75</v>
+        <v>46.7667</v>
       </c>
       <c r="D107" t="n">
-        <v>240.54</v>
+        <v>241.626</v>
       </c>
       <c r="E107" t="n">
-        <v>78.485</v>
+        <v>78.3994</v>
       </c>
       <c r="F107" t="n">
-        <v>240.57</v>
+        <v>240.047</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>60.5475</v>
+        <v>61.2997</v>
       </c>
       <c r="C108" t="n">
-        <v>81.5801</v>
+        <v>81.8651</v>
       </c>
       <c r="D108" t="n">
-        <v>237.822</v>
+        <v>238.427</v>
       </c>
       <c r="E108" t="n">
-        <v>65.70610000000001</v>
+        <v>76.0896</v>
       </c>
       <c r="F108" t="n">
-        <v>240.352</v>
+        <v>239.547</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>51.6102</v>
+        <v>59.7564</v>
       </c>
       <c r="C109" t="n">
-        <v>65.84269999999999</v>
+        <v>79.81870000000001</v>
       </c>
       <c r="D109" t="n">
-        <v>235.927</v>
+        <v>237.603</v>
       </c>
       <c r="E109" t="n">
-        <v>74.28619999999999</v>
+        <v>73.7396</v>
       </c>
       <c r="F109" t="n">
-        <v>241.684</v>
+        <v>241.375</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>84.595</v>
+        <v>92.50369999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>64.31140000000001</v>
+        <v>77.99160000000001</v>
       </c>
       <c r="D110" t="n">
-        <v>234.518</v>
+        <v>234.96</v>
       </c>
       <c r="E110" t="n">
-        <v>72.2672</v>
+        <v>71.5583</v>
       </c>
       <c r="F110" t="n">
-        <v>240.314</v>
+        <v>241.765</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>88.94</v>
+        <v>79.4755</v>
       </c>
       <c r="C111" t="n">
-        <v>76.05329999999999</v>
+        <v>62.9594</v>
       </c>
       <c r="D111" t="n">
-        <v>232.837</v>
+        <v>233.998</v>
       </c>
       <c r="E111" t="n">
-        <v>60.6395</v>
+        <v>60.2359</v>
       </c>
       <c r="F111" t="n">
-        <v>241.683</v>
+        <v>240.53</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>80.7248</v>
+        <v>86.0622</v>
       </c>
       <c r="C112" t="n">
-        <v>61.4045</v>
+        <v>73.96850000000001</v>
       </c>
       <c r="D112" t="n">
-        <v>231.866</v>
+        <v>233.38</v>
       </c>
       <c r="E112" t="n">
-        <v>59.0014</v>
+        <v>58.6111</v>
       </c>
       <c r="F112" t="n">
-        <v>241.542</v>
+        <v>242.096</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>78.1902</v>
+        <v>84.1707</v>
       </c>
       <c r="C113" t="n">
-        <v>59.9867</v>
+        <v>72.0749</v>
       </c>
       <c r="D113" t="n">
-        <v>233.337</v>
+        <v>234.416</v>
       </c>
       <c r="E113" t="n">
-        <v>66.1057</v>
+        <v>65.4704</v>
       </c>
       <c r="F113" t="n">
-        <v>241.061</v>
+        <v>241.153</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>83.31950000000001</v>
+        <v>84.5827</v>
       </c>
       <c r="C114" t="n">
-        <v>70.24039999999999</v>
+        <v>70.2914</v>
       </c>
       <c r="D114" t="n">
-        <v>243.823</v>
+        <v>238.618</v>
       </c>
       <c r="E114" t="n">
-        <v>64.3182</v>
+        <v>55.7351</v>
       </c>
       <c r="F114" t="n">
-        <v>244.236</v>
+        <v>221.361</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>83.2235</v>
+        <v>81.66759999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>68.6237</v>
+        <v>68.59</v>
       </c>
       <c r="D115" t="n">
-        <v>240.392</v>
+        <v>243.252</v>
       </c>
       <c r="E115" t="n">
-        <v>62.7491</v>
+        <v>62.0613</v>
       </c>
       <c r="F115" t="n">
-        <v>244.576</v>
+        <v>242.88</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>80.29259999999999</v>
+        <v>81.7591</v>
       </c>
       <c r="C116" t="n">
-        <v>66.9267</v>
+        <v>66.9362</v>
       </c>
       <c r="D116" t="n">
-        <v>246.008</v>
+        <v>244.556</v>
       </c>
       <c r="E116" t="n">
-        <v>61.1097</v>
+        <v>60.44</v>
       </c>
       <c r="F116" t="n">
-        <v>244.678</v>
+        <v>243.722</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>77.8856</v>
+        <v>80</v>
       </c>
       <c r="C117" t="n">
-        <v>65.3883</v>
+        <v>65.3552</v>
       </c>
       <c r="D117" t="n">
-        <v>245.839</v>
+        <v>244.501</v>
       </c>
       <c r="E117" t="n">
-        <v>59.4744</v>
+        <v>51.9313</v>
       </c>
       <c r="F117" t="n">
-        <v>245.396</v>
+        <v>243.715</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>71.54349999999999</v>
+        <v>73.7285</v>
       </c>
       <c r="C118" t="n">
-        <v>54.5512</v>
+        <v>54.5313</v>
       </c>
       <c r="D118" t="n">
-        <v>232.438</v>
+        <v>232.536</v>
       </c>
       <c r="E118" t="n">
-        <v>51.4298</v>
+        <v>50.9732</v>
       </c>
       <c r="F118" t="n">
-        <v>245.165</v>
+        <v>244.029</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>76.42400000000001</v>
+        <v>77.1593</v>
       </c>
       <c r="C119" t="n">
-        <v>62.5714</v>
+        <v>62.5716</v>
       </c>
       <c r="D119" t="n">
-        <v>233.628</v>
+        <v>233.502</v>
       </c>
       <c r="E119" t="n">
-        <v>50.418</v>
+        <v>88.75069999999999</v>
       </c>
       <c r="F119" t="n">
-        <v>152.924</v>
+        <v>293.025</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>76.0106</v>
+        <v>71.7234</v>
       </c>
       <c r="C120" t="n">
-        <v>61.3225</v>
+        <v>52.8458</v>
       </c>
       <c r="D120" t="n">
-        <v>234.319</v>
+        <v>234.638</v>
       </c>
       <c r="E120" t="n">
-        <v>49.5099</v>
+        <v>86.863</v>
       </c>
       <c r="F120" t="n">
-        <v>246.7</v>
+        <v>292.041</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>68.645</v>
+        <v>69.9944</v>
       </c>
       <c r="C121" t="n">
-        <v>52.0142</v>
+        <v>52.0615</v>
       </c>
       <c r="D121" t="n">
-        <v>307.425</v>
+        <v>307.571</v>
       </c>
       <c r="E121" t="n">
-        <v>84.9609</v>
+        <v>84.76430000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>294.76</v>
+        <v>291.809</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>73.1198</v>
+        <v>66.70099999999999</v>
       </c>
       <c r="C122" t="n">
-        <v>94.9576</v>
+        <v>87.24299999999999</v>
       </c>
       <c r="D122" t="n">
-        <v>302.816</v>
+        <v>303.421</v>
       </c>
       <c r="E122" t="n">
-        <v>83.0749</v>
+        <v>82.9148</v>
       </c>
       <c r="F122" t="n">
-        <v>293.313</v>
+        <v>291.54</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>71.5792</v>
+        <v>67.3064</v>
       </c>
       <c r="C123" t="n">
-        <v>93.0206</v>
+        <v>85.68340000000001</v>
       </c>
       <c r="D123" t="n">
-        <v>298.96</v>
+        <v>299.028</v>
       </c>
       <c r="E123" t="n">
-        <v>81.15219999999999</v>
+        <v>80.943</v>
       </c>
       <c r="F123" t="n">
-        <v>292.559</v>
+        <v>290.917</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>97.53700000000001</v>
+        <v>99.0612</v>
       </c>
       <c r="C124" t="n">
-        <v>84.3425</v>
+        <v>84.6221</v>
       </c>
       <c r="D124" t="n">
-        <v>295.548</v>
+        <v>295.441</v>
       </c>
       <c r="E124" t="n">
-        <v>79.20099999999999</v>
+        <v>79.2111</v>
       </c>
       <c r="F124" t="n">
-        <v>291.401</v>
+        <v>290.199</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>98.6819</v>
+        <v>97.6377</v>
       </c>
       <c r="C125" t="n">
-        <v>82.8291</v>
+        <v>82.9759</v>
       </c>
       <c r="D125" t="n">
-        <v>292.328</v>
+        <v>292.779</v>
       </c>
       <c r="E125" t="n">
-        <v>77.66540000000001</v>
+        <v>77.563</v>
       </c>
       <c r="F125" t="n">
-        <v>291.954</v>
+        <v>288.802</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>95.22410000000001</v>
+        <v>97.51730000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>81.233</v>
+        <v>81.2694</v>
       </c>
       <c r="D126" t="n">
-        <v>290.044</v>
+        <v>290.488</v>
       </c>
       <c r="E126" t="n">
-        <v>76.0039</v>
+        <v>76.0055</v>
       </c>
       <c r="F126" t="n">
-        <v>290.314</v>
+        <v>289.08</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>98.68040000000001</v>
+        <v>94.89579999999999</v>
       </c>
       <c r="C127" t="n">
-        <v>85.75879999999999</v>
+        <v>79.889</v>
       </c>
       <c r="D127" t="n">
-        <v>288.06</v>
+        <v>288.104</v>
       </c>
       <c r="E127" t="n">
-        <v>78.6982</v>
+        <v>74.419</v>
       </c>
       <c r="F127" t="n">
-        <v>290.451</v>
+        <v>289.729</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>97.05889999999999</v>
+        <v>93.9355</v>
       </c>
       <c r="C128" t="n">
-        <v>84.12779999999999</v>
+        <v>78.5197</v>
       </c>
       <c r="D128" t="n">
-        <v>286.048</v>
+        <v>285.87</v>
       </c>
       <c r="E128" t="n">
-        <v>72.42529999999999</v>
+        <v>76.92440000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>289.779</v>
+        <v>288.571</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>90.6807</v>
+        <v>92.2209</v>
       </c>
       <c r="C129" t="n">
-        <v>76.3815</v>
+        <v>77.1546</v>
       </c>
       <c r="D129" t="n">
-        <v>283.881</v>
+        <v>283.39</v>
       </c>
       <c r="E129" t="n">
-        <v>71.0282</v>
+        <v>71.50749999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>289.048</v>
+        <v>287.569</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>89.53449999999999</v>
+        <v>90.21510000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>75.21729999999999</v>
+        <v>75.8905</v>
       </c>
       <c r="D130" t="n">
-        <v>282.815</v>
+        <v>283.192</v>
       </c>
       <c r="E130" t="n">
-        <v>69.65900000000001</v>
+        <v>70.3013</v>
       </c>
       <c r="F130" t="n">
-        <v>288.947</v>
+        <v>287.723</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>87.8655</v>
+        <v>89.9187</v>
       </c>
       <c r="C131" t="n">
-        <v>74.0615</v>
+        <v>74.8574</v>
       </c>
       <c r="D131" t="n">
-        <v>281.949</v>
+        <v>281.967</v>
       </c>
       <c r="E131" t="n">
-        <v>68.5438</v>
+        <v>69.1871</v>
       </c>
       <c r="F131" t="n">
-        <v>288.321</v>
+        <v>287.076</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>88.1395</v>
+        <v>88.1001</v>
       </c>
       <c r="C132" t="n">
-        <v>72.9385</v>
+        <v>73.7122</v>
       </c>
       <c r="D132" t="n">
-        <v>281.278</v>
+        <v>281.516</v>
       </c>
       <c r="E132" t="n">
-        <v>67.47790000000001</v>
+        <v>67.98869999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>288.003</v>
+        <v>286.661</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>85.7328</v>
+        <v>89.5591</v>
       </c>
       <c r="C133" t="n">
-        <v>71.9868</v>
+        <v>77.1495</v>
       </c>
       <c r="D133" t="n">
-        <v>281.344</v>
+        <v>283.049</v>
       </c>
       <c r="E133" t="n">
-        <v>66.52500000000001</v>
+        <v>66.89</v>
       </c>
       <c r="F133" t="n">
-        <v>288.287</v>
+        <v>287.743</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>84.63339999999999</v>
+        <v>85.02070000000001</v>
       </c>
       <c r="C134" t="n">
-        <v>71.14749999999999</v>
+        <v>71.6275</v>
       </c>
       <c r="D134" t="n">
-        <v>278.286</v>
+        <v>276.954</v>
       </c>
       <c r="E134" t="n">
-        <v>65.5814</v>
+        <v>97.7794</v>
       </c>
       <c r="F134" t="n">
-        <v>288.032</v>
+        <v>330.745</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>83.47490000000001</v>
+        <v>84.438</v>
       </c>
       <c r="C135" t="n">
-        <v>70.3847</v>
+        <v>70.7756</v>
       </c>
       <c r="D135" t="n">
-        <v>352.957</v>
+        <v>353.115</v>
       </c>
       <c r="E135" t="n">
-        <v>94.9192</v>
+        <v>96.4242</v>
       </c>
       <c r="F135" t="n">
-        <v>331.93</v>
+        <v>330.903</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>79.93340000000001</v>
+        <v>84.3545</v>
       </c>
       <c r="C136" t="n">
-        <v>97.34139999999999</v>
+        <v>105.524</v>
       </c>
       <c r="D136" t="n">
-        <v>346.682</v>
+        <v>346.855</v>
       </c>
       <c r="E136" t="n">
-        <v>92.9413</v>
+        <v>93.8082</v>
       </c>
       <c r="F136" t="n">
-        <v>332.036</v>
+        <v>328.789</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>82.90000000000001</v>
+        <v>83.7067</v>
       </c>
       <c r="C137" t="n">
-        <v>102.374</v>
+        <v>103.556</v>
       </c>
       <c r="D137" t="n">
-        <v>341.154</v>
+        <v>341.803</v>
       </c>
       <c r="E137" t="n">
-        <v>91.1343</v>
+        <v>92.3223</v>
       </c>
       <c r="F137" t="n">
-        <v>331.502</v>
+        <v>326.899</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>108.866</v>
+        <v>116.343</v>
       </c>
       <c r="C138" t="n">
-        <v>94.80710000000001</v>
+        <v>103.003</v>
       </c>
       <c r="D138" t="n">
-        <v>336.325</v>
+        <v>337.99</v>
       </c>
       <c r="E138" t="n">
-        <v>89.42570000000001</v>
+        <v>90.6422</v>
       </c>
       <c r="F138" t="n">
-        <v>327.259</v>
+        <v>329.973</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>110.761</v>
+        <v>107.517</v>
       </c>
       <c r="C139" t="n">
-        <v>93.80159999999999</v>
+        <v>94.758</v>
       </c>
       <c r="D139" t="n">
-        <v>332.082</v>
+        <v>332.318</v>
       </c>
       <c r="E139" t="n">
-        <v>87.9837</v>
+        <v>88.93819999999999</v>
       </c>
       <c r="F139" t="n">
-        <v>328.233</v>
+        <v>329.286</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>108.307</v>
+        <v>112.872</v>
       </c>
       <c r="C140" t="n">
-        <v>92.60980000000001</v>
+        <v>99.7411</v>
       </c>
       <c r="D140" t="n">
-        <v>330.169</v>
+        <v>328.518</v>
       </c>
       <c r="E140" t="n">
-        <v>90.7924</v>
+        <v>87.58669999999999</v>
       </c>
       <c r="F140" t="n">
-        <v>327.857</v>
+        <v>327.084</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>110.197</v>
+        <v>111.136</v>
       </c>
       <c r="C141" t="n">
-        <v>97.28100000000001</v>
+        <v>98.38209999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>326.275</v>
+        <v>326.638</v>
       </c>
       <c r="E141" t="n">
-        <v>88.9188</v>
+        <v>86.01479999999999</v>
       </c>
       <c r="F141" t="n">
-        <v>327.186</v>
+        <v>325.971</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>108.638</v>
+        <v>106.593</v>
       </c>
       <c r="C142" t="n">
-        <v>95.89579999999999</v>
+        <v>91.0921</v>
       </c>
       <c r="D142" t="n">
-        <v>325.625</v>
+        <v>326.093</v>
       </c>
       <c r="E142" t="n">
-        <v>83.3389</v>
+        <v>84.4499</v>
       </c>
       <c r="F142" t="n">
-        <v>325.938</v>
+        <v>325.214</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>102.362</v>
+        <v>103.314</v>
       </c>
       <c r="C143" t="n">
-        <v>89.0467</v>
+        <v>90.0483</v>
       </c>
       <c r="D143" t="n">
-        <v>323.932</v>
+        <v>324.145</v>
       </c>
       <c r="E143" t="n">
-        <v>82.4897</v>
+        <v>86.9462</v>
       </c>
       <c r="F143" t="n">
-        <v>324.278</v>
+        <v>323.885</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Running insertion.xlsx
+++ b/gcc-x64/Running insertion.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>24.0762</v>
+        <v>24.0552</v>
       </c>
       <c r="C2" t="n">
-        <v>20.2937</v>
+        <v>20.3763</v>
       </c>
       <c r="D2" t="n">
-        <v>53.5625</v>
+        <v>53.7104</v>
       </c>
       <c r="E2" t="n">
-        <v>17.5561</v>
+        <v>17.5154</v>
       </c>
       <c r="F2" t="n">
-        <v>32.3824</v>
+        <v>32.4866</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>23.3991</v>
+        <v>22.7172</v>
       </c>
       <c r="C3" t="n">
-        <v>19.7694</v>
+        <v>19.711</v>
       </c>
       <c r="D3" t="n">
-        <v>52.9713</v>
+        <v>53.0993</v>
       </c>
       <c r="E3" t="n">
-        <v>17.0435</v>
+        <v>16.9709</v>
       </c>
       <c r="F3" t="n">
-        <v>32.005</v>
+        <v>32.0488</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>23.3284</v>
+        <v>23.0591</v>
       </c>
       <c r="C4" t="n">
-        <v>19.2641</v>
+        <v>19.2533</v>
       </c>
       <c r="D4" t="n">
-        <v>52.4426</v>
+        <v>52.5927</v>
       </c>
       <c r="E4" t="n">
-        <v>16.5624</v>
+        <v>16.49</v>
       </c>
       <c r="F4" t="n">
-        <v>31.6943</v>
+        <v>31.764</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>22.4221</v>
+        <v>22.631</v>
       </c>
       <c r="C5" t="n">
-        <v>18.8614</v>
+        <v>18.8385</v>
       </c>
       <c r="D5" t="n">
-        <v>52.0225</v>
+        <v>52.0896</v>
       </c>
       <c r="E5" t="n">
-        <v>25.9546</v>
+        <v>25.8111</v>
       </c>
       <c r="F5" t="n">
-        <v>40.5426</v>
+        <v>40.7307</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>22.5631</v>
+        <v>21.6975</v>
       </c>
       <c r="C6" t="n">
-        <v>18.4948</v>
+        <v>18.4109</v>
       </c>
       <c r="D6" t="n">
-        <v>51.5592</v>
+        <v>51.7437</v>
       </c>
       <c r="E6" t="n">
-        <v>24.9427</v>
+        <v>25.1776</v>
       </c>
       <c r="F6" t="n">
-        <v>39.8663</v>
+        <v>39.7452</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>22.2089</v>
+        <v>22.0142</v>
       </c>
       <c r="C7" t="n">
-        <v>18.1848</v>
+        <v>18.1339</v>
       </c>
       <c r="D7" t="n">
-        <v>66.07380000000001</v>
+        <v>65.88809999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>24.105</v>
+        <v>24.3433</v>
       </c>
       <c r="F7" t="n">
-        <v>38.9797</v>
+        <v>38.8317</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>21.3702</v>
+        <v>22.1159</v>
       </c>
       <c r="C8" t="n">
-        <v>26.934</v>
+        <v>26.8648</v>
       </c>
       <c r="D8" t="n">
-        <v>64.36790000000001</v>
+        <v>64.348</v>
       </c>
       <c r="E8" t="n">
-        <v>23.3028</v>
+        <v>23.9963</v>
       </c>
       <c r="F8" t="n">
-        <v>38.0439</v>
+        <v>38.1327</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>21.3489</v>
+        <v>21.7882</v>
       </c>
       <c r="C9" t="n">
-        <v>26.0584</v>
+        <v>26.0462</v>
       </c>
       <c r="D9" t="n">
-        <v>63.0016</v>
+        <v>62.9843</v>
       </c>
       <c r="E9" t="n">
-        <v>22.6059</v>
+        <v>22.9334</v>
       </c>
       <c r="F9" t="n">
-        <v>37.241</v>
+        <v>37.2037</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>30.5578</v>
+        <v>30.1232</v>
       </c>
       <c r="C10" t="n">
-        <v>25.2347</v>
+        <v>25.1724</v>
       </c>
       <c r="D10" t="n">
-        <v>61.7734</v>
+        <v>61.6037</v>
       </c>
       <c r="E10" t="n">
-        <v>21.7992</v>
+        <v>21.7727</v>
       </c>
       <c r="F10" t="n">
-        <v>36.4906</v>
+        <v>36.4401</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>29.5858</v>
+        <v>29.4705</v>
       </c>
       <c r="C11" t="n">
-        <v>24.4212</v>
+        <v>24.3543</v>
       </c>
       <c r="D11" t="n">
-        <v>60.65</v>
+        <v>60.6774</v>
       </c>
       <c r="E11" t="n">
-        <v>21.0353</v>
+        <v>21.2507</v>
       </c>
       <c r="F11" t="n">
-        <v>35.7642</v>
+        <v>35.6399</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>28.1558</v>
+        <v>28.6409</v>
       </c>
       <c r="C12" t="n">
-        <v>23.6978</v>
+        <v>23.6099</v>
       </c>
       <c r="D12" t="n">
-        <v>59.5896</v>
+        <v>59.4075</v>
       </c>
       <c r="E12" t="n">
-        <v>20.4105</v>
+        <v>20.653</v>
       </c>
       <c r="F12" t="n">
-        <v>35.063</v>
+        <v>35.0384</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>27.2384</v>
+        <v>27.7373</v>
       </c>
       <c r="C13" t="n">
-        <v>22.9332</v>
+        <v>22.875</v>
       </c>
       <c r="D13" t="n">
-        <v>58.6892</v>
+        <v>58.4949</v>
       </c>
       <c r="E13" t="n">
-        <v>19.8083</v>
+        <v>19.9609</v>
       </c>
       <c r="F13" t="n">
-        <v>34.4232</v>
+        <v>34.4261</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>26.9471</v>
+        <v>26.6641</v>
       </c>
       <c r="C14" t="n">
-        <v>22.2069</v>
+        <v>22.254</v>
       </c>
       <c r="D14" t="n">
-        <v>57.9107</v>
+        <v>57.8615</v>
       </c>
       <c r="E14" t="n">
-        <v>19.1675</v>
+        <v>19.3037</v>
       </c>
       <c r="F14" t="n">
-        <v>33.888</v>
+        <v>33.8234</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>25.9565</v>
+        <v>25.9253</v>
       </c>
       <c r="C15" t="n">
-        <v>21.5411</v>
+        <v>21.6395</v>
       </c>
       <c r="D15" t="n">
-        <v>57.2786</v>
+        <v>57.0081</v>
       </c>
       <c r="E15" t="n">
-        <v>18.8442</v>
+        <v>18.8334</v>
       </c>
       <c r="F15" t="n">
-        <v>33.3254</v>
+        <v>33.2954</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>25.5557</v>
+        <v>25.6943</v>
       </c>
       <c r="C16" t="n">
-        <v>20.9228</v>
+        <v>20.9491</v>
       </c>
       <c r="D16" t="n">
-        <v>57.012</v>
+        <v>56.5824</v>
       </c>
       <c r="E16" t="n">
-        <v>18.5295</v>
+        <v>18.2124</v>
       </c>
       <c r="F16" t="n">
-        <v>32.8585</v>
+        <v>32.8344</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>25.1532</v>
+        <v>24.846</v>
       </c>
       <c r="C17" t="n">
-        <v>20.4046</v>
+        <v>20.4079</v>
       </c>
       <c r="D17" t="n">
-        <v>56.1807</v>
+        <v>55.8275</v>
       </c>
       <c r="E17" t="n">
-        <v>17.7892</v>
+        <v>17.7613</v>
       </c>
       <c r="F17" t="n">
-        <v>32.4439</v>
+        <v>32.4088</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>23.9048</v>
+        <v>24.5476</v>
       </c>
       <c r="C18" t="n">
-        <v>19.8742</v>
+        <v>19.8261</v>
       </c>
       <c r="D18" t="n">
-        <v>55.5338</v>
+        <v>55.4224</v>
       </c>
       <c r="E18" t="n">
-        <v>17.2327</v>
+        <v>17.258</v>
       </c>
       <c r="F18" t="n">
-        <v>32.0827</v>
+        <v>32.0382</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>23.7658</v>
+        <v>23.6515</v>
       </c>
       <c r="C19" t="n">
-        <v>19.3599</v>
+        <v>19.3536</v>
       </c>
       <c r="D19" t="n">
-        <v>54.7333</v>
+        <v>54.5368</v>
       </c>
       <c r="E19" t="n">
-        <v>16.7687</v>
+        <v>16.9129</v>
       </c>
       <c r="F19" t="n">
-        <v>31.7034</v>
+        <v>31.7347</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>23.0896</v>
+        <v>23.3991</v>
       </c>
       <c r="C20" t="n">
-        <v>18.9722</v>
+        <v>18.9182</v>
       </c>
       <c r="D20" t="n">
-        <v>54.0915</v>
+        <v>54.1942</v>
       </c>
       <c r="E20" t="n">
-        <v>26.607</v>
+        <v>26.1568</v>
       </c>
       <c r="F20" t="n">
-        <v>40.3236</v>
+        <v>40.2818</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>23.3263</v>
+        <v>22.8275</v>
       </c>
       <c r="C21" t="n">
-        <v>18.7154</v>
+        <v>18.6787</v>
       </c>
       <c r="D21" t="n">
-        <v>71.8643</v>
+        <v>71.7129</v>
       </c>
       <c r="E21" t="n">
-        <v>25.1581</v>
+        <v>25.1424</v>
       </c>
       <c r="F21" t="n">
-        <v>39.5304</v>
+        <v>39.4663</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>22.491</v>
+        <v>22.8071</v>
       </c>
       <c r="C22" t="n">
-        <v>27.3646</v>
+        <v>27.3438</v>
       </c>
       <c r="D22" t="n">
-        <v>70.2925</v>
+        <v>70.029</v>
       </c>
       <c r="E22" t="n">
-        <v>24.8955</v>
+        <v>24.379</v>
       </c>
       <c r="F22" t="n">
-        <v>38.7298</v>
+        <v>38.6284</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>22.6151</v>
+        <v>22.5956</v>
       </c>
       <c r="C23" t="n">
-        <v>26.5407</v>
+        <v>26.4909</v>
       </c>
       <c r="D23" t="n">
-        <v>68.7546</v>
+        <v>68.60899999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>23.6585</v>
+        <v>23.7053</v>
       </c>
       <c r="F23" t="n">
-        <v>37.9413</v>
+        <v>37.8635</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>30.7411</v>
+        <v>30.9252</v>
       </c>
       <c r="C24" t="n">
-        <v>25.7136</v>
+        <v>25.7169</v>
       </c>
       <c r="D24" t="n">
-        <v>67.5917</v>
+        <v>67.2864</v>
       </c>
       <c r="E24" t="n">
-        <v>22.8941</v>
+        <v>22.8374</v>
       </c>
       <c r="F24" t="n">
-        <v>37.1976</v>
+        <v>37.1075</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>29.6767</v>
+        <v>30.1053</v>
       </c>
       <c r="C25" t="n">
-        <v>24.9351</v>
+        <v>24.9123</v>
       </c>
       <c r="D25" t="n">
-        <v>66.2912</v>
+        <v>66.03149999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>22.1509</v>
+        <v>22.1053</v>
       </c>
       <c r="F25" t="n">
-        <v>36.5025</v>
+        <v>36.3647</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>29.2466</v>
+        <v>29.3804</v>
       </c>
       <c r="C26" t="n">
-        <v>24.1903</v>
+        <v>24.2027</v>
       </c>
       <c r="D26" t="n">
-        <v>64.81740000000001</v>
+        <v>64.50069999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>21.2756</v>
+        <v>21.4456</v>
       </c>
       <c r="F26" t="n">
-        <v>35.8221</v>
+        <v>36.1309</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>28.6266</v>
+        <v>29.0581</v>
       </c>
       <c r="C27" t="n">
-        <v>23.4537</v>
+        <v>23.4009</v>
       </c>
       <c r="D27" t="n">
-        <v>63.8404</v>
+        <v>63.5659</v>
       </c>
       <c r="E27" t="n">
-        <v>20.722</v>
+        <v>20.8766</v>
       </c>
       <c r="F27" t="n">
-        <v>35.1682</v>
+        <v>35.4048</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>27.9216</v>
+        <v>28.2189</v>
       </c>
       <c r="C28" t="n">
-        <v>22.7711</v>
+        <v>22.7144</v>
       </c>
       <c r="D28" t="n">
-        <v>62.8472</v>
+        <v>62.6652</v>
       </c>
       <c r="E28" t="n">
-        <v>20.1535</v>
+        <v>20.3215</v>
       </c>
       <c r="F28" t="n">
-        <v>34.5064</v>
+        <v>34.8006</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>26.961</v>
+        <v>26.8407</v>
       </c>
       <c r="C29" t="n">
-        <v>22.1214</v>
+        <v>22.0423</v>
       </c>
       <c r="D29" t="n">
-        <v>62.146</v>
+        <v>61.9521</v>
       </c>
       <c r="E29" t="n">
-        <v>19.497</v>
+        <v>19.5368</v>
       </c>
       <c r="F29" t="n">
-        <v>33.9807</v>
+        <v>34.2411</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>26.2767</v>
+        <v>26.1759</v>
       </c>
       <c r="C30" t="n">
-        <v>21.4847</v>
+        <v>21.4419</v>
       </c>
       <c r="D30" t="n">
-        <v>61.2473</v>
+        <v>61.0205</v>
       </c>
       <c r="E30" t="n">
-        <v>19.0767</v>
+        <v>18.9639</v>
       </c>
       <c r="F30" t="n">
-        <v>33.5035</v>
+        <v>33.7138</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>25.7473</v>
+        <v>25.9407</v>
       </c>
       <c r="C31" t="n">
-        <v>20.9139</v>
+        <v>20.8292</v>
       </c>
       <c r="D31" t="n">
-        <v>60.7258</v>
+        <v>60.4645</v>
       </c>
       <c r="E31" t="n">
-        <v>18.5601</v>
+        <v>18.4827</v>
       </c>
       <c r="F31" t="n">
-        <v>32.9061</v>
+        <v>32.9646</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>25.0886</v>
+        <v>25.6047</v>
       </c>
       <c r="C32" t="n">
-        <v>20.4114</v>
+        <v>20.3468</v>
       </c>
       <c r="D32" t="n">
-        <v>60.2534</v>
+        <v>60.0217</v>
       </c>
       <c r="E32" t="n">
-        <v>18.1611</v>
+        <v>18.1641</v>
       </c>
       <c r="F32" t="n">
-        <v>32.5312</v>
+        <v>32.585</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>24.3918</v>
+        <v>24.3837</v>
       </c>
       <c r="C33" t="n">
-        <v>19.9047</v>
+        <v>19.8861</v>
       </c>
       <c r="D33" t="n">
-        <v>59.8176</v>
+        <v>59.5846</v>
       </c>
       <c r="E33" t="n">
-        <v>17.6036</v>
+        <v>17.6297</v>
       </c>
       <c r="F33" t="n">
-        <v>32.3218</v>
+        <v>32.236</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>24.0062</v>
+        <v>24.185</v>
       </c>
       <c r="C34" t="n">
-        <v>19.5554</v>
+        <v>19.4626</v>
       </c>
       <c r="D34" t="n">
-        <v>58.9791</v>
+        <v>58.7013</v>
       </c>
       <c r="E34" t="n">
-        <v>26.9116</v>
+        <v>26.869</v>
       </c>
       <c r="F34" t="n">
-        <v>41.0996</v>
+        <v>41.2384</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>23.9854</v>
+        <v>24.1234</v>
       </c>
       <c r="C35" t="n">
-        <v>19.151</v>
+        <v>19.1112</v>
       </c>
       <c r="D35" t="n">
-        <v>77.29559999999999</v>
+        <v>76.94970000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>26.3316</v>
+        <v>25.9828</v>
       </c>
       <c r="F35" t="n">
-        <v>40.361</v>
+        <v>40.3664</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>22.9529</v>
+        <v>23.2417</v>
       </c>
       <c r="C36" t="n">
-        <v>18.8577</v>
+        <v>18.8775</v>
       </c>
       <c r="D36" t="n">
-        <v>75.5151</v>
+        <v>75.2546</v>
       </c>
       <c r="E36" t="n">
-        <v>25.2655</v>
+        <v>25.0393</v>
       </c>
       <c r="F36" t="n">
-        <v>39.5804</v>
+        <v>39.647</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>23.2329</v>
+        <v>23.1408</v>
       </c>
       <c r="C37" t="n">
-        <v>27.1329</v>
+        <v>27.1606</v>
       </c>
       <c r="D37" t="n">
-        <v>73.92789999999999</v>
+        <v>73.6802</v>
       </c>
       <c r="E37" t="n">
-        <v>24.3547</v>
+        <v>24.3608</v>
       </c>
       <c r="F37" t="n">
-        <v>38.8171</v>
+        <v>38.8609</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>31.8479</v>
+        <v>31.3306</v>
       </c>
       <c r="C38" t="n">
-        <v>26.3408</v>
+        <v>26.3526</v>
       </c>
       <c r="D38" t="n">
-        <v>72.4299</v>
+        <v>72.2432</v>
       </c>
       <c r="E38" t="n">
-        <v>23.557</v>
+        <v>23.4347</v>
       </c>
       <c r="F38" t="n">
-        <v>38.112</v>
+        <v>38.0042</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>30.3005</v>
+        <v>30.2962</v>
       </c>
       <c r="C39" t="n">
-        <v>25.5297</v>
+        <v>25.5455</v>
       </c>
       <c r="D39" t="n">
-        <v>71.08369999999999</v>
+        <v>70.85290000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>22.9431</v>
+        <v>22.897</v>
       </c>
       <c r="F39" t="n">
-        <v>37.4496</v>
+        <v>37.2735</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>29.4707</v>
+        <v>29.4314</v>
       </c>
       <c r="C40" t="n">
-        <v>24.7896</v>
+        <v>24.8002</v>
       </c>
       <c r="D40" t="n">
-        <v>69.7805</v>
+        <v>69.6313</v>
       </c>
       <c r="E40" t="n">
-        <v>22.1858</v>
+        <v>22.1738</v>
       </c>
       <c r="F40" t="n">
-        <v>36.8474</v>
+        <v>36.6692</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>28.9336</v>
+        <v>29.4567</v>
       </c>
       <c r="C41" t="n">
-        <v>24.0674</v>
+        <v>24.0822</v>
       </c>
       <c r="D41" t="n">
-        <v>68.64149999999999</v>
+        <v>68.4173</v>
       </c>
       <c r="E41" t="n">
-        <v>21.4557</v>
+        <v>21.4336</v>
       </c>
       <c r="F41" t="n">
-        <v>36.2496</v>
+        <v>36.0975</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>28.1275</v>
+        <v>28.7075</v>
       </c>
       <c r="C42" t="n">
-        <v>23.4199</v>
+        <v>23.3861</v>
       </c>
       <c r="D42" t="n">
-        <v>67.8552</v>
+        <v>67.4725</v>
       </c>
       <c r="E42" t="n">
-        <v>20.8871</v>
+        <v>20.8097</v>
       </c>
       <c r="F42" t="n">
-        <v>35.6083</v>
+        <v>35.4933</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>27.6371</v>
+        <v>27.7226</v>
       </c>
       <c r="C43" t="n">
-        <v>22.7436</v>
+        <v>22.7579</v>
       </c>
       <c r="D43" t="n">
-        <v>66.50149999999999</v>
+        <v>66.34220000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>20.402</v>
+        <v>20.2753</v>
       </c>
       <c r="F43" t="n">
-        <v>35.1086</v>
+        <v>35.0747</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>26.4792</v>
+        <v>26.2604</v>
       </c>
       <c r="C44" t="n">
-        <v>22.1397</v>
+        <v>22.2358</v>
       </c>
       <c r="D44" t="n">
-        <v>65.7462</v>
+        <v>65.51479999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>19.8575</v>
+        <v>19.7218</v>
       </c>
       <c r="F44" t="n">
-        <v>34.626</v>
+        <v>34.5176</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>26.2942</v>
+        <v>25.868</v>
       </c>
       <c r="C45" t="n">
-        <v>21.6532</v>
+        <v>21.8758</v>
       </c>
       <c r="D45" t="n">
-        <v>65.0877</v>
+        <v>64.93819999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>19.3197</v>
+        <v>19.4145</v>
       </c>
       <c r="F45" t="n">
-        <v>34.3202</v>
+        <v>34.2131</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>25.1811</v>
+        <v>25.644</v>
       </c>
       <c r="C46" t="n">
-        <v>21.0334</v>
+        <v>21.0629</v>
       </c>
       <c r="D46" t="n">
-        <v>64.50239999999999</v>
+        <v>64.3078</v>
       </c>
       <c r="E46" t="n">
-        <v>18.8857</v>
+        <v>18.8743</v>
       </c>
       <c r="F46" t="n">
-        <v>33.8437</v>
+        <v>33.8502</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>24.7107</v>
+        <v>24.7098</v>
       </c>
       <c r="C47" t="n">
-        <v>20.6063</v>
+        <v>20.5947</v>
       </c>
       <c r="D47" t="n">
-        <v>63.9867</v>
+        <v>63.8265</v>
       </c>
       <c r="E47" t="n">
-        <v>18.4859</v>
+        <v>18.4173</v>
       </c>
       <c r="F47" t="n">
-        <v>33.5445</v>
+        <v>33.4051</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>24.2738</v>
+        <v>24.5938</v>
       </c>
       <c r="C48" t="n">
-        <v>20.1252</v>
+        <v>20.104</v>
       </c>
       <c r="D48" t="n">
-        <v>63.2576</v>
+        <v>62.9872</v>
       </c>
       <c r="E48" t="n">
-        <v>27.5997</v>
+        <v>27.9809</v>
       </c>
       <c r="F48" t="n">
-        <v>42.8668</v>
+        <v>42.3373</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>24.2417</v>
+        <v>24.7248</v>
       </c>
       <c r="C49" t="n">
-        <v>19.6563</v>
+        <v>19.9938</v>
       </c>
       <c r="D49" t="n">
-        <v>62.8759</v>
+        <v>62.597</v>
       </c>
       <c r="E49" t="n">
-        <v>26.8585</v>
+        <v>27.1512</v>
       </c>
       <c r="F49" t="n">
-        <v>42.0282</v>
+        <v>41.7424</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>23.5271</v>
+        <v>23.4628</v>
       </c>
       <c r="C50" t="n">
-        <v>19.5526</v>
+        <v>19.5759</v>
       </c>
       <c r="D50" t="n">
-        <v>80.1726</v>
+        <v>79.82559999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>26.1561</v>
+        <v>26.4292</v>
       </c>
       <c r="F50" t="n">
-        <v>41.4184</v>
+        <v>40.939</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>23.6218</v>
+        <v>23.4298</v>
       </c>
       <c r="C51" t="n">
-        <v>27.9094</v>
+        <v>27.9655</v>
       </c>
       <c r="D51" t="n">
-        <v>78.4057</v>
+        <v>78.2041</v>
       </c>
       <c r="E51" t="n">
-        <v>25.2029</v>
+        <v>25.5479</v>
       </c>
       <c r="F51" t="n">
-        <v>40.4936</v>
+        <v>40.4496</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>23.6655</v>
+        <v>23.9876</v>
       </c>
       <c r="C52" t="n">
-        <v>27.0727</v>
+        <v>27.1833</v>
       </c>
       <c r="D52" t="n">
-        <v>76.67359999999999</v>
+        <v>76.4885</v>
       </c>
       <c r="E52" t="n">
-        <v>24.502</v>
+        <v>24.7976</v>
       </c>
       <c r="F52" t="n">
-        <v>39.931</v>
+        <v>39.7156</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>32.6294</v>
+        <v>31.8931</v>
       </c>
       <c r="C53" t="n">
-        <v>26.4093</v>
+        <v>26.3811</v>
       </c>
       <c r="D53" t="n">
-        <v>75.15479999999999</v>
+        <v>74.983</v>
       </c>
       <c r="E53" t="n">
-        <v>24.0073</v>
+        <v>23.9264</v>
       </c>
       <c r="F53" t="n">
-        <v>39.273</v>
+        <v>39.0843</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>30.4206</v>
+        <v>31.6579</v>
       </c>
       <c r="C54" t="n">
-        <v>25.6122</v>
+        <v>25.6686</v>
       </c>
       <c r="D54" t="n">
-        <v>73.73569999999999</v>
+        <v>73.51949999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>23.0126</v>
+        <v>23.2926</v>
       </c>
       <c r="F54" t="n">
-        <v>38.6649</v>
+        <v>38.5906</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>29.6119</v>
+        <v>29.9993</v>
       </c>
       <c r="C55" t="n">
-        <v>24.9705</v>
+        <v>25.0207</v>
       </c>
       <c r="D55" t="n">
-        <v>72.54519999999999</v>
+        <v>72.336</v>
       </c>
       <c r="E55" t="n">
-        <v>22.4696</v>
+        <v>22.6611</v>
       </c>
       <c r="F55" t="n">
-        <v>38.0273</v>
+        <v>37.9962</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>28.8312</v>
+        <v>30.0041</v>
       </c>
       <c r="C56" t="n">
-        <v>24.2916</v>
+        <v>24.3712</v>
       </c>
       <c r="D56" t="n">
-        <v>71.4648</v>
+        <v>71.2814</v>
       </c>
       <c r="E56" t="n">
-        <v>21.8255</v>
+        <v>22.0115</v>
       </c>
       <c r="F56" t="n">
-        <v>37.5298</v>
+        <v>37.5041</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>28.3599</v>
+        <v>28.4744</v>
       </c>
       <c r="C57" t="n">
-        <v>23.8208</v>
+        <v>23.7422</v>
       </c>
       <c r="D57" t="n">
-        <v>70.2402</v>
+        <v>70.0779</v>
       </c>
       <c r="E57" t="n">
-        <v>21.4215</v>
+        <v>21.6014</v>
       </c>
       <c r="F57" t="n">
-        <v>37.2157</v>
+        <v>37.0842</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>27.9324</v>
+        <v>28.2908</v>
       </c>
       <c r="C58" t="n">
-        <v>23.1472</v>
+        <v>23.1958</v>
       </c>
       <c r="D58" t="n">
-        <v>69.378</v>
+        <v>69.27070000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>20.7993</v>
+        <v>20.8651</v>
       </c>
       <c r="F58" t="n">
-        <v>36.7401</v>
+        <v>36.6043</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>27.6105</v>
+        <v>27.726</v>
       </c>
       <c r="C59" t="n">
-        <v>22.5827</v>
+        <v>22.7153</v>
       </c>
       <c r="D59" t="n">
-        <v>68.5183</v>
+        <v>68.36499999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>20.2516</v>
+        <v>20.4984</v>
       </c>
       <c r="F59" t="n">
-        <v>36.4165</v>
+        <v>36.1036</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>26.3892</v>
+        <v>26.9778</v>
       </c>
       <c r="C60" t="n">
-        <v>22.089</v>
+        <v>22.0867</v>
       </c>
       <c r="D60" t="n">
-        <v>67.875</v>
+        <v>67.71980000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>19.8803</v>
+        <v>20.0719</v>
       </c>
       <c r="F60" t="n">
-        <v>36.0734</v>
+        <v>35.9277</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>26.1055</v>
+        <v>26.5658</v>
       </c>
       <c r="C61" t="n">
-        <v>21.8322</v>
+        <v>21.6662</v>
       </c>
       <c r="D61" t="n">
-        <v>67.1026</v>
+        <v>66.9614</v>
       </c>
       <c r="E61" t="n">
-        <v>19.4198</v>
+        <v>19.8043</v>
       </c>
       <c r="F61" t="n">
-        <v>35.8239</v>
+        <v>35.5716</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>25.88</v>
+        <v>25.8893</v>
       </c>
       <c r="C62" t="n">
-        <v>21.2073</v>
+        <v>21.2449</v>
       </c>
       <c r="D62" t="n">
-        <v>66.422</v>
+        <v>66.34699999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>19.3797</v>
+        <v>19.4031</v>
       </c>
       <c r="F62" t="n">
-        <v>35.6392</v>
+        <v>35.4688</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>25.026</v>
+        <v>26.2221</v>
       </c>
       <c r="C63" t="n">
-        <v>20.8573</v>
+        <v>20.8625</v>
       </c>
       <c r="D63" t="n">
-        <v>66.0592</v>
+        <v>65.9443</v>
       </c>
       <c r="E63" t="n">
-        <v>31.8285</v>
+        <v>32.5267</v>
       </c>
       <c r="F63" t="n">
-        <v>44.8794</v>
+        <v>46.1432</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>25.3795</v>
+        <v>25.699</v>
       </c>
       <c r="C64" t="n">
-        <v>20.6199</v>
+        <v>20.6041</v>
       </c>
       <c r="D64" t="n">
-        <v>87.3933</v>
+        <v>88.32040000000001</v>
       </c>
       <c r="E64" t="n">
-        <v>31.0475</v>
+        <v>31.7104</v>
       </c>
       <c r="F64" t="n">
-        <v>44.3309</v>
+        <v>45.5433</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>25.5167</v>
+        <v>24.9879</v>
       </c>
       <c r="C65" t="n">
-        <v>29.5778</v>
+        <v>29.6666</v>
       </c>
       <c r="D65" t="n">
-        <v>85.3502</v>
+        <v>86.02379999999999</v>
       </c>
       <c r="E65" t="n">
-        <v>30.239</v>
+        <v>30.2525</v>
       </c>
       <c r="F65" t="n">
-        <v>43.6903</v>
+        <v>44.9877</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>25.1907</v>
+        <v>25.3042</v>
       </c>
       <c r="C66" t="n">
-        <v>28.9279</v>
+        <v>28.9607</v>
       </c>
       <c r="D66" t="n">
-        <v>83.5467</v>
+        <v>84.1305</v>
       </c>
       <c r="E66" t="n">
-        <v>30.0125</v>
+        <v>30.1384</v>
       </c>
       <c r="F66" t="n">
-        <v>43.2531</v>
+        <v>44.44</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>39.134</v>
+        <v>38.7804</v>
       </c>
       <c r="C67" t="n">
-        <v>28.3137</v>
+        <v>28.3399</v>
       </c>
       <c r="D67" t="n">
-        <v>81.84950000000001</v>
+        <v>82.4644</v>
       </c>
       <c r="E67" t="n">
-        <v>28.6058</v>
+        <v>28.8421</v>
       </c>
       <c r="F67" t="n">
-        <v>42.6353</v>
+        <v>43.7785</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>39.0131</v>
+        <v>39.1303</v>
       </c>
       <c r="C68" t="n">
-        <v>27.7161</v>
+        <v>27.7485</v>
       </c>
       <c r="D68" t="n">
-        <v>80.36020000000001</v>
+        <v>80.9804</v>
       </c>
       <c r="E68" t="n">
-        <v>27.9622</v>
+        <v>28.666</v>
       </c>
       <c r="F68" t="n">
-        <v>42.1286</v>
+        <v>43.1975</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>39.326</v>
+        <v>39.0123</v>
       </c>
       <c r="C69" t="n">
-        <v>27.1728</v>
+        <v>27.2632</v>
       </c>
       <c r="D69" t="n">
-        <v>78.84829999999999</v>
+        <v>79.6661</v>
       </c>
       <c r="E69" t="n">
-        <v>27.2149</v>
+        <v>28.0084</v>
       </c>
       <c r="F69" t="n">
-        <v>41.4738</v>
+        <v>42.6249</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>40.0769</v>
+        <v>37.8465</v>
       </c>
       <c r="C70" t="n">
-        <v>26.6548</v>
+        <v>26.7597</v>
       </c>
       <c r="D70" t="n">
-        <v>77.81399999999999</v>
+        <v>78.6193</v>
       </c>
       <c r="E70" t="n">
-        <v>26.6976</v>
+        <v>26.9267</v>
       </c>
       <c r="F70" t="n">
-        <v>41.1459</v>
+        <v>42.1734</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>37.9637</v>
+        <v>37.2795</v>
       </c>
       <c r="C71" t="n">
-        <v>26.2514</v>
+        <v>26.2834</v>
       </c>
       <c r="D71" t="n">
-        <v>76.9646</v>
+        <v>77.8544</v>
       </c>
       <c r="E71" t="n">
-        <v>26.4489</v>
+        <v>26.6284</v>
       </c>
       <c r="F71" t="n">
-        <v>40.6885</v>
+        <v>41.8052</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>35.8097</v>
+        <v>36.6869</v>
       </c>
       <c r="C72" t="n">
-        <v>25.8109</v>
+        <v>25.8053</v>
       </c>
       <c r="D72" t="n">
-        <v>76.30419999999999</v>
+        <v>77.2196</v>
       </c>
       <c r="E72" t="n">
-        <v>26.0261</v>
+        <v>25.3731</v>
       </c>
       <c r="F72" t="n">
-        <v>40.4058</v>
+        <v>41.3949</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>35.4461</v>
+        <v>36.3004</v>
       </c>
       <c r="C73" t="n">
-        <v>25.2981</v>
+        <v>25.3674</v>
       </c>
       <c r="D73" t="n">
-        <v>75.8505</v>
+        <v>76.75790000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>25.373</v>
+        <v>25.4635</v>
       </c>
       <c r="F73" t="n">
-        <v>40.0744</v>
+        <v>41.0568</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>35.5404</v>
+        <v>34.8309</v>
       </c>
       <c r="C74" t="n">
-        <v>24.8689</v>
+        <v>24.9574</v>
       </c>
       <c r="D74" t="n">
-        <v>75.2004</v>
+        <v>76.4251</v>
       </c>
       <c r="E74" t="n">
-        <v>24.4834</v>
+        <v>24.7605</v>
       </c>
       <c r="F74" t="n">
-        <v>39.885</v>
+        <v>40.8301</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>34.8649</v>
+        <v>34.2622</v>
       </c>
       <c r="C75" t="n">
-        <v>24.4466</v>
+        <v>24.5341</v>
       </c>
       <c r="D75" t="n">
-        <v>74.3292</v>
+        <v>75.14790000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>24.4719</v>
+        <v>24.509</v>
       </c>
       <c r="F75" t="n">
-        <v>39.7365</v>
+        <v>40.5748</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>34.7823</v>
+        <v>33.7043</v>
       </c>
       <c r="C76" t="n">
-        <v>24.1226</v>
+        <v>24.1708</v>
       </c>
       <c r="D76" t="n">
-        <v>74.3672</v>
+        <v>75.1438</v>
       </c>
       <c r="E76" t="n">
-        <v>23.6087</v>
+        <v>23.9471</v>
       </c>
       <c r="F76" t="n">
-        <v>39.5765</v>
+        <v>40.4291</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>34.1382</v>
+        <v>34.2279</v>
       </c>
       <c r="C77" t="n">
-        <v>23.7208</v>
+        <v>23.7611</v>
       </c>
       <c r="D77" t="n">
-        <v>74.7081</v>
+        <v>75.4092</v>
       </c>
       <c r="E77" t="n">
-        <v>41.6825</v>
+        <v>41.7351</v>
       </c>
       <c r="F77" t="n">
-        <v>65.5616</v>
+        <v>64.5916</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>36.7127</v>
+        <v>32.7991</v>
       </c>
       <c r="C78" t="n">
-        <v>23.4252</v>
+        <v>23.3606</v>
       </c>
       <c r="D78" t="n">
-        <v>122.05</v>
+        <v>119.834</v>
       </c>
       <c r="E78" t="n">
-        <v>41.0421</v>
+        <v>40.6795</v>
       </c>
       <c r="F78" t="n">
-        <v>65.34350000000001</v>
+        <v>63.9573</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>36.2767</v>
+        <v>33.2347</v>
       </c>
       <c r="C79" t="n">
-        <v>33.1348</v>
+        <v>33.0402</v>
       </c>
       <c r="D79" t="n">
-        <v>119.865</v>
+        <v>118.104</v>
       </c>
       <c r="E79" t="n">
-        <v>40.0376</v>
+        <v>39.5565</v>
       </c>
       <c r="F79" t="n">
-        <v>65.0672</v>
+        <v>63.7668</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>32.8032</v>
+        <v>33.6039</v>
       </c>
       <c r="C80" t="n">
-        <v>32.8778</v>
+        <v>32.7664</v>
       </c>
       <c r="D80" t="n">
-        <v>118.507</v>
+        <v>116.06</v>
       </c>
       <c r="E80" t="n">
-        <v>39.1223</v>
+        <v>38.7313</v>
       </c>
       <c r="F80" t="n">
-        <v>64.4175</v>
+        <v>63.6735</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>51.677</v>
+        <v>49.9361</v>
       </c>
       <c r="C81" t="n">
-        <v>32.5286</v>
+        <v>32.7646</v>
       </c>
       <c r="D81" t="n">
-        <v>116.721</v>
+        <v>117.315</v>
       </c>
       <c r="E81" t="n">
-        <v>38.1324</v>
+        <v>37.7861</v>
       </c>
       <c r="F81" t="n">
-        <v>63.8556</v>
+        <v>63.5602</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>49.9434</v>
+        <v>51.235</v>
       </c>
       <c r="C82" t="n">
-        <v>32.1367</v>
+        <v>32.3307</v>
       </c>
       <c r="D82" t="n">
-        <v>115.408</v>
+        <v>115.927</v>
       </c>
       <c r="E82" t="n">
-        <v>36.9392</v>
+        <v>36.9297</v>
       </c>
       <c r="F82" t="n">
-        <v>62.8588</v>
+        <v>62.5968</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>45.8548</v>
+        <v>50.7075</v>
       </c>
       <c r="C83" t="n">
-        <v>31.8391</v>
+        <v>32.0306</v>
       </c>
       <c r="D83" t="n">
-        <v>114.565</v>
+        <v>115.091</v>
       </c>
       <c r="E83" t="n">
-        <v>36.1082</v>
+        <v>36.0102</v>
       </c>
       <c r="F83" t="n">
-        <v>62.0767</v>
+        <v>61.7075</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>43.1052</v>
+        <v>47.8476</v>
       </c>
       <c r="C84" t="n">
-        <v>31.4963</v>
+        <v>31.7053</v>
       </c>
       <c r="D84" t="n">
-        <v>114.177</v>
+        <v>114.643</v>
       </c>
       <c r="E84" t="n">
-        <v>35.182</v>
+        <v>35.1836</v>
       </c>
       <c r="F84" t="n">
-        <v>60.8396</v>
+        <v>60.9317</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>47.7361</v>
+        <v>45.752</v>
       </c>
       <c r="C85" t="n">
-        <v>31.08</v>
+        <v>31.333</v>
       </c>
       <c r="D85" t="n">
-        <v>114.075</v>
+        <v>114.451</v>
       </c>
       <c r="E85" t="n">
-        <v>34.3344</v>
+        <v>34.1967</v>
       </c>
       <c r="F85" t="n">
-        <v>60.3703</v>
+        <v>60.0566</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>45.3631</v>
+        <v>47.1541</v>
       </c>
       <c r="C86" t="n">
-        <v>30.8341</v>
+        <v>31.0091</v>
       </c>
       <c r="D86" t="n">
-        <v>114.136</v>
+        <v>114.738</v>
       </c>
       <c r="E86" t="n">
-        <v>33.2669</v>
+        <v>33.2398</v>
       </c>
       <c r="F86" t="n">
-        <v>59.3206</v>
+        <v>59.3831</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>46.8204</v>
+        <v>45.3942</v>
       </c>
       <c r="C87" t="n">
-        <v>30.4186</v>
+        <v>30.7052</v>
       </c>
       <c r="D87" t="n">
-        <v>114.376</v>
+        <v>114.937</v>
       </c>
       <c r="E87" t="n">
-        <v>32.5555</v>
+        <v>32.5673</v>
       </c>
       <c r="F87" t="n">
-        <v>58.4144</v>
+        <v>58.5823</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>46.0722</v>
+        <v>47.0418</v>
       </c>
       <c r="C88" t="n">
-        <v>30.0782</v>
+        <v>30.3796</v>
       </c>
       <c r="D88" t="n">
-        <v>115.238</v>
+        <v>115.469</v>
       </c>
       <c r="E88" t="n">
-        <v>31.8454</v>
+        <v>31.7002</v>
       </c>
       <c r="F88" t="n">
-        <v>57.5472</v>
+        <v>57.6288</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>44.4402</v>
+        <v>43.0734</v>
       </c>
       <c r="C89" t="n">
-        <v>29.8421</v>
+        <v>30.0069</v>
       </c>
       <c r="D89" t="n">
-        <v>115.851</v>
+        <v>115.824</v>
       </c>
       <c r="E89" t="n">
-        <v>31.2186</v>
+        <v>31.0748</v>
       </c>
       <c r="F89" t="n">
-        <v>56.6829</v>
+        <v>56.4684</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>43.1161</v>
+        <v>45.1487</v>
       </c>
       <c r="C90" t="n">
-        <v>29.5669</v>
+        <v>29.7078</v>
       </c>
       <c r="D90" t="n">
-        <v>117.606</v>
+        <v>116.76</v>
       </c>
       <c r="E90" t="n">
-        <v>30.6061</v>
+        <v>30.3836</v>
       </c>
       <c r="F90" t="n">
-        <v>56.2776</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>42.8381</v>
+        <v>43.3603</v>
       </c>
       <c r="C91" t="n">
-        <v>29.2566</v>
+        <v>29.3012</v>
       </c>
       <c r="D91" t="n">
-        <v>118.353</v>
+        <v>118.199</v>
       </c>
       <c r="E91" t="n">
-        <v>66.0938</v>
+        <v>65.9178</v>
       </c>
       <c r="F91" t="n">
-        <v>87.71080000000001</v>
+        <v>88.2338</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>45.4307</v>
+        <v>42.1028</v>
       </c>
       <c r="C92" t="n">
-        <v>28.8908</v>
+        <v>28.9154</v>
       </c>
       <c r="D92" t="n">
-        <v>177.156</v>
+        <v>176.738</v>
       </c>
       <c r="E92" t="n">
-        <v>64.61190000000001</v>
+        <v>64.6058</v>
       </c>
       <c r="F92" t="n">
-        <v>87.73390000000001</v>
+        <v>90.03700000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>48.3555</v>
+        <v>42.3891</v>
       </c>
       <c r="C93" t="n">
-        <v>28.8852</v>
+        <v>28.8667</v>
       </c>
       <c r="D93" t="n">
-        <v>176.99</v>
+        <v>176.181</v>
       </c>
       <c r="E93" t="n">
-        <v>62.5363</v>
+        <v>62.5599</v>
       </c>
       <c r="F93" t="n">
-        <v>86.2398</v>
+        <v>88.5598</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>45.5429</v>
+        <v>40.9479</v>
       </c>
       <c r="C94" t="n">
-        <v>61.932</v>
+        <v>61.9131</v>
       </c>
       <c r="D94" t="n">
-        <v>175.757</v>
+        <v>175.107</v>
       </c>
       <c r="E94" t="n">
-        <v>60.8163</v>
+        <v>60.7158</v>
       </c>
       <c r="F94" t="n">
-        <v>85.43640000000001</v>
+        <v>87.5625</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>76.8952</v>
+        <v>74.38290000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>60.759</v>
+        <v>60.7258</v>
       </c>
       <c r="D95" t="n">
-        <v>174.538</v>
+        <v>174.248</v>
       </c>
       <c r="E95" t="n">
-        <v>58.8653</v>
+        <v>58.6638</v>
       </c>
       <c r="F95" t="n">
-        <v>85.54510000000001</v>
+        <v>86.36450000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>74.7257</v>
+        <v>73.337</v>
       </c>
       <c r="C96" t="n">
-        <v>59.3094</v>
+        <v>59.2345</v>
       </c>
       <c r="D96" t="n">
-        <v>173.901</v>
+        <v>173.346</v>
       </c>
       <c r="E96" t="n">
-        <v>56.9874</v>
+        <v>56.8703</v>
       </c>
       <c r="F96" t="n">
-        <v>84.2993</v>
+        <v>85.5177</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>72.59610000000001</v>
+        <v>71.31270000000001</v>
       </c>
       <c r="C97" t="n">
-        <v>57.7918</v>
+        <v>57.8736</v>
       </c>
       <c r="D97" t="n">
-        <v>173.317</v>
+        <v>172.659</v>
       </c>
       <c r="E97" t="n">
-        <v>55.1056</v>
+        <v>55.0265</v>
       </c>
       <c r="F97" t="n">
-        <v>83.61960000000001</v>
+        <v>84.5471</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>72.8045</v>
+        <v>67.1949</v>
       </c>
       <c r="C98" t="n">
-        <v>56.4035</v>
+        <v>56.3688</v>
       </c>
       <c r="D98" t="n">
-        <v>173.091</v>
+        <v>172.563</v>
       </c>
       <c r="E98" t="n">
-        <v>53.4947</v>
+        <v>53.5312</v>
       </c>
       <c r="F98" t="n">
-        <v>81.7564</v>
+        <v>84.02889999999999</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>70.0684</v>
+        <v>70.1926</v>
       </c>
       <c r="C99" t="n">
-        <v>55.1271</v>
+        <v>55.1468</v>
       </c>
       <c r="D99" t="n">
-        <v>172.914</v>
+        <v>172.684</v>
       </c>
       <c r="E99" t="n">
-        <v>51.8871</v>
+        <v>51.8994</v>
       </c>
       <c r="F99" t="n">
-        <v>81.2115</v>
+        <v>81.7461</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>69.3828</v>
+        <v>67.54949999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>53.8696</v>
+        <v>53.7679</v>
       </c>
       <c r="D100" t="n">
-        <v>173.276</v>
+        <v>173.222</v>
       </c>
       <c r="E100" t="n">
-        <v>50.388</v>
+        <v>50.352</v>
       </c>
       <c r="F100" t="n">
-        <v>80.16030000000001</v>
+        <v>79.7777</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>68.1828</v>
+        <v>69.4158</v>
       </c>
       <c r="C101" t="n">
-        <v>52.6317</v>
+        <v>52.5918</v>
       </c>
       <c r="D101" t="n">
-        <v>172.787</v>
+        <v>172.569</v>
       </c>
       <c r="E101" t="n">
-        <v>48.9883</v>
+        <v>48.8891</v>
       </c>
       <c r="F101" t="n">
-        <v>80.4567</v>
+        <v>82.36799999999999</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>66.9671</v>
+        <v>63.8519</v>
       </c>
       <c r="C102" t="n">
-        <v>51.4586</v>
+        <v>51.6602</v>
       </c>
       <c r="D102" t="n">
-        <v>174.47</v>
+        <v>174.201</v>
       </c>
       <c r="E102" t="n">
-        <v>47.7139</v>
+        <v>47.6547</v>
       </c>
       <c r="F102" t="n">
-        <v>79.2975</v>
+        <v>79.0196</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>66.771</v>
+        <v>64.9455</v>
       </c>
       <c r="C103" t="n">
-        <v>50.4832</v>
+        <v>50.4312</v>
       </c>
       <c r="D103" t="n">
-        <v>176.448</v>
+        <v>175.452</v>
       </c>
       <c r="E103" t="n">
-        <v>46.3921</v>
+        <v>46.4029</v>
       </c>
       <c r="F103" t="n">
-        <v>78.4718</v>
+        <v>80.8271</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>63.4577</v>
+        <v>61.6955</v>
       </c>
       <c r="C104" t="n">
-        <v>49.4771</v>
+        <v>49.5158</v>
       </c>
       <c r="D104" t="n">
-        <v>177.091</v>
+        <v>176.975</v>
       </c>
       <c r="E104" t="n">
-        <v>45.2715</v>
+        <v>45.2615</v>
       </c>
       <c r="F104" t="n">
-        <v>77.2139</v>
+        <v>77.0711</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>63.2704</v>
+        <v>63.2812</v>
       </c>
       <c r="C105" t="n">
-        <v>48.5191</v>
+        <v>48.5521</v>
       </c>
       <c r="D105" t="n">
-        <v>179.168</v>
+        <v>178.454</v>
       </c>
       <c r="E105" t="n">
-        <v>82.7152</v>
+        <v>82.624</v>
       </c>
       <c r="F105" t="n">
-        <v>238.436</v>
+        <v>237.07</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>60.7328</v>
+        <v>61.2725</v>
       </c>
       <c r="C106" t="n">
-        <v>47.5931</v>
+        <v>47.6102</v>
       </c>
       <c r="D106" t="n">
-        <v>180.156</v>
+        <v>180.695</v>
       </c>
       <c r="E106" t="n">
-        <v>80.6306</v>
+        <v>80.8052</v>
       </c>
       <c r="F106" t="n">
-        <v>240.857</v>
+        <v>238.582</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>61.6603</v>
+        <v>61.0389</v>
       </c>
       <c r="C107" t="n">
-        <v>46.7667</v>
+        <v>46.6746</v>
       </c>
       <c r="D107" t="n">
-        <v>241.626</v>
+        <v>241.048</v>
       </c>
       <c r="E107" t="n">
-        <v>78.3994</v>
+        <v>78.4579</v>
       </c>
       <c r="F107" t="n">
-        <v>240.047</v>
+        <v>239.24</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>61.2997</v>
+        <v>59.0491</v>
       </c>
       <c r="C108" t="n">
-        <v>81.8651</v>
+        <v>81.86150000000001</v>
       </c>
       <c r="D108" t="n">
-        <v>238.427</v>
+        <v>238.669</v>
       </c>
       <c r="E108" t="n">
-        <v>76.0896</v>
+        <v>75.9472</v>
       </c>
       <c r="F108" t="n">
-        <v>239.547</v>
+        <v>238.066</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>59.7564</v>
+        <v>59.9661</v>
       </c>
       <c r="C109" t="n">
-        <v>79.81870000000001</v>
+        <v>79.7764</v>
       </c>
       <c r="D109" t="n">
-        <v>237.603</v>
+        <v>236.576</v>
       </c>
       <c r="E109" t="n">
-        <v>73.7396</v>
+        <v>73.7834</v>
       </c>
       <c r="F109" t="n">
-        <v>241.375</v>
+        <v>238.077</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>92.50369999999999</v>
+        <v>90.47880000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>77.99160000000001</v>
+        <v>78.00190000000001</v>
       </c>
       <c r="D110" t="n">
-        <v>234.96</v>
+        <v>234.152</v>
       </c>
       <c r="E110" t="n">
-        <v>71.5583</v>
+        <v>71.6258</v>
       </c>
       <c r="F110" t="n">
-        <v>241.765</v>
+        <v>239.956</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>79.4755</v>
+        <v>83.5895</v>
       </c>
       <c r="C111" t="n">
-        <v>62.9594</v>
+        <v>62.7844</v>
       </c>
       <c r="D111" t="n">
-        <v>233.998</v>
+        <v>233.512</v>
       </c>
       <c r="E111" t="n">
-        <v>60.2359</v>
+        <v>60.0918</v>
       </c>
       <c r="F111" t="n">
-        <v>240.53</v>
+        <v>240.255</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>86.0622</v>
+        <v>79.23869999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>73.96850000000001</v>
+        <v>61.3339</v>
       </c>
       <c r="D112" t="n">
-        <v>233.38</v>
+        <v>232.508</v>
       </c>
       <c r="E112" t="n">
-        <v>58.6111</v>
+        <v>67.3796</v>
       </c>
       <c r="F112" t="n">
-        <v>242.096</v>
+        <v>240.681</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>84.1707</v>
+        <v>87.0146</v>
       </c>
       <c r="C113" t="n">
-        <v>72.0749</v>
+        <v>71.8948</v>
       </c>
       <c r="D113" t="n">
-        <v>234.416</v>
+        <v>234.256</v>
       </c>
       <c r="E113" t="n">
-        <v>65.4704</v>
+        <v>57.1056</v>
       </c>
       <c r="F113" t="n">
-        <v>241.153</v>
+        <v>239.485</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>84.5827</v>
+        <v>77.3616</v>
       </c>
       <c r="C114" t="n">
-        <v>70.2914</v>
+        <v>58.893</v>
       </c>
       <c r="D114" t="n">
-        <v>238.618</v>
+        <v>244.455</v>
       </c>
       <c r="E114" t="n">
-        <v>55.7351</v>
+        <v>63.6159</v>
       </c>
       <c r="F114" t="n">
-        <v>221.361</v>
+        <v>241.52</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>81.66759999999999</v>
+        <v>84.248</v>
       </c>
       <c r="C115" t="n">
-        <v>68.59</v>
+        <v>68.55629999999999</v>
       </c>
       <c r="D115" t="n">
-        <v>243.252</v>
+        <v>240.338</v>
       </c>
       <c r="E115" t="n">
-        <v>62.0613</v>
+        <v>61.889</v>
       </c>
       <c r="F115" t="n">
-        <v>242.88</v>
+        <v>241.463</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>81.7591</v>
+        <v>80.7666</v>
       </c>
       <c r="C116" t="n">
-        <v>66.9362</v>
+        <v>66.97790000000001</v>
       </c>
       <c r="D116" t="n">
-        <v>244.556</v>
+        <v>240.133</v>
       </c>
       <c r="E116" t="n">
-        <v>60.44</v>
+        <v>60.3587</v>
       </c>
       <c r="F116" t="n">
-        <v>243.722</v>
+        <v>242.643</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>80</v>
+        <v>73.0916</v>
       </c>
       <c r="C117" t="n">
-        <v>65.3552</v>
+        <v>55.4007</v>
       </c>
       <c r="D117" t="n">
-        <v>244.501</v>
+        <v>245.671</v>
       </c>
       <c r="E117" t="n">
-        <v>51.9313</v>
+        <v>58.826</v>
       </c>
       <c r="F117" t="n">
-        <v>243.715</v>
+        <v>243.525</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>73.7285</v>
+        <v>72.33620000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>54.5313</v>
+        <v>54.607</v>
       </c>
       <c r="D118" t="n">
-        <v>232.536</v>
+        <v>232.104</v>
       </c>
       <c r="E118" t="n">
-        <v>50.9732</v>
+        <v>50.8967</v>
       </c>
       <c r="F118" t="n">
-        <v>244.029</v>
+        <v>243.48</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>77.1593</v>
+        <v>75.5489</v>
       </c>
       <c r="C119" t="n">
-        <v>62.5716</v>
+        <v>62.6274</v>
       </c>
       <c r="D119" t="n">
-        <v>233.502</v>
+        <v>233.006</v>
       </c>
       <c r="E119" t="n">
-        <v>88.75069999999999</v>
+        <v>88.5257</v>
       </c>
       <c r="F119" t="n">
-        <v>293.025</v>
+        <v>292.545</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>71.7234</v>
+        <v>76.1754</v>
       </c>
       <c r="C120" t="n">
-        <v>52.8458</v>
+        <v>61.2317</v>
       </c>
       <c r="D120" t="n">
-        <v>234.638</v>
+        <v>234.405</v>
       </c>
       <c r="E120" t="n">
-        <v>86.863</v>
+        <v>86.71850000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>292.041</v>
+        <v>292.239</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>69.9944</v>
+        <v>72.87860000000001</v>
       </c>
       <c r="C121" t="n">
-        <v>52.0615</v>
+        <v>60.1259</v>
       </c>
       <c r="D121" t="n">
-        <v>307.571</v>
+        <v>307.359</v>
       </c>
       <c r="E121" t="n">
-        <v>84.76430000000001</v>
+        <v>84.6317</v>
       </c>
       <c r="F121" t="n">
-        <v>291.809</v>
+        <v>290.764</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>66.70099999999999</v>
+        <v>68.3682</v>
       </c>
       <c r="C122" t="n">
-        <v>87.24299999999999</v>
+        <v>87.1585</v>
       </c>
       <c r="D122" t="n">
-        <v>303.421</v>
+        <v>302.473</v>
       </c>
       <c r="E122" t="n">
-        <v>82.9148</v>
+        <v>82.7795</v>
       </c>
       <c r="F122" t="n">
-        <v>291.54</v>
+        <v>289.973</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>67.3064</v>
+        <v>66.6643</v>
       </c>
       <c r="C123" t="n">
-        <v>85.68340000000001</v>
+        <v>85.5681</v>
       </c>
       <c r="D123" t="n">
-        <v>299.028</v>
+        <v>298.827</v>
       </c>
       <c r="E123" t="n">
-        <v>80.943</v>
+        <v>80.7501</v>
       </c>
       <c r="F123" t="n">
-        <v>290.917</v>
+        <v>289.859</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>99.0612</v>
+        <v>103.354</v>
       </c>
       <c r="C124" t="n">
-        <v>84.6221</v>
+        <v>91.27030000000001</v>
       </c>
       <c r="D124" t="n">
-        <v>295.441</v>
+        <v>295.519</v>
       </c>
       <c r="E124" t="n">
-        <v>79.2111</v>
+        <v>79.1275</v>
       </c>
       <c r="F124" t="n">
-        <v>290.199</v>
+        <v>289.917</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>97.6377</v>
+        <v>101.762</v>
       </c>
       <c r="C125" t="n">
-        <v>82.9759</v>
+        <v>89.3284</v>
       </c>
       <c r="D125" t="n">
-        <v>292.779</v>
+        <v>292.561</v>
       </c>
       <c r="E125" t="n">
-        <v>77.563</v>
+        <v>82.15649999999999</v>
       </c>
       <c r="F125" t="n">
-        <v>288.802</v>
+        <v>289.488</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>97.51730000000001</v>
+        <v>100.136</v>
       </c>
       <c r="C126" t="n">
-        <v>81.2694</v>
+        <v>87.5804</v>
       </c>
       <c r="D126" t="n">
-        <v>290.488</v>
+        <v>289.795</v>
       </c>
       <c r="E126" t="n">
-        <v>76.0055</v>
+        <v>75.7787</v>
       </c>
       <c r="F126" t="n">
-        <v>289.08</v>
+        <v>287.529</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>94.89579999999999</v>
+        <v>95.3421</v>
       </c>
       <c r="C127" t="n">
-        <v>79.889</v>
+        <v>79.813</v>
       </c>
       <c r="D127" t="n">
-        <v>288.104</v>
+        <v>287.755</v>
       </c>
       <c r="E127" t="n">
-        <v>74.419</v>
+        <v>74.3921</v>
       </c>
       <c r="F127" t="n">
-        <v>289.729</v>
+        <v>287.905</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>93.9355</v>
+        <v>93.14790000000001</v>
       </c>
       <c r="C128" t="n">
-        <v>78.5197</v>
+        <v>78.2856</v>
       </c>
       <c r="D128" t="n">
-        <v>285.87</v>
+        <v>285.606</v>
       </c>
       <c r="E128" t="n">
-        <v>76.92440000000001</v>
+        <v>72.8873</v>
       </c>
       <c r="F128" t="n">
-        <v>288.571</v>
+        <v>287.531</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>92.2209</v>
+        <v>92.9362</v>
       </c>
       <c r="C129" t="n">
-        <v>77.1546</v>
+        <v>77.05759999999999</v>
       </c>
       <c r="D129" t="n">
-        <v>283.39</v>
+        <v>284.151</v>
       </c>
       <c r="E129" t="n">
-        <v>71.50749999999999</v>
+        <v>71.489</v>
       </c>
       <c r="F129" t="n">
-        <v>287.569</v>
+        <v>286.663</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>90.21510000000001</v>
+        <v>89.7808</v>
       </c>
       <c r="C130" t="n">
-        <v>75.8905</v>
+        <v>75.82550000000001</v>
       </c>
       <c r="D130" t="n">
-        <v>283.192</v>
+        <v>282.917</v>
       </c>
       <c r="E130" t="n">
-        <v>70.3013</v>
+        <v>70.09699999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>287.723</v>
+        <v>286.602</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>89.9187</v>
+        <v>87.9091</v>
       </c>
       <c r="C131" t="n">
-        <v>74.8574</v>
+        <v>74.5735</v>
       </c>
       <c r="D131" t="n">
-        <v>281.967</v>
+        <v>281.571</v>
       </c>
       <c r="E131" t="n">
-        <v>69.1871</v>
+        <v>68.98390000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>287.076</v>
+        <v>286.36</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>88.1001</v>
+        <v>87.1062</v>
       </c>
       <c r="C132" t="n">
-        <v>73.7122</v>
+        <v>73.61750000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>281.516</v>
+        <v>281.664</v>
       </c>
       <c r="E132" t="n">
-        <v>67.98869999999999</v>
+        <v>67.8948</v>
       </c>
       <c r="F132" t="n">
-        <v>286.661</v>
+        <v>287.385</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>89.5591</v>
+        <v>87.04859999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>77.1495</v>
+        <v>72.6138</v>
       </c>
       <c r="D133" t="n">
-        <v>283.049</v>
+        <v>281.552</v>
       </c>
       <c r="E133" t="n">
-        <v>66.89</v>
+        <v>67.1079</v>
       </c>
       <c r="F133" t="n">
-        <v>287.743</v>
+        <v>287.304</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>85.02070000000001</v>
+        <v>85.774</v>
       </c>
       <c r="C134" t="n">
-        <v>71.6275</v>
+        <v>71.7534</v>
       </c>
       <c r="D134" t="n">
-        <v>276.954</v>
+        <v>276.84</v>
       </c>
       <c r="E134" t="n">
-        <v>97.7794</v>
+        <v>104.093</v>
       </c>
       <c r="F134" t="n">
-        <v>330.745</v>
+        <v>333.225</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>84.438</v>
+        <v>84.29689999999999</v>
       </c>
       <c r="C135" t="n">
-        <v>70.7756</v>
+        <v>70.7627</v>
       </c>
       <c r="D135" t="n">
-        <v>353.115</v>
+        <v>354.732</v>
       </c>
       <c r="E135" t="n">
-        <v>96.4242</v>
+        <v>95.99769999999999</v>
       </c>
       <c r="F135" t="n">
-        <v>330.903</v>
+        <v>331.097</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>84.3545</v>
+        <v>84.3767</v>
       </c>
       <c r="C136" t="n">
-        <v>105.524</v>
+        <v>105.489</v>
       </c>
       <c r="D136" t="n">
-        <v>346.855</v>
+        <v>346.755</v>
       </c>
       <c r="E136" t="n">
-        <v>93.8082</v>
+        <v>94.17</v>
       </c>
       <c r="F136" t="n">
-        <v>328.789</v>
+        <v>329.721</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>83.7067</v>
+        <v>80.96169999999999</v>
       </c>
       <c r="C137" t="n">
-        <v>103.556</v>
+        <v>97.21259999999999</v>
       </c>
       <c r="D137" t="n">
-        <v>341.803</v>
+        <v>341.772</v>
       </c>
       <c r="E137" t="n">
-        <v>92.3223</v>
+        <v>92.4868</v>
       </c>
       <c r="F137" t="n">
-        <v>326.899</v>
+        <v>327.732</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>116.343</v>
+        <v>110.741</v>
       </c>
       <c r="C138" t="n">
-        <v>103.003</v>
+        <v>96.02849999999999</v>
       </c>
       <c r="D138" t="n">
-        <v>337.99</v>
+        <v>336.692</v>
       </c>
       <c r="E138" t="n">
-        <v>90.6422</v>
+        <v>90.7756</v>
       </c>
       <c r="F138" t="n">
-        <v>329.973</v>
+        <v>329.509</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>107.517</v>
+        <v>114.191</v>
       </c>
       <c r="C139" t="n">
-        <v>94.758</v>
+        <v>101.322</v>
       </c>
       <c r="D139" t="n">
-        <v>332.318</v>
+        <v>333.032</v>
       </c>
       <c r="E139" t="n">
-        <v>88.93819999999999</v>
+        <v>89.0381</v>
       </c>
       <c r="F139" t="n">
-        <v>329.286</v>
+        <v>327.986</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>112.872</v>
+        <v>106.594</v>
       </c>
       <c r="C140" t="n">
-        <v>99.7411</v>
+        <v>93.6242</v>
       </c>
       <c r="D140" t="n">
-        <v>328.518</v>
+        <v>329.055</v>
       </c>
       <c r="E140" t="n">
-        <v>87.58669999999999</v>
+        <v>87.4029</v>
       </c>
       <c r="F140" t="n">
-        <v>327.084</v>
+        <v>326.358</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>111.136</v>
+        <v>106.293</v>
       </c>
       <c r="C141" t="n">
-        <v>98.38209999999999</v>
+        <v>92.37909999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>326.638</v>
+        <v>327.356</v>
       </c>
       <c r="E141" t="n">
-        <v>86.01479999999999</v>
+        <v>86.06489999999999</v>
       </c>
       <c r="F141" t="n">
-        <v>325.971</v>
+        <v>325.662</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>106.593</v>
+        <v>104.576</v>
       </c>
       <c r="C142" t="n">
-        <v>91.0921</v>
+        <v>91.1382</v>
       </c>
       <c r="D142" t="n">
-        <v>326.093</v>
+        <v>326.003</v>
       </c>
       <c r="E142" t="n">
-        <v>84.4499</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>325.214</v>
+        <v>324.957</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>103.314</v>
+        <v>108.486</v>
       </c>
       <c r="C143" t="n">
-        <v>90.0483</v>
+        <v>95.559</v>
       </c>
       <c r="D143" t="n">
-        <v>324.145</v>
+        <v>324.633</v>
       </c>
       <c r="E143" t="n">
-        <v>86.9462</v>
+        <v>83.1073</v>
       </c>
       <c r="F143" t="n">
-        <v>323.885</v>
+        <v>323.721</v>
       </c>
     </row>
   </sheetData>
